--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE97712B-FE97-4B22-80FA-66E1889E4863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5400BF06-9BAA-4E3E-884A-C6F383469AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="406">
   <si>
     <t>—</t>
   </si>
@@ -6633,13 +6633,24 @@
   </si>
   <si>
     <t>10-12 4차(입문) 48개 추가: 목표를 달성해 단계가 오르는 사람이 많지 않아 대부분 입문 문구를 보므로, 축마다 입문 6개(낮 4 · 저녁·새벽 2)를 더함. 합계 111개</t>
+  </si>
+  <si>
+    <t>입문</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10-12 1~3차 중 쉬운 문구 13개의 단계를 낮춤(입문 12 · 기본 1). 바뀐 단계 칸은 빨간 글씨</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6704,6 +6715,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -6748,7 +6765,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6769,6 +6786,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7104,7 +7124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F51797-492B-40AC-833D-E19CEF6E9FA5}">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="120.58203125" style="1" customWidth="1"/>
@@ -7154,6 +7174,11 @@
     <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>402</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -7285,8 +7310,8 @@
       <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>8</v>
+      <c r="E3" s="7" t="s">
+        <v>403</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>82</v>
@@ -7495,8 +7520,8 @@
       <c r="D8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>8</v>
+      <c r="E8" s="7" t="s">
+        <v>403</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>97</v>
@@ -7579,8 +7604,8 @@
       <c r="D10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>8</v>
+      <c r="E10" s="7" t="s">
+        <v>403</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>103</v>
@@ -7663,8 +7688,8 @@
       <c r="D12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
+      <c r="E12" s="7" t="s">
+        <v>403</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>109</v>
@@ -7747,8 +7772,8 @@
       <c r="D14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
+      <c r="E14" s="7" t="s">
+        <v>403</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>115</v>
@@ -7831,8 +7856,8 @@
       <c r="D16" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>8</v>
+      <c r="E16" s="7" t="s">
+        <v>403</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>121</v>
@@ -7915,8 +7940,8 @@
       <c r="D18" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>8</v>
+      <c r="E18" s="7" t="s">
+        <v>403</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>127</v>
@@ -8209,8 +8234,8 @@
       <c r="D25" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>8</v>
+      <c r="E25" s="7" t="s">
+        <v>403</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>148</v>
@@ -8251,8 +8276,8 @@
       <c r="D26" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>13</v>
+      <c r="E26" s="7" t="s">
+        <v>403</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>151</v>
@@ -8377,8 +8402,8 @@
       <c r="D29" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>13</v>
+      <c r="E29" s="7" t="s">
+        <v>404</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>160</v>
@@ -8503,8 +8528,8 @@
       <c r="D32" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>13</v>
+      <c r="E32" s="7" t="s">
+        <v>403</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>169</v>
@@ -8881,8 +8906,8 @@
       <c r="D41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>8</v>
+      <c r="E41" s="7" t="s">
+        <v>403</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>195</v>
@@ -8965,8 +8990,8 @@
       <c r="D43" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>8</v>
+      <c r="E43" s="7" t="s">
+        <v>403</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>201</v>
@@ -9899,7 +9924,7 @@
         <v>0</v>
       </c>
       <c r="H65" s="3">
-        <f>LEN(F65)</f>
+        <f t="shared" ref="H65:H112" si="2">LEN(F65)</f>
         <v>18</v>
       </c>
       <c r="I65" s="3" t="s">
@@ -9941,7 +9966,7 @@
         <v>0</v>
       </c>
       <c r="H66" s="3">
-        <f>LEN(F66)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="I66" s="3" t="s">
@@ -9983,7 +10008,7 @@
         <v>0</v>
       </c>
       <c r="H67" s="3">
-        <f>LEN(F67)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="I67" s="3" t="s">
@@ -10025,7 +10050,7 @@
         <v>0</v>
       </c>
       <c r="H68" s="3">
-        <f>LEN(F68)</f>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="I68" s="3" t="s">
@@ -10067,7 +10092,7 @@
         <v>0</v>
       </c>
       <c r="H69" s="3">
-        <f>LEN(F69)</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="I69" s="3" t="s">
@@ -10109,7 +10134,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <f>LEN(F70)</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="I70" s="3" t="s">
@@ -10151,7 +10176,7 @@
         <v>0</v>
       </c>
       <c r="H71" s="3">
-        <f>LEN(F71)</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="I71" s="3" t="s">
@@ -10193,7 +10218,7 @@
         <v>0</v>
       </c>
       <c r="H72" s="3">
-        <f>LEN(F72)</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="I72" s="3" t="s">
@@ -10235,7 +10260,7 @@
         <v>0</v>
       </c>
       <c r="H73" s="3">
-        <f>LEN(F73)</f>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="I73" s="3" t="s">
@@ -10277,7 +10302,7 @@
         <v>0</v>
       </c>
       <c r="H74" s="3">
-        <f>LEN(F74)</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="I74" s="3" t="s">
@@ -10319,7 +10344,7 @@
         <v>0</v>
       </c>
       <c r="H75" s="3">
-        <f>LEN(F75)</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="I75" s="3" t="s">
@@ -10361,7 +10386,7 @@
         <v>0</v>
       </c>
       <c r="H76" s="3">
-        <f>LEN(F76)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="I76" s="3" t="s">
@@ -10403,7 +10428,7 @@
         <v>0</v>
       </c>
       <c r="H77" s="3">
-        <f>LEN(F77)</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="I77" s="3" t="s">
@@ -10445,7 +10470,7 @@
         <v>0</v>
       </c>
       <c r="H78" s="3">
-        <f>LEN(F78)</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="I78" s="3" t="s">
@@ -10487,7 +10512,7 @@
         <v>0</v>
       </c>
       <c r="H79" s="3">
-        <f>LEN(F79)</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="I79" s="3" t="s">
@@ -10529,7 +10554,7 @@
         <v>0</v>
       </c>
       <c r="H80" s="3">
-        <f>LEN(F80)</f>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="I80" s="3" t="s">
@@ -10571,7 +10596,7 @@
         <v>0</v>
       </c>
       <c r="H81" s="3">
-        <f>LEN(F81)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="I81" s="3" t="s">
@@ -10613,7 +10638,7 @@
         <v>0</v>
       </c>
       <c r="H82" s="3">
-        <f>LEN(F82)</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="I82" s="3" t="s">
@@ -10655,7 +10680,7 @@
         <v>0</v>
       </c>
       <c r="H83" s="3">
-        <f>LEN(F83)</f>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I83" s="3" t="s">
@@ -10697,7 +10722,7 @@
         <v>0</v>
       </c>
       <c r="H84" s="3">
-        <f>LEN(F84)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="I84" s="3" t="s">
@@ -10739,7 +10764,7 @@
         <v>0</v>
       </c>
       <c r="H85" s="3">
-        <f>LEN(F85)</f>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="I85" s="3" t="s">
@@ -10781,7 +10806,7 @@
         <v>0</v>
       </c>
       <c r="H86" s="3">
-        <f>LEN(F86)</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="I86" s="3" t="s">
@@ -10823,7 +10848,7 @@
         <v>0</v>
       </c>
       <c r="H87" s="3">
-        <f>LEN(F87)</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="I87" s="3" t="s">
@@ -10865,7 +10890,7 @@
         <v>0</v>
       </c>
       <c r="H88" s="3">
-        <f>LEN(F88)</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="I88" s="3" t="s">
@@ -10907,7 +10932,7 @@
         <v>0</v>
       </c>
       <c r="H89" s="3">
-        <f>LEN(F89)</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="I89" s="3" t="s">
@@ -10949,7 +10974,7 @@
         <v>0</v>
       </c>
       <c r="H90" s="3">
-        <f>LEN(F90)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="I90" s="3" t="s">
@@ -10991,7 +11016,7 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
-        <f>LEN(F91)</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="I91" s="3" t="s">
@@ -11033,7 +11058,7 @@
         <v>0</v>
       </c>
       <c r="H92" s="3">
-        <f>LEN(F92)</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="I92" s="3" t="s">
@@ -11075,7 +11100,7 @@
         <v>0</v>
       </c>
       <c r="H93" s="3">
-        <f>LEN(F93)</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="I93" s="3" t="s">
@@ -11117,7 +11142,7 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
-        <f>LEN(F94)</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="I94" s="3" t="s">
@@ -11159,7 +11184,7 @@
         <v>0</v>
       </c>
       <c r="H95" s="3">
-        <f>LEN(F95)</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="I95" s="3" t="s">
@@ -11201,7 +11226,7 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <f>LEN(F96)</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="I96" s="3" t="s">
@@ -11243,7 +11268,7 @@
         <v>0</v>
       </c>
       <c r="H97" s="3">
-        <f>LEN(F97)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="I97" s="3" t="s">
@@ -11285,7 +11310,7 @@
         <v>0</v>
       </c>
       <c r="H98" s="3">
-        <f>LEN(F98)</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="I98" s="3" t="s">
@@ -11327,7 +11352,7 @@
         <v>0</v>
       </c>
       <c r="H99" s="3">
-        <f>LEN(F99)</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="I99" s="3" t="s">
@@ -11369,7 +11394,7 @@
         <v>0</v>
       </c>
       <c r="H100" s="3">
-        <f>LEN(F100)</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="I100" s="3" t="s">
@@ -11411,7 +11436,7 @@
         <v>0</v>
       </c>
       <c r="H101" s="3">
-        <f>LEN(F101)</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="I101" s="3" t="s">
@@ -11453,7 +11478,7 @@
         <v>0</v>
       </c>
       <c r="H102" s="3">
-        <f>LEN(F102)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="I102" s="3" t="s">
@@ -11495,7 +11520,7 @@
         <v>0</v>
       </c>
       <c r="H103" s="3">
-        <f>LEN(F103)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="I103" s="3" t="s">
@@ -11537,7 +11562,7 @@
         <v>0</v>
       </c>
       <c r="H104" s="3">
-        <f>LEN(F104)</f>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="I104" s="3" t="s">
@@ -11579,7 +11604,7 @@
         <v>0</v>
       </c>
       <c r="H105" s="3">
-        <f>LEN(F105)</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="I105" s="3" t="s">
@@ -11621,7 +11646,7 @@
         <v>0</v>
       </c>
       <c r="H106" s="3">
-        <f>LEN(F106)</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="I106" s="3" t="s">
@@ -11663,7 +11688,7 @@
         <v>0</v>
       </c>
       <c r="H107" s="3">
-        <f>LEN(F107)</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I107" s="3" t="s">
@@ -11705,7 +11730,7 @@
         <v>0</v>
       </c>
       <c r="H108" s="3">
-        <f>LEN(F108)</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="I108" s="3" t="s">
@@ -11747,7 +11772,7 @@
         <v>0</v>
       </c>
       <c r="H109" s="3">
-        <f>LEN(F109)</f>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I109" s="3" t="s">
@@ -11789,7 +11814,7 @@
         <v>0</v>
       </c>
       <c r="H110" s="3">
-        <f>LEN(F110)</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="I110" s="3" t="s">
@@ -11831,7 +11856,7 @@
         <v>0</v>
       </c>
       <c r="H111" s="3">
-        <f>LEN(F111)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="I111" s="3" t="s">
@@ -11873,7 +11898,7 @@
         <v>0</v>
       </c>
       <c r="H112" s="3">
-        <f>LEN(F112)</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="I112" s="3" t="s">

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5400BF06-9BAA-4E3E-884A-C6F383469AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7B26F1-D3FC-4E58-8190-D17620D96D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="407">
   <si>
     <t>—</t>
   </si>
@@ -6590,60 +6590,66 @@
     <t>기름진 음식</t>
   </si>
   <si>
+    <t>WHO 포화지방 줄이기 권고</t>
+  </si>
+  <si>
+    <t>볶음보다 무침 반찬 고르기</t>
+  </si>
+  <si>
+    <t>무침은 기름을 덜 쓰는 반찬이에요.</t>
+  </si>
+  <si>
+    <t>식생활지침 「기름진 음식 줄이기」</t>
+  </si>
+  <si>
+    <t>튀김옷은 벗겨서 먹기</t>
+  </si>
+  <si>
+    <t>튀김옷에 기름이 가장 많이 배어 있어요.</t>
+  </si>
+  <si>
+    <t>드레싱은 따로 달라고 하기</t>
+  </si>
+  <si>
+    <t>따로 받으면 뿌리는 양을 조절할 수 있어요.</t>
+  </si>
+  <si>
+    <t>내일 반찬은 무침으로 정하기</t>
+  </si>
+  <si>
+    <t>무침은 기름을 덜 쓰는 조리법이에요.</t>
+  </si>
+  <si>
+    <t>기름 덜 쓰는 요리 하나 찾기</t>
+  </si>
+  <si>
+    <t>요리법을 알면 기름을 덜 쓰게 돼요.</t>
+  </si>
+  <si>
+    <t>10-12 4차(입문) 48개 추가: 목표를 달성해 단계가 오르는 사람이 많지 않아 대부분 입문 문구를 보므로, 축마다 입문 6개(낮 4 · 저녁·새벽 2)를 더함. 합계 111개</t>
+  </si>
+  <si>
+    <t>입문</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10-12 1~3차 중 쉬운 문구 13개의 단계를 낮춤(입문 12 · 기본 1). 바뀐 단계 칸은 빨간 글씨</t>
+  </si>
+  <si>
     <t>고기는 구워서 먹기</t>
-  </si>
-  <si>
-    <t>구우면 튀길 때보다 기름이 덜 들어가요.</t>
-  </si>
-  <si>
-    <t>WHO 포화지방 줄이기 권고</t>
-  </si>
-  <si>
-    <t>볶음보다 무침 반찬 고르기</t>
-  </si>
-  <si>
-    <t>무침은 기름을 덜 쓰는 반찬이에요.</t>
-  </si>
-  <si>
-    <t>식생활지침 「기름진 음식 줄이기」</t>
-  </si>
-  <si>
-    <t>튀김옷은 벗겨서 먹기</t>
-  </si>
-  <si>
-    <t>튀김옷에 기름이 가장 많이 배어 있어요.</t>
-  </si>
-  <si>
-    <t>드레싱은 따로 달라고 하기</t>
-  </si>
-  <si>
-    <t>따로 받으면 뿌리는 양을 조절할 수 있어요.</t>
-  </si>
-  <si>
-    <t>내일 반찬은 무침으로 정하기</t>
-  </si>
-  <si>
-    <t>무침은 기름을 덜 쓰는 조리법이에요.</t>
-  </si>
-  <si>
-    <t>기름 덜 쓰는 요리 하나 찾기</t>
-  </si>
-  <si>
-    <t>요리법을 알면 기름을 덜 쓰게 돼요.</t>
-  </si>
-  <si>
-    <t>10-12 4차(입문) 48개 추가: 목표를 달성해 단계가 오르는 사람이 많지 않아 대부분 입문 문구를 보므로, 축마다 입문 6개(낮 4 · 저녁·새벽 2)를 더함. 합계 111개</t>
-  </si>
-  <si>
-    <t>입문</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10-12 1~3차 중 쉬운 문구 13개의 단계를 낮춤(입문 12 · 기본 1). 바뀐 단계 칸은 빨간 글씨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고기는 튀김 대신 구이로 고르기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구이는 튀김보다 기름이 덜 들어가요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -7173,12 +7179,12 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -7311,7 +7317,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>82</v>
@@ -7521,7 +7527,7 @@
         <v>15</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>97</v>
@@ -7605,7 +7611,7 @@
         <v>18</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>103</v>
@@ -7689,7 +7695,7 @@
         <v>21</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>109</v>
@@ -7773,7 +7779,7 @@
         <v>23</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>115</v>
@@ -7857,7 +7863,7 @@
         <v>26</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>121</v>
@@ -7941,7 +7947,7 @@
         <v>29</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>127</v>
@@ -8235,7 +8241,7 @@
         <v>10</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>148</v>
@@ -8277,7 +8283,7 @@
         <v>15</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>151</v>
@@ -8403,7 +8409,7 @@
         <v>18</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>160</v>
@@ -8529,7 +8535,7 @@
         <v>23</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>169</v>
@@ -8907,7 +8913,7 @@
         <v>3</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>195</v>
@@ -8991,7 +8997,7 @@
         <v>10</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>201</v>
@@ -11681,21 +11687,21 @@
       <c r="E107" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="F107" s="3" t="s">
-        <v>388</v>
+      <c r="F107" s="7" t="s">
+        <v>405</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="H107" s="3">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>389</v>
+        <v>406</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="K107" s="3" t="s">
         <v>274</v>
@@ -11724,7 +11730,7 @@
         <v>270</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G108" s="5" t="s">
         <v>0</v>
@@ -11734,10 +11740,10 @@
         <v>14</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="K108" s="3" t="s">
         <v>274</v>
@@ -11766,7 +11772,7 @@
         <v>270</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="G109" s="5" t="s">
         <v>0</v>
@@ -11776,7 +11782,7 @@
         <v>11</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="J109" s="3" t="s">
         <v>321</v>
@@ -11808,7 +11814,7 @@
         <v>270</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G110" s="5" t="s">
         <v>0</v>
@@ -11818,10 +11824,10 @@
         <v>14</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="K110" s="3" t="s">
         <v>274</v>
@@ -11850,7 +11856,7 @@
         <v>270</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G111" s="5" t="s">
         <v>0</v>
@@ -11860,10 +11866,10 @@
         <v>15</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="K111" s="3" t="s">
         <v>287</v>
@@ -11892,7 +11898,7 @@
         <v>270</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G112" s="5" t="s">
         <v>0</v>
@@ -11902,10 +11908,10 @@
         <v>16</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="K112" s="3" t="s">
         <v>287</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7B26F1-D3FC-4E58-8190-D17620D96D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1006B8-F358-4982-8684-D350AC0327D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="추가 문구" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'추가 문구'!$A$1:$O$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'추가 문구'!$A$1:$O$118</definedName>
   </definedNames>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="421">
   <si>
     <t>—</t>
   </si>
@@ -6644,12 +6644,54 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>고기는 튀김 대신 구이로 고르기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>구이는 튀김보다 기름이 덜 들어가요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>삼겹살 대신 수육·보쌈 고르기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삶은 고기는 구운 삼겹살보다 기름이 덜해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>돈가스 대신 생선구이 고르기</t>
+  </si>
+  <si>
+    <t>생선구이는 돈가스보다 기름이 덜 들어가요.</t>
+  </si>
+  <si>
+    <t>WHO·한국지질동맥경화학회 포화지방 줄이기 권고</t>
+  </si>
+  <si>
+    <t>치킨 대신 닭백숙 고르기</t>
+  </si>
+  <si>
+    <t>삶은 닭은 튀긴 닭보다 기름이 적어요.</t>
+  </si>
+  <si>
+    <t>김치찌개 대신 맑은 국 고르기</t>
+  </si>
+  <si>
+    <t>국민건강영양조사 · 식약처 나트륨 줄이기 안내</t>
+  </si>
+  <si>
+    <t>믹스커피 대신 아메리카노 고르기</t>
+  </si>
+  <si>
+    <t>아메리카노에는 설탕이 들어 있지 않아요.</t>
+  </si>
+  <si>
+    <t>케이크 대신 플레인 요거트 고르기</t>
+  </si>
+  <si>
+    <t>플레인 요거트는 단맛이 훨씬 덜해요.</t>
+  </si>
+  <si>
+    <t>짜장면 대신 비빔밥 고르기</t>
+  </si>
+  <si>
+    <t>비빔밥은 채소를 넉넉히 먹을 수 있어요.</t>
+  </si>
+  <si>
+    <t>10-12 메뉴 바꾸기 문구 6개 추가(삼겹살 대신 수육·보쌈처럼 구체적인 메뉴를 권함). 합계 117개</t>
   </si>
 </sst>
 </file>
@@ -7130,7 +7172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F51797-492B-40AC-833D-E19CEF6E9FA5}">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="120.58203125" style="1" customWidth="1"/>
@@ -7187,6 +7229,11 @@
         <v>403</v>
       </c>
     </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7195,7 +7242,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{243C8A1C-2FBA-4873-BD31-7545635970F1}">
-  <dimension ref="A1:O112"/>
+  <dimension ref="A1:O118"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="6.58203125" style="1" customWidth="1"/>
@@ -11695,7 +11742,7 @@
       </c>
       <c r="H107" s="3">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>406</v>
@@ -11923,11 +11970,263 @@
       <c r="N112" s="3"/>
       <c r="O112" s="3"/>
     </row>
+    <row r="113" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A113" s="7">
+        <v>112</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="E113" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="G113" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H113" s="7">
+        <f>LEN(F113)</f>
+        <v>15</v>
+      </c>
+      <c r="I113" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="J113" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="K113" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="L113" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="M113" s="3"/>
+      <c r="N113" s="3"/>
+      <c r="O113" s="3"/>
+    </row>
+    <row r="114" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A114" s="7">
+        <v>113</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="E114" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="G114" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H114" s="7">
+        <f>LEN(F114)</f>
+        <v>13</v>
+      </c>
+      <c r="I114" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="J114" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="K114" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="L114" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="M114" s="3"/>
+      <c r="N114" s="3"/>
+      <c r="O114" s="3"/>
+    </row>
+    <row r="115" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A115" s="7">
+        <v>114</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="E115" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="F115" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="G115" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H115" s="7">
+        <f>LEN(F115)</f>
+        <v>16</v>
+      </c>
+      <c r="I115" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="J115" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="K115" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="L115" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="M115" s="3"/>
+      <c r="N115" s="3"/>
+      <c r="O115" s="3"/>
+    </row>
+    <row r="116" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A116" s="7">
+        <v>115</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="E116" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="G116" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H116" s="7">
+        <f>LEN(F116)</f>
+        <v>17</v>
+      </c>
+      <c r="I116" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="J116" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="K116" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="L116" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="M116" s="3"/>
+      <c r="N116" s="3"/>
+      <c r="O116" s="3"/>
+    </row>
+    <row r="117" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A117" s="7">
+        <v>116</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="E117" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="F117" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="G117" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H117" s="7">
+        <f>LEN(F117)</f>
+        <v>18</v>
+      </c>
+      <c r="I117" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="J117" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="K117" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="L117" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="M117" s="3"/>
+      <c r="N117" s="3"/>
+      <c r="O117" s="3"/>
+    </row>
+    <row r="118" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A118" s="7">
+        <v>117</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="E118" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="G118" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H118" s="7">
+        <f>LEN(F118)</f>
+        <v>14</v>
+      </c>
+      <c r="I118" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="J118" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="K118" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="L118" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="M118" s="3"/>
+      <c r="N118" s="3"/>
+      <c r="O118" s="3"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O112" xr:uid="{243C8A1C-2FBA-4873-BD31-7545635970F1}"/>
+  <autoFilter ref="A1:O118" xr:uid="{243C8A1C-2FBA-4873-BD31-7545635970F1}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M112" xr:uid="{29F577E0-A9A7-4D3D-B3E7-99484ADFB535}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M118" xr:uid="{29F577E0-A9A7-4D3D-B3E7-99484ADFB535}">
       <formula1>"승인,수정,제외"</formula1>
     </dataValidation>
   </dataValidations>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1006B8-F358-4982-8684-D350AC0327D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC0DE1B8-752A-4BFF-875E-73C2266697DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="473">
   <si>
     <t>—</t>
   </si>
@@ -4280,369 +4280,6 @@
         <charset val="129"/>
       </rPr>
       <t>개</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>공통</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>조건</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>저녁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>새벽에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>쓸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · 22</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이내</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>먹는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>양을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>늘리거나</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>줄이라는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>말</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>없음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>신장질환</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>당뇨병</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사용자도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>받음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
     </r>
   </si>
   <si>
@@ -5524,9 +5161,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>처음 초안</t>
-  </si>
-  <si>
     <t>글자 수</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5535,9 +5169,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 아침 메뉴 정해 두기</t>
-  </si>
-  <si>
     <t>아침 거르지 않게 메뉴 정하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5546,9 +5177,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 점심 먹을 시간 적기</t>
-  </si>
-  <si>
     <t>점심 거르지 않게 시간 적어 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5557,9 +5185,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 먹을 채소 꺼내 두기</t>
-  </si>
-  <si>
     <t>내일 바로 먹게 채소 꺼내 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5568,9 +5193,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>채소 반찬 하나 미리 만들기</t>
-  </si>
-  <si>
     <t>바쁜 날 대비 채소 반찬 만들어 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5579,9 +5201,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 도시락에 채소 담기</t>
-  </si>
-  <si>
     <t>밖에서도 먹게 도시락에 채소 담기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5590,9 +5209,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>단 간식 안 보이게 두기</t>
-  </si>
-  <si>
     <t>단 간식은 안 보이는 곳에 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5601,9 +5217,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>오늘 마신 단 음료 떠올리기</t>
-  </si>
-  <si>
     <t>오늘 마신 단 음료 돌아보기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5612,9 +5225,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>작은 국그릇 꺼내 두기</t>
-  </si>
-  <si>
     <t>국물 덜 먹게 작은 국그릇 꺼내 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5623,9 +5233,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>장 목록에 저염 제품 적기</t>
-  </si>
-  <si>
     <t>장 목록에 덜 짠 제품 적어 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5634,9 +5241,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 저녁 시각 정해 두기</t>
-  </si>
-  <si>
     <t>늦지 않게 내일 저녁 시각 정하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5645,9 +5249,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>잠들기 전 주방 불 끄기</t>
-  </si>
-  <si>
     <t>야식 줄이게 주방 불 일찍 끄기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5656,9 +5257,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>오늘 식사 속도 떠올리기</t>
-  </si>
-  <si>
     <t>오늘 먹은 속도 돌아보기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5667,9 +5265,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 쓸 작은 그릇 꺼내 두기</t>
-  </si>
-  <si>
     <t>먹을 만큼 담게 작은 그릇 꺼내기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5678,9 +5273,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 단백질 반찬 정하기</t>
-  </si>
-  <si>
     <t>내일 먹을 단백질 반찬 정하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5689,9 +5281,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>장 목록에 두부·달걀 적기</t>
-  </si>
-  <si>
     <t>장 볼 때 두부·달걀 잊지 않게 적기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5700,9 +5289,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 메뉴는 구이로 정하기</t>
-  </si>
-  <si>
     <t>내일은 튀김 대신 구이로 정하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5711,9 +5297,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>튀김 대신할 메뉴 적어 두기</t>
-  </si>
-  <si>
     <t>튀김 대신 먹을 메뉴 적어 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5722,9 +5305,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>오늘 먹은 끼니 적어 두기</t>
-  </si>
-  <si>
     <t>오늘 먹은 끼니 적고 내일 챙기기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5733,9 +5313,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>먹기 편한 시간 찾아 두기</t>
-  </si>
-  <si>
     <t>먹기 편한 시간 찾아 적어 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5744,9 +5321,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 먹을 것 하나 정하기</t>
-  </si>
-  <si>
     <t>내일 먹을 음식 하나 정해 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5755,9 +5329,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 세 끼 시간 적어 두기</t>
-  </si>
-  <si>
     <t>거르지 않게 내일 세 끼 시간 정하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5766,9 +5337,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>오늘 거른 끼니 떠올리기</t>
-  </si>
-  <si>
     <t>오늘 거른 끼니 돌아보기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5777,9 +5345,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>오늘 먹은 채소 떠올리기</t>
-  </si>
-  <si>
     <t>오늘 먹은 채소 돌아보기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5788,9 +5353,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>장 목록에 제철 채소 적기</t>
-  </si>
-  <si>
     <t>맛있는 제철 채소 장 목록에 적기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5799,9 +5361,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 마실 음료 정해 두기</t>
-  </si>
-  <si>
     <t>단 음료 대신 마실 것 정해 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5810,9 +5369,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>단 음료 대신 둘 것 정하기</t>
-  </si>
-  <si>
     <t>단 간식 대신 먹을 것 챙겨 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5821,9 +5377,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>오늘 먹은 국물 양 떠올리기</t>
-  </si>
-  <si>
     <t>오늘 먹은 국물 양 돌아보기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5832,9 +5385,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 국은 싱겁게 정하기</t>
-  </si>
-  <si>
     <t>내일 국은 싱겁게 끓이기로 정하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5843,9 +5393,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>늦은 끼니 피할 시각 정하기</t>
-  </si>
-  <si>
     <t>늦은 끼니 없게 마지막 식사 시각 정하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5854,9 +5401,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>오늘 저녁 먹은 시각 적기</t>
-  </si>
-  <si>
     <t>오늘 저녁 먹은 시각 적어 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5865,9 +5409,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 천천히 먹을 끼니 정하기</t>
-  </si>
-  <si>
     <t>내일 천천히 먹을 끼니 하나 정하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5876,9 +5417,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>식탁 위 휴대폰 자리 치우기</t>
-  </si>
-  <si>
     <t>식사에 집중하게 휴대폰 치워 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5887,9 +5425,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 세 끼 단백질 정해 두기</t>
-  </si>
-  <si>
     <t>끼니마다 먹을 단백질 정해 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5898,9 +5433,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>오늘 먹은 단백질 떠올리기</t>
-  </si>
-  <si>
     <t>오늘 먹은 단백질 돌아보기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5909,9 +5441,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 조리법 미리 정하기</t>
-  </si>
-  <si>
     <t>기름 덜 쓰게 내일 조리법 정하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5920,16 +5449,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>오늘 먹은 튀김 떠올리기</t>
-  </si>
-  <si>
     <t>오늘 먹은 튀긴 음식 돌아보기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>오늘 기운 남은 때 적어 두기</t>
-  </si>
-  <si>
     <t>기운 나는 시간 적어 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5938,9 +5461,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 첫 끼 시간 정하기</t>
-  </si>
-  <si>
     <t>내일 첫 끼 먹을 시간 정하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5949,9 +5469,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 아침거리 장 목록에 적기</t>
-  </si>
-  <si>
     <t>아침거리 잊지 않게 장 목록에 적기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5960,9 +5477,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 바쁜 끼니 대비 메뉴 정하기</t>
-  </si>
-  <si>
     <t>바쁜 날 먹을 간단 메뉴 정하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5971,9 +5485,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>냉장고 앞칸에 채소 두기</t>
-  </si>
-  <si>
     <t>잘 보이게 냉장고 앞칸에 채소 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5983,9 +5494,6 @@
   </si>
   <si>
     <t>내일 국에 넣을 채소 정하기</t>
-  </si>
-  <si>
-    <t>내일 국에 넣을 채소 정하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -5993,9 +5501,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이번 주 채소 반찬 계획 세우기</t>
-  </si>
-  <si>
     <t>이번 주 채소 반찬 미리 정하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6004,9 +5509,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>음료 살 때 당류 표시 보기</t>
-  </si>
-  <si>
     <t>음료 살 때 당류 표시 확인하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6015,9 +5517,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>집에 단 음료 쌓아 두지 않기</t>
-  </si>
-  <si>
     <t>단 음료는 집에 사 두지 않기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6026,9 +5525,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이번 주 단 음료 없는 날 정하기</t>
-  </si>
-  <si>
     <t>이번 주 단 음료 쉬는 날 정하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6037,9 +5533,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>식탁 소금통 치워 두기</t>
-  </si>
-  <si>
     <t>식탁 위 소금통 치워 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6048,9 +5541,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 국물은 적게 담기로 정하기</t>
-  </si>
-  <si>
     <t>내일 국은 건더기 위주로 담기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6059,9 +5549,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>가공식품 나트륨 표시 비교하기</t>
-  </si>
-  <si>
     <t>덜 짠 걸 고르게 나트륨 표시 보기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6070,9 +5557,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>저녁 뒤 간식 자리 정리하기</t>
-  </si>
-  <si>
     <t>야식 줄이게 간식 자리 정리하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6081,9 +5565,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>잠들기 2시간 전 먹기 마치기</t>
-  </si>
-  <si>
     <t>편히 잠들게 저녁 일찍 마치기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6092,9 +5573,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이번 주 저녁 시각 일정하게 정하기</t>
-  </si>
-  <si>
     <t>이번 주 저녁 시각 일정하게 맞추기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6103,9 +5581,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 식사 시간 20분 비워 두기</t>
-  </si>
-  <si>
     <t>천천히 먹게 식사 시간 넉넉히 잡기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6115,9 +5590,6 @@
   </si>
   <si>
     <t>내일 TV 끄고 먹을 끼니 정하기</t>
-  </si>
-  <si>
-    <t>내일 TV 끄고 먹을 끼니 정하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -6125,9 +5597,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이번 주 함께 먹는 끼니 정하기</t>
-  </si>
-  <si>
     <t>이번 주 함께 먹을 끼니 정하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6136,9 +5605,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 아침 달걀 꺼내 두기</t>
-  </si>
-  <si>
     <t>아침에 먹게 달걀 꺼내 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6148,9 +5614,6 @@
   </si>
   <si>
     <t>이번 주 생선 먹을 날 정하기</t>
-  </si>
-  <si>
-    <t>이번 주 생선 먹을 날 정하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -6158,9 +5621,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>콩 · 두부 요리법 하나 찾아 두기</t>
-  </si>
-  <si>
     <t>콩·두부 요리법 하나 찾아 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6169,9 +5629,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>튀김 대신 구울 재료 꺼내 두기</t>
-  </si>
-  <si>
     <t>튀김 대신 구워 먹을 재료 꺼내 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6180,9 +5637,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 볶음 대신 찜 메뉴 정하기</t>
-  </si>
-  <si>
     <t>기름 덜 쓰게 내일은 찜 요리 정하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6192,9 +5646,6 @@
   </si>
   <si>
     <t>이번 주 외식 메뉴 미리 정하기</t>
-  </si>
-  <si>
-    <t>이번 주 외식 메뉴 미리 정하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -6202,9 +5653,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 먹기 쉬운 음식 정해 두기</t>
-  </si>
-  <si>
     <t>내일 먹기 편한 음식 정해 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6213,9 +5661,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>오늘 식사 느낌 한 줄 적기</t>
-  </si>
-  <si>
     <t>오늘 식사가 어땠는지 한 줄 적기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6239,459 +5684,977 @@
     <t>입문</t>
   </si>
   <si>
+    <t>알림이 있으면 바쁜 날에도 점심을 놓치지 않아요.</t>
+  </si>
+  <si>
+    <t>식생활지침 「규칙적인 식사」</t>
+  </si>
+  <si>
+    <t>언제나(낮 포함)</t>
+  </si>
+  <si>
+    <t>아니오</t>
+  </si>
+  <si>
+    <t>적어 두면 끼니 시간을 지키기 쉬워요.</t>
+  </si>
+  <si>
+    <t>너무 배고프면 한꺼번에 많이 먹기 쉬워요.</t>
+  </si>
+  <si>
+    <t>식사 간격과 과식(일반 상식)</t>
+  </si>
+  <si>
+    <t>요깃거리가 있으면 끼니를 건너뛰지 않아요.</t>
+  </si>
+  <si>
+    <t>식생활지침 · 일반 상식</t>
+  </si>
+  <si>
+    <t>그릇이 나와 있으면 아침을 차리기 쉬워요.</t>
+  </si>
+  <si>
+    <t>식생활지침 「아침밥 먹기」</t>
+  </si>
+  <si>
+    <t>저녁(17시 이후) · 새벽</t>
+  </si>
+  <si>
+    <t>예</t>
+  </si>
+  <si>
+    <t>떠올려 두면 아침에 바로 챙길 수 있어요.</t>
+  </si>
+  <si>
+    <t>채소</t>
+  </si>
+  <si>
+    <t>먼저 고르면 채소를 빠뜨리지 않아요.</t>
+  </si>
+  <si>
+    <t>식생활지침 「채소 충분히」</t>
+  </si>
+  <si>
+    <t>채소를 넣으면 한 끼 채소가 늘어요.</t>
+  </si>
+  <si>
+    <t>WHO 채소 섭취 권고</t>
+  </si>
+  <si>
+    <t>채소가 많은 메뉴로 쉽게 채소를 더할 수 있어요.</t>
+  </si>
+  <si>
+    <t>씹는 채소 간식은 출출할 때 좋아요.</t>
+  </si>
+  <si>
+    <t>손질해 두면 내일 바로 조리할 수 있어요.</t>
+  </si>
+  <si>
+    <t>통에 담아 두면 꺼내 먹기 쉬워요.</t>
+  </si>
+  <si>
+    <t>음식 배치 연구 · 일반 상식</t>
+  </si>
+  <si>
+    <t>단 음료 · 단 간식</t>
+  </si>
+  <si>
+    <t>시럽을 빼면 커피의 당이 줄어요.</t>
+  </si>
+  <si>
+    <t>WHO 당류 섭취 권고</t>
+  </si>
+  <si>
+    <t>무가당 음료는 당 걱정이 없어요.</t>
+  </si>
+  <si>
+    <t>식약처 영양성분 표시 안내</t>
+  </si>
+  <si>
+    <t>덜 단 빵을 고르면 당을 줄일 수 있어요.</t>
+  </si>
+  <si>
+    <t>물이 있으면 단 음료를 덜 사게 돼요.</t>
+  </si>
+  <si>
+    <t>WHO 당류 권고 · 일반 상식</t>
+  </si>
+  <si>
+    <t>보리차가 있으면 단 음료에 손이 덜 가요.</t>
+  </si>
+  <si>
+    <t>일반 상식</t>
+  </si>
+  <si>
+    <t>목록대로 사면 충동구매가 줄어요.</t>
+  </si>
+  <si>
+    <t>음식 환경 연구 · 일반 상식</t>
+  </si>
+  <si>
+    <t>짠맛 · 국물</t>
+  </si>
+  <si>
+    <t>국은 건더기부터 먹기</t>
+  </si>
+  <si>
+    <t>건더기부터 먹으면 국물을 덜 먹게 돼요.</t>
+  </si>
+  <si>
+    <t>대한고혈압학회 나트륨 줄이기 권고</t>
+  </si>
+  <si>
+    <t>이미 간이 된 음식은 그대로도 충분해요.</t>
+  </si>
+  <si>
+    <t>WHO 나트륨 줄이기 권고</t>
+  </si>
+  <si>
+    <t>덜어 먹으면 소스를 덜 쓰게 돼요.</t>
+  </si>
+  <si>
+    <t>식약처 나트륨 줄이기 안내</t>
+  </si>
+  <si>
+    <t>주문할 때 말하면 간을 줄일 수 있어요.</t>
+  </si>
+  <si>
+    <t>맑은 국은 찌개보다 덜 짠 편이에요.</t>
+  </si>
+  <si>
+    <t>국민건강영양조사 · 식약처</t>
+  </si>
+  <si>
+    <t>저염 제품을 쓰면 간을 덜 짜게 할 수 있어요.</t>
+  </si>
+  <si>
+    <t>식약처 나트륨 표시 안내</t>
+  </si>
+  <si>
+    <t>식사 시각</t>
+  </si>
+  <si>
+    <t>간식 시간이 있으면 저녁 과식을 막기 쉬워요.</t>
+  </si>
+  <si>
+    <t>미리 정하면 늦은 저녁을 피하기 쉬워요.</t>
+  </si>
+  <si>
+    <t>시간을 비워 두면 아침을 거르지 않아요.</t>
+  </si>
+  <si>
+    <t>일정한 식사 시간이 하루 리듬을 잡아 줘요.</t>
+  </si>
+  <si>
+    <t>물을 마시면 잠깐의 허기가 가라앉기도 해요.</t>
+  </si>
+  <si>
+    <t>잠들 시간이 정해지면 늦은 야식이 줄어요.</t>
+  </si>
+  <si>
+    <t>수면과 야식(일반 상식)</t>
+  </si>
+  <si>
+    <t>식사 속도 · 양</t>
+  </si>
+  <si>
+    <t>잠깐 쉬면 천천히 먹는 흐름이 생겨요.</t>
+  </si>
+  <si>
+    <t>식사 속도와 포만감 연구</t>
+  </si>
+  <si>
+    <t>중간에 쉬면 배부름을 느끼기 쉬워요.</t>
+  </si>
+  <si>
+    <t>늘 쓰는 그릇에 담으면 양을 가늠하기 쉬워요.</t>
+  </si>
+  <si>
+    <t>그릇 크기와 섭취량 연구</t>
+  </si>
+  <si>
+    <t>배고픈 정도를 알면 알맞게 먹기 쉬워요.</t>
+  </si>
+  <si>
+    <t>주의 깊은 식사 연구</t>
+  </si>
+  <si>
+    <t>돌아보면 내일 알맞은 양을 정하기 쉬워요.</t>
+  </si>
+  <si>
+    <t>미리 생각해 두면 과식을 막기 쉬워요.</t>
+  </si>
+  <si>
+    <t>단백질</t>
+  </si>
+  <si>
+    <t>한 가지라도 고르면 끼니 단백질이 채워져요.</t>
+  </si>
+  <si>
+    <t>한국인 영양소 섭취기준</t>
+  </si>
+  <si>
+    <t>두유는 간편하게 단백질을 더해 줘요.</t>
+  </si>
+  <si>
+    <t>간편식 중에도 단백질을 챙길 수 있어요.</t>
+  </si>
+  <si>
+    <t>두부를 넣으면 국 한 그릇에 단백질이 더해져요.</t>
+  </si>
+  <si>
+    <t>썰어 두면 아침에 바로 조리할 수 있어요.</t>
+  </si>
+  <si>
+    <t>도시락에 담으면 밖에서도 단백질을 챙겨요.</t>
+  </si>
+  <si>
+    <t>기름진 음식</t>
+  </si>
+  <si>
+    <t>WHO 포화지방 줄이기 권고</t>
+  </si>
+  <si>
+    <t>무침은 기름을 덜 쓰는 반찬이에요.</t>
+  </si>
+  <si>
+    <t>식생활지침 「기름진 음식 줄이기」</t>
+  </si>
+  <si>
+    <t>튀김옷은 벗겨서 먹기</t>
+  </si>
+  <si>
+    <t>튀김옷에 기름이 가장 많이 배어 있어요.</t>
+  </si>
+  <si>
+    <t>따로 받으면 뿌리는 양을 조절할 수 있어요.</t>
+  </si>
+  <si>
+    <t>무침은 기름을 덜 쓰는 조리법이에요.</t>
+  </si>
+  <si>
+    <t>요리법을 알면 기름을 덜 쓰게 돼요.</t>
+  </si>
+  <si>
+    <t>10-12 4차(입문) 48개 추가: 목표를 달성해 단계가 오르는 사람이 많지 않아 대부분 입문 문구를 보므로, 축마다 입문 6개(낮 4 · 저녁·새벽 2)를 더함. 합계 111개</t>
+  </si>
+  <si>
+    <t>입문</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10-12 1~3차 중 쉬운 문구 13개의 단계를 낮춤(입문 12 · 기본 1). 바뀐 단계 칸은 빨간 글씨</t>
+  </si>
+  <si>
+    <t>삼겹살 대신 수육·보쌈 고르기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삶은 고기는 구운 삼겹살보다 기름이 덜해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생선구이는 돈가스보다 기름이 덜 들어가요.</t>
+  </si>
+  <si>
+    <t>WHO·한국지질동맥경화학회 포화지방 줄이기 권고</t>
+  </si>
+  <si>
+    <t>삶은 닭은 튀긴 닭보다 기름이 적어요.</t>
+  </si>
+  <si>
+    <t>국민건강영양조사 · 식약처 나트륨 줄이기 안내</t>
+  </si>
+  <si>
+    <t>아메리카노에는 설탕이 들어 있지 않아요.</t>
+  </si>
+  <si>
+    <t>플레인 요거트는 단맛이 훨씬 덜해요.</t>
+  </si>
+  <si>
+    <t>비빔밥은 채소를 넉넉히 먹을 수 있어요.</t>
+  </si>
+  <si>
+    <t>10-12 메뉴 바꾸기 문구 6개 추가(삼겹살 대신 수육·보쌈처럼 구체적인 메뉴를 권함). 합계 117개</t>
+  </si>
+  <si>
+    <t>이전 문구(12자 넘음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침 메뉴 미리 정하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>점심시간 적어 두기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일 채소 꺼내 두기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>채소 반찬 만들어 두기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밖에서도 채소 챙기기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단 간식 치워 두기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘 단 음료 돌아보기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작은 국그릇 쓰기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저염 제품 적어 두기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일 저녁 시각 정하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주방 불 일찍 끄기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>식사 속도 돌아보기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작은 그릇 꺼내 두기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단백질 반찬 정해 두기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>두부·달걀 사 두기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일은 구이로 정하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>튀김 대신 메뉴 적기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘 먹은 끼니 적기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>먹기 편한 시간 적기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일 먹을 것 정하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일 세 끼 계획하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>거른 끼니 돌아보기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>먹은 채소 돌아보기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제철 채소 장보기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대신 마실 음료 정하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대신 먹을 간식 챙기기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>먹은 국물 양 돌아보기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일 국 싱겁게 끓이기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>식사 마칠 시각 정하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁 먹은 시각 적기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일은 천천히 먹기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>식탁에서 휴대폰 치우기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>끼니별 단백질 정하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>먹은 단백질 돌아보기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구이·찜 메뉴 정하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>먹은 튀김 돌아보기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기운 나는 때 적기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>첫 끼 시간 정하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침거리 사 두기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>간단 메뉴 정해 두기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>채소는 앞칸에 두기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국에 넣을 채소 정하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주간 채소 반찬 정하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>음료 당류 표시 보기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단 음료 사 두지 않기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단 음료 쉬는 날 두기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소금통 치워 두기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국은 건더기 위주로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나트륨 표시 비교하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>간식 자리 정리하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁 일찍 마치기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁 시각 맞춰 먹기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>식사 시간 넉넉히 잡기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TV 끄고 식사하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>함께 먹는 끼니 정하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침 달걀 꺼내 두기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생선 먹을 날 정하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>콩·두부 요리법 찾기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구워 먹을 재료 꺼내기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>찜 요리 메뉴 정하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>외식 메뉴 미리 정하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>먹기 편한 음식 정하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>식사 느낌 한 줄 적기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>점심 거르지 않게 알림 맞춰 두기</t>
-  </si>
-  <si>
-    <t>알림이 있으면 바쁜 날에도 점심을 놓치지 않아요.</t>
-  </si>
-  <si>
-    <t>식생활지침 「규칙적인 식사」</t>
-  </si>
-  <si>
-    <t>언제나(낮 포함)</t>
-  </si>
-  <si>
-    <t>아니오</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>점심 알림 맞춰 두기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>식사 시간 달력에 적어 두기</t>
-  </si>
-  <si>
-    <t>적어 두면 끼니 시간을 지키기 쉬워요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>식사 시간 달력에 적기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>배고파지기 전에 끼니 챙기기</t>
-  </si>
-  <si>
-    <t>너무 배고프면 한꺼번에 많이 먹기 쉬워요.</t>
-  </si>
-  <si>
-    <t>식사 간격과 과식(일반 상식)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배고프기 전에 먹기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>외출할 때 간단한 요깃거리 챙기기</t>
-  </si>
-  <si>
-    <t>요깃거리가 있으면 끼니를 건너뛰지 않아요.</t>
-  </si>
-  <si>
-    <t>식생활지침 · 일반 상식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>요깃거리 챙겨 나가기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>내일 아침 먹을 그릇 꺼내 두기</t>
-  </si>
-  <si>
-    <t>그릇이 나와 있으면 아침을 차리기 쉬워요.</t>
-  </si>
-  <si>
-    <t>식생활지침 「아침밥 먹기」</t>
-  </si>
-  <si>
-    <t>저녁(17시 이후) · 새벽</t>
-  </si>
-  <si>
-    <t>예</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침 그릇 꺼내 두기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>자기 전 내일 첫 끼 떠올리기</t>
-  </si>
-  <si>
-    <t>떠올려 두면 아침에 바로 챙길 수 있어요.</t>
-  </si>
-  <si>
-    <t>채소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일 첫 끼 떠올리기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>점심엔 채소 반찬 먼저 고르기</t>
-  </si>
-  <si>
-    <t>먼저 고르면 채소를 빠뜨리지 않아요.</t>
-  </si>
-  <si>
-    <t>식생활지침 「채소 충분히」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>채소 반찬 먼저 고르기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>라면 끓일 때 채소 한 줌 넣기</t>
-  </si>
-  <si>
-    <t>채소를 넣으면 한 끼 채소가 늘어요.</t>
-  </si>
-  <si>
-    <t>WHO 채소 섭취 권고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>라면에 채소 넣기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>김밥 살 때 채소 많은 것 고르기</t>
-  </si>
-  <si>
-    <t>채소가 많은 메뉴로 쉽게 채소를 더할 수 있어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>채소 많은 김밥 고르기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>간식으로 오이·당근 챙기기</t>
-  </si>
-  <si>
-    <t>씹는 채소 간식은 출출할 때 좋아요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오이·당근 간식 챙기기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>내일 반찬에 쓸 채소 손질하기</t>
-  </si>
-  <si>
-    <t>손질해 두면 내일 바로 조리할 수 있어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일 쓸 채소 손질하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>샐러드 채소 씻어 통에 담기</t>
-  </si>
-  <si>
-    <t>통에 담아 두면 꺼내 먹기 쉬워요.</t>
-  </si>
-  <si>
-    <t>음식 배치 연구 · 일반 상식</t>
-  </si>
-  <si>
-    <t>단 음료 · 단 간식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>샐러드 채소 씻어 두기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>커피는 시럽 없이 주문하기</t>
-  </si>
-  <si>
-    <t>시럽을 빼면 커피의 당이 줄어요.</t>
-  </si>
-  <si>
-    <t>WHO 당류 섭취 권고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시럽 뺀 커피 고르기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>편의점에선 무가당 음료 고르기</t>
-  </si>
-  <si>
-    <t>무가당 음료는 당 걱정이 없어요.</t>
-  </si>
-  <si>
-    <t>식약처 영양성분 표시 안내</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무가당 음료 고르기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>빵 고를 때 덜 단 것 고르기</t>
-  </si>
-  <si>
-    <t>덜 단 빵을 고르면 당을 줄일 수 있어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>덜 단 빵 고르기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>가방에 물병 챙겨 다니기</t>
-  </si>
-  <si>
-    <t>물이 있으면 단 음료를 덜 사게 돼요.</t>
-  </si>
-  <si>
-    <t>WHO 당류 권고 · 일반 상식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물병 챙겨 다니기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>내일 마실 보리차 끓여 두기</t>
-  </si>
-  <si>
-    <t>보리차가 있으면 단 음료에 손이 덜 가요.</t>
-  </si>
-  <si>
-    <t>일반 상식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보리차 끓여 두기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>단 간식 덜 사게 장 목록 쓰기</t>
-  </si>
-  <si>
-    <t>목록대로 사면 충동구매가 줄어요.</t>
-  </si>
-  <si>
-    <t>음식 환경 연구 · 일반 상식</t>
-  </si>
-  <si>
-    <t>짠맛 · 국물</t>
-  </si>
-  <si>
-    <t>국은 건더기부터 먹기</t>
-  </si>
-  <si>
-    <t>건더기부터 먹으면 국물을 덜 먹게 돼요.</t>
-  </si>
-  <si>
-    <t>대한고혈압학회 나트륨 줄이기 권고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단 간식 빼고 장보기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>간 보고 소금 더 넣지 않기</t>
-  </si>
-  <si>
-    <t>이미 간이 된 음식은 그대로도 충분해요.</t>
-  </si>
-  <si>
-    <t>WHO 나트륨 줄이기 권고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소금 더 넣지 않기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>소스는 찍을 만큼만 덜기</t>
-  </si>
-  <si>
-    <t>덜어 먹으면 소스를 덜 쓰게 돼요.</t>
-  </si>
-  <si>
-    <t>식약처 나트륨 줄이기 안내</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소스 조금만 찍기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>외식 땐 싱겁게 해 달라고 하기</t>
-  </si>
-  <si>
-    <t>주문할 때 말하면 간을 줄일 수 있어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>싱겁게 해 달라고 하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>내일 국은 맑은 국으로 정하기</t>
-  </si>
-  <si>
-    <t>맑은 국은 찌개보다 덜 짠 편이에요.</t>
-  </si>
-  <si>
-    <t>국민건강영양조사 · 식약처</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일은 맑은 국으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>저염 간장 장 목록에 적기</t>
-  </si>
-  <si>
-    <t>저염 제품을 쓰면 간을 덜 짜게 할 수 있어요.</t>
-  </si>
-  <si>
-    <t>식약처 나트륨 표시 안내</t>
-  </si>
-  <si>
-    <t>식사 시각</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저염 간장 사 두기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>오후 간식 시간 정해 두기</t>
-  </si>
-  <si>
-    <t>간식 시간이 있으면 저녁 과식을 막기 쉬워요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>간식 시간 정해 두기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>저녁 먹을 시간 미리 정하기</t>
-  </si>
-  <si>
-    <t>미리 정하면 늦은 저녁을 피하기 쉬워요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁 시간 미리 정하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>출근 전 아침 먹을 시간 비우기</t>
-  </si>
-  <si>
-    <t>시간을 비워 두면 아침을 거르지 않아요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침 먹을 시간 비우기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>식사 시간 일정하게 맞추기</t>
-  </si>
-  <si>
-    <t>일정한 식사 시간이 하루 리듬을 잡아 줘요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>끼니 시간 맞춰 먹기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>야식 생각나면 물 한 잔 먼저</t>
-  </si>
-  <si>
-    <t>물을 마시면 잠깐의 허기가 가라앉기도 해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>야식 대신 물 한 잔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>잠들 시간 미리 정해 두기</t>
-  </si>
-  <si>
-    <t>잠들 시간이 정해지면 늦은 야식이 줄어요.</t>
-  </si>
-  <si>
-    <t>수면과 야식(일반 상식)</t>
-  </si>
-  <si>
-    <t>식사 속도 · 양</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠들 시간 정해 두기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>첫 숟가락 뒤 잠깐 쉬어 가기</t>
-  </si>
-  <si>
-    <t>잠깐 쉬면 천천히 먹는 흐름이 생겨요.</t>
-  </si>
-  <si>
-    <t>식사 속도와 포만감 연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>첫술 뒤 잠깐 쉬기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>식사 중 물 한 모금 쉬어 가기</t>
-  </si>
-  <si>
-    <t>중간에 쉬면 배부름을 느끼기 쉬워요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물 마시며 쉬어 가기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>밥은 평소 그릇에 담아 먹기</t>
-  </si>
-  <si>
-    <t>늘 쓰는 그릇에 담으면 양을 가늠하기 쉬워요.</t>
-  </si>
-  <si>
-    <t>그릇 크기와 섭취량 연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밥은 평소 그릇으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>먹기 전에 배고픈 정도 살피기</t>
-  </si>
-  <si>
-    <t>배고픈 정도를 알면 알맞게 먹기 쉬워요.</t>
-  </si>
-  <si>
-    <t>주의 깊은 식사 연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배고픈 정도 살피기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>오늘 배부른 정도 돌아보기</t>
-  </si>
-  <si>
-    <t>돌아보면 내일 알맞은 양을 정하기 쉬워요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배부른 정도 돌아보기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>내일 먹을 양 미리 생각해 두기</t>
-  </si>
-  <si>
-    <t>미리 생각해 두면 과식을 막기 쉬워요.</t>
-  </si>
-  <si>
-    <t>단백질</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일 먹을 양 정하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>점심 메뉴에 단백질 하나 고르기</t>
-  </si>
-  <si>
-    <t>한 가지라도 고르면 끼니 단백질이 채워져요.</t>
-  </si>
-  <si>
-    <t>한국인 영양소 섭취기준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>점심에 단백질 고르기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>간식으로 두유 한 팩 챙기기</t>
-  </si>
-  <si>
-    <t>두유는 간편하게 단백질을 더해 줘요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>두유 한 팩 챙기기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>편의점에선 달걀·두부 고르기</t>
-  </si>
-  <si>
-    <t>간편식 중에도 단백질을 챙길 수 있어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>편의점에선 달걀 고르기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>국에 두부 몇 조각 넣기</t>
-  </si>
-  <si>
-    <t>두부를 넣으면 국 한 그릇에 단백질이 더해져요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국에 두부 넣기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>내일 아침 두부 썰어 두기</t>
-  </si>
-  <si>
-    <t>썰어 두면 아침에 바로 조리할 수 있어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일 아침 두부 썰기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>내일 도시락에 단백질 담기</t>
-  </si>
-  <si>
-    <t>도시락에 담으면 밖에서도 단백질을 챙겨요.</t>
-  </si>
-  <si>
-    <t>기름진 음식</t>
-  </si>
-  <si>
-    <t>WHO 포화지방 줄이기 권고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도시락에 단백질 담기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼겹살 대신 보쌈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>볶음보다 무침 반찬 고르기</t>
-  </si>
-  <si>
-    <t>무침은 기름을 덜 쓰는 반찬이에요.</t>
-  </si>
-  <si>
-    <t>식생활지침 「기름진 음식 줄이기」</t>
-  </si>
-  <si>
-    <t>튀김옷은 벗겨서 먹기</t>
-  </si>
-  <si>
-    <t>튀김옷에 기름이 가장 많이 배어 있어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>볶음 대신 무침 고르기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>드레싱은 따로 달라고 하기</t>
-  </si>
-  <si>
-    <t>따로 받으면 뿌리는 양을 조절할 수 있어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>드레싱은 따로 받기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>내일 반찬은 무침으로 정하기</t>
-  </si>
-  <si>
-    <t>무침은 기름을 덜 쓰는 조리법이에요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일 반찬은 무침으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>기름 덜 쓰는 요리 하나 찾기</t>
-  </si>
-  <si>
-    <t>요리법을 알면 기름을 덜 쓰게 돼요.</t>
-  </si>
-  <si>
-    <t>10-12 4차(입문) 48개 추가: 목표를 달성해 단계가 오르는 사람이 많지 않아 대부분 입문 문구를 보므로, 축마다 입문 6개(낮 4 · 저녁·새벽 2)를 더함. 합계 111개</t>
-  </si>
-  <si>
-    <t>입문</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10-12 1~3차 중 쉬운 문구 13개의 단계를 낮춤(입문 12 · 기본 1). 바뀐 단계 칸은 빨간 글씨</t>
-  </si>
-  <si>
-    <t>고기는 구워서 먹기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>삼겹살 대신 수육·보쌈 고르기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>삶은 고기는 구운 삼겹살보다 기름이 덜해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기름 적은 요리 찾기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>돈가스 대신 생선구이 고르기</t>
-  </si>
-  <si>
-    <t>생선구이는 돈가스보다 기름이 덜 들어가요.</t>
-  </si>
-  <si>
-    <t>WHO·한국지질동맥경화학회 포화지방 줄이기 권고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>돈가스 대신 생선구이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>치킨 대신 닭백숙 고르기</t>
-  </si>
-  <si>
-    <t>삶은 닭은 튀긴 닭보다 기름이 적어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>치킨 대신 닭백숙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>김치찌개 대신 맑은 국 고르기</t>
-  </si>
-  <si>
-    <t>국민건강영양조사 · 식약처 나트륨 줄이기 안내</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김치찌개 대신 맑은 국</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>믹스커피 대신 아메리카노 고르기</t>
-  </si>
-  <si>
-    <t>아메리카노에는 설탕이 들어 있지 않아요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>믹스 대신 블랙커피</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>케이크 대신 플레인 요거트 고르기</t>
-  </si>
-  <si>
-    <t>플레인 요거트는 단맛이 훨씬 덜해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>케이크 대신 요거트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>짜장면 대신 비빔밥 고르기</t>
-  </si>
-  <si>
-    <t>비빔밥은 채소를 넉넉히 먹을 수 있어요.</t>
-  </si>
-  <si>
-    <t>10-12 메뉴 바꾸기 문구 6개 추가(삼겹살 대신 수육·보쌈처럼 구체적인 메뉴를 권함). 합계 117개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>짜장면 대신 비빔밥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10-12 글자 수 정책 맞춤: 타일 문구는 띄어쓰기 포함 12자 이내(09-29 확정, 화면 폭 한도는 22자). 12자를 넘던 115개를 모두 12자 이내로 줄임(평균 10.8자). 줄이기 전 문장은 「이전 문구」 열에 남김. 「왜 하는지」는 이유 한 줄 열에 둠</t>
+  </si>
+  <si>
+    <t>공통 조건: 띄어쓰기 포함 12자 이내 · 먹는 양을 늘리거나 줄이라는 말 없음(신장질환·당뇨병 사용자도 받음) · 저녁·새벽 문구는 식후 가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -7172,7 +7135,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F51797-492B-40AC-833D-E19CEF6E9FA5}">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="120.58203125" style="1" customWidth="1"/>
@@ -7181,7 +7144,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="20.5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="16" x14ac:dyDescent="0.45">
@@ -7196,42 +7159,47 @@
     </row>
     <row r="5" spans="1:1" ht="16" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>69</v>
+        <v>472</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="16" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="16" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="16" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>266</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>400</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>403</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>420</v>
+        <v>303</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -7278,16 +7246,16 @@
         <v>60</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>61</v>
@@ -7324,18 +7292,18 @@
       <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>79</v>
+      <c r="F2" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H2" s="3">
         <f t="shared" ref="H2:H33" si="0">LEN(F2)</f>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>5</v>
@@ -7364,20 +7332,20 @@
         <v>3</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>82</v>
+        <v>291</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>306</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H3" s="3">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>9</v>
@@ -7408,18 +7376,18 @@
       <c r="E4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>85</v>
+      <c r="F4" s="7" t="s">
+        <v>307</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>11</v>
@@ -7434,7 +7402,7 @@
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
     </row>
-    <row r="5" spans="1:15" ht="16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -7450,18 +7418,18 @@
       <c r="E5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>88</v>
+      <c r="F5" s="7" t="s">
+        <v>308</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>12</v>
@@ -7492,18 +7460,18 @@
       <c r="E6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>91</v>
+      <c r="F6" s="7" t="s">
+        <v>309</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>14</v>
@@ -7534,18 +7502,18 @@
       <c r="E7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>94</v>
+      <c r="F7" s="7" t="s">
+        <v>310</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>16</v>
@@ -7574,20 +7542,20 @@
         <v>15</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>97</v>
+        <v>291</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>311</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>17</v>
@@ -7602,7 +7570,7 @@
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
     </row>
-    <row r="9" spans="1:15" ht="16" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -7618,18 +7586,18 @@
       <c r="E9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>100</v>
+      <c r="F9" s="7" t="s">
+        <v>312</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>19</v>
@@ -7658,20 +7626,20 @@
         <v>18</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>103</v>
+        <v>291</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>313</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>20</v>
@@ -7702,18 +7670,18 @@
       <c r="E11" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>106</v>
+      <c r="F11" s="7" t="s">
+        <v>314</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>9</v>
@@ -7742,20 +7710,20 @@
         <v>21</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>109</v>
+        <v>291</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>315</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>22</v>
@@ -7786,18 +7754,18 @@
       <c r="E13" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>112</v>
+      <c r="F13" s="7" t="s">
+        <v>316</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="H13" s="3">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>24</v>
@@ -7826,20 +7794,20 @@
         <v>23</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>115</v>
+        <v>291</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>317</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>25</v>
@@ -7870,18 +7838,18 @@
       <c r="E15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>118</v>
+      <c r="F15" s="7" t="s">
+        <v>318</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>27</v>
@@ -7910,20 +7878,20 @@
         <v>26</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>121</v>
+        <v>291</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>319</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="H16" s="3">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>28</v>
@@ -7954,18 +7922,18 @@
       <c r="E17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>124</v>
+      <c r="F17" s="7" t="s">
+        <v>320</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="H17" s="3">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>30</v>
@@ -7994,20 +7962,20 @@
         <v>29</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>127</v>
+        <v>291</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>321</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>31</v>
@@ -8038,18 +8006,18 @@
       <c r="E19" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>130</v>
+      <c r="F19" s="7" t="s">
+        <v>322</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="H19" s="3">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>17</v>
@@ -8080,18 +8048,18 @@
       <c r="E20" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>133</v>
+      <c r="F20" s="7" t="s">
+        <v>323</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="H20" s="3">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>33</v>
@@ -8122,18 +8090,18 @@
       <c r="E21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>136</v>
+      <c r="F21" s="7" t="s">
+        <v>324</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="H21" s="3">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>33</v>
@@ -8148,7 +8116,7 @@
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
     </row>
-    <row r="22" spans="1:15" ht="16" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -8164,18 +8132,18 @@
       <c r="E22" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>139</v>
+      <c r="F22" s="7" t="s">
+        <v>325</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="H22" s="3">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>9</v>
@@ -8206,18 +8174,18 @@
       <c r="E23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>142</v>
+      <c r="F23" s="7" t="s">
+        <v>326</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="H23" s="3">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>17</v>
@@ -8248,18 +8216,18 @@
       <c r="E24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>145</v>
+      <c r="F24" s="7" t="s">
+        <v>327</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="H24" s="3">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>17</v>
@@ -8288,20 +8256,20 @@
         <v>10</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>148</v>
+        <v>291</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>328</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="H25" s="3">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>12</v>
@@ -8330,20 +8298,20 @@
         <v>15</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>151</v>
+        <v>291</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>329</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="H26" s="3">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>35</v>
@@ -8374,18 +8342,18 @@
       <c r="E27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>154</v>
+      <c r="F27" s="7" t="s">
+        <v>330</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="H27" s="3">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>35</v>
@@ -8416,18 +8384,18 @@
       <c r="E28" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>157</v>
+      <c r="F28" s="7" t="s">
+        <v>331</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="H28" s="3">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>36</v>
@@ -8456,20 +8424,20 @@
         <v>18</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>160</v>
+        <v>292</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>332</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>37</v>
@@ -8500,18 +8468,18 @@
       <c r="E30" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F30" s="3" t="s">
-        <v>163</v>
+      <c r="F30" s="7" t="s">
+        <v>333</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="H30" s="3">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>9</v>
@@ -8542,18 +8510,18 @@
       <c r="E31" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F31" s="3" t="s">
-        <v>166</v>
+      <c r="F31" s="7" t="s">
+        <v>334</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="H31" s="3">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>17</v>
@@ -8582,20 +8550,20 @@
         <v>23</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>169</v>
+        <v>291</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>335</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="H32" s="3">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>38</v>
@@ -8626,18 +8594,18 @@
       <c r="E33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>172</v>
+      <c r="F33" s="7" t="s">
+        <v>336</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="H33" s="3">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>39</v>
@@ -8668,18 +8636,18 @@
       <c r="E34" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F34" s="3" t="s">
-        <v>175</v>
+      <c r="F34" s="7" t="s">
+        <v>337</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="H34" s="3">
         <f t="shared" ref="H34:H64" si="1">LEN(F34)</f>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>176</v>
+        <v>141</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>28</v>
@@ -8710,18 +8678,18 @@
       <c r="E35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>178</v>
+      <c r="F35" s="7" t="s">
+        <v>338</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="H35" s="3">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>179</v>
+        <v>143</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>17</v>
@@ -8752,18 +8720,18 @@
       <c r="E36" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>181</v>
+      <c r="F36" s="7" t="s">
+        <v>339</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>180</v>
+        <v>144</v>
       </c>
       <c r="H36" s="3">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>182</v>
+        <v>145</v>
       </c>
       <c r="J36" s="3" t="s">
         <v>31</v>
@@ -8794,18 +8762,18 @@
       <c r="E37" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F37" s="3" t="s">
-        <v>184</v>
+      <c r="F37" s="7" t="s">
+        <v>340</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="H37" s="3">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="J37" s="3" t="s">
         <v>17</v>
@@ -8836,18 +8804,18 @@
       <c r="E38" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F38" s="3" t="s">
-        <v>186</v>
+      <c r="F38" s="7" t="s">
+        <v>341</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>185</v>
+        <v>147</v>
       </c>
       <c r="H38" s="3">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>187</v>
+        <v>148</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>33</v>
@@ -8878,18 +8846,18 @@
       <c r="E39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F39" s="3" t="s">
-        <v>189</v>
+      <c r="F39" s="7" t="s">
+        <v>342</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>188</v>
+        <v>149</v>
       </c>
       <c r="H39" s="3">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>40</v>
@@ -8920,18 +8888,18 @@
       <c r="E40" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F40" s="3" t="s">
-        <v>192</v>
+      <c r="F40" s="7" t="s">
+        <v>343</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="H40" s="3">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>193</v>
+        <v>152</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>40</v>
@@ -8960,20 +8928,20 @@
         <v>3</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>195</v>
+        <v>291</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>344</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>194</v>
+        <v>153</v>
       </c>
       <c r="H41" s="3">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>196</v>
+        <v>154</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>42</v>
@@ -9004,18 +8972,18 @@
       <c r="E42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>198</v>
+      <c r="F42" s="7" t="s">
+        <v>345</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>197</v>
+        <v>155</v>
       </c>
       <c r="H42" s="3">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>199</v>
+        <v>156</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>16</v>
@@ -9044,20 +9012,20 @@
         <v>10</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>201</v>
+        <v>291</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>346</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>200</v>
+        <v>157</v>
       </c>
       <c r="H43" s="3">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>14</v>
@@ -9088,18 +9056,18 @@
       <c r="E44" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>204</v>
+      <c r="F44" s="7" t="s">
+        <v>347</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>203</v>
+        <v>159</v>
       </c>
       <c r="H44" s="3">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>205</v>
+        <v>160</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>43</v>
@@ -9130,18 +9098,18 @@
       <c r="E45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>207</v>
+      <c r="F45" s="7" t="s">
+        <v>348</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>206</v>
+        <v>161</v>
       </c>
       <c r="H45" s="3">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>208</v>
+        <v>162</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>44</v>
@@ -9172,18 +9140,18 @@
       <c r="E46" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>210</v>
+      <c r="F46" s="7" t="s">
+        <v>349</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>209</v>
+        <v>163</v>
       </c>
       <c r="H46" s="3">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>211</v>
+        <v>164</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>45</v>
@@ -9214,18 +9182,18 @@
       <c r="E47" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>213</v>
+      <c r="F47" s="7" t="s">
+        <v>350</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>212</v>
+        <v>165</v>
       </c>
       <c r="H47" s="3">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>46</v>
@@ -9256,18 +9224,18 @@
       <c r="E48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>216</v>
+      <c r="F48" s="7" t="s">
+        <v>351</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>215</v>
+        <v>167</v>
       </c>
       <c r="H48" s="3">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>217</v>
+        <v>168</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>19</v>
@@ -9298,18 +9266,18 @@
       <c r="E49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>219</v>
+      <c r="F49" s="7" t="s">
+        <v>352</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>218</v>
+        <v>169</v>
       </c>
       <c r="H49" s="3">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>47</v>
@@ -9340,18 +9308,18 @@
       <c r="E50" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F50" s="3" t="s">
-        <v>222</v>
+      <c r="F50" s="7" t="s">
+        <v>353</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>221</v>
+        <v>171</v>
       </c>
       <c r="H50" s="3">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>223</v>
+        <v>172</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>48</v>
@@ -9382,18 +9350,18 @@
       <c r="E51" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F51" s="3" t="s">
-        <v>225</v>
+      <c r="F51" s="7" t="s">
+        <v>354</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>224</v>
+        <v>173</v>
       </c>
       <c r="H51" s="3">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>226</v>
+        <v>174</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>22</v>
@@ -9424,18 +9392,18 @@
       <c r="E52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>228</v>
+      <c r="F52" s="7" t="s">
+        <v>355</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>227</v>
+        <v>175</v>
       </c>
       <c r="H52" s="3">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>229</v>
+        <v>176</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>49</v>
@@ -9466,18 +9434,18 @@
       <c r="E53" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F53" s="3" t="s">
-        <v>231</v>
+      <c r="F53" s="7" t="s">
+        <v>356</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>230</v>
+        <v>177</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>232</v>
+        <v>178</v>
       </c>
       <c r="J53" s="3" t="s">
         <v>9</v>
@@ -9508,18 +9476,18 @@
       <c r="E54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>234</v>
+      <c r="F54" s="7" t="s">
+        <v>357</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>233</v>
+        <v>179</v>
       </c>
       <c r="H54" s="3">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>235</v>
+        <v>180</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>24</v>
@@ -9550,18 +9518,18 @@
       <c r="E55" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F55" s="3" t="s">
-        <v>237</v>
+      <c r="F55" s="7" t="s">
+        <v>358</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>236</v>
+        <v>181</v>
       </c>
       <c r="H55" s="3">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>238</v>
+        <v>182</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>50</v>
@@ -9592,18 +9560,18 @@
       <c r="E56" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F56" s="3" t="s">
-        <v>240</v>
+      <c r="F56" s="7" t="s">
+        <v>359</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>239</v>
+        <v>183</v>
       </c>
       <c r="H56" s="3">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>241</v>
+        <v>184</v>
       </c>
       <c r="J56" s="3" t="s">
         <v>51</v>
@@ -9634,18 +9602,18 @@
       <c r="E57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>243</v>
+      <c r="F57" s="7" t="s">
+        <v>360</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>242</v>
+        <v>185</v>
       </c>
       <c r="H57" s="3">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>244</v>
+        <v>186</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>28</v>
@@ -9676,18 +9644,18 @@
       <c r="E58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>246</v>
+      <c r="F58" s="7" t="s">
+        <v>361</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>245</v>
+        <v>187</v>
       </c>
       <c r="H58" s="3">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>52</v>
@@ -9718,18 +9686,18 @@
       <c r="E59" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>249</v>
+      <c r="F59" s="7" t="s">
+        <v>362</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>248</v>
+        <v>189</v>
       </c>
       <c r="H59" s="3">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>250</v>
+        <v>190</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>53</v>
@@ -9744,7 +9712,7 @@
       <c r="N59" s="3"/>
       <c r="O59" s="3"/>
     </row>
-    <row r="60" spans="1:15" ht="16" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -9760,18 +9728,18 @@
       <c r="E60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>252</v>
+      <c r="F60" s="7" t="s">
+        <v>363</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>251</v>
+        <v>191</v>
       </c>
       <c r="H60" s="3">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>253</v>
+        <v>192</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>54</v>
@@ -9786,7 +9754,7 @@
       <c r="N60" s="3"/>
       <c r="O60" s="3"/>
     </row>
-    <row r="61" spans="1:15" ht="16" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -9802,18 +9770,18 @@
       <c r="E61" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F61" s="3" t="s">
-        <v>255</v>
+      <c r="F61" s="7" t="s">
+        <v>364</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>254</v>
+        <v>193</v>
       </c>
       <c r="H61" s="3">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>256</v>
+        <v>194</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>31</v>
@@ -9844,18 +9812,18 @@
       <c r="E62" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>258</v>
+      <c r="F62" s="7" t="s">
+        <v>365</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>257</v>
+        <v>195</v>
       </c>
       <c r="H62" s="3">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>259</v>
+        <v>196</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>55</v>
@@ -9886,18 +9854,18 @@
       <c r="E63" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F63" s="3" t="s">
-        <v>261</v>
+      <c r="F63" s="7" t="s">
+        <v>366</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>260</v>
+        <v>197</v>
       </c>
       <c r="H63" s="3">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>262</v>
+        <v>198</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>33</v>
@@ -9928,18 +9896,18 @@
       <c r="E64" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F64" s="3" t="s">
-        <v>264</v>
+      <c r="F64" s="7" t="s">
+        <v>367</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>263</v>
+        <v>199</v>
       </c>
       <c r="H64" s="3">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>265</v>
+        <v>200</v>
       </c>
       <c r="J64" s="3" t="s">
         <v>17</v>
@@ -9959,38 +9927,38 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>269</v>
+        <v>204</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>271</v>
+        <v>205</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>369</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>0</v>
+        <v>368</v>
       </c>
       <c r="H65" s="3">
         <f t="shared" ref="H65:H112" si="2">LEN(F65)</f>
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>272</v>
+        <v>206</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>273</v>
+        <v>207</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M65" s="3"/>
       <c r="N65" s="3"/>
@@ -10001,38 +9969,38 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>269</v>
+        <v>204</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>276</v>
+        <v>205</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>371</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="H66" s="3">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>277</v>
+        <v>210</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>273</v>
+        <v>207</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M66" s="3"/>
       <c r="N66" s="3"/>
@@ -10043,38 +10011,38 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>269</v>
+        <v>204</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>278</v>
+        <v>205</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>373</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>0</v>
+        <v>372</v>
       </c>
       <c r="H67" s="3">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>279</v>
+        <v>211</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>280</v>
+        <v>212</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
@@ -10085,38 +10053,38 @@
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>269</v>
+        <v>204</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>281</v>
+        <v>205</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>375</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="H68" s="3">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>282</v>
+        <v>213</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>283</v>
+        <v>214</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M68" s="3"/>
       <c r="N68" s="3"/>
@@ -10127,38 +10095,38 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>269</v>
+        <v>204</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>284</v>
+        <v>205</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>377</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>0</v>
+        <v>376</v>
       </c>
       <c r="H69" s="3">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>285</v>
+        <v>215</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>286</v>
+        <v>216</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>287</v>
+        <v>217</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>288</v>
+        <v>218</v>
       </c>
       <c r="M69" s="3"/>
       <c r="N69" s="3"/>
@@ -10169,38 +10137,38 @@
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>269</v>
+        <v>204</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>289</v>
+        <v>205</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>379</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>0</v>
+        <v>378</v>
       </c>
       <c r="H70" s="3">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>290</v>
+        <v>219</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>286</v>
+        <v>216</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>287</v>
+        <v>217</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>288</v>
+        <v>218</v>
       </c>
       <c r="M70" s="3"/>
       <c r="N70" s="3"/>
@@ -10211,38 +10179,38 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>291</v>
+        <v>220</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>292</v>
+        <v>205</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>381</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="H71" s="3">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>293</v>
+        <v>221</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>294</v>
+        <v>222</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M71" s="3"/>
       <c r="N71" s="3"/>
@@ -10253,38 +10221,38 @@
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>291</v>
+        <v>220</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>295</v>
+        <v>205</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>383</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="H72" s="3">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>296</v>
+        <v>223</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>297</v>
+        <v>224</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M72" s="3"/>
       <c r="N72" s="3"/>
@@ -10295,38 +10263,38 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>291</v>
+        <v>220</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>298</v>
+        <v>205</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>385</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="H73" s="3">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>299</v>
+        <v>225</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>294</v>
+        <v>222</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M73" s="3"/>
       <c r="N73" s="3"/>
@@ -10337,38 +10305,38 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>291</v>
+        <v>220</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>300</v>
+        <v>205</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>387</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>0</v>
+        <v>386</v>
       </c>
       <c r="H74" s="3">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>301</v>
+        <v>226</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>297</v>
+        <v>224</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M74" s="3"/>
       <c r="N74" s="3"/>
@@ -10379,38 +10347,38 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>291</v>
+        <v>220</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>302</v>
+        <v>205</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>389</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>0</v>
+        <v>388</v>
       </c>
       <c r="H75" s="3">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>303</v>
+        <v>227</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>294</v>
+        <v>222</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>287</v>
+        <v>217</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>288</v>
+        <v>218</v>
       </c>
       <c r="M75" s="3"/>
       <c r="N75" s="3"/>
@@ -10421,38 +10389,38 @@
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>291</v>
+        <v>220</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>304</v>
+        <v>205</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>391</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="H76" s="3">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>306</v>
+        <v>229</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>287</v>
+        <v>217</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>288</v>
+        <v>218</v>
       </c>
       <c r="M76" s="3"/>
       <c r="N76" s="3"/>
@@ -10463,38 +10431,38 @@
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>307</v>
+        <v>230</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>308</v>
+        <v>205</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>393</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="H77" s="3">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>309</v>
+        <v>231</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M77" s="3"/>
       <c r="N77" s="3"/>
@@ -10505,38 +10473,38 @@
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>307</v>
+        <v>230</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>311</v>
+        <v>205</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>395</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="H78" s="3">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>312</v>
+        <v>233</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>313</v>
+        <v>234</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M78" s="3"/>
       <c r="N78" s="3"/>
@@ -10547,38 +10515,38 @@
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>307</v>
+        <v>230</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>314</v>
+        <v>205</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>397</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="H79" s="3">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>315</v>
+        <v>235</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M79" s="3"/>
       <c r="N79" s="3"/>
@@ -10589,38 +10557,38 @@
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>307</v>
+        <v>230</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>316</v>
+        <v>205</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>399</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="H80" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>317</v>
+        <v>236</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>318</v>
+        <v>237</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M80" s="3"/>
       <c r="N80" s="3"/>
@@ -10631,38 +10599,38 @@
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>307</v>
+        <v>230</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>319</v>
+        <v>205</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>401</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H81" s="3">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>320</v>
+        <v>238</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>321</v>
+        <v>239</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>287</v>
+        <v>217</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>288</v>
+        <v>218</v>
       </c>
       <c r="M81" s="3"/>
       <c r="N81" s="3"/>
@@ -10673,38 +10641,38 @@
         <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>307</v>
+        <v>230</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>322</v>
+        <v>205</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>403</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>0</v>
+        <v>402</v>
       </c>
       <c r="H82" s="3">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>323</v>
+        <v>240</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>324</v>
+        <v>241</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>287</v>
+        <v>217</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>288</v>
+        <v>218</v>
       </c>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
@@ -10715,19 +10683,19 @@
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>325</v>
+        <v>242</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>270</v>
+        <v>205</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>326</v>
+        <v>243</v>
       </c>
       <c r="G83" s="5" t="s">
         <v>0</v>
@@ -10737,16 +10705,16 @@
         <v>11</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>327</v>
+        <v>244</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>328</v>
+        <v>245</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M83" s="3"/>
       <c r="N83" s="3"/>
@@ -10757,38 +10725,38 @@
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>325</v>
+        <v>242</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>329</v>
+        <v>205</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>405</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="H84" s="3">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>330</v>
+        <v>246</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>331</v>
+        <v>247</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M84" s="3"/>
       <c r="N84" s="3"/>
@@ -10799,38 +10767,38 @@
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>325</v>
+        <v>242</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>332</v>
+        <v>205</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>407</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>0</v>
+        <v>406</v>
       </c>
       <c r="H85" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>333</v>
+        <v>248</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>334</v>
+        <v>249</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M85" s="3"/>
       <c r="N85" s="3"/>
@@ -10841,38 +10809,38 @@
         <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>325</v>
+        <v>242</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>335</v>
+        <v>205</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>409</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>0</v>
+        <v>408</v>
       </c>
       <c r="H86" s="3">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>336</v>
+        <v>250</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>334</v>
+        <v>249</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M86" s="3"/>
       <c r="N86" s="3"/>
@@ -10883,38 +10851,38 @@
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>325</v>
+        <v>242</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>337</v>
+        <v>205</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>411</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="H87" s="3">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>338</v>
+        <v>251</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>339</v>
+        <v>252</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>287</v>
+        <v>217</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>288</v>
+        <v>218</v>
       </c>
       <c r="M87" s="3"/>
       <c r="N87" s="3"/>
@@ -10925,38 +10893,38 @@
         <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>325</v>
+        <v>242</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>340</v>
+        <v>205</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>413</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>0</v>
+        <v>412</v>
       </c>
       <c r="H88" s="3">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>341</v>
+        <v>253</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>342</v>
+        <v>254</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>287</v>
+        <v>217</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>288</v>
+        <v>218</v>
       </c>
       <c r="M88" s="3"/>
       <c r="N88" s="3"/>
@@ -10967,38 +10935,38 @@
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>343</v>
+        <v>255</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>344</v>
+        <v>205</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>415</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>0</v>
+        <v>414</v>
       </c>
       <c r="H89" s="3">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>345</v>
+        <v>256</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>280</v>
+        <v>212</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M89" s="3"/>
       <c r="N89" s="3"/>
@@ -11009,38 +10977,38 @@
         <v>89</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>343</v>
+        <v>255</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>346</v>
+        <v>205</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>417</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>0</v>
+        <v>416</v>
       </c>
       <c r="H90" s="3">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>347</v>
+        <v>257</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>273</v>
+        <v>207</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
@@ -11051,38 +11019,38 @@
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>343</v>
+        <v>255</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>348</v>
+        <v>205</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>419</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>0</v>
+        <v>418</v>
       </c>
       <c r="H91" s="3">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>349</v>
+        <v>258</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>286</v>
+        <v>216</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L91" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M91" s="3"/>
       <c r="N91" s="3"/>
@@ -11093,38 +11061,38 @@
         <v>91</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>343</v>
+        <v>255</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>350</v>
+        <v>205</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>421</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="H92" s="3">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>273</v>
+        <v>207</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M92" s="3"/>
       <c r="N92" s="3"/>
@@ -11135,38 +11103,38 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>343</v>
+        <v>255</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>352</v>
+        <v>205</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>423</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>0</v>
+        <v>422</v>
       </c>
       <c r="H93" s="3">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>353</v>
+        <v>260</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>321</v>
+        <v>239</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>287</v>
+        <v>217</v>
       </c>
       <c r="L93" s="3" t="s">
-        <v>288</v>
+        <v>218</v>
       </c>
       <c r="M93" s="3"/>
       <c r="N93" s="3"/>
@@ -11177,38 +11145,38 @@
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>343</v>
+        <v>255</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>354</v>
+        <v>205</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>425</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>0</v>
+        <v>424</v>
       </c>
       <c r="H94" s="3">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>355</v>
+        <v>261</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>356</v>
+        <v>262</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>287</v>
+        <v>217</v>
       </c>
       <c r="L94" s="3" t="s">
-        <v>288</v>
+        <v>218</v>
       </c>
       <c r="M94" s="3"/>
       <c r="N94" s="3"/>
@@ -11219,38 +11187,38 @@
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>357</v>
+        <v>263</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>358</v>
+        <v>205</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>427</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="H95" s="3">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>359</v>
+        <v>264</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>360</v>
+        <v>265</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
@@ -11261,38 +11229,38 @@
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>357</v>
+        <v>263</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>361</v>
+        <v>205</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>429</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="H96" s="3">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>362</v>
+        <v>266</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>360</v>
+        <v>265</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M96" s="3"/>
       <c r="N96" s="3"/>
@@ -11303,38 +11271,38 @@
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>357</v>
+        <v>263</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>363</v>
+        <v>205</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>431</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="H97" s="3">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>364</v>
+        <v>267</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>365</v>
+        <v>268</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M97" s="3"/>
       <c r="N97" s="3"/>
@@ -11345,38 +11313,38 @@
         <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>357</v>
+        <v>263</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>366</v>
+        <v>205</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>433</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>0</v>
+        <v>432</v>
       </c>
       <c r="H98" s="3">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>367</v>
+        <v>269</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>368</v>
+        <v>270</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M98" s="3"/>
       <c r="N98" s="3"/>
@@ -11387,38 +11355,38 @@
         <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>357</v>
+        <v>263</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F99" s="3" t="s">
-        <v>369</v>
+        <v>205</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>435</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>0</v>
+        <v>434</v>
       </c>
       <c r="H99" s="3">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>370</v>
+        <v>271</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>368</v>
+        <v>270</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>287</v>
+        <v>217</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>288</v>
+        <v>218</v>
       </c>
       <c r="M99" s="3"/>
       <c r="N99" s="3"/>
@@ -11429,38 +11397,38 @@
         <v>99</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>357</v>
+        <v>263</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>371</v>
+        <v>205</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>437</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>0</v>
+        <v>436</v>
       </c>
       <c r="H100" s="3">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>372</v>
+        <v>272</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>368</v>
+        <v>270</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>287</v>
+        <v>217</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>288</v>
+        <v>218</v>
       </c>
       <c r="M100" s="3"/>
       <c r="N100" s="3"/>
@@ -11471,38 +11439,38 @@
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>373</v>
+        <v>273</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>374</v>
+        <v>205</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>439</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>0</v>
+        <v>438</v>
       </c>
       <c r="H101" s="3">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>375</v>
+        <v>274</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>376</v>
+        <v>275</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M101" s="3"/>
       <c r="N101" s="3"/>
@@ -11513,38 +11481,38 @@
         <v>101</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>373</v>
+        <v>273</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>377</v>
+        <v>205</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>441</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="H102" s="3">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>378</v>
+        <v>276</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>376</v>
+        <v>275</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M102" s="3"/>
       <c r="N102" s="3"/>
@@ -11555,38 +11523,38 @@
         <v>102</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>373</v>
+        <v>273</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F103" s="3" t="s">
-        <v>379</v>
+        <v>205</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>443</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>0</v>
+        <v>442</v>
       </c>
       <c r="H103" s="3">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>380</v>
+        <v>277</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>376</v>
+        <v>275</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M103" s="3"/>
       <c r="N103" s="3"/>
@@ -11597,38 +11565,38 @@
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>373</v>
+        <v>273</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F104" s="3" t="s">
-        <v>381</v>
+        <v>205</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>445</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>0</v>
+        <v>444</v>
       </c>
       <c r="H104" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>382</v>
+        <v>278</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>376</v>
+        <v>275</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L104" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M104" s="3"/>
       <c r="N104" s="3"/>
@@ -11639,38 +11607,38 @@
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>373</v>
+        <v>273</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F105" s="3" t="s">
-        <v>383</v>
+        <v>205</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>447</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>0</v>
+        <v>446</v>
       </c>
       <c r="H105" s="3">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>384</v>
+        <v>279</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>376</v>
+        <v>275</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>287</v>
+        <v>217</v>
       </c>
       <c r="L105" s="3" t="s">
-        <v>288</v>
+        <v>218</v>
       </c>
       <c r="M105" s="3"/>
       <c r="N105" s="3"/>
@@ -11681,38 +11649,38 @@
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>373</v>
+        <v>273</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F106" s="3" t="s">
-        <v>385</v>
+        <v>205</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>449</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="H106" s="3">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>386</v>
+        <v>280</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>376</v>
+        <v>275</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>287</v>
+        <v>217</v>
       </c>
       <c r="L106" s="3" t="s">
-        <v>288</v>
+        <v>218</v>
       </c>
       <c r="M106" s="3"/>
       <c r="N106" s="3"/>
@@ -11723,38 +11691,38 @@
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>387</v>
+        <v>281</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>270</v>
+        <v>205</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>405</v>
+        <v>450</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>404</v>
+        <v>294</v>
       </c>
       <c r="H107" s="3">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>406</v>
+        <v>295</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>388</v>
+        <v>282</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M107" s="3"/>
       <c r="N107" s="3"/>
@@ -11765,38 +11733,38 @@
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>387</v>
+        <v>281</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F108" s="3" t="s">
-        <v>389</v>
+        <v>205</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>452</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>0</v>
+        <v>451</v>
       </c>
       <c r="H108" s="3">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>390</v>
+        <v>283</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>391</v>
+        <v>284</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L108" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M108" s="3"/>
       <c r="N108" s="3"/>
@@ -11807,19 +11775,19 @@
         <v>108</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>387</v>
+        <v>281</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>270</v>
+        <v>205</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>392</v>
+        <v>285</v>
       </c>
       <c r="G109" s="5" t="s">
         <v>0</v>
@@ -11829,16 +11797,16 @@
         <v>11</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>393</v>
+        <v>286</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>321</v>
+        <v>239</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L109" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M109" s="3"/>
       <c r="N109" s="3"/>
@@ -11849,38 +11817,38 @@
         <v>109</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>387</v>
+        <v>281</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>394</v>
+        <v>205</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>454</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>0</v>
+        <v>453</v>
       </c>
       <c r="H110" s="3">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>395</v>
+        <v>287</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>391</v>
+        <v>284</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L110" s="3" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M110" s="3"/>
       <c r="N110" s="3"/>
@@ -11891,38 +11859,38 @@
         <v>110</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>387</v>
+        <v>281</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>396</v>
+        <v>205</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>456</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>0</v>
+        <v>455</v>
       </c>
       <c r="H111" s="3">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>397</v>
+        <v>288</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>391</v>
+        <v>284</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>287</v>
+        <v>217</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>288</v>
+        <v>218</v>
       </c>
       <c r="M111" s="3"/>
       <c r="N111" s="3"/>
@@ -11933,38 +11901,38 @@
         <v>111</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>387</v>
+        <v>281</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F112" s="3" t="s">
-        <v>398</v>
+        <v>205</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>458</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>0</v>
+        <v>457</v>
       </c>
       <c r="H112" s="3">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>399</v>
+        <v>289</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>388</v>
+        <v>282</v>
       </c>
       <c r="K112" s="3" t="s">
-        <v>287</v>
+        <v>217</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>288</v>
+        <v>218</v>
       </c>
       <c r="M112" s="3"/>
       <c r="N112" s="3"/>
@@ -11975,38 +11943,38 @@
         <v>112</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>387</v>
+        <v>281</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>270</v>
+        <v>205</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>407</v>
+        <v>460</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="H113" s="7">
-        <f>LEN(F113)</f>
-        <v>15</v>
+        <f t="shared" ref="H113:H118" si="3">LEN(F113)</f>
+        <v>11</v>
       </c>
       <c r="I113" s="7" t="s">
-        <v>408</v>
+        <v>296</v>
       </c>
       <c r="J113" s="7" t="s">
-        <v>409</v>
+        <v>297</v>
       </c>
       <c r="K113" s="7" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L113" s="7" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M113" s="3"/>
       <c r="N113" s="3"/>
@@ -12017,38 +11985,38 @@
         <v>113</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>387</v>
+        <v>281</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>270</v>
+        <v>205</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>410</v>
+        <v>462</v>
       </c>
       <c r="G114" s="7" t="s">
-        <v>0</v>
+        <v>461</v>
       </c>
       <c r="H114" s="7">
-        <f>LEN(F114)</f>
-        <v>13</v>
+        <f t="shared" si="3"/>
+        <v>9</v>
       </c>
       <c r="I114" s="7" t="s">
-        <v>411</v>
+        <v>298</v>
       </c>
       <c r="J114" s="7" t="s">
-        <v>391</v>
+        <v>284</v>
       </c>
       <c r="K114" s="7" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L114" s="7" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M114" s="3"/>
       <c r="N114" s="3"/>
@@ -12059,38 +12027,38 @@
         <v>114</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>325</v>
+        <v>242</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>270</v>
+        <v>205</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>412</v>
+        <v>464</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>0</v>
+        <v>463</v>
       </c>
       <c r="H115" s="7">
-        <f>LEN(F115)</f>
-        <v>16</v>
+        <f t="shared" si="3"/>
+        <v>12</v>
       </c>
       <c r="I115" s="7" t="s">
-        <v>338</v>
+        <v>251</v>
       </c>
       <c r="J115" s="7" t="s">
-        <v>413</v>
+        <v>299</v>
       </c>
       <c r="K115" s="7" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L115" s="7" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M115" s="3"/>
       <c r="N115" s="3"/>
@@ -12101,38 +12069,38 @@
         <v>115</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>307</v>
+        <v>230</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>270</v>
+        <v>205</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>414</v>
+        <v>466</v>
       </c>
       <c r="G116" s="7" t="s">
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="H116" s="7">
-        <f>LEN(F116)</f>
-        <v>17</v>
+        <f t="shared" si="3"/>
+        <v>10</v>
       </c>
       <c r="I116" s="7" t="s">
-        <v>415</v>
+        <v>300</v>
       </c>
       <c r="J116" s="7" t="s">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="K116" s="7" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L116" s="7" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M116" s="3"/>
       <c r="N116" s="3"/>
@@ -12143,38 +12111,38 @@
         <v>116</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>307</v>
+        <v>230</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>270</v>
+        <v>205</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>416</v>
+        <v>468</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="H117" s="7">
-        <f>LEN(F117)</f>
-        <v>18</v>
+        <f t="shared" si="3"/>
+        <v>10</v>
       </c>
       <c r="I117" s="7" t="s">
-        <v>417</v>
+        <v>301</v>
       </c>
       <c r="J117" s="7" t="s">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="K117" s="7" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L117" s="7" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M117" s="3"/>
       <c r="N117" s="3"/>
@@ -12185,38 +12153,38 @@
         <v>117</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>267</v>
+        <v>202</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>291</v>
+        <v>220</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>270</v>
+        <v>205</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>418</v>
+        <v>470</v>
       </c>
       <c r="G118" s="7" t="s">
-        <v>0</v>
+        <v>469</v>
       </c>
       <c r="H118" s="7">
-        <f>LEN(F118)</f>
-        <v>14</v>
+        <f t="shared" si="3"/>
+        <v>10</v>
       </c>
       <c r="I118" s="7" t="s">
-        <v>419</v>
+        <v>302</v>
       </c>
       <c r="J118" s="7" t="s">
-        <v>294</v>
+        <v>222</v>
       </c>
       <c r="K118" s="7" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="L118" s="7" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="M118" s="3"/>
       <c r="N118" s="3"/>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC0DE1B8-752A-4BFF-875E-73C2266697DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A64D35-3788-48A5-8669-3451CE570E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="2" r:id="rId1"/>
     <sheet name="추가 문구" sheetId="1" r:id="rId2"/>
+    <sheet name="기존 문구 수정" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'추가 문구'!$A$1:$O$118</definedName>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="503">
   <si>
     <t>—</t>
   </si>
@@ -6655,6 +6656,1070 @@
   <si>
     <t>공통 조건: 띄어쓰기 포함 12자 이내 · 먹는 양을 늘리거나 줄이라는 말 없음(신장질환·당뇨병 사용자도 받음) · 저녁·새벽 문구는 식후 가능</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DIET-P-0036</t>
+  </si>
+  <si>
+    <t>부담 줄이기</t>
+  </si>
+  <si>
+    <t>DIET-P-0269</t>
+  </si>
+  <si>
+    <t>DIET-P-0270</t>
+  </si>
+  <si>
+    <t>DIET-P-0271</t>
+  </si>
+  <si>
+    <t>DIET-P-0272</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부담</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>줄이기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>늦은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>카페인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>줄이기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저녁엔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>카페인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쉬기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>「늦은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시간」은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사람마다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다르게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>읽혀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>「저녁엔」으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>분명히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>함</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>출출하면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가볍게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요기하기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>출출하면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가볍게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>맞춤</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따뜻한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우유나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>두유</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잔</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따뜻한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우유</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잔</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>챙길</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>것</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준비하기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아침거리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준비하기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>입맛</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>날</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>두기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>입맛</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>날</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지금</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>글자</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바꿀</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이유</t>
+    </r>
+  </si>
+  <si>
+    <t>기존 데이터계약 문구 중 12자(09-29 확정)를 넘는 5개. 검수 후 데이터계약·참조설정데이터·번역_en·시뮬레이터에 함께 반영</t>
+  </si>
+  <si>
+    <t>5차</t>
+  </si>
+  <si>
+    <t>오후엔 카페인 쉬기</t>
+  </si>
+  <si>
+    <t>오후부터 카페인을 쉬면 밤잠이 편해져요.</t>
+  </si>
+  <si>
+    <t>대한수면학회 수면위생 수칙</t>
   </si>
 </sst>
 </file>
@@ -6776,7 +7841,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6800,6 +7865,12 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7157,7 +8228,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>472</v>
       </c>
@@ -7210,7 +8281,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{243C8A1C-2FBA-4873-BD31-7545635970F1}">
-  <dimension ref="A1:O118"/>
+  <dimension ref="A1:O119"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="6.58203125" style="1" customWidth="1"/>
@@ -12190,11 +13261,250 @@
       <c r="N118" s="3"/>
       <c r="O118" s="3"/>
     </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A119" s="7">
+        <v>118</v>
+      </c>
+      <c r="B119" s="7" t="s">
+        <v>499</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="D119" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E119" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>500</v>
+      </c>
+      <c r="G119" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H119" s="7">
+        <f>LEN(F119)</f>
+        <v>10</v>
+      </c>
+      <c r="I119" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="J119" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="K119" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="L119" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="M119" s="3"/>
+      <c r="N119" s="3"/>
+      <c r="O119" s="3"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O118" xr:uid="{243C8A1C-2FBA-4873-BD31-7545635970F1}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M118" xr:uid="{29F577E0-A9A7-4D3D-B3E7-99484ADFB535}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M119" xr:uid="{29F577E0-A9A7-4D3D-B3E7-99484ADFB535}">
+      <formula1>"승인,수정,제외"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EED92CAC-4CB7-4BF1-8B2D-6B06A2BD32CE}">
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="13.58203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26.58203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="7.58203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.58203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.58203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="40.58203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="30.58203125" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="16" x14ac:dyDescent="0.45">
+      <c r="A1" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="D2" s="9">
+        <f>LEN(C2)</f>
+        <v>14</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="F2" s="9">
+        <f>LEN(E2)</f>
+        <v>10</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+    </row>
+    <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.45">
+      <c r="A3" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="D3" s="9">
+        <f>LEN(C3)</f>
+        <v>13</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="F3" s="9">
+        <f>LEN(E3)</f>
+        <v>11</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+    </row>
+    <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.45">
+      <c r="A4" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="D4" s="9">
+        <f>LEN(C4)</f>
+        <v>14</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="F4" s="9">
+        <f>LEN(E4)</f>
+        <v>10</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+    </row>
+    <row r="5" spans="1:9" ht="16" x14ac:dyDescent="0.45">
+      <c r="A5" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="D5" s="9">
+        <f>LEN(C5)</f>
+        <v>15</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="F5" s="9">
+        <f>LEN(E5)</f>
+        <v>12</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+    </row>
+    <row r="6" spans="1:9" ht="16" x14ac:dyDescent="0.45">
+      <c r="A6" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="D6" s="9">
+        <f>LEN(C6)</f>
+        <v>13</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="F6" s="9">
+        <f>LEN(E6)</f>
+        <v>10</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H6" xr:uid="{CA4C3A0C-44FE-4DB1-B6A5-13CDD0FA640C}">
       <formula1>"승인,수정,제외"</formula1>
     </dataValidation>
   </dataValidations>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A64D35-3788-48A5-8669-3451CE570E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF15AA44-3B1C-4A6F-9C9A-6399E9FFBC85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="505">
   <si>
     <t>—</t>
   </si>
@@ -5274,14 +5274,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 먹을 단백질 반찬 정하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>정해 두면 내일 끼니에 단백질을 챙기기 쉬워요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>장 볼 때 두부·달걀 잊지 않게 적기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5290,22 +5282,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일은 튀김 대신 구이로 정하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>메뉴를 먼저 정하면 튀김을 덜 고르게 돼요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>튀김 대신 먹을 메뉴 적어 두기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>대신 먹을 메뉴가 있으면 고르기 쉬워요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>오늘 먹은 끼니 적고 내일 챙기기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5322,14 +5298,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 먹을 음식 하나 정해 두기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>하나만 정해 둬도 내일 끼니가 한결 쉬워요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>거르지 않게 내일 세 끼 시간 정하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5362,22 +5330,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>단 음료 대신 마실 것 정해 두기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>미리 정해 두면 단 음료를 덜 고르게 돼요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>단 간식 대신 먹을 것 챙겨 두기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>대신할 것이 있으면 단 간식에 손이 덜 가요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>오늘 먹은 국물 양 돌아보기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5386,14 +5338,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 국은 싱겁게 끓이기로 정하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>미리 정해 두면 간을 덜 하게 돼요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>늦은 끼니 없게 마지막 식사 시각 정하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5426,14 +5370,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>끼니마다 먹을 단백질 정해 두기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>단백질을 세 끼에 나눠 먹기 쉬워요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>오늘 먹은 단백질 돌아보기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5442,14 +5378,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>기름 덜 쓰게 내일 조리법 정하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>조리법을 정해 두면 기름을 덜 쓰게 돼요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>오늘 먹은 튀긴 음식 돌아보기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5478,14 +5406,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>바쁜 날 먹을 간단 메뉴 정하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>미리 정해 두면 바쁜 날에도 끼니를 챙겨요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>잘 보이게 냉장고 앞칸에 채소 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5494,22 +5414,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 국에 넣을 채소 정하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>국에 채소를 더하면 한 끼 채소가 늘어요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이번 주 채소 반찬 미리 정하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>계획이 있으면 매일 채소를 챙기기 쉬워요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>음료 살 때 당류 표시 확인하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5622,14 +5526,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>콩·두부 요리법 하나 찾아 두기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>요리법이 있으면 콩·두부를 자주 먹게 돼요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>튀김 대신 구워 먹을 재료 꺼내 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5638,30 +5534,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>기름 덜 쓰게 내일은 찜 요리 정하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>찜은 기름을 덜 쓰는 조리법이에요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이번 주 외식 메뉴 미리 정하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>미리 정해 두면 덜 기름진 메뉴를 고르기 쉬워요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>내일 먹기 편한 음식 정해 두기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>먹기 편한 음식부터 정하면 부담이 줄어요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>오늘 식사가 어땠는지 한 줄 적기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5916,9 +5788,6 @@
     <t>WHO 포화지방 줄이기 권고</t>
   </si>
   <si>
-    <t>무침은 기름을 덜 쓰는 반찬이에요.</t>
-  </si>
-  <si>
     <t>식생활지침 「기름진 음식 줄이기」</t>
   </si>
   <si>
@@ -5931,12 +5800,6 @@
     <t>따로 받으면 뿌리는 양을 조절할 수 있어요.</t>
   </si>
   <si>
-    <t>무침은 기름을 덜 쓰는 조리법이에요.</t>
-  </si>
-  <si>
-    <t>요리법을 알면 기름을 덜 쓰게 돼요.</t>
-  </si>
-  <si>
     <t>10-12 4차(입문) 48개 추가: 목표를 달성해 단계가 오르는 사람이 많지 않아 대부분 입문 문구를 보므로, 축마다 입문 6개(낮 4 · 저녁·새벽 2)를 더함. 합계 111개</t>
   </si>
   <si>
@@ -6407,10 +6270,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 국은 맑은 국으로 정하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>내일은 맑은 국으로</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6571,10 +6430,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>볶음보다 무침 반찬 고르기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>볶음 대신 무침 고르기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6587,18 +6442,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내일 반찬은 무침으로 정하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>내일 반찬은 무침으로</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>기름 덜 쓰는 요리 하나 찾기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>기름 적은 요리 찾기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -7720,6 +7567,169 @@
   </si>
   <si>
     <t>대한수면학회 수면위생 수칙</t>
+  </si>
+  <si>
+    <t>내일 반찬은 고등어구이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고등어구이는 튀김보다 기름이 덜 들어가요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>튀김 대신 달걀찜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달걀찜은 기름 없이 만드는 반찬이에요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전 대신 나물 반찬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나물은 전보다 기름을 훨씬 덜 써요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>감자튀김 대신 찐 감자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>찐 감자는 튀긴 감자보다 기름이 적어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제육볶음 대신 수육</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삶은 수육은 볶은 고기보다 기름이 덜해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>잡채 대신 나물무침</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나물무침은 잡채보다 기름을 덜 써요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일 반찬은 콩나물무침</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>콩나물무침은 기름을 거의 쓰지 않아요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>외식은 백반집으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백반은 튀김·볶음 메뉴보다 덜 기름져요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일은 맑은 콩나물국</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>맑은 콩나물국은 찌개보다 덜 짜요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장아찌 대신 생채 반찬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생채는 장아찌보다 소금이 훨씬 적어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바쁜 날엔 김밥 한 줄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바쁜 날에도 김밥 한 줄이면 끼니를 챙겨요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일 된장국에 애호박</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>애호박을 넣으면 국 한 그릇에 채소가 더해져요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매일 나물 한 가지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나물 한 가지로 매일 채소를 챙길 수 있어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일 반찬은 두부조림</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>두부조림은 손쉬운 단백질 반찬이에요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>점심엔 닭가슴살 샐러드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>닭가슴살 샐러드는 단백질과 채소를 함께 챙겨요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주스 대신 생수 한 병</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주스 대신 물을 마시면 당을 줄일 수 있어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>과자 대신 찐 고구마</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>찐 고구마는 달지 않고 든든한 간식이에요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>두부부침 반찬 만들기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>두부부침은 쉽게 만드는 단백질 반찬이에요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일은 죽 한 그릇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>죽은 입맛이 없을 때도 먹기 편해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>따뜻한 국에 밥 말기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>따뜻한 국물에 만 밥은 넘기기 편해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10-12 「~ 정하기」처럼 막연한 문구 20개를 구체적인 메뉴 추천으로 바꿈(예: 내일은 구이로 정하기 → 내일 반찬은 고등어구이). 바꾸기 전 문장은 「이전 문구」 열</t>
   </si>
 </sst>
 </file>
@@ -8206,7 +8216,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F51797-492B-40AC-833D-E19CEF6E9FA5}">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="120.58203125" style="1" customWidth="1"/>
@@ -8230,7 +8240,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>472</v>
+        <v>433</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="16" x14ac:dyDescent="0.45">
@@ -8250,27 +8260,32 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>290</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>293</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>303</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>471</v>
+        <v>432</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>504</v>
       </c>
     </row>
   </sheetData>
@@ -8320,7 +8335,7 @@
         <v>73</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>74</v>
@@ -8364,7 +8379,7 @@
         <v>4</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>305</v>
+        <v>270</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>76</v>
@@ -8403,10 +8418,10 @@
         <v>3</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>306</v>
+        <v>271</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>78</v>
@@ -8448,7 +8463,7 @@
         <v>4</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>307</v>
+        <v>272</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>80</v>
@@ -8490,7 +8505,7 @@
         <v>8</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>308</v>
+        <v>273</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>82</v>
@@ -8532,7 +8547,7 @@
         <v>13</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>309</v>
+        <v>274</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>84</v>
@@ -8574,7 +8589,7 @@
         <v>4</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>310</v>
+        <v>275</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>86</v>
@@ -8613,10 +8628,10 @@
         <v>15</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>311</v>
+        <v>276</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>88</v>
@@ -8658,7 +8673,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>312</v>
+        <v>277</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>90</v>
@@ -8697,10 +8712,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>313</v>
+        <v>278</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>92</v>
@@ -8742,7 +8757,7 @@
         <v>4</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>314</v>
+        <v>279</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>94</v>
@@ -8781,10 +8796,10 @@
         <v>21</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>315</v>
+        <v>280</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>96</v>
@@ -8826,7 +8841,7 @@
         <v>4</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>316</v>
+        <v>281</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>98</v>
@@ -8865,10 +8880,10 @@
         <v>23</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>317</v>
+        <v>282</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>100</v>
@@ -8910,17 +8925,17 @@
         <v>4</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>318</v>
+        <v>490</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>102</v>
+        <v>283</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>103</v>
+        <v>11</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>491</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>27</v>
@@ -8949,20 +8964,20 @@
         <v>26</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>319</v>
+        <v>284</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H16" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>28</v>
@@ -8994,17 +9009,17 @@
         <v>4</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>320</v>
+        <v>464</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>106</v>
+        <v>285</v>
       </c>
       <c r="H17" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>107</v>
+        <v>12</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>465</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>30</v>
@@ -9033,20 +9048,20 @@
         <v>29</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>321</v>
+        <v>466</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>108</v>
+        <v>286</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>109</v>
+        <v>9</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>467</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>31</v>
@@ -9078,17 +9093,17 @@
         <v>0</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>322</v>
+        <v>287</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="H19" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>17</v>
@@ -9120,17 +9135,17 @@
         <v>0</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>323</v>
+        <v>288</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="H20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>33</v>
@@ -9162,17 +9177,17 @@
         <v>0</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>324</v>
+        <v>500</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>114</v>
+        <v>289</v>
       </c>
       <c r="H21" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>115</v>
+        <v>10</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>501</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>33</v>
@@ -9204,17 +9219,17 @@
         <v>13</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>325</v>
+        <v>290</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="H22" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>9</v>
@@ -9246,17 +9261,17 @@
         <v>4</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>326</v>
+        <v>291</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="H23" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>17</v>
@@ -9288,17 +9303,17 @@
         <v>4</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>327</v>
+        <v>292</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="H24" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>17</v>
@@ -9327,20 +9342,20 @@
         <v>10</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>328</v>
+        <v>293</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="H25" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>12</v>
@@ -9369,20 +9384,20 @@
         <v>15</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>329</v>
+        <v>494</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>124</v>
+        <v>294</v>
       </c>
       <c r="H26" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>125</v>
+      <c r="I26" s="7" t="s">
+        <v>495</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>35</v>
@@ -9414,17 +9429,17 @@
         <v>4</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>330</v>
+        <v>496</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>126</v>
+        <v>295</v>
       </c>
       <c r="H27" s="3">
         <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>127</v>
+        <v>11</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>497</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>35</v>
@@ -9456,17 +9471,17 @@
         <v>4</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H28" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>36</v>
@@ -9495,20 +9510,20 @@
         <v>18</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>332</v>
+        <v>482</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>130</v>
+        <v>297</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>131</v>
+      <c r="I29" s="7" t="s">
+        <v>483</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>37</v>
@@ -9540,17 +9555,17 @@
         <v>13</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>333</v>
+        <v>298</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="H30" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>9</v>
@@ -9582,17 +9597,17 @@
         <v>4</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>334</v>
+        <v>299</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="H31" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>17</v>
@@ -9621,20 +9636,20 @@
         <v>23</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>335</v>
+        <v>300</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="H32" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>38</v>
@@ -9666,17 +9681,17 @@
         <v>4</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>336</v>
+        <v>301</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="H33" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>39</v>
@@ -9708,17 +9723,17 @@
         <v>13</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>337</v>
+        <v>492</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>140</v>
+        <v>302</v>
       </c>
       <c r="H34" s="3">
         <f t="shared" ref="H34:H64" si="1">LEN(F34)</f>
-        <v>11</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>141</v>
+        <v>12</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>493</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>28</v>
@@ -9750,17 +9765,17 @@
         <v>4</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>338</v>
+        <v>303</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="H35" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>17</v>
@@ -9792,17 +9807,17 @@
         <v>13</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>339</v>
+        <v>468</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>144</v>
+        <v>304</v>
       </c>
       <c r="H36" s="3">
         <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>145</v>
+        <v>10</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>469</v>
       </c>
       <c r="J36" s="3" t="s">
         <v>31</v>
@@ -9834,10 +9849,10 @@
         <v>4</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>340</v>
+        <v>305</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="H37" s="3">
         <f t="shared" si="1"/>
@@ -9876,17 +9891,17 @@
         <v>0</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>341</v>
+        <v>306</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="H38" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>33</v>
@@ -9918,17 +9933,17 @@
         <v>0</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>342</v>
+        <v>307</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="H39" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>40</v>
@@ -9960,17 +9975,17 @@
         <v>4</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>343</v>
+        <v>308</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="H40" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>40</v>
@@ -9999,20 +10014,20 @@
         <v>3</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>344</v>
+        <v>484</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>153</v>
+        <v>309</v>
       </c>
       <c r="H41" s="3">
         <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>154</v>
+        <v>12</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>485</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>42</v>
@@ -10044,17 +10059,17 @@
         <v>4</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>345</v>
+        <v>310</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="H42" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>16</v>
@@ -10083,20 +10098,20 @@
         <v>10</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>346</v>
+        <v>486</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>157</v>
+        <v>311</v>
       </c>
       <c r="H43" s="3">
         <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>158</v>
+        <v>11</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>487</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>14</v>
@@ -10128,17 +10143,17 @@
         <v>13</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>347</v>
+        <v>488</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>159</v>
+        <v>312</v>
       </c>
       <c r="H44" s="3">
         <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>160</v>
+        <v>10</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>489</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>43</v>
@@ -10170,17 +10185,17 @@
         <v>4</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>348</v>
+        <v>313</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="H45" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>44</v>
@@ -10212,17 +10227,17 @@
         <v>8</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>349</v>
+        <v>314</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="H46" s="3">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>45</v>
@@ -10254,17 +10269,17 @@
         <v>13</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>350</v>
+        <v>315</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="H47" s="3">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>46</v>
@@ -10296,17 +10311,17 @@
         <v>4</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>351</v>
+        <v>316</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="H48" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>19</v>
@@ -10338,17 +10353,17 @@
         <v>8</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>352</v>
+        <v>317</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="H49" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>47</v>
@@ -10380,17 +10395,17 @@
         <v>13</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>353</v>
+        <v>318</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="H50" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>48</v>
@@ -10422,17 +10437,17 @@
         <v>4</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>354</v>
+        <v>319</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="H51" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>22</v>
@@ -10464,17 +10479,17 @@
         <v>8</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>355</v>
+        <v>320</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="H52" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>49</v>
@@ -10506,17 +10521,17 @@
         <v>13</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="J53" s="3" t="s">
         <v>9</v>
@@ -10548,17 +10563,17 @@
         <v>4</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>357</v>
+        <v>322</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="H54" s="3">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>24</v>
@@ -10590,17 +10605,17 @@
         <v>8</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>358</v>
+        <v>323</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="H55" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>50</v>
@@ -10632,17 +10647,17 @@
         <v>13</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>359</v>
+        <v>324</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="H56" s="3">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="J56" s="3" t="s">
         <v>51</v>
@@ -10674,17 +10689,17 @@
         <v>4</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>360</v>
+        <v>325</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="H57" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>28</v>
@@ -10716,17 +10731,17 @@
         <v>8</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>361</v>
+        <v>326</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="H58" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>52</v>
@@ -10758,17 +10773,17 @@
         <v>13</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>362</v>
+        <v>498</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>189</v>
+        <v>327</v>
       </c>
       <c r="H59" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>190</v>
+      <c r="I59" s="7" t="s">
+        <v>499</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>53</v>
@@ -10800,17 +10815,17 @@
         <v>4</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>363</v>
+        <v>328</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="H60" s="3">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>54</v>
@@ -10825,7 +10840,7 @@
       <c r="N60" s="3"/>
       <c r="O60" s="3"/>
     </row>
-    <row r="61" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:15" ht="16" x14ac:dyDescent="0.45">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -10842,17 +10857,17 @@
         <v>8</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>364</v>
+        <v>470</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>193</v>
+        <v>329</v>
       </c>
       <c r="H61" s="3">
         <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>194</v>
+        <v>12</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>471</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>31</v>
@@ -10884,17 +10899,17 @@
         <v>13</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>365</v>
+        <v>478</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>195</v>
+        <v>330</v>
       </c>
       <c r="H62" s="3">
         <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>196</v>
+        <v>9</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>479</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>55</v>
@@ -10926,17 +10941,17 @@
         <v>0</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>366</v>
+        <v>502</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>197</v>
+        <v>331</v>
       </c>
       <c r="H63" s="3">
         <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>198</v>
+        <v>11</v>
+      </c>
+      <c r="I63" s="7" t="s">
+        <v>503</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>33</v>
@@ -10968,17 +10983,17 @@
         <v>0</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>367</v>
+        <v>332</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="H64" s="3">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="J64" s="3" t="s">
         <v>17</v>
@@ -10998,38 +11013,38 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>369</v>
+        <v>334</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>368</v>
+        <v>333</v>
       </c>
       <c r="H65" s="3">
         <f t="shared" ref="H65:H112" si="2">LEN(F65)</f>
         <v>11</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M65" s="3"/>
       <c r="N65" s="3"/>
@@ -11040,38 +11055,38 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>371</v>
+        <v>336</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>370</v>
+        <v>335</v>
       </c>
       <c r="H66" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M66" s="3"/>
       <c r="N66" s="3"/>
@@ -11082,38 +11097,38 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>373</v>
+        <v>338</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>372</v>
+        <v>337</v>
       </c>
       <c r="H67" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
@@ -11124,38 +11139,38 @@
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>375</v>
+        <v>340</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>374</v>
+        <v>339</v>
       </c>
       <c r="H68" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M68" s="3"/>
       <c r="N68" s="3"/>
@@ -11166,38 +11181,38 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>377</v>
+        <v>342</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>376</v>
+        <v>341</v>
       </c>
       <c r="H69" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="M69" s="3"/>
       <c r="N69" s="3"/>
@@ -11208,38 +11223,38 @@
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>379</v>
+        <v>344</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>378</v>
+        <v>343</v>
       </c>
       <c r="H70" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="M70" s="3"/>
       <c r="N70" s="3"/>
@@ -11250,38 +11265,38 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>381</v>
+        <v>346</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>380</v>
+        <v>345</v>
       </c>
       <c r="H71" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>222</v>
+        <v>190</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M71" s="3"/>
       <c r="N71" s="3"/>
@@ -11292,38 +11307,38 @@
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>383</v>
+        <v>348</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>382</v>
+        <v>347</v>
       </c>
       <c r="H72" s="3">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>224</v>
+        <v>192</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M72" s="3"/>
       <c r="N72" s="3"/>
@@ -11334,38 +11349,38 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>385</v>
+        <v>350</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>384</v>
+        <v>349</v>
       </c>
       <c r="H73" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>222</v>
+        <v>190</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M73" s="3"/>
       <c r="N73" s="3"/>
@@ -11376,38 +11391,38 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>387</v>
+        <v>352</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>386</v>
+        <v>351</v>
       </c>
       <c r="H74" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>224</v>
+        <v>192</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M74" s="3"/>
       <c r="N74" s="3"/>
@@ -11418,38 +11433,38 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>389</v>
+        <v>354</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>388</v>
+        <v>353</v>
       </c>
       <c r="H75" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>227</v>
+        <v>195</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>222</v>
+        <v>190</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="M75" s="3"/>
       <c r="N75" s="3"/>
@@ -11460,38 +11475,38 @@
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>391</v>
+        <v>356</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>390</v>
+        <v>355</v>
       </c>
       <c r="H76" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>228</v>
+        <v>196</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="M76" s="3"/>
       <c r="N76" s="3"/>
@@ -11502,38 +11517,38 @@
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>393</v>
+        <v>358</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>392</v>
+        <v>357</v>
       </c>
       <c r="H77" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>231</v>
+        <v>199</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>232</v>
+        <v>200</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M77" s="3"/>
       <c r="N77" s="3"/>
@@ -11544,38 +11559,38 @@
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>395</v>
+        <v>360</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>394</v>
+        <v>359</v>
       </c>
       <c r="H78" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>234</v>
+        <v>202</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M78" s="3"/>
       <c r="N78" s="3"/>
@@ -11586,38 +11601,38 @@
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>397</v>
+        <v>362</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>396</v>
+        <v>361</v>
       </c>
       <c r="H79" s="3">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>232</v>
+        <v>200</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M79" s="3"/>
       <c r="N79" s="3"/>
@@ -11628,38 +11643,38 @@
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>399</v>
+        <v>364</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>398</v>
+        <v>363</v>
       </c>
       <c r="H80" s="3">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>237</v>
+        <v>205</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M80" s="3"/>
       <c r="N80" s="3"/>
@@ -11670,38 +11685,38 @@
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>401</v>
+        <v>366</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>400</v>
+        <v>365</v>
       </c>
       <c r="H81" s="3">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>238</v>
+        <v>206</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="M81" s="3"/>
       <c r="N81" s="3"/>
@@ -11712,38 +11727,38 @@
         <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>403</v>
+        <v>368</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>402</v>
+        <v>367</v>
       </c>
       <c r="H82" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>240</v>
+        <v>208</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
@@ -11754,19 +11769,19 @@
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>243</v>
+        <v>211</v>
       </c>
       <c r="G83" s="5" t="s">
         <v>0</v>
@@ -11776,16 +11791,16 @@
         <v>11</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>244</v>
+        <v>212</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M83" s="3"/>
       <c r="N83" s="3"/>
@@ -11796,38 +11811,38 @@
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>405</v>
+        <v>370</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>404</v>
+        <v>369</v>
       </c>
       <c r="H84" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M84" s="3"/>
       <c r="N84" s="3"/>
@@ -11838,38 +11853,38 @@
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>407</v>
+        <v>372</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>406</v>
+        <v>371</v>
       </c>
       <c r="H85" s="3">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>249</v>
+        <v>217</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M85" s="3"/>
       <c r="N85" s="3"/>
@@ -11880,38 +11895,38 @@
         <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>409</v>
+        <v>374</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>408</v>
+        <v>373</v>
       </c>
       <c r="H86" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>249</v>
+        <v>217</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M86" s="3"/>
       <c r="N86" s="3"/>
@@ -11922,38 +11937,38 @@
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>411</v>
+        <v>480</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>410</v>
+        <v>375</v>
       </c>
       <c r="H87" s="3">
         <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>251</v>
+        <v>11</v>
+      </c>
+      <c r="I87" s="7" t="s">
+        <v>481</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="M87" s="3"/>
       <c r="N87" s="3"/>
@@ -11964,38 +11979,38 @@
         <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>413</v>
+        <v>377</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>412</v>
+        <v>376</v>
       </c>
       <c r="H88" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>253</v>
+        <v>221</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>254</v>
+        <v>222</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="M88" s="3"/>
       <c r="N88" s="3"/>
@@ -12006,38 +12021,38 @@
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>255</v>
+        <v>223</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>415</v>
+        <v>379</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>414</v>
+        <v>378</v>
       </c>
       <c r="H89" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M89" s="3"/>
       <c r="N89" s="3"/>
@@ -12048,38 +12063,38 @@
         <v>89</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>255</v>
+        <v>223</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>417</v>
+        <v>381</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>416</v>
+        <v>380</v>
       </c>
       <c r="H90" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
@@ -12090,38 +12105,38 @@
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>255</v>
+        <v>223</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>419</v>
+        <v>383</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>418</v>
+        <v>382</v>
       </c>
       <c r="H91" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>258</v>
+        <v>226</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L91" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M91" s="3"/>
       <c r="N91" s="3"/>
@@ -12132,38 +12147,38 @@
         <v>91</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>255</v>
+        <v>223</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>421</v>
+        <v>385</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>420</v>
+        <v>384</v>
       </c>
       <c r="H92" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>259</v>
+        <v>227</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M92" s="3"/>
       <c r="N92" s="3"/>
@@ -12174,38 +12189,38 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>255</v>
+        <v>223</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>423</v>
+        <v>387</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>422</v>
+        <v>386</v>
       </c>
       <c r="H93" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>260</v>
+        <v>228</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="L93" s="3" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="M93" s="3"/>
       <c r="N93" s="3"/>
@@ -12216,38 +12231,38 @@
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>255</v>
+        <v>223</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>425</v>
+        <v>389</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>424</v>
+        <v>388</v>
       </c>
       <c r="H94" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>261</v>
+        <v>229</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>262</v>
+        <v>230</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="L94" s="3" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="M94" s="3"/>
       <c r="N94" s="3"/>
@@ -12258,38 +12273,38 @@
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>263</v>
+        <v>231</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>427</v>
+        <v>391</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>426</v>
+        <v>390</v>
       </c>
       <c r="H95" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>264</v>
+        <v>232</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>265</v>
+        <v>233</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
@@ -12300,38 +12315,38 @@
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>263</v>
+        <v>231</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>429</v>
+        <v>393</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>428</v>
+        <v>392</v>
       </c>
       <c r="H96" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>265</v>
+        <v>233</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M96" s="3"/>
       <c r="N96" s="3"/>
@@ -12342,38 +12357,38 @@
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>263</v>
+        <v>231</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>431</v>
+        <v>395</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>430</v>
+        <v>394</v>
       </c>
       <c r="H97" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>268</v>
+        <v>236</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M97" s="3"/>
       <c r="N97" s="3"/>
@@ -12384,38 +12399,38 @@
         <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>263</v>
+        <v>231</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>433</v>
+        <v>397</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>432</v>
+        <v>396</v>
       </c>
       <c r="H98" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>269</v>
+        <v>237</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>270</v>
+        <v>238</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M98" s="3"/>
       <c r="N98" s="3"/>
@@ -12426,38 +12441,38 @@
         <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>263</v>
+        <v>231</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>435</v>
+        <v>399</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>434</v>
+        <v>398</v>
       </c>
       <c r="H99" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>271</v>
+        <v>239</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>270</v>
+        <v>238</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="M99" s="3"/>
       <c r="N99" s="3"/>
@@ -12468,38 +12483,38 @@
         <v>99</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>263</v>
+        <v>231</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>437</v>
+        <v>401</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>436</v>
+        <v>400</v>
       </c>
       <c r="H100" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>272</v>
+        <v>240</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>270</v>
+        <v>238</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="M100" s="3"/>
       <c r="N100" s="3"/>
@@ -12510,38 +12525,38 @@
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>273</v>
+        <v>241</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>439</v>
+        <v>403</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>438</v>
+        <v>402</v>
       </c>
       <c r="H101" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>275</v>
+        <v>243</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M101" s="3"/>
       <c r="N101" s="3"/>
@@ -12552,38 +12567,38 @@
         <v>101</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>273</v>
+        <v>241</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>441</v>
+        <v>405</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>440</v>
+        <v>404</v>
       </c>
       <c r="H102" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>276</v>
+        <v>244</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>275</v>
+        <v>243</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M102" s="3"/>
       <c r="N102" s="3"/>
@@ -12594,38 +12609,38 @@
         <v>102</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>273</v>
+        <v>241</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>443</v>
+        <v>407</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>442</v>
+        <v>406</v>
       </c>
       <c r="H103" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>277</v>
+        <v>245</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>275</v>
+        <v>243</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M103" s="3"/>
       <c r="N103" s="3"/>
@@ -12636,38 +12651,38 @@
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>273</v>
+        <v>241</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>445</v>
+        <v>409</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>444</v>
+        <v>408</v>
       </c>
       <c r="H104" s="3">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>278</v>
+        <v>246</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>275</v>
+        <v>243</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L104" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M104" s="3"/>
       <c r="N104" s="3"/>
@@ -12678,38 +12693,38 @@
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>273</v>
+        <v>241</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>447</v>
+        <v>411</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>446</v>
+        <v>410</v>
       </c>
       <c r="H105" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>279</v>
+        <v>247</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>275</v>
+        <v>243</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="L105" s="3" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="M105" s="3"/>
       <c r="N105" s="3"/>
@@ -12720,38 +12735,38 @@
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>273</v>
+        <v>241</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>449</v>
+        <v>413</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>448</v>
+        <v>412</v>
       </c>
       <c r="H106" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>280</v>
+        <v>248</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>275</v>
+        <v>243</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="L106" s="3" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="M106" s="3"/>
       <c r="N106" s="3"/>
@@ -12762,38 +12777,38 @@
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>450</v>
+        <v>414</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>294</v>
+        <v>259</v>
       </c>
       <c r="H107" s="3">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>295</v>
+        <v>260</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>282</v>
+        <v>250</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M107" s="3"/>
       <c r="N107" s="3"/>
@@ -12804,38 +12819,38 @@
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>452</v>
+        <v>474</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>451</v>
+        <v>415</v>
       </c>
       <c r="H108" s="3">
         <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="I108" s="3" t="s">
-        <v>283</v>
+        <v>10</v>
+      </c>
+      <c r="I108" s="7" t="s">
+        <v>475</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>284</v>
+        <v>251</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L108" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M108" s="3"/>
       <c r="N108" s="3"/>
@@ -12846,19 +12861,19 @@
         <v>108</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>285</v>
+        <v>252</v>
       </c>
       <c r="G109" s="5" t="s">
         <v>0</v>
@@ -12868,16 +12883,16 @@
         <v>11</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>286</v>
+        <v>253</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L109" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M109" s="3"/>
       <c r="N109" s="3"/>
@@ -12888,38 +12903,38 @@
         <v>109</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>454</v>
+        <v>417</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>453</v>
+        <v>416</v>
       </c>
       <c r="H110" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>287</v>
+        <v>254</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>284</v>
+        <v>251</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L110" s="3" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M110" s="3"/>
       <c r="N110" s="3"/>
@@ -12930,38 +12945,38 @@
         <v>110</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>455</v>
+        <v>418</v>
       </c>
       <c r="H111" s="3">
         <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-      <c r="I111" s="3" t="s">
-        <v>288</v>
+        <v>12</v>
+      </c>
+      <c r="I111" s="7" t="s">
+        <v>477</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>284</v>
+        <v>251</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="M111" s="3"/>
       <c r="N111" s="3"/>
@@ -12972,38 +12987,38 @@
         <v>111</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>457</v>
+        <v>419</v>
       </c>
       <c r="H112" s="3">
         <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-      <c r="I112" s="3" t="s">
-        <v>289</v>
+        <v>10</v>
+      </c>
+      <c r="I112" s="7" t="s">
+        <v>473</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>282</v>
+        <v>250</v>
       </c>
       <c r="K112" s="3" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="M112" s="3"/>
       <c r="N112" s="3"/>
@@ -13014,38 +13029,38 @@
         <v>112</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>460</v>
+        <v>421</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>459</v>
+        <v>420</v>
       </c>
       <c r="H113" s="7">
         <f t="shared" ref="H113:H118" si="3">LEN(F113)</f>
         <v>11</v>
       </c>
       <c r="I113" s="7" t="s">
-        <v>296</v>
+        <v>261</v>
       </c>
       <c r="J113" s="7" t="s">
-        <v>297</v>
+        <v>262</v>
       </c>
       <c r="K113" s="7" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L113" s="7" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M113" s="3"/>
       <c r="N113" s="3"/>
@@ -13056,38 +13071,38 @@
         <v>113</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>462</v>
+        <v>423</v>
       </c>
       <c r="G114" s="7" t="s">
-        <v>461</v>
+        <v>422</v>
       </c>
       <c r="H114" s="7">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="I114" s="7" t="s">
-        <v>298</v>
+        <v>263</v>
       </c>
       <c r="J114" s="7" t="s">
-        <v>284</v>
+        <v>251</v>
       </c>
       <c r="K114" s="7" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L114" s="7" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M114" s="3"/>
       <c r="N114" s="3"/>
@@ -13098,38 +13113,38 @@
         <v>114</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>464</v>
+        <v>425</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>463</v>
+        <v>424</v>
       </c>
       <c r="H115" s="7">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="I115" s="7" t="s">
-        <v>251</v>
+        <v>219</v>
       </c>
       <c r="J115" s="7" t="s">
-        <v>299</v>
+        <v>264</v>
       </c>
       <c r="K115" s="7" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L115" s="7" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M115" s="3"/>
       <c r="N115" s="3"/>
@@ -13140,38 +13155,38 @@
         <v>115</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>466</v>
+        <v>427</v>
       </c>
       <c r="G116" s="7" t="s">
-        <v>465</v>
+        <v>426</v>
       </c>
       <c r="H116" s="7">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="I116" s="7" t="s">
-        <v>300</v>
+        <v>265</v>
       </c>
       <c r="J116" s="7" t="s">
-        <v>232</v>
+        <v>200</v>
       </c>
       <c r="K116" s="7" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L116" s="7" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M116" s="3"/>
       <c r="N116" s="3"/>
@@ -13182,38 +13197,38 @@
         <v>116</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>468</v>
+        <v>429</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>467</v>
+        <v>428</v>
       </c>
       <c r="H117" s="7">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="I117" s="7" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="J117" s="7" t="s">
-        <v>232</v>
+        <v>200</v>
       </c>
       <c r="K117" s="7" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L117" s="7" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M117" s="3"/>
       <c r="N117" s="3"/>
@@ -13224,38 +13239,38 @@
         <v>117</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>470</v>
+        <v>431</v>
       </c>
       <c r="G118" s="7" t="s">
-        <v>469</v>
+        <v>430</v>
       </c>
       <c r="H118" s="7">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="I118" s="7" t="s">
-        <v>302</v>
+        <v>267</v>
       </c>
       <c r="J118" s="7" t="s">
-        <v>222</v>
+        <v>190</v>
       </c>
       <c r="K118" s="7" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L118" s="7" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M118" s="3"/>
       <c r="N118" s="3"/>
@@ -13266,10 +13281,10 @@
         <v>118</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>499</v>
+        <v>460</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>474</v>
+        <v>435</v>
       </c>
       <c r="D119" s="7" t="s">
         <v>0</v>
@@ -13278,7 +13293,7 @@
         <v>0</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>500</v>
+        <v>461</v>
       </c>
       <c r="G119" s="7" t="s">
         <v>0</v>
@@ -13288,16 +13303,16 @@
         <v>10</v>
       </c>
       <c r="I119" s="7" t="s">
-        <v>501</v>
+        <v>462</v>
       </c>
       <c r="J119" s="7" t="s">
-        <v>502</v>
+        <v>463</v>
       </c>
       <c r="K119" s="7" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="L119" s="7" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="M119" s="3"/>
       <c r="N119" s="3"/>
@@ -13334,25 +13349,25 @@
   <sheetData>
     <row r="1" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>493</v>
+        <v>454</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>58</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>494</v>
+        <v>455</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>495</v>
+        <v>456</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>496</v>
+        <v>457</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>495</v>
+        <v>456</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>497</v>
+        <v>458</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>64</v>
@@ -13363,142 +13378,142 @@
     </row>
     <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A2" s="9" t="s">
-        <v>473</v>
+        <v>434</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>479</v>
+        <v>440</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>480</v>
+        <v>441</v>
       </c>
       <c r="D2" s="9">
         <f>LEN(C2)</f>
         <v>14</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>481</v>
+        <v>442</v>
       </c>
       <c r="F2" s="9">
         <f>LEN(E2)</f>
         <v>10</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>482</v>
+        <v>443</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
     </row>
     <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A3" s="9" t="s">
-        <v>475</v>
+        <v>436</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>483</v>
+        <v>444</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>484</v>
+        <v>445</v>
       </c>
       <c r="D3" s="9">
         <f>LEN(C3)</f>
         <v>13</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>485</v>
+        <v>446</v>
       </c>
       <c r="F3" s="9">
         <f>LEN(E3)</f>
         <v>11</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>486</v>
+        <v>447</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
     </row>
     <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A4" s="9" t="s">
-        <v>476</v>
+        <v>437</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>483</v>
+        <v>444</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>487</v>
+        <v>448</v>
       </c>
       <c r="D4" s="9">
         <f>LEN(C4)</f>
         <v>14</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>488</v>
+        <v>449</v>
       </c>
       <c r="F4" s="9">
         <f>LEN(E4)</f>
         <v>10</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>486</v>
+        <v>447</v>
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
     </row>
     <row r="5" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A5" s="9" t="s">
-        <v>477</v>
+        <v>438</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>483</v>
+        <v>444</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>489</v>
+        <v>450</v>
       </c>
       <c r="D5" s="9">
         <f>LEN(C5)</f>
         <v>15</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>490</v>
+        <v>451</v>
       </c>
       <c r="F5" s="9">
         <f>LEN(E5)</f>
         <v>12</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>486</v>
+        <v>447</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
     <row r="6" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A6" s="9" t="s">
-        <v>478</v>
+        <v>439</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>483</v>
+        <v>444</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>491</v>
+        <v>452</v>
       </c>
       <c r="D6" s="9">
         <f>LEN(C6)</f>
         <v>13</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>492</v>
+        <v>453</v>
       </c>
       <c r="F6" s="9">
         <f>LEN(E6)</f>
         <v>10</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>486</v>
+        <v>447</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>498</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF15AA44-3B1C-4A6F-9C9A-6399E9FFBC85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C703201-BF6F-40EC-88A1-6CB1164F99DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="기존 문구 수정" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'추가 문구'!$A$1:$O$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'추가 문구'!$A$1:$O$155</definedName>
   </definedNames>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="581">
   <si>
     <t>—</t>
   </si>
@@ -5689,9 +5689,6 @@
     <t>식약처 나트륨 줄이기 안내</t>
   </si>
   <si>
-    <t>주문할 때 말하면 간을 줄일 수 있어요.</t>
-  </si>
-  <si>
     <t>맑은 국은 찌개보다 덜 짠 편이에요.</t>
   </si>
   <si>
@@ -5770,9 +5767,6 @@
     <t>두유는 간편하게 단백질을 더해 줘요.</t>
   </si>
   <si>
-    <t>간편식 중에도 단백질을 챙길 수 있어요.</t>
-  </si>
-  <si>
     <t>두부를 넣으면 국 한 그릇에 단백질이 더해져요.</t>
   </si>
   <si>
@@ -5797,9 +5791,6 @@
     <t>튀김옷에 기름이 가장 많이 배어 있어요.</t>
   </si>
   <si>
-    <t>따로 받으면 뿌리는 양을 조절할 수 있어요.</t>
-  </si>
-  <si>
     <t>10-12 4차(입문) 48개 추가: 목표를 달성해 단계가 오르는 사람이 많지 않아 대부분 입문 문구를 보므로, 축마다 입문 6개(낮 4 · 저녁·새벽 2)를 더함. 합계 111개</t>
   </si>
   <si>
@@ -6090,10 +6081,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>외식 메뉴 미리 정하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>먹기 편한 음식 정하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6262,14 +6249,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>외식 땐 싱겁게 해 달라고 하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>싱겁게 해 달라고 하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>내일은 맑은 국으로</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6394,14 +6373,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>편의점에선 달걀·두부 고르기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>편의점에선 달걀 고르기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>국에 두부 몇 조각 넣기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6434,14 +6405,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>드레싱은 따로 달라고 하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>드레싱은 따로 받기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>내일 반찬은 무침으로</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -7625,14 +7588,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>외식은 백반집으로</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>백반은 튀김·볶음 메뉴보다 덜 기름져요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>내일은 맑은 콩나물국</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -7730,6 +7685,282 @@
   </si>
   <si>
     <t>10-12 「~ 정하기」처럼 막연한 문구 20개를 구체적인 메뉴 추천으로 바꿈(예: 내일은 구이로 정하기 → 내일 반찬은 고등어구이). 바꾸기 전 문장은 「이전 문구」 열</t>
+  </si>
+  <si>
+    <t>외식은 백반집으로 (상황 전제 규칙 위반)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>돼지갈비 대신 생선찜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생선찜은 양념 고기보다 기름이 덜해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>싱겁게 해 달라고 하기 (상황 전제 규칙 위반)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국은 덜 짜게 끓이기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국을 덜 짜게 끓이면 한 끼 나트륨이 줄어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>편의점에선 달걀 고르기 (상황 전제 규칙 위반)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침엔 두유 한 잔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>두유 한 잔으로 아침 단백질을 더해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>드레싱은 따로 받기 (상황 전제 규칙 위반)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>샐러드는 소스 조금만</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소스를 조금만 뿌리면 기름과 염분이 줄어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7차(끼니 추천)</t>
+  </si>
+  <si>
+    <t>아침 추천: 누룽지</t>
+  </si>
+  <si>
+    <t>따뜻한 누룽지는 아침에 부담 없이 먹기 좋아요.</t>
+  </si>
+  <si>
+    <t>오전(04~10시)</t>
+  </si>
+  <si>
+    <t>아침 추천: 찐 고구마</t>
+  </si>
+  <si>
+    <t>찐 고구마는 든든하고 준비가 간단해요.</t>
+  </si>
+  <si>
+    <t>아침 추천: 달걀말이</t>
+  </si>
+  <si>
+    <t>달걀말이로 아침 단백질을 챙길 수 있어요.</t>
+  </si>
+  <si>
+    <t>아침 추천: 두부부침</t>
+  </si>
+  <si>
+    <t>두부부침은 부드러운 단백질 반찬이에요.</t>
+  </si>
+  <si>
+    <t>아침 추천: 두유</t>
+  </si>
+  <si>
+    <t>두유 한 잔으로 간편하게 단백질을 더해요.</t>
+  </si>
+  <si>
+    <t>아침 추천: 시금치국</t>
+  </si>
+  <si>
+    <t>시금치국으로 아침에도 채소를 먹어요.</t>
+  </si>
+  <si>
+    <t>아침 추천: 비빔밥</t>
+  </si>
+  <si>
+    <t>비빔밥은 나물을 넉넉히 먹을 수 있어요.</t>
+  </si>
+  <si>
+    <t>아침 추천: 맑은 국</t>
+  </si>
+  <si>
+    <t>맑은 국은 찌개보다 덜 짜서 아침에 좋아요.</t>
+  </si>
+  <si>
+    <t>저녁 추천: 고등어구이</t>
+  </si>
+  <si>
+    <t>고등어구이는 튀김보다 기름이 덜 들어가요.</t>
+  </si>
+  <si>
+    <t>오후(12~17시)</t>
+  </si>
+  <si>
+    <t>저녁 추천: 수육</t>
+  </si>
+  <si>
+    <t>삶은 수육은 구운 고기보다 기름이 덜해요.</t>
+  </si>
+  <si>
+    <t>저녁 추천: 닭백숙</t>
+  </si>
+  <si>
+    <t>저녁 추천: 두부조림</t>
+  </si>
+  <si>
+    <t>두부조림은 손쉬운 단백질 반찬이에요.</t>
+  </si>
+  <si>
+    <t>저녁 추천: 달걀찜</t>
+  </si>
+  <si>
+    <t>달걀찜은 부드럽고 기름 없이 만들어요.</t>
+  </si>
+  <si>
+    <t>저녁 추천: 쌈밥</t>
+  </si>
+  <si>
+    <t>쌈밥은 채소를 듬뿍 먹을 수 있어요.</t>
+  </si>
+  <si>
+    <t>저녁 추천: 나물 반찬</t>
+  </si>
+  <si>
+    <t>나물 반찬 하나로 저녁 채소가 채워져요.</t>
+  </si>
+  <si>
+    <t>저녁 추천: 생선찜</t>
+  </si>
+  <si>
+    <t>생선찜은 찌개보다 국물이 적고 덜 짜요.</t>
+  </si>
+  <si>
+    <t>6차(새 표현)</t>
+  </si>
+  <si>
+    <t>아침엔 누룽지 한 그릇</t>
+  </si>
+  <si>
+    <t>바쁜 아침엔 삶은 달걀</t>
+  </si>
+  <si>
+    <t>삶은 달걀 하나면 바쁜 아침도 챙길 수 있어요.</t>
+  </si>
+  <si>
+    <t>라면엔 콩나물 한 줌</t>
+  </si>
+  <si>
+    <t>콩나물을 넣으면 라면에도 채소가 더해져요.</t>
+  </si>
+  <si>
+    <t>비빔밥은 나물 듬뿍</t>
+  </si>
+  <si>
+    <t>나물을 듬뿍 넣으면 한 끼 채소가 늘어요.</t>
+  </si>
+  <si>
+    <t>달걀말이에 부추 넣기</t>
+  </si>
+  <si>
+    <t>부추를 넣으면 반찬 하나에 채소가 더해져요.</t>
+  </si>
+  <si>
+    <t>라면에 달걀 하나</t>
+  </si>
+  <si>
+    <t>달걀을 넣으면 라면에도 단백질이 더해져요.</t>
+  </si>
+  <si>
+    <t>김밥은 참치·계란으로</t>
+  </si>
+  <si>
+    <t>참치·계란 김밥으로 단백질을 챙겨요.</t>
+  </si>
+  <si>
+    <t>샐러드엔 삶은 달걀</t>
+  </si>
+  <si>
+    <t>삶은 달걀을 올리면 샐러드가 든든해져요.</t>
+  </si>
+  <si>
+    <t>식혜 대신 보리차</t>
+  </si>
+  <si>
+    <t>보리차는 달지 않아 당 걱정이 없어요.</t>
+  </si>
+  <si>
+    <t>라떼는 시럽 빼고</t>
+  </si>
+  <si>
+    <t>시럽을 빼면 라떼의 당이 크게 줄어요.</t>
+  </si>
+  <si>
+    <t>믹스커피는 반 봉지만</t>
+  </si>
+  <si>
+    <t>반 봉지만 타도 단맛은 충분해요.</t>
+  </si>
+  <si>
+    <t>라면 스프는 반만</t>
+  </si>
+  <si>
+    <t>스프를 반만 넣으면 나트륨이 크게 줄어요.</t>
+  </si>
+  <si>
+    <t>김치는 백김치로</t>
+  </si>
+  <si>
+    <t>백김치는 빨간 김치보다 덜 짠 편이에요.</t>
+  </si>
+  <si>
+    <t>오징어튀김 대신 숙회</t>
+  </si>
+  <si>
+    <t>숙회는 튀김옷 없이 데쳐 먹어 기름이 적어요.</t>
+  </si>
+  <si>
+    <t>치킨은 오븐구이로</t>
+  </si>
+  <si>
+    <t>오븐구이는 튀긴 치킨보다 기름이 덜해요.</t>
+  </si>
+  <si>
+    <t>야식 대신 따뜻한 차</t>
+  </si>
+  <si>
+    <t>따뜻한 차 한 잔이 늦은 밤 허기를 달래 줘요.</t>
+  </si>
+  <si>
+    <t>늦은 밤 섭취 줄이기(일반 상식)</t>
+  </si>
+  <si>
+    <t>잠들기 전 양치 먼저</t>
+  </si>
+  <si>
+    <t>양치를 하면 야식 생각이 줄어요.</t>
+  </si>
+  <si>
+    <t>한 숟갈 뒤 숨 고르기</t>
+  </si>
+  <si>
+    <t>한 숟갈마다 쉬면 천천히 먹게 돼요.</t>
+  </si>
+  <si>
+    <t>밥은 작은 공기에</t>
+  </si>
+  <si>
+    <t>작은 공기에 담으면 양을 가늠하기 쉬워요.</t>
+  </si>
+  <si>
+    <t>국수는 천천히 후루룩</t>
+  </si>
+  <si>
+    <t>면은 천천히 먹어야 배부름을 느끼기 쉬워요.</t>
+  </si>
+  <si>
+    <t>10-12 상황 전제 규칙(편의점·외식)에 걸린 4개 수정 · 6차 새 표현 20개 · 7차 끼니 추천 16개(아침 추천 8은 04~10시, 저녁 추천 8은 12~17시 — 있는 시간 조건만 사용) 추가. 합계 154개</t>
   </si>
 </sst>
 </file>
@@ -8216,7 +8447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F51797-492B-40AC-833D-E19CEF6E9FA5}">
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="120.58203125" style="1" customWidth="1"/>
@@ -8240,7 +8471,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="16" x14ac:dyDescent="0.45">
@@ -8265,27 +8496,32 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>504</v>
+        <v>492</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A15" s="1" t="s">
+        <v>580</v>
       </c>
     </row>
   </sheetData>
@@ -8296,7 +8532,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{243C8A1C-2FBA-4873-BD31-7545635970F1}">
-  <dimension ref="A1:O119"/>
+  <dimension ref="A1:O155"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="6.58203125" style="1" customWidth="1"/>
@@ -8335,7 +8571,7 @@
         <v>73</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>74</v>
@@ -8379,7 +8615,7 @@
         <v>4</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>76</v>
@@ -8418,10 +8654,10 @@
         <v>3</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>78</v>
@@ -8463,7 +8699,7 @@
         <v>4</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>80</v>
@@ -8505,7 +8741,7 @@
         <v>8</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>82</v>
@@ -8547,7 +8783,7 @@
         <v>13</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>84</v>
@@ -8589,7 +8825,7 @@
         <v>4</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>86</v>
@@ -8628,10 +8864,10 @@
         <v>15</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>88</v>
@@ -8673,7 +8909,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>90</v>
@@ -8712,10 +8948,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>92</v>
@@ -8757,7 +8993,7 @@
         <v>4</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>94</v>
@@ -8796,10 +9032,10 @@
         <v>21</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>96</v>
@@ -8841,7 +9077,7 @@
         <v>4</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>98</v>
@@ -8880,10 +9116,10 @@
         <v>23</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>100</v>
@@ -8925,17 +9161,17 @@
         <v>4</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>27</v>
@@ -8964,10 +9200,10 @@
         <v>26</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>102</v>
@@ -9009,17 +9245,17 @@
         <v>4</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H17" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>30</v>
@@ -9048,20 +9284,20 @@
         <v>29</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>31</v>
@@ -9093,7 +9329,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>104</v>
@@ -9135,7 +9371,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>106</v>
@@ -9177,17 +9413,17 @@
         <v>0</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H21" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>33</v>
@@ -9219,7 +9455,7 @@
         <v>13</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>108</v>
@@ -9261,7 +9497,7 @@
         <v>4</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>110</v>
@@ -9303,7 +9539,7 @@
         <v>4</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>112</v>
@@ -9342,10 +9578,10 @@
         <v>10</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>114</v>
@@ -9384,20 +9620,20 @@
         <v>15</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H26" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>35</v>
@@ -9429,17 +9665,17 @@
         <v>4</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H27" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>35</v>
@@ -9471,7 +9707,7 @@
         <v>4</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>116</v>
@@ -9510,20 +9746,20 @@
         <v>18</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>37</v>
@@ -9555,7 +9791,7 @@
         <v>13</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>118</v>
@@ -9597,7 +9833,7 @@
         <v>4</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>120</v>
@@ -9636,10 +9872,10 @@
         <v>23</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>122</v>
@@ -9681,7 +9917,7 @@
         <v>4</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>124</v>
@@ -9723,17 +9959,17 @@
         <v>13</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="H34" s="3">
         <f t="shared" ref="H34:H64" si="1">LEN(F34)</f>
         <v>12</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>28</v>
@@ -9765,7 +10001,7 @@
         <v>4</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>126</v>
@@ -9807,17 +10043,17 @@
         <v>13</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="H36" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="J36" s="3" t="s">
         <v>31</v>
@@ -9849,7 +10085,7 @@
         <v>4</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>128</v>
@@ -9891,7 +10127,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>129</v>
@@ -9933,7 +10169,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>131</v>
@@ -9975,7 +10211,7 @@
         <v>4</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>133</v>
@@ -10014,20 +10250,20 @@
         <v>3</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="H41" s="3">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>42</v>
@@ -10059,7 +10295,7 @@
         <v>4</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>135</v>
@@ -10098,20 +10334,20 @@
         <v>10</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H43" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>14</v>
@@ -10143,17 +10379,17 @@
         <v>13</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="H44" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>43</v>
@@ -10185,7 +10421,7 @@
         <v>4</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>137</v>
@@ -10227,7 +10463,7 @@
         <v>8</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>139</v>
@@ -10269,7 +10505,7 @@
         <v>13</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>141</v>
@@ -10311,7 +10547,7 @@
         <v>4</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>143</v>
@@ -10353,7 +10589,7 @@
         <v>8</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>145</v>
@@ -10395,7 +10631,7 @@
         <v>13</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>147</v>
@@ -10437,7 +10673,7 @@
         <v>4</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G51" s="5" t="s">
         <v>149</v>
@@ -10479,7 +10715,7 @@
         <v>8</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>151</v>
@@ -10521,7 +10757,7 @@
         <v>13</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>153</v>
@@ -10563,7 +10799,7 @@
         <v>4</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>155</v>
@@ -10605,7 +10841,7 @@
         <v>8</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>157</v>
@@ -10647,7 +10883,7 @@
         <v>13</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G56" s="5" t="s">
         <v>159</v>
@@ -10689,7 +10925,7 @@
         <v>4</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G57" s="5" t="s">
         <v>161</v>
@@ -10731,7 +10967,7 @@
         <v>8</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>163</v>
@@ -10773,17 +11009,17 @@
         <v>13</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H59" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>53</v>
@@ -10815,7 +11051,7 @@
         <v>4</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="G60" s="5" t="s">
         <v>165</v>
@@ -10857,17 +11093,17 @@
         <v>8</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="H61" s="3">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>31</v>
@@ -10882,7 +11118,7 @@
       <c r="N61" s="3"/>
       <c r="O61" s="3"/>
     </row>
-    <row r="62" spans="1:15" ht="16" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -10899,17 +11135,17 @@
         <v>13</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>478</v>
+        <v>494</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>330</v>
+        <v>493</v>
       </c>
       <c r="H62" s="3">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I62" s="7" t="s">
-        <v>479</v>
+        <v>495</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>55</v>
@@ -10941,17 +11177,17 @@
         <v>0</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="H63" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="I63" s="7" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>33</v>
@@ -10983,7 +11219,7 @@
         <v>0</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="G64" s="5" t="s">
         <v>167</v>
@@ -11025,10 +11261,10 @@
         <v>173</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="H65" s="3">
         <f t="shared" ref="H65:H112" si="2">LEN(F65)</f>
@@ -11067,10 +11303,10 @@
         <v>173</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="H66" s="3">
         <f t="shared" si="2"/>
@@ -11109,10 +11345,10 @@
         <v>173</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="H67" s="3">
         <f t="shared" si="2"/>
@@ -11151,10 +11387,10 @@
         <v>173</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H68" s="3">
         <f t="shared" si="2"/>
@@ -11193,10 +11429,10 @@
         <v>173</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="H69" s="3">
         <f t="shared" si="2"/>
@@ -11235,10 +11471,10 @@
         <v>173</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="H70" s="3">
         <f t="shared" si="2"/>
@@ -11277,10 +11513,10 @@
         <v>173</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="H71" s="3">
         <f t="shared" si="2"/>
@@ -11319,10 +11555,10 @@
         <v>173</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="H72" s="3">
         <f t="shared" si="2"/>
@@ -11361,10 +11597,10 @@
         <v>173</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="H73" s="3">
         <f t="shared" si="2"/>
@@ -11403,10 +11639,10 @@
         <v>173</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="H74" s="3">
         <f t="shared" si="2"/>
@@ -11445,10 +11681,10 @@
         <v>173</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="H75" s="3">
         <f t="shared" si="2"/>
@@ -11487,10 +11723,10 @@
         <v>173</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="H76" s="3">
         <f t="shared" si="2"/>
@@ -11529,10 +11765,10 @@
         <v>173</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="H77" s="3">
         <f t="shared" si="2"/>
@@ -11571,10 +11807,10 @@
         <v>173</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="H78" s="3">
         <f t="shared" si="2"/>
@@ -11613,10 +11849,10 @@
         <v>173</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="H79" s="3">
         <f t="shared" si="2"/>
@@ -11655,10 +11891,10 @@
         <v>173</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="H80" s="3">
         <f t="shared" si="2"/>
@@ -11697,10 +11933,10 @@
         <v>173</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="H81" s="3">
         <f t="shared" si="2"/>
@@ -11739,10 +11975,10 @@
         <v>173</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="H82" s="3">
         <f t="shared" si="2"/>
@@ -11823,10 +12059,10 @@
         <v>173</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="H84" s="3">
         <f t="shared" si="2"/>
@@ -11865,10 +12101,10 @@
         <v>173</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="H85" s="3">
         <f t="shared" si="2"/>
@@ -11907,17 +12143,17 @@
         <v>173</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>374</v>
+        <v>497</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>373</v>
+        <v>496</v>
       </c>
       <c r="H86" s="3">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>218</v>
+        <v>498</v>
       </c>
       <c r="J86" s="3" t="s">
         <v>217</v>
@@ -11949,20 +12185,20 @@
         <v>173</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="H87" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I87" s="7" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K87" s="3" t="s">
         <v>185</v>
@@ -11991,20 +12227,20 @@
         <v>173</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="H88" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I88" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="J88" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="J88" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="K88" s="3" t="s">
         <v>185</v>
@@ -12027,23 +12263,23 @@
         <v>171</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="H89" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>180</v>
@@ -12069,23 +12305,23 @@
         <v>171</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="H90" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J90" s="3" t="s">
         <v>175</v>
@@ -12111,23 +12347,23 @@
         <v>171</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="H91" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>184</v>
@@ -12153,23 +12389,23 @@
         <v>171</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="H92" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J92" s="3" t="s">
         <v>175</v>
@@ -12195,23 +12431,23 @@
         <v>171</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="H93" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J93" s="3" t="s">
         <v>207</v>
@@ -12237,26 +12473,26 @@
         <v>171</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="H94" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I94" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="J94" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>230</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>185</v>
@@ -12279,26 +12515,26 @@
         <v>171</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="H95" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I95" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="J95" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="J95" s="3" t="s">
-        <v>233</v>
       </c>
       <c r="K95" s="3" t="s">
         <v>176</v>
@@ -12321,26 +12557,26 @@
         <v>171</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="H96" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>176</v>
@@ -12363,26 +12599,26 @@
         <v>171</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="H97" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I97" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="J97" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="J97" s="3" t="s">
-        <v>236</v>
       </c>
       <c r="K97" s="3" t="s">
         <v>176</v>
@@ -12405,26 +12641,26 @@
         <v>171</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="H98" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I98" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="J98" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="J98" s="3" t="s">
-        <v>238</v>
       </c>
       <c r="K98" s="3" t="s">
         <v>176</v>
@@ -12447,26 +12683,26 @@
         <v>171</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="H99" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K99" s="3" t="s">
         <v>185</v>
@@ -12489,26 +12725,26 @@
         <v>171</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="H100" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>185</v>
@@ -12531,26 +12767,26 @@
         <v>171</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="H101" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I101" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="J101" s="3" t="s">
         <v>242</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>243</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>176</v>
@@ -12573,26 +12809,26 @@
         <v>171</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="H102" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>176</v>
@@ -12615,26 +12851,26 @@
         <v>171</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>407</v>
+        <v>500</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>406</v>
+        <v>499</v>
       </c>
       <c r="H103" s="3">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>245</v>
+        <v>501</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K103" s="3" t="s">
         <v>176</v>
@@ -12657,26 +12893,26 @@
         <v>171</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="H104" s="3">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K104" s="3" t="s">
         <v>176</v>
@@ -12699,26 +12935,26 @@
         <v>171</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="H105" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K105" s="3" t="s">
         <v>185</v>
@@ -12741,26 +12977,26 @@
         <v>171</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="H106" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K106" s="3" t="s">
         <v>185</v>
@@ -12783,26 +13019,26 @@
         <v>171</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="H107" s="3">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="K107" s="3" t="s">
         <v>176</v>
@@ -12825,26 +13061,26 @@
         <v>171</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="H108" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I108" s="7" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K108" s="3" t="s">
         <v>176</v>
@@ -12867,13 +13103,13 @@
         <v>171</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G109" s="5" t="s">
         <v>0</v>
@@ -12883,7 +13119,7 @@
         <v>11</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J109" s="3" t="s">
         <v>207</v>
@@ -12909,26 +13145,26 @@
         <v>171</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>417</v>
+        <v>503</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>416</v>
+        <v>502</v>
       </c>
       <c r="H110" s="3">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>254</v>
+        <v>504</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K110" s="3" t="s">
         <v>176</v>
@@ -12951,26 +13187,26 @@
         <v>171</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="H111" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I111" s="7" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K111" s="3" t="s">
         <v>185</v>
@@ -12993,26 +13229,26 @@
         <v>171</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>173</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="H112" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I112" s="7" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="K112" s="3" t="s">
         <v>185</v>
@@ -13035,26 +13271,26 @@
         <v>171</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E113" s="7" t="s">
         <v>173</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="H113" s="7">
         <f t="shared" ref="H113:H118" si="3">LEN(F113)</f>
         <v>11</v>
       </c>
       <c r="I113" s="7" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="J113" s="7" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="K113" s="7" t="s">
         <v>176</v>
@@ -13077,26 +13313,26 @@
         <v>171</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E114" s="7" t="s">
         <v>173</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="G114" s="7" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="H114" s="7">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="I114" s="7" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="J114" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K114" s="7" t="s">
         <v>176</v>
@@ -13125,20 +13361,20 @@
         <v>173</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="H115" s="7">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="I115" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J115" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="K115" s="7" t="s">
         <v>176</v>
@@ -13167,17 +13403,17 @@
         <v>173</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="G116" s="7" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="H116" s="7">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="I116" s="7" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="J116" s="7" t="s">
         <v>200</v>
@@ -13209,17 +13445,17 @@
         <v>173</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="H117" s="7">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="I117" s="7" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="J117" s="7" t="s">
         <v>200</v>
@@ -13251,17 +13487,17 @@
         <v>173</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="G118" s="7" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="H118" s="7">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="I118" s="7" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="J118" s="7" t="s">
         <v>190</v>
@@ -13281,10 +13517,10 @@
         <v>118</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="D119" s="7" t="s">
         <v>0</v>
@@ -13293,7 +13529,7 @@
         <v>0</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="G119" s="7" t="s">
         <v>0</v>
@@ -13303,10 +13539,10 @@
         <v>10</v>
       </c>
       <c r="I119" s="7" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="J119" s="7" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="K119" s="7" t="s">
         <v>176</v>
@@ -13318,11 +13554,1523 @@
       <c r="N119" s="3"/>
       <c r="O119" s="3"/>
     </row>
+    <row r="120" spans="1:15" ht="37.5" x14ac:dyDescent="0.45">
+      <c r="A120" s="7">
+        <v>119</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D120" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="E120" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="G120" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H120" s="7">
+        <f>LEN(F120)</f>
+        <v>10</v>
+      </c>
+      <c r="I120" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="J120" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="K120" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="L120" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M120" s="3"/>
+      <c r="N120" s="3"/>
+      <c r="O120" s="3"/>
+    </row>
+    <row r="121" spans="1:15" ht="37.5" x14ac:dyDescent="0.45">
+      <c r="A121" s="7">
+        <v>120</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D121" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="E121" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="G121" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H121" s="7">
+        <f>LEN(F121)</f>
+        <v>12</v>
+      </c>
+      <c r="I121" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="J121" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="K121" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="L121" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M121" s="3"/>
+      <c r="N121" s="3"/>
+      <c r="O121" s="3"/>
+    </row>
+    <row r="122" spans="1:15" ht="37.5" x14ac:dyDescent="0.45">
+      <c r="A122" s="7">
+        <v>121</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="E122" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F122" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="G122" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H122" s="7">
+        <f>LEN(F122)</f>
+        <v>11</v>
+      </c>
+      <c r="I122" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="J122" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="K122" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="L122" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M122" s="3"/>
+      <c r="N122" s="3"/>
+      <c r="O122" s="3"/>
+    </row>
+    <row r="123" spans="1:15" ht="37.5" x14ac:dyDescent="0.45">
+      <c r="A123" s="7">
+        <v>122</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="E123" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F123" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="G123" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H123" s="7">
+        <f>LEN(F123)</f>
+        <v>11</v>
+      </c>
+      <c r="I123" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="J123" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="K123" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="L123" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M123" s="3"/>
+      <c r="N123" s="3"/>
+      <c r="O123" s="3"/>
+    </row>
+    <row r="124" spans="1:15" ht="37.5" x14ac:dyDescent="0.45">
+      <c r="A124" s="7">
+        <v>123</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D124" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="E124" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="G124" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H124" s="7">
+        <f>LEN(F124)</f>
+        <v>9</v>
+      </c>
+      <c r="I124" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="J124" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="K124" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="L124" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M124" s="3"/>
+      <c r="N124" s="3"/>
+      <c r="O124" s="3"/>
+    </row>
+    <row r="125" spans="1:15" ht="37.5" x14ac:dyDescent="0.45">
+      <c r="A125" s="7">
+        <v>124</v>
+      </c>
+      <c r="B125" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F125" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="G125" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H125" s="7">
+        <f>LEN(F125)</f>
+        <v>11</v>
+      </c>
+      <c r="I125" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="J125" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="K125" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="L125" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M125" s="3"/>
+      <c r="N125" s="3"/>
+      <c r="O125" s="3"/>
+    </row>
+    <row r="126" spans="1:15" ht="37.5" x14ac:dyDescent="0.45">
+      <c r="A126" s="7">
+        <v>125</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E126" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="G126" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H126" s="7">
+        <f>LEN(F126)</f>
+        <v>10</v>
+      </c>
+      <c r="I126" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="J126" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="K126" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="L126" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M126" s="3"/>
+      <c r="N126" s="3"/>
+      <c r="O126" s="3"/>
+    </row>
+    <row r="127" spans="1:15" ht="37.5" x14ac:dyDescent="0.45">
+      <c r="A127" s="7">
+        <v>126</v>
+      </c>
+      <c r="B127" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="E127" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="G127" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H127" s="7">
+        <f>LEN(F127)</f>
+        <v>11</v>
+      </c>
+      <c r="I127" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="J127" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="K127" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="L127" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M127" s="3"/>
+      <c r="N127" s="3"/>
+      <c r="O127" s="3"/>
+    </row>
+    <row r="128" spans="1:15" ht="37.5" x14ac:dyDescent="0.45">
+      <c r="A128" s="7">
+        <v>127</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="E128" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F128" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="G128" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H128" s="7">
+        <f>LEN(F128)</f>
+        <v>12</v>
+      </c>
+      <c r="I128" s="7" t="s">
+        <v>524</v>
+      </c>
+      <c r="J128" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="K128" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="L128" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M128" s="3"/>
+      <c r="N128" s="3"/>
+      <c r="O128" s="3"/>
+    </row>
+    <row r="129" spans="1:15" ht="37.5" x14ac:dyDescent="0.45">
+      <c r="A129" s="7">
+        <v>128</v>
+      </c>
+      <c r="B129" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="E129" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F129" s="7" t="s">
+        <v>526</v>
+      </c>
+      <c r="G129" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H129" s="7">
+        <f>LEN(F129)</f>
+        <v>9</v>
+      </c>
+      <c r="I129" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="J129" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="K129" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="L129" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M129" s="3"/>
+      <c r="N129" s="3"/>
+      <c r="O129" s="3"/>
+    </row>
+    <row r="130" spans="1:15" ht="37.5" x14ac:dyDescent="0.45">
+      <c r="A130" s="7">
+        <v>129</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="E130" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F130" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="G130" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H130" s="7">
+        <f>LEN(F130)</f>
+        <v>10</v>
+      </c>
+      <c r="I130" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="J130" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="K130" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="L130" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M130" s="3"/>
+      <c r="N130" s="3"/>
+      <c r="O130" s="3"/>
+    </row>
+    <row r="131" spans="1:15" ht="37.5" x14ac:dyDescent="0.45">
+      <c r="A131" s="7">
+        <v>130</v>
+      </c>
+      <c r="B131" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="E131" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F131" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="G131" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H131" s="7">
+        <f>LEN(F131)</f>
+        <v>11</v>
+      </c>
+      <c r="I131" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="J131" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="K131" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="L131" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M131" s="3"/>
+      <c r="N131" s="3"/>
+      <c r="O131" s="3"/>
+    </row>
+    <row r="132" spans="1:15" ht="37.5" x14ac:dyDescent="0.45">
+      <c r="A132" s="7">
+        <v>131</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="E132" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F132" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="G132" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H132" s="7">
+        <f>LEN(F132)</f>
+        <v>10</v>
+      </c>
+      <c r="I132" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="J132" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="K132" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="L132" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M132" s="3"/>
+      <c r="N132" s="3"/>
+      <c r="O132" s="3"/>
+    </row>
+    <row r="133" spans="1:15" ht="37.5" x14ac:dyDescent="0.45">
+      <c r="A133" s="7">
+        <v>132</v>
+      </c>
+      <c r="B133" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E133" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F133" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="G133" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H133" s="7">
+        <f>LEN(F133)</f>
+        <v>9</v>
+      </c>
+      <c r="I133" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="J133" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="K133" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="L133" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M133" s="3"/>
+      <c r="N133" s="3"/>
+      <c r="O133" s="3"/>
+    </row>
+    <row r="134" spans="1:15" ht="37.5" x14ac:dyDescent="0.45">
+      <c r="A134" s="7">
+        <v>133</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E134" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F134" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="G134" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H134" s="7">
+        <f>LEN(F134)</f>
+        <v>12</v>
+      </c>
+      <c r="I134" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="J134" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="K134" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="L134" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M134" s="3"/>
+      <c r="N134" s="3"/>
+      <c r="O134" s="3"/>
+    </row>
+    <row r="135" spans="1:15" ht="37.5" x14ac:dyDescent="0.45">
+      <c r="A135" s="7">
+        <v>134</v>
+      </c>
+      <c r="B135" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="E135" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F135" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="G135" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H135" s="7">
+        <f>LEN(F135)</f>
+        <v>10</v>
+      </c>
+      <c r="I135" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="J135" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="K135" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="L135" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M135" s="3"/>
+      <c r="N135" s="3"/>
+      <c r="O135" s="3"/>
+    </row>
+    <row r="136" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A136" s="7">
+        <v>135</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="E136" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F136" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="G136" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H136" s="7">
+        <f>LEN(F136)</f>
+        <v>12</v>
+      </c>
+      <c r="I136" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="J136" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="K136" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="L136" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M136" s="3"/>
+      <c r="N136" s="3"/>
+      <c r="O136" s="3"/>
+    </row>
+    <row r="137" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A137" s="7">
+        <v>136</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D137" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="E137" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F137" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="G137" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H137" s="7">
+        <f>LEN(F137)</f>
+        <v>12</v>
+      </c>
+      <c r="I137" s="7" t="s">
+        <v>542</v>
+      </c>
+      <c r="J137" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="K137" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="L137" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M137" s="3"/>
+      <c r="N137" s="3"/>
+      <c r="O137" s="3"/>
+    </row>
+    <row r="138" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A138" s="7">
+        <v>137</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E138" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F138" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="G138" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H138" s="7">
+        <f>LEN(F138)</f>
+        <v>11</v>
+      </c>
+      <c r="I138" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="J138" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="K138" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="L138" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M138" s="3"/>
+      <c r="N138" s="3"/>
+      <c r="O138" s="3"/>
+    </row>
+    <row r="139" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A139" s="7">
+        <v>138</v>
+      </c>
+      <c r="B139" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E139" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F139" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="G139" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H139" s="7">
+        <f>LEN(F139)</f>
+        <v>10</v>
+      </c>
+      <c r="I139" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="J139" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="K139" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="L139" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M139" s="3"/>
+      <c r="N139" s="3"/>
+      <c r="O139" s="3"/>
+    </row>
+    <row r="140" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A140" s="7">
+        <v>139</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E140" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F140" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="G140" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H140" s="7">
+        <f>LEN(F140)</f>
+        <v>11</v>
+      </c>
+      <c r="I140" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="J140" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="K140" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="L140" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M140" s="3"/>
+      <c r="N140" s="3"/>
+      <c r="O140" s="3"/>
+    </row>
+    <row r="141" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A141" s="7">
+        <v>140</v>
+      </c>
+      <c r="B141" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D141" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="E141" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F141" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="G141" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H141" s="7">
+        <f>LEN(F141)</f>
+        <v>9</v>
+      </c>
+      <c r="I141" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="J141" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="K141" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="L141" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M141" s="3"/>
+      <c r="N141" s="3"/>
+      <c r="O141" s="3"/>
+    </row>
+    <row r="142" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A142" s="7">
+        <v>141</v>
+      </c>
+      <c r="B142" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="E142" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F142" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="G142" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H142" s="7">
+        <f>LEN(F142)</f>
+        <v>11</v>
+      </c>
+      <c r="I142" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="J142" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="K142" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="L142" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M142" s="3"/>
+      <c r="N142" s="3"/>
+      <c r="O142" s="3"/>
+    </row>
+    <row r="143" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A143" s="7">
+        <v>142</v>
+      </c>
+      <c r="B143" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C143" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="E143" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F143" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="G143" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H143" s="7">
+        <f>LEN(F143)</f>
+        <v>10</v>
+      </c>
+      <c r="I143" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="J143" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="K143" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="L143" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M143" s="3"/>
+      <c r="N143" s="3"/>
+      <c r="O143" s="3"/>
+    </row>
+    <row r="144" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A144" s="7">
+        <v>143</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="E144" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F144" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="G144" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H144" s="7">
+        <f>LEN(F144)</f>
+        <v>9</v>
+      </c>
+      <c r="I144" s="7" t="s">
+        <v>556</v>
+      </c>
+      <c r="J144" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="K144" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="L144" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M144" s="3"/>
+      <c r="N144" s="3"/>
+      <c r="O144" s="3"/>
+    </row>
+    <row r="145" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A145" s="7">
+        <v>144</v>
+      </c>
+      <c r="B145" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C145" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="E145" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F145" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="G145" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H145" s="7">
+        <f>LEN(F145)</f>
+        <v>9</v>
+      </c>
+      <c r="I145" s="7" t="s">
+        <v>558</v>
+      </c>
+      <c r="J145" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="K145" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="L145" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M145" s="3"/>
+      <c r="N145" s="3"/>
+      <c r="O145" s="3"/>
+    </row>
+    <row r="146" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A146" s="7">
+        <v>145</v>
+      </c>
+      <c r="B146" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="E146" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F146" s="7" t="s">
+        <v>559</v>
+      </c>
+      <c r="G146" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H146" s="7">
+        <f>LEN(F146)</f>
+        <v>11</v>
+      </c>
+      <c r="I146" s="7" t="s">
+        <v>560</v>
+      </c>
+      <c r="J146" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="K146" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="L146" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M146" s="3"/>
+      <c r="N146" s="3"/>
+      <c r="O146" s="3"/>
+    </row>
+    <row r="147" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A147" s="7">
+        <v>146</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="E147" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F147" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="G147" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H147" s="7">
+        <f>LEN(F147)</f>
+        <v>9</v>
+      </c>
+      <c r="I147" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="J147" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="K147" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="L147" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M147" s="3"/>
+      <c r="N147" s="3"/>
+      <c r="O147" s="3"/>
+    </row>
+    <row r="148" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A148" s="7">
+        <v>147</v>
+      </c>
+      <c r="B148" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="E148" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F148" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="G148" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H148" s="7">
+        <f>LEN(F148)</f>
+        <v>8</v>
+      </c>
+      <c r="I148" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="J148" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="K148" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="L148" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M148" s="3"/>
+      <c r="N148" s="3"/>
+      <c r="O148" s="3"/>
+    </row>
+    <row r="149" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A149" s="7">
+        <v>148</v>
+      </c>
+      <c r="B149" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C149" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="E149" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F149" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="G149" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H149" s="7">
+        <f>LEN(F149)</f>
+        <v>11</v>
+      </c>
+      <c r="I149" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="J149" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="K149" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="L149" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M149" s="3"/>
+      <c r="N149" s="3"/>
+      <c r="O149" s="3"/>
+    </row>
+    <row r="150" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A150" s="7">
+        <v>149</v>
+      </c>
+      <c r="B150" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F150" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="G150" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H150" s="7">
+        <f>LEN(F150)</f>
+        <v>9</v>
+      </c>
+      <c r="I150" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="J150" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="K150" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="L150" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M150" s="3"/>
+      <c r="N150" s="3"/>
+      <c r="O150" s="3"/>
+    </row>
+    <row r="151" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A151" s="7">
+        <v>150</v>
+      </c>
+      <c r="B151" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D151" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="E151" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F151" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="G151" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H151" s="7">
+        <f>LEN(F151)</f>
+        <v>11</v>
+      </c>
+      <c r="I151" s="7" t="s">
+        <v>570</v>
+      </c>
+      <c r="J151" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="K151" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="L151" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="M151" s="3"/>
+      <c r="N151" s="3"/>
+      <c r="O151" s="3"/>
+    </row>
+    <row r="152" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A152" s="7">
+        <v>151</v>
+      </c>
+      <c r="B152" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C152" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="E152" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F152" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="G152" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H152" s="7">
+        <f>LEN(F152)</f>
+        <v>11</v>
+      </c>
+      <c r="I152" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="J152" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="K152" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="L152" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="M152" s="3"/>
+      <c r="N152" s="3"/>
+      <c r="O152" s="3"/>
+    </row>
+    <row r="153" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A153" s="7">
+        <v>152</v>
+      </c>
+      <c r="B153" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D153" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E153" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F153" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="G153" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H153" s="7">
+        <f>LEN(F153)</f>
+        <v>12</v>
+      </c>
+      <c r="I153" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="J153" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="K153" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="L153" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M153" s="3"/>
+      <c r="N153" s="3"/>
+      <c r="O153" s="3"/>
+    </row>
+    <row r="154" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A154" s="7">
+        <v>153</v>
+      </c>
+      <c r="B154" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D154" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E154" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F154" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="G154" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H154" s="7">
+        <f>LEN(F154)</f>
+        <v>9</v>
+      </c>
+      <c r="I154" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="J154" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="K154" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="L154" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M154" s="3"/>
+      <c r="N154" s="3"/>
+      <c r="O154" s="3"/>
+    </row>
+    <row r="155" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A155" s="7">
+        <v>154</v>
+      </c>
+      <c r="B155" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D155" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E155" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F155" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="G155" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H155" s="7">
+        <f>LEN(F155)</f>
+        <v>11</v>
+      </c>
+      <c r="I155" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="J155" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="K155" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="L155" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="M155" s="3"/>
+      <c r="N155" s="3"/>
+      <c r="O155" s="3"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O118" xr:uid="{243C8A1C-2FBA-4873-BD31-7545635970F1}"/>
+  <autoFilter ref="A1:O155" xr:uid="{243C8A1C-2FBA-4873-BD31-7545635970F1}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M119" xr:uid="{29F577E0-A9A7-4D3D-B3E7-99484ADFB535}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M155" xr:uid="{29F577E0-A9A7-4D3D-B3E7-99484ADFB535}">
       <formula1>"승인,수정,제외"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13349,25 +15097,25 @@
   <sheetData>
     <row r="1" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>58</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>64</v>
@@ -13378,142 +15126,142 @@
     </row>
     <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A2" s="9" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="D2" s="9">
         <f>LEN(C2)</f>
         <v>14</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="F2" s="9">
         <f>LEN(E2)</f>
         <v>10</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
     </row>
     <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A3" s="9" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="D3" s="9">
         <f>LEN(C3)</f>
         <v>13</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="F3" s="9">
         <f>LEN(E3)</f>
         <v>11</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
     </row>
     <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A4" s="9" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="D4" s="9">
         <f>LEN(C4)</f>
         <v>14</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="F4" s="9">
         <f>LEN(E4)</f>
         <v>10</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
     </row>
     <row r="5" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A5" s="9" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="D5" s="9">
         <f>LEN(C5)</f>
         <v>15</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="F5" s="9">
         <f>LEN(E5)</f>
         <v>12</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
     <row r="6" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A6" s="9" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="D6" s="9">
         <f>LEN(C6)</f>
         <v>13</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="F6" s="9">
         <f>LEN(E6)</f>
         <v>10</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3E8CAE-1DE9-404B-BE0B-EBB6D790C492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F31D75D-1F6B-4E40-A133-6224419DF063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -5316,14 +5316,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>기운 나는 시간 적어 두기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기운 있는 때를 알면 끼니를 맞추기 쉬워요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>내일 첫 끼 먹을 시간 정하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8243,6 +8235,14 @@
   </si>
   <si>
     <t>아니오</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입맛 있을 때 먹어 두기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입맛이 돌 때 먹어 두면 하루 식사를 채우기 쉬워요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8754,7 +8754,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="16" x14ac:dyDescent="0.45">
@@ -8774,42 +8774,42 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
   </sheetData>
@@ -8845,7 +8845,7 @@
         <v>53</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>54</v>
@@ -8860,7 +8860,7 @@
         <v>69</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>70</v>
@@ -8892,7 +8892,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -8904,7 +8904,7 @@
         <v>3</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>72</v>
@@ -8934,7 +8934,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -8943,10 +8943,10 @@
         <v>2</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>74</v>
@@ -8976,7 +8976,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -8988,7 +8988,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>76</v>
@@ -9018,7 +9018,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -9030,7 +9030,7 @@
         <v>7</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>78</v>
@@ -9060,7 +9060,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -9072,7 +9072,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>80</v>
@@ -9102,7 +9102,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -9114,7 +9114,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>82</v>
@@ -9144,7 +9144,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -9153,10 +9153,10 @@
         <v>14</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>84</v>
@@ -9186,7 +9186,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -9198,7 +9198,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>86</v>
@@ -9228,7 +9228,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -9237,10 +9237,10 @@
         <v>17</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>88</v>
@@ -9270,7 +9270,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -9282,7 +9282,7 @@
         <v>3</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>90</v>
@@ -9312,7 +9312,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -9321,10 +9321,10 @@
         <v>20</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>92</v>
@@ -9354,7 +9354,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -9366,7 +9366,7 @@
         <v>3</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>94</v>
@@ -9396,7 +9396,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -9405,10 +9405,10 @@
         <v>22</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>96</v>
@@ -9438,7 +9438,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -9450,17 +9450,17 @@
         <v>3</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>26</v>
@@ -9480,7 +9480,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -9489,10 +9489,10 @@
         <v>25</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>98</v>
@@ -9522,7 +9522,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -9534,17 +9534,17 @@
         <v>3</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H17" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>29</v>
@@ -9564,7 +9564,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -9573,20 +9573,20 @@
         <v>28</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>30</v>
@@ -9606,7 +9606,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>31</v>
@@ -9618,7 +9618,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>100</v>
@@ -9648,7 +9648,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>31</v>
@@ -9660,7 +9660,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>102</v>
@@ -9690,7 +9690,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>31</v>
@@ -9702,17 +9702,17 @@
         <v>0</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H21" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>32</v>
@@ -9732,7 +9732,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1</v>
@@ -9744,7 +9744,7 @@
         <v>12</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>104</v>
@@ -9774,7 +9774,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>1</v>
@@ -9786,7 +9786,7 @@
         <v>3</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>106</v>
@@ -9816,7 +9816,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>1</v>
@@ -9828,7 +9828,7 @@
         <v>3</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>108</v>
@@ -9858,7 +9858,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>1</v>
@@ -9867,10 +9867,10 @@
         <v>9</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>110</v>
@@ -9900,7 +9900,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>1</v>
@@ -9909,20 +9909,20 @@
         <v>14</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="H26" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>33</v>
@@ -9942,7 +9942,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>1</v>
@@ -9954,17 +9954,17 @@
         <v>3</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H27" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>33</v>
@@ -9984,7 +9984,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>1</v>
@@ -9996,7 +9996,7 @@
         <v>3</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>112</v>
@@ -10026,7 +10026,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>1</v>
@@ -10035,20 +10035,20 @@
         <v>17</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>35</v>
@@ -10068,7 +10068,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>1</v>
@@ -10080,7 +10080,7 @@
         <v>12</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>114</v>
@@ -10110,7 +10110,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>1</v>
@@ -10122,7 +10122,7 @@
         <v>3</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>116</v>
@@ -10152,7 +10152,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>1</v>
@@ -10161,29 +10161,29 @@
         <v>22</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H32" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
@@ -10194,7 +10194,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>1</v>
@@ -10206,7 +10206,7 @@
         <v>3</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>118</v>
@@ -10236,7 +10236,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>1</v>
@@ -10248,17 +10248,17 @@
         <v>12</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H34" s="3">
         <f t="shared" ref="H34:H64" si="1">LEN(F34)</f>
         <v>12</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>27</v>
@@ -10278,7 +10278,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>1</v>
@@ -10290,7 +10290,7 @@
         <v>3</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>120</v>
@@ -10320,7 +10320,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>1</v>
@@ -10332,17 +10332,17 @@
         <v>12</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H36" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="J36" s="3" t="s">
         <v>30</v>
@@ -10362,7 +10362,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>1</v>
@@ -10374,7 +10374,7 @@
         <v>3</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>122</v>
@@ -10404,7 +10404,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>31</v>
@@ -10416,17 +10416,17 @@
         <v>0</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>296</v>
+        <v>686</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>123</v>
+        <v>294</v>
       </c>
       <c r="H38" s="3">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>124</v>
+        <v>13</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>687</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>32</v>
@@ -10446,7 +10446,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>31</v>
@@ -10458,17 +10458,17 @@
         <v>0</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H39" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>38</v>
@@ -10488,7 +10488,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>1</v>
@@ -10500,17 +10500,17 @@
         <v>3</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H40" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>38</v>
@@ -10530,7 +10530,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>1</v>
@@ -10539,20 +10539,20 @@
         <v>2</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="H41" s="3">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>39</v>
@@ -10572,7 +10572,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>1</v>
@@ -10584,17 +10584,17 @@
         <v>3</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H42" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>15</v>
@@ -10614,7 +10614,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>1</v>
@@ -10623,20 +10623,20 @@
         <v>9</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H43" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>13</v>
@@ -10656,7 +10656,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>1</v>
@@ -10668,17 +10668,17 @@
         <v>12</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H44" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>40</v>
@@ -10698,7 +10698,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>1</v>
@@ -10710,17 +10710,17 @@
         <v>3</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H45" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>41</v>
@@ -10740,7 +10740,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>1</v>
@@ -10752,17 +10752,17 @@
         <v>7</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H46" s="3">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>42</v>
@@ -10782,7 +10782,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>1</v>
@@ -10794,17 +10794,17 @@
         <v>12</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H47" s="3">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>43</v>
@@ -10824,7 +10824,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>1</v>
@@ -10836,17 +10836,17 @@
         <v>3</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H48" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>18</v>
@@ -10866,7 +10866,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>1</v>
@@ -10878,17 +10878,17 @@
         <v>7</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H49" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>44</v>
@@ -10908,7 +10908,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>1</v>
@@ -10920,17 +10920,17 @@
         <v>12</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H50" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>45</v>
@@ -10950,7 +10950,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>1</v>
@@ -10962,17 +10962,17 @@
         <v>3</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H51" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>21</v>
@@ -10992,7 +10992,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>1</v>
@@ -11004,17 +11004,17 @@
         <v>7</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H52" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>46</v>
@@ -11034,7 +11034,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>1</v>
@@ -11046,17 +11046,17 @@
         <v>12</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J53" s="3" t="s">
         <v>8</v>
@@ -11076,7 +11076,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>1</v>
@@ -11088,17 +11088,17 @@
         <v>3</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H54" s="3">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>23</v>
@@ -11118,7 +11118,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>1</v>
@@ -11130,17 +11130,17 @@
         <v>7</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H55" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>47</v>
@@ -11160,7 +11160,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>1</v>
@@ -11172,17 +11172,17 @@
         <v>12</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H56" s="3">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J56" s="3" t="s">
         <v>48</v>
@@ -11202,7 +11202,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>1</v>
@@ -11214,17 +11214,17 @@
         <v>3</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H57" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>27</v>
@@ -11244,7 +11244,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>1</v>
@@ -11256,17 +11256,17 @@
         <v>7</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H58" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>49</v>
@@ -11286,7 +11286,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>1</v>
@@ -11298,17 +11298,17 @@
         <v>12</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H59" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>50</v>
@@ -11328,7 +11328,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>1</v>
@@ -11340,17 +11340,17 @@
         <v>3</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H60" s="3">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>51</v>
@@ -11370,7 +11370,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>1</v>
@@ -11382,17 +11382,17 @@
         <v>7</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H61" s="3">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>30</v>
@@ -11412,7 +11412,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>1</v>
@@ -11424,17 +11424,17 @@
         <v>12</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="H62" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="I62" s="7" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>52</v>
@@ -11454,7 +11454,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>31</v>
@@ -11466,17 +11466,17 @@
         <v>0</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H63" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="I63" s="7" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>32</v>
@@ -11496,7 +11496,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>31</v>
@@ -11508,17 +11508,17 @@
         <v>0</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H64" s="3">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J64" s="3" t="s">
         <v>16</v>
@@ -11538,38 +11538,38 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C65" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E65" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F65" s="7" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H65" s="3">
         <f t="shared" ref="H65:H112" si="2">LEN(F65)</f>
         <v>11</v>
       </c>
       <c r="I65" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="K65" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="J65" s="3" t="s">
+      <c r="L65" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="K65" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="L65" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="M65" s="3"/>
       <c r="N65" s="3"/>
@@ -11580,38 +11580,38 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C66" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E66" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F66" s="7" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H66" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J66" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="L66" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="M66" s="3"/>
       <c r="N66" s="3"/>
@@ -11622,38 +11622,38 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C67" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E67" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F67" s="7" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H67" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
@@ -11664,38 +11664,38 @@
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C68" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E68" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F68" s="7" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H68" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M68" s="3"/>
       <c r="N68" s="3"/>
@@ -11706,38 +11706,38 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C69" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F69" s="7" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="H69" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I69" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="K69" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="J69" s="3" t="s">
+      <c r="L69" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="K69" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="L69" s="3" t="s">
-        <v>179</v>
       </c>
       <c r="M69" s="3"/>
       <c r="N69" s="3"/>
@@ -11748,38 +11748,38 @@
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C70" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E70" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F70" s="7" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H70" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J70" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="L70" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="K70" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="L70" s="3" t="s">
-        <v>179</v>
       </c>
       <c r="M70" s="3"/>
       <c r="N70" s="3"/>
@@ -11790,38 +11790,38 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C71" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E71" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D71" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F71" s="7" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H71" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M71" s="3"/>
       <c r="N71" s="3"/>
@@ -11832,38 +11832,38 @@
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C72" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F72" s="7" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H72" s="3">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M72" s="3"/>
       <c r="N72" s="3"/>
@@ -11874,38 +11874,38 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C73" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E73" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D73" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F73" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H73" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M73" s="3"/>
       <c r="N73" s="3"/>
@@ -11916,38 +11916,38 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C74" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E74" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F74" s="7" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H74" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M74" s="3"/>
       <c r="N74" s="3"/>
@@ -11958,38 +11958,38 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C75" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E75" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F75" s="7" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H75" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M75" s="3"/>
       <c r="N75" s="3"/>
@@ -12000,38 +12000,38 @@
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C76" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E76" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F76" s="7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H76" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M76" s="3"/>
       <c r="N76" s="3"/>
@@ -12042,38 +12042,38 @@
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C77" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E77" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D77" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F77" s="7" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H77" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M77" s="3"/>
       <c r="N77" s="3"/>
@@ -12084,38 +12084,38 @@
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C78" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E78" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D78" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F78" s="7" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H78" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M78" s="3"/>
       <c r="N78" s="3"/>
@@ -12126,38 +12126,38 @@
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C79" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D79" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F79" s="7" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="H79" s="3">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M79" s="3"/>
       <c r="N79" s="3"/>
@@ -12168,38 +12168,38 @@
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C80" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E80" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D80" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F80" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="H80" s="3">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M80" s="3"/>
       <c r="N80" s="3"/>
@@ -12210,38 +12210,38 @@
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C81" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E81" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F81" s="7" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H81" s="3">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M81" s="3"/>
       <c r="N81" s="3"/>
@@ -12252,38 +12252,38 @@
         <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C82" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E82" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D82" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F82" s="7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="H82" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
@@ -12294,19 +12294,19 @@
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C83" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F83" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G83" s="5" t="s">
         <v>0</v>
@@ -12316,16 +12316,16 @@
         <v>11</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M83" s="3"/>
       <c r="N83" s="3"/>
@@ -12336,38 +12336,38 @@
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C84" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E84" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D84" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F84" s="7" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H84" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M84" s="3"/>
       <c r="N84" s="3"/>
@@ -12378,38 +12378,38 @@
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C85" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E85" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D85" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F85" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="H85" s="3">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M85" s="3"/>
       <c r="N85" s="3"/>
@@ -12420,38 +12420,38 @@
         <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C86" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E86" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D86" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F86" s="7" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="H86" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M86" s="3"/>
       <c r="N86" s="3"/>
@@ -12462,38 +12462,38 @@
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C87" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E87" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D87" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F87" s="7" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="H87" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I87" s="7" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M87" s="3"/>
       <c r="N87" s="3"/>
@@ -12504,38 +12504,38 @@
         <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C88" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E88" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D88" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F88" s="7" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H88" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M88" s="3"/>
       <c r="N88" s="3"/>
@@ -12546,38 +12546,38 @@
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C89" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E89" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F89" s="7" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="H89" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M89" s="3"/>
       <c r="N89" s="3"/>
@@ -12588,38 +12588,38 @@
         <v>89</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C90" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E90" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D90" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F90" s="7" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="H90" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J90" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="K90" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="L90" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="K90" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="L90" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
@@ -12630,38 +12630,38 @@
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C91" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E91" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F91" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="H91" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L91" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M91" s="3"/>
       <c r="N91" s="3"/>
@@ -12672,38 +12672,38 @@
         <v>91</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C92" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E92" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D92" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F92" s="7" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H92" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J92" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="L92" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="K92" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="L92" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="M92" s="3"/>
       <c r="N92" s="3"/>
@@ -12714,38 +12714,38 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C93" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E93" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D93" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F93" s="7" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="H93" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L93" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M93" s="3"/>
       <c r="N93" s="3"/>
@@ -12756,38 +12756,38 @@
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C94" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E94" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F94" s="7" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="H94" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L94" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M94" s="3"/>
       <c r="N94" s="3"/>
@@ -12798,38 +12798,38 @@
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C95" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E95" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D95" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F95" s="7" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H95" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
@@ -12840,38 +12840,38 @@
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C96" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E96" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F96" s="7" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="H96" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M96" s="3"/>
       <c r="N96" s="3"/>
@@ -12882,38 +12882,38 @@
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C97" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E97" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D97" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F97" s="7" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="H97" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M97" s="3"/>
       <c r="N97" s="3"/>
@@ -12924,38 +12924,38 @@
         <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C98" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E98" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D98" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F98" s="7" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="H98" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M98" s="3"/>
       <c r="N98" s="3"/>
@@ -12966,38 +12966,38 @@
         <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C99" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E99" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D99" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F99" s="7" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H99" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M99" s="3"/>
       <c r="N99" s="3"/>
@@ -13008,38 +13008,38 @@
         <v>99</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C100" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E100" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F100" s="7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H100" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M100" s="3"/>
       <c r="N100" s="3"/>
@@ -13050,38 +13050,38 @@
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C101" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E101" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F101" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H101" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M101" s="3"/>
       <c r="N101" s="3"/>
@@ -13092,38 +13092,38 @@
         <v>101</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C102" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E102" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F102" s="7" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H102" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M102" s="3"/>
       <c r="N102" s="3"/>
@@ -13134,38 +13134,38 @@
         <v>102</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C103" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E103" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D103" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F103" s="7" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H103" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M103" s="3"/>
       <c r="N103" s="3"/>
@@ -13176,38 +13176,38 @@
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C104" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E104" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D104" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F104" s="7" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H104" s="3">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L104" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M104" s="3"/>
       <c r="N104" s="3"/>
@@ -13218,38 +13218,38 @@
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C105" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E105" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D105" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F105" s="7" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="H105" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L105" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M105" s="3"/>
       <c r="N105" s="3"/>
@@ -13260,38 +13260,38 @@
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C106" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E106" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D106" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F106" s="7" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H106" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L106" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M106" s="3"/>
       <c r="N106" s="3"/>
@@ -13302,38 +13302,38 @@
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C107" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E107" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D107" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E107" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F107" s="7" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H107" s="3">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M107" s="3"/>
       <c r="N107" s="3"/>
@@ -13344,38 +13344,38 @@
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C108" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E108" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D108" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E108" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F108" s="7" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H108" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I108" s="7" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L108" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M108" s="3"/>
       <c r="N108" s="3"/>
@@ -13386,19 +13386,19 @@
         <v>108</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C109" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E109" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D109" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F109" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G109" s="5" t="s">
         <v>0</v>
@@ -13408,16 +13408,16 @@
         <v>11</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L109" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M109" s="3"/>
       <c r="N109" s="3"/>
@@ -13428,38 +13428,38 @@
         <v>109</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C110" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E110" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D110" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F110" s="7" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="H110" s="3">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L110" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M110" s="3"/>
       <c r="N110" s="3"/>
@@ -13470,38 +13470,38 @@
         <v>110</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C111" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E111" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D111" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F111" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H111" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I111" s="7" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M111" s="3"/>
       <c r="N111" s="3"/>
@@ -13512,38 +13512,38 @@
         <v>111</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C112" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E112" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D112" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="F112" s="7" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H112" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="I112" s="7" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="K112" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M112" s="3"/>
       <c r="N112" s="3"/>
@@ -13554,38 +13554,38 @@
         <v>112</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C113" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E113" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D113" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="E113" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F113" s="7" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="H113" s="7">
         <f t="shared" ref="H113:H118" si="3">LEN(F113)</f>
         <v>11</v>
       </c>
       <c r="I113" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J113" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="K113" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L113" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M113" s="3"/>
       <c r="N113" s="3"/>
@@ -13596,38 +13596,38 @@
         <v>113</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C114" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E114" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D114" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="E114" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F114" s="7" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="G114" s="7" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="H114" s="7">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="I114" s="7" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J114" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="K114" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L114" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M114" s="3"/>
       <c r="N114" s="3"/>
@@ -13638,38 +13638,38 @@
         <v>114</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C115" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E115" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D115" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="E115" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F115" s="7" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H115" s="7">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="I115" s="7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J115" s="7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="K115" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L115" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M115" s="3"/>
       <c r="N115" s="3"/>
@@ -13680,38 +13680,38 @@
         <v>115</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C116" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="E116" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D116" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="E116" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F116" s="7" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G116" s="7" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H116" s="7">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="I116" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J116" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K116" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L116" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M116" s="3"/>
       <c r="N116" s="3"/>
@@ -13722,38 +13722,38 @@
         <v>116</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C117" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="E117" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D117" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="E117" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F117" s="7" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H117" s="7">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="I117" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="J117" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K117" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L117" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M117" s="3"/>
       <c r="N117" s="3"/>
@@ -13764,38 +13764,38 @@
         <v>117</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C118" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E118" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D118" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E118" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F118" s="7" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="G118" s="7" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H118" s="7">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="I118" s="7" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J118" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K118" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L118" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M118" s="3"/>
       <c r="N118" s="3"/>
@@ -13806,10 +13806,10 @@
         <v>118</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D119" s="7" t="s">
         <v>0</v>
@@ -13818,7 +13818,7 @@
         <v>0</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="G119" s="7" t="s">
         <v>0</v>
@@ -13828,16 +13828,16 @@
         <v>10</v>
       </c>
       <c r="I119" s="7" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="J119" s="7" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="K119" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L119" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M119" s="3"/>
       <c r="N119" s="3"/>
@@ -13848,19 +13848,19 @@
         <v>119</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C120" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D120" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E120" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D120" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E120" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F120" s="7" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="G120" s="7" t="s">
         <v>0</v>
@@ -13870,16 +13870,16 @@
         <v>10</v>
       </c>
       <c r="I120" s="7" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="J120" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K120" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L120" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M120" s="3"/>
       <c r="N120" s="3"/>
@@ -13890,19 +13890,19 @@
         <v>120</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C121" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D121" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E121" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D121" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E121" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F121" s="7" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G121" s="7" t="s">
         <v>0</v>
@@ -13912,16 +13912,16 @@
         <v>12</v>
       </c>
       <c r="I121" s="7" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="J121" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K121" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L121" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M121" s="3"/>
       <c r="N121" s="3"/>
@@ -13932,19 +13932,19 @@
         <v>121</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C122" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E122" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D122" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E122" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F122" s="7" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="G122" s="7" t="s">
         <v>0</v>
@@ -13954,16 +13954,16 @@
         <v>11</v>
       </c>
       <c r="I122" s="7" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="J122" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K122" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L122" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M122" s="3"/>
       <c r="N122" s="3"/>
@@ -13974,19 +13974,19 @@
         <v>122</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C123" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E123" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D123" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E123" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F123" s="7" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="G123" s="7" t="s">
         <v>0</v>
@@ -13996,16 +13996,16 @@
         <v>11</v>
       </c>
       <c r="I123" s="7" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="J123" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K123" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L123" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M123" s="3"/>
       <c r="N123" s="3"/>
@@ -14016,19 +14016,19 @@
         <v>123</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C124" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D124" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E124" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D124" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E124" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F124" s="7" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="G124" s="7" t="s">
         <v>0</v>
@@ -14038,16 +14038,16 @@
         <v>9</v>
       </c>
       <c r="I124" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="J124" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K124" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L124" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M124" s="3"/>
       <c r="N124" s="3"/>
@@ -14058,19 +14058,19 @@
         <v>124</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C125" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E125" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D125" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E125" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F125" s="7" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="G125" s="7" t="s">
         <v>0</v>
@@ -14080,16 +14080,16 @@
         <v>11</v>
       </c>
       <c r="I125" s="7" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="J125" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K125" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L125" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M125" s="3"/>
       <c r="N125" s="3"/>
@@ -14100,19 +14100,19 @@
         <v>125</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C126" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E126" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D126" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E126" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F126" s="7" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="G126" s="7" t="s">
         <v>0</v>
@@ -14122,16 +14122,16 @@
         <v>10</v>
       </c>
       <c r="I126" s="7" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="J126" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K126" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L126" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M126" s="3"/>
       <c r="N126" s="3"/>
@@ -14142,19 +14142,19 @@
         <v>126</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C127" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E127" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D127" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="E127" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F127" s="7" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="G127" s="7" t="s">
         <v>0</v>
@@ -14164,16 +14164,16 @@
         <v>11</v>
       </c>
       <c r="I127" s="7" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="J127" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K127" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L127" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M127" s="3"/>
       <c r="N127" s="3"/>
@@ -14184,19 +14184,19 @@
         <v>127</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C128" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E128" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D128" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="E128" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F128" s="7" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="G128" s="7" t="s">
         <v>0</v>
@@ -14206,16 +14206,16 @@
         <v>12</v>
       </c>
       <c r="I128" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="J128" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="K128" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L128" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M128" s="3"/>
       <c r="N128" s="3"/>
@@ -14226,19 +14226,19 @@
         <v>128</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C129" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E129" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D129" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="E129" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F129" s="7" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="G129" s="7" t="s">
         <v>0</v>
@@ -14248,16 +14248,16 @@
         <v>9</v>
       </c>
       <c r="I129" s="7" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="J129" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="K129" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L129" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M129" s="3"/>
       <c r="N129" s="3"/>
@@ -14268,19 +14268,19 @@
         <v>129</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C130" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E130" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D130" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="E130" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F130" s="7" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G130" s="7" t="s">
         <v>0</v>
@@ -14290,16 +14290,16 @@
         <v>10</v>
       </c>
       <c r="I130" s="7" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J130" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="K130" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L130" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M130" s="3"/>
       <c r="N130" s="3"/>
@@ -14310,19 +14310,19 @@
         <v>130</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C131" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E131" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D131" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E131" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F131" s="7" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G131" s="7" t="s">
         <v>0</v>
@@ -14332,16 +14332,16 @@
         <v>11</v>
       </c>
       <c r="I131" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="J131" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K131" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L131" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M131" s="3"/>
       <c r="N131" s="3"/>
@@ -14352,19 +14352,19 @@
         <v>131</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C132" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E132" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D132" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E132" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F132" s="7" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="G132" s="7" t="s">
         <v>0</v>
@@ -14374,16 +14374,16 @@
         <v>10</v>
       </c>
       <c r="I132" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="J132" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K132" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L132" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M132" s="3"/>
       <c r="N132" s="3"/>
@@ -14394,19 +14394,19 @@
         <v>132</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C133" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E133" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D133" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E133" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F133" s="7" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="G133" s="7" t="s">
         <v>0</v>
@@ -14416,16 +14416,16 @@
         <v>9</v>
       </c>
       <c r="I133" s="7" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J133" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="K133" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L133" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M133" s="3"/>
       <c r="N133" s="3"/>
@@ -14436,19 +14436,19 @@
         <v>133</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C134" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E134" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D134" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E134" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F134" s="7" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="G134" s="7" t="s">
         <v>0</v>
@@ -14458,16 +14458,16 @@
         <v>12</v>
       </c>
       <c r="I134" s="7" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="J134" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K134" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L134" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M134" s="3"/>
       <c r="N134" s="3"/>
@@ -14478,19 +14478,19 @@
         <v>134</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C135" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E135" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D135" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="E135" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F135" s="7" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="G135" s="7" t="s">
         <v>0</v>
@@ -14500,16 +14500,16 @@
         <v>10</v>
       </c>
       <c r="I135" s="7" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="J135" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K135" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L135" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M135" s="3"/>
       <c r="N135" s="3"/>
@@ -14520,19 +14520,19 @@
         <v>135</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C136" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E136" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D136" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E136" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F136" s="7" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="G136" s="7" t="s">
         <v>0</v>
@@ -14542,16 +14542,16 @@
         <v>12</v>
       </c>
       <c r="I136" s="7" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="J136" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K136" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L136" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M136" s="3"/>
       <c r="N136" s="3"/>
@@ -14562,19 +14562,19 @@
         <v>136</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C137" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D137" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E137" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D137" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E137" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F137" s="7" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="G137" s="7" t="s">
         <v>0</v>
@@ -14584,16 +14584,16 @@
         <v>12</v>
       </c>
       <c r="I137" s="7" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="J137" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K137" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L137" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M137" s="3"/>
       <c r="N137" s="3"/>
@@ -14604,19 +14604,19 @@
         <v>137</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C138" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E138" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D138" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E138" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F138" s="7" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="G138" s="7" t="s">
         <v>0</v>
@@ -14626,16 +14626,16 @@
         <v>11</v>
       </c>
       <c r="I138" s="7" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="J138" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="K138" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L138" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M138" s="3"/>
       <c r="N138" s="3"/>
@@ -14646,19 +14646,19 @@
         <v>138</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C139" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E139" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D139" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E139" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F139" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G139" s="7" t="s">
         <v>0</v>
@@ -14668,16 +14668,16 @@
         <v>10</v>
       </c>
       <c r="I139" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="J139" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K139" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L139" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M139" s="3"/>
       <c r="N139" s="3"/>
@@ -14688,19 +14688,19 @@
         <v>139</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C140" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E140" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D140" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E140" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F140" s="7" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="G140" s="7" t="s">
         <v>0</v>
@@ -14710,16 +14710,16 @@
         <v>11</v>
       </c>
       <c r="I140" s="7" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J140" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K140" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L140" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M140" s="3"/>
       <c r="N140" s="3"/>
@@ -14730,19 +14730,19 @@
         <v>140</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C141" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D141" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E141" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D141" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E141" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F141" s="7" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="G141" s="7" t="s">
         <v>0</v>
@@ -14752,16 +14752,16 @@
         <v>9</v>
       </c>
       <c r="I141" s="7" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="J141" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K141" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L141" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M141" s="3"/>
       <c r="N141" s="3"/>
@@ -14772,19 +14772,19 @@
         <v>141</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C142" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E142" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D142" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E142" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F142" s="7" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="G142" s="7" t="s">
         <v>0</v>
@@ -14794,16 +14794,16 @@
         <v>11</v>
       </c>
       <c r="I142" s="7" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="J142" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K142" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L142" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M142" s="3"/>
       <c r="N142" s="3"/>
@@ -14814,19 +14814,19 @@
         <v>142</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C143" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E143" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D143" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E143" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F143" s="7" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="G143" s="7" t="s">
         <v>0</v>
@@ -14836,16 +14836,16 @@
         <v>10</v>
       </c>
       <c r="I143" s="7" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="J143" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K143" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L143" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M143" s="3"/>
       <c r="N143" s="3"/>
@@ -14856,19 +14856,19 @@
         <v>143</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C144" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="E144" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D144" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="E144" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F144" s="7" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="G144" s="7" t="s">
         <v>0</v>
@@ -14878,16 +14878,16 @@
         <v>9</v>
       </c>
       <c r="I144" s="7" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="J144" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K144" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L144" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M144" s="3"/>
       <c r="N144" s="3"/>
@@ -14898,19 +14898,19 @@
         <v>144</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C145" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="E145" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D145" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="E145" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F145" s="7" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="G145" s="7" t="s">
         <v>0</v>
@@ -14920,16 +14920,16 @@
         <v>9</v>
       </c>
       <c r="I145" s="7" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="J145" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K145" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L145" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M145" s="3"/>
       <c r="N145" s="3"/>
@@ -14940,19 +14940,19 @@
         <v>145</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C146" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="E146" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D146" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="E146" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F146" s="7" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="G146" s="7" t="s">
         <v>0</v>
@@ -14962,16 +14962,16 @@
         <v>11</v>
       </c>
       <c r="I146" s="7" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="J146" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K146" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L146" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M146" s="3"/>
       <c r="N146" s="3"/>
@@ -14982,19 +14982,19 @@
         <v>146</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C147" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E147" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D147" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="E147" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F147" s="7" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G147" s="7" t="s">
         <v>0</v>
@@ -15004,16 +15004,16 @@
         <v>9</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="J147" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K147" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L147" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M147" s="3"/>
       <c r="N147" s="3"/>
@@ -15024,19 +15024,19 @@
         <v>147</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C148" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E148" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D148" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="E148" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F148" s="7" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="G148" s="7" t="s">
         <v>0</v>
@@ -15046,16 +15046,16 @@
         <v>8</v>
       </c>
       <c r="I148" s="7" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="J148" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K148" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L148" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M148" s="3"/>
       <c r="N148" s="3"/>
@@ -15066,19 +15066,19 @@
         <v>148</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C149" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E149" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D149" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="E149" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F149" s="7" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="G149" s="7" t="s">
         <v>0</v>
@@ -15088,16 +15088,16 @@
         <v>11</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="J149" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="K149" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L149" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M149" s="3"/>
       <c r="N149" s="3"/>
@@ -15108,19 +15108,19 @@
         <v>149</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C150" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E150" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D150" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="E150" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F150" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="G150" s="7" t="s">
         <v>0</v>
@@ -15130,16 +15130,16 @@
         <v>9</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="J150" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="K150" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L150" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M150" s="3"/>
       <c r="N150" s="3"/>
@@ -15150,19 +15150,19 @@
         <v>150</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C151" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D151" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E151" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D151" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="E151" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F151" s="7" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="G151" s="7" t="s">
         <v>0</v>
@@ -15172,16 +15172,16 @@
         <v>11</v>
       </c>
       <c r="I151" s="7" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="J151" s="7" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="K151" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L151" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M151" s="3"/>
       <c r="N151" s="3"/>
@@ -15192,19 +15192,19 @@
         <v>151</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C152" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E152" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D152" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="E152" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F152" s="7" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="G152" s="7" t="s">
         <v>0</v>
@@ -15214,16 +15214,16 @@
         <v>11</v>
       </c>
       <c r="I152" s="7" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="J152" s="7" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="K152" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L152" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M152" s="3"/>
       <c r="N152" s="3"/>
@@ -15234,19 +15234,19 @@
         <v>152</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C153" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D153" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="E153" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D153" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="E153" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F153" s="7" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G153" s="7" t="s">
         <v>0</v>
@@ -15256,16 +15256,16 @@
         <v>12</v>
       </c>
       <c r="I153" s="7" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="J153" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K153" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L153" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M153" s="3"/>
       <c r="N153" s="3"/>
@@ -15276,19 +15276,19 @@
         <v>153</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C154" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D154" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="E154" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D154" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="E154" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F154" s="7" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G154" s="7" t="s">
         <v>0</v>
@@ -15298,16 +15298,16 @@
         <v>9</v>
       </c>
       <c r="I154" s="7" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="J154" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K154" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L154" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M154" s="3"/>
       <c r="N154" s="3"/>
@@ -15318,19 +15318,19 @@
         <v>154</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C155" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D155" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="E155" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D155" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="E155" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F155" s="7" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="G155" s="7" t="s">
         <v>0</v>
@@ -15340,16 +15340,16 @@
         <v>11</v>
       </c>
       <c r="I155" s="7" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="J155" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K155" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L155" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M155" s="3"/>
       <c r="N155" s="3"/>
@@ -15360,19 +15360,19 @@
         <v>155</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C156" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D156" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E156" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D156" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E156" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F156" s="7" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="G156" s="7" t="s">
         <v>0</v>
@@ -15382,16 +15382,16 @@
         <v>10</v>
       </c>
       <c r="I156" s="7" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="J156" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K156" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L156" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M156" s="3"/>
       <c r="N156" s="3"/>
@@ -15402,19 +15402,19 @@
         <v>156</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C157" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D157" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E157" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D157" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E157" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F157" s="7" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G157" s="7" t="s">
         <v>0</v>
@@ -15424,16 +15424,16 @@
         <v>10</v>
       </c>
       <c r="I157" s="7" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="J157" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K157" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L157" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M157" s="3"/>
       <c r="N157" s="3"/>
@@ -15444,19 +15444,19 @@
         <v>157</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C158" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D158" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E158" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D158" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E158" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F158" s="7" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="G158" s="7" t="s">
         <v>0</v>
@@ -15466,16 +15466,16 @@
         <v>10</v>
       </c>
       <c r="I158" s="7" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="J158" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K158" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L158" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M158" s="3"/>
       <c r="N158" s="3"/>
@@ -15486,19 +15486,19 @@
         <v>158</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C159" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D159" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E159" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D159" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E159" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F159" s="7" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="G159" s="7" t="s">
         <v>0</v>
@@ -15508,16 +15508,16 @@
         <v>10</v>
       </c>
       <c r="I159" s="7" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="J159" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K159" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L159" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M159" s="3"/>
       <c r="N159" s="3"/>
@@ -15528,19 +15528,19 @@
         <v>159</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C160" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D160" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E160" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D160" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E160" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F160" s="7" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="G160" s="7" t="s">
         <v>0</v>
@@ -15550,16 +15550,16 @@
         <v>10</v>
       </c>
       <c r="I160" s="7" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="J160" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K160" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L160" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M160" s="3"/>
       <c r="N160" s="3"/>
@@ -15570,19 +15570,19 @@
         <v>160</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C161" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D161" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E161" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D161" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E161" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F161" s="7" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G161" s="7" t="s">
         <v>0</v>
@@ -15592,16 +15592,16 @@
         <v>10</v>
       </c>
       <c r="I161" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="J161" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K161" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L161" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M161" s="3"/>
       <c r="N161" s="3"/>
@@ -15612,19 +15612,19 @@
         <v>161</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C162" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D162" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E162" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D162" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E162" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F162" s="7" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="G162" s="7" t="s">
         <v>0</v>
@@ -15634,16 +15634,16 @@
         <v>10</v>
       </c>
       <c r="I162" s="7" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="J162" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K162" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L162" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M162" s="3"/>
       <c r="N162" s="3"/>
@@ -15654,19 +15654,19 @@
         <v>162</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C163" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D163" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E163" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D163" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E163" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F163" s="7" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="G163" s="7" t="s">
         <v>0</v>
@@ -15676,16 +15676,16 @@
         <v>10</v>
       </c>
       <c r="I163" s="7" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="J163" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K163" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L163" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M163" s="3"/>
       <c r="N163" s="3"/>
@@ -15696,19 +15696,19 @@
         <v>163</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C164" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D164" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E164" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D164" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E164" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F164" s="7" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="G164" s="7" t="s">
         <v>0</v>
@@ -15718,16 +15718,16 @@
         <v>11</v>
       </c>
       <c r="I164" s="7" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="J164" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K164" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L164" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M164" s="3"/>
       <c r="N164" s="3"/>
@@ -15738,19 +15738,19 @@
         <v>164</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C165" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D165" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E165" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D165" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E165" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F165" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="G165" s="7" t="s">
         <v>0</v>
@@ -15760,16 +15760,16 @@
         <v>10</v>
       </c>
       <c r="I165" s="7" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="J165" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K165" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L165" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M165" s="3"/>
       <c r="N165" s="3"/>
@@ -15780,19 +15780,19 @@
         <v>165</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C166" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D166" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E166" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D166" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E166" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F166" s="7" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="G166" s="7" t="s">
         <v>0</v>
@@ -15802,16 +15802,16 @@
         <v>10</v>
       </c>
       <c r="I166" s="7" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J166" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K166" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L166" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M166" s="3"/>
       <c r="N166" s="3"/>
@@ -15822,19 +15822,19 @@
         <v>166</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C167" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D167" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E167" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D167" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E167" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F167" s="7" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="G167" s="7" t="s">
         <v>0</v>
@@ -15844,16 +15844,16 @@
         <v>9</v>
       </c>
       <c r="I167" s="7" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="J167" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K167" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L167" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M167" s="3"/>
       <c r="N167" s="3"/>
@@ -15864,19 +15864,19 @@
         <v>167</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C168" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D168" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E168" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D168" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E168" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F168" s="7" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="G168" s="7" t="s">
         <v>0</v>
@@ -15886,16 +15886,16 @@
         <v>12</v>
       </c>
       <c r="I168" s="7" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="J168" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K168" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L168" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M168" s="3"/>
       <c r="N168" s="3"/>
@@ -15906,19 +15906,19 @@
         <v>168</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C169" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D169" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E169" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D169" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E169" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F169" s="7" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G169" s="7" t="s">
         <v>0</v>
@@ -15928,16 +15928,16 @@
         <v>11</v>
       </c>
       <c r="I169" s="7" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="J169" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K169" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L169" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M169" s="3"/>
       <c r="N169" s="3"/>
@@ -15948,19 +15948,19 @@
         <v>169</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C170" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D170" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E170" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D170" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E170" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F170" s="7" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G170" s="7" t="s">
         <v>0</v>
@@ -15970,16 +15970,16 @@
         <v>11</v>
       </c>
       <c r="I170" s="7" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="J170" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K170" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L170" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M170" s="3"/>
       <c r="N170" s="3"/>
@@ -15990,19 +15990,19 @@
         <v>170</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C171" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D171" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E171" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D171" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E171" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F171" s="7" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G171" s="7" t="s">
         <v>0</v>
@@ -16012,20 +16012,20 @@
         <v>10</v>
       </c>
       <c r="I171" s="7" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="J171" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K171" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L171" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M171" s="3"/>
       <c r="N171" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="O171" s="3"/>
     </row>
@@ -16034,19 +16034,19 @@
         <v>171</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C172" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D172" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E172" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D172" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E172" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F172" s="7" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G172" s="7" t="s">
         <v>0</v>
@@ -16056,20 +16056,20 @@
         <v>10</v>
       </c>
       <c r="I172" s="7" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="J172" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K172" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L172" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M172" s="3"/>
       <c r="N172" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="O172" s="3"/>
     </row>
@@ -16078,19 +16078,19 @@
         <v>172</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C173" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D173" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E173" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D173" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E173" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F173" s="7" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="G173" s="7" t="s">
         <v>0</v>
@@ -16100,20 +16100,20 @@
         <v>10</v>
       </c>
       <c r="I173" s="7" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="J173" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K173" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L173" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M173" s="3"/>
       <c r="N173" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="O173" s="3"/>
     </row>
@@ -16122,19 +16122,19 @@
         <v>173</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C174" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E174" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D174" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E174" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F174" s="7" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="G174" s="7" t="s">
         <v>0</v>
@@ -16144,20 +16144,20 @@
         <v>12</v>
       </c>
       <c r="I174" s="7" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J174" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K174" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L174" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M174" s="3"/>
       <c r="N174" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="O174" s="3"/>
     </row>
@@ -16166,19 +16166,19 @@
         <v>174</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C175" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D175" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E175" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D175" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E175" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F175" s="7" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="G175" s="7" t="s">
         <v>0</v>
@@ -16188,20 +16188,20 @@
         <v>10</v>
       </c>
       <c r="I175" s="7" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="J175" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K175" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L175" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M175" s="3"/>
       <c r="N175" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="O175" s="3"/>
     </row>
@@ -16210,19 +16210,19 @@
         <v>175</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C176" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D176" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E176" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D176" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E176" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F176" s="7" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="G176" s="7" t="s">
         <v>0</v>
@@ -16232,20 +16232,20 @@
         <v>10</v>
       </c>
       <c r="I176" s="7" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="J176" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K176" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L176" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M176" s="3"/>
       <c r="N176" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="O176" s="3"/>
     </row>
@@ -16254,19 +16254,19 @@
         <v>176</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C177" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D177" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E177" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D177" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E177" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F177" s="7" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="G177" s="7" t="s">
         <v>0</v>
@@ -16276,20 +16276,20 @@
         <v>12</v>
       </c>
       <c r="I177" s="7" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="J177" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K177" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L177" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M177" s="3"/>
       <c r="N177" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="O177" s="3"/>
     </row>
@@ -16298,19 +16298,19 @@
         <v>177</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C178" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D178" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E178" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D178" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E178" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F178" s="7" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="G178" s="7" t="s">
         <v>0</v>
@@ -16320,20 +16320,20 @@
         <v>9</v>
       </c>
       <c r="I178" s="7" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="J178" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K178" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L178" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M178" s="3"/>
       <c r="N178" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="O178" s="3"/>
     </row>
@@ -16342,19 +16342,19 @@
         <v>178</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C179" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D179" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E179" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D179" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="E179" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F179" s="7" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="G179" s="7" t="s">
         <v>0</v>
@@ -16364,16 +16364,16 @@
         <v>11</v>
       </c>
       <c r="I179" s="7" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="J179" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="K179" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L179" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M179" s="3"/>
       <c r="N179" s="3"/>
@@ -16384,19 +16384,19 @@
         <v>179</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C180" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D180" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E180" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D180" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="E180" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F180" s="7" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="G180" s="7" t="s">
         <v>0</v>
@@ -16406,16 +16406,16 @@
         <v>11</v>
       </c>
       <c r="I180" s="7" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="J180" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="K180" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L180" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M180" s="3"/>
       <c r="N180" s="3"/>
@@ -16426,19 +16426,19 @@
         <v>180</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C181" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D181" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E181" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D181" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="E181" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F181" s="7" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="G181" s="7" t="s">
         <v>0</v>
@@ -16448,16 +16448,16 @@
         <v>11</v>
       </c>
       <c r="I181" s="7" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="J181" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="K181" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L181" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M181" s="3"/>
       <c r="N181" s="3"/>
@@ -16468,19 +16468,19 @@
         <v>181</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C182" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D182" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E182" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D182" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="E182" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F182" s="7" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G182" s="7" t="s">
         <v>0</v>
@@ -16490,16 +16490,16 @@
         <v>11</v>
       </c>
       <c r="I182" s="7" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="J182" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="K182" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L182" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M182" s="3"/>
       <c r="N182" s="3"/>
@@ -16510,19 +16510,19 @@
         <v>182</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C183" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D183" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E183" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D183" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="E183" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F183" s="7" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="G183" s="7" t="s">
         <v>0</v>
@@ -16532,16 +16532,16 @@
         <v>9</v>
       </c>
       <c r="I183" s="7" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="J183" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="K183" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L183" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M183" s="3"/>
       <c r="N183" s="3"/>
@@ -16552,19 +16552,19 @@
         <v>183</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C184" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D184" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E184" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D184" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="E184" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F184" s="7" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="G184" s="7" t="s">
         <v>0</v>
@@ -16574,16 +16574,16 @@
         <v>11</v>
       </c>
       <c r="I184" s="7" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="J184" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="K184" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L184" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M184" s="3"/>
       <c r="N184" s="3"/>
@@ -16594,19 +16594,19 @@
         <v>184</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C185" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D185" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E185" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D185" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="E185" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F185" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G185" s="7" t="s">
         <v>0</v>
@@ -16616,16 +16616,16 @@
         <v>12</v>
       </c>
       <c r="I185" s="7" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="J185" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="K185" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L185" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M185" s="3"/>
       <c r="N185" s="3"/>
@@ -16636,19 +16636,19 @@
         <v>185</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C186" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D186" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E186" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D186" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E186" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F186" s="7" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="G186" s="7" t="s">
         <v>0</v>
@@ -16658,20 +16658,20 @@
         <v>11</v>
       </c>
       <c r="I186" s="7" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="J186" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K186" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L186" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M186" s="3"/>
       <c r="N186" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="O186" s="3"/>
     </row>
@@ -16680,19 +16680,19 @@
         <v>186</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C187" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D187" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E187" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D187" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E187" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F187" s="7" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="G187" s="7" t="s">
         <v>0</v>
@@ -16702,20 +16702,20 @@
         <v>11</v>
       </c>
       <c r="I187" s="7" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="J187" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K187" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L187" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M187" s="3"/>
       <c r="N187" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="O187" s="3"/>
     </row>
@@ -16724,19 +16724,19 @@
         <v>187</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C188" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D188" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E188" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D188" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E188" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F188" s="7" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="G188" s="7" t="s">
         <v>0</v>
@@ -16746,20 +16746,20 @@
         <v>11</v>
       </c>
       <c r="I188" s="7" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="J188" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K188" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L188" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M188" s="3"/>
       <c r="N188" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="O188" s="3"/>
     </row>
@@ -16768,19 +16768,19 @@
         <v>188</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C189" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D189" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E189" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D189" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E189" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F189" s="7" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G189" s="7" t="s">
         <v>0</v>
@@ -16790,20 +16790,20 @@
         <v>12</v>
       </c>
       <c r="I189" s="7" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="J189" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K189" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L189" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M189" s="3"/>
       <c r="N189" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="O189" s="3"/>
     </row>
@@ -16812,19 +16812,19 @@
         <v>189</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C190" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D190" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E190" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D190" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E190" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F190" s="7" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="G190" s="7" t="s">
         <v>0</v>
@@ -16834,20 +16834,20 @@
         <v>10</v>
       </c>
       <c r="I190" s="7" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="J190" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K190" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L190" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M190" s="3"/>
       <c r="N190" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="O190" s="3"/>
     </row>
@@ -16856,19 +16856,19 @@
         <v>190</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C191" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D191" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E191" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D191" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E191" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F191" s="7" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="G191" s="7" t="s">
         <v>0</v>
@@ -16878,20 +16878,20 @@
         <v>11</v>
       </c>
       <c r="I191" s="7" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="J191" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K191" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L191" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M191" s="3"/>
       <c r="N191" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="O191" s="3"/>
     </row>
@@ -16900,19 +16900,19 @@
         <v>191</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C192" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D192" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E192" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D192" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E192" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F192" s="7" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="G192" s="7" t="s">
         <v>0</v>
@@ -16922,20 +16922,20 @@
         <v>10</v>
       </c>
       <c r="I192" s="7" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="J192" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K192" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L192" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M192" s="3"/>
       <c r="N192" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="O192" s="3"/>
     </row>
@@ -16944,19 +16944,19 @@
         <v>192</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C193" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D193" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E193" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D193" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E193" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F193" s="7" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G193" s="7" t="s">
         <v>0</v>
@@ -16966,20 +16966,20 @@
         <v>12</v>
       </c>
       <c r="I193" s="7" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="J193" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K193" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L193" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M193" s="3"/>
       <c r="N193" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="O193" s="3"/>
     </row>
@@ -16988,19 +16988,19 @@
         <v>193</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C194" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D194" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E194" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D194" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E194" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F194" s="7" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="G194" s="7" t="s">
         <v>0</v>
@@ -17010,16 +17010,16 @@
         <v>12</v>
       </c>
       <c r="I194" s="7" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="J194" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K194" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L194" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M194" s="3"/>
       <c r="N194" s="3"/>
@@ -17030,19 +17030,19 @@
         <v>194</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C195" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D195" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E195" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D195" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E195" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F195" s="7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="G195" s="7" t="s">
         <v>0</v>
@@ -17052,16 +17052,16 @@
         <v>11</v>
       </c>
       <c r="I195" s="7" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="J195" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K195" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L195" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M195" s="3"/>
       <c r="N195" s="3"/>
@@ -17072,19 +17072,19 @@
         <v>195</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C196" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D196" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E196" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D196" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E196" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F196" s="7" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G196" s="7" t="s">
         <v>0</v>
@@ -17094,16 +17094,16 @@
         <v>10</v>
       </c>
       <c r="I196" s="7" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="J196" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K196" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L196" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M196" s="3"/>
       <c r="N196" s="3"/>
@@ -17114,19 +17114,19 @@
         <v>196</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C197" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D197" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E197" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D197" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E197" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F197" s="7" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G197" s="7" t="s">
         <v>0</v>
@@ -17136,16 +17136,16 @@
         <v>11</v>
       </c>
       <c r="I197" s="7" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="J197" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K197" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L197" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M197" s="3"/>
       <c r="N197" s="3"/>
@@ -17156,19 +17156,19 @@
         <v>197</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C198" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D198" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E198" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D198" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E198" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F198" s="7" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="G198" s="7" t="s">
         <v>0</v>
@@ -17178,16 +17178,16 @@
         <v>11</v>
       </c>
       <c r="I198" s="7" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="J198" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K198" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L198" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M198" s="3"/>
       <c r="N198" s="3"/>
@@ -17198,19 +17198,19 @@
         <v>198</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C199" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D199" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E199" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D199" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E199" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F199" s="7" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G199" s="7" t="s">
         <v>0</v>
@@ -17220,16 +17220,16 @@
         <v>12</v>
       </c>
       <c r="I199" s="7" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="J199" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K199" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L199" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M199" s="3"/>
       <c r="N199" s="3"/>
@@ -17240,19 +17240,19 @@
         <v>199</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C200" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D200" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E200" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D200" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E200" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F200" s="7" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G200" s="7" t="s">
         <v>0</v>
@@ -17262,16 +17262,16 @@
         <v>12</v>
       </c>
       <c r="I200" s="7" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="J200" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K200" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L200" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M200" s="3"/>
       <c r="N200" s="3"/>
@@ -17282,19 +17282,19 @@
         <v>200</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C201" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D201" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E201" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D201" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E201" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F201" s="7" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G201" s="7" t="s">
         <v>0</v>
@@ -17304,16 +17304,16 @@
         <v>12</v>
       </c>
       <c r="I201" s="7" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="J201" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K201" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L201" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M201" s="3"/>
       <c r="N201" s="3"/>
@@ -17324,19 +17324,19 @@
         <v>201</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C202" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D202" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E202" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D202" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E202" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F202" s="7" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="G202" s="7" t="s">
         <v>0</v>
@@ -17346,16 +17346,16 @@
         <v>11</v>
       </c>
       <c r="I202" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J202" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K202" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L202" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M202" s="3"/>
       <c r="N202" s="3"/>
@@ -17366,19 +17366,19 @@
         <v>202</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C203" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D203" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E203" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D203" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E203" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F203" s="7" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G203" s="7" t="s">
         <v>0</v>
@@ -17388,16 +17388,16 @@
         <v>11</v>
       </c>
       <c r="I203" s="7" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="J203" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K203" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L203" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M203" s="3"/>
       <c r="N203" s="3"/>
@@ -17408,19 +17408,19 @@
         <v>203</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C204" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D204" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E204" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D204" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E204" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F204" s="7" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="G204" s="7" t="s">
         <v>0</v>
@@ -17430,16 +17430,16 @@
         <v>10</v>
       </c>
       <c r="I204" s="7" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="J204" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K204" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L204" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M204" s="3"/>
       <c r="N204" s="3"/>
@@ -17450,19 +17450,19 @@
         <v>204</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C205" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D205" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E205" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D205" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="E205" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F205" s="7" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="G205" s="7" t="s">
         <v>0</v>
@@ -17472,16 +17472,16 @@
         <v>12</v>
       </c>
       <c r="I205" s="7" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="J205" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K205" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L205" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M205" s="3"/>
       <c r="N205" s="3"/>
@@ -17492,19 +17492,19 @@
         <v>205</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C206" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D206" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E206" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D206" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="E206" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F206" s="7" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="G206" s="7" t="s">
         <v>0</v>
@@ -17514,16 +17514,16 @@
         <v>11</v>
       </c>
       <c r="I206" s="7" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="J206" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K206" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L206" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M206" s="3"/>
       <c r="N206" s="3"/>
@@ -17534,19 +17534,19 @@
         <v>206</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C207" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D207" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E207" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D207" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="E207" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="F207" s="7" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G207" s="7" t="s">
         <v>0</v>
@@ -17556,16 +17556,16 @@
         <v>11</v>
       </c>
       <c r="I207" s="7" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="J207" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K207" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L207" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M207" s="3"/>
       <c r="N207" s="3"/>
@@ -17602,25 +17602,25 @@
   <sheetData>
     <row r="1" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>54</v>
       </c>
       <c r="C1" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>438</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="F1" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>439</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>440</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>439</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>441</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>60</v>
@@ -17631,142 +17631,142 @@
     </row>
     <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A2" s="9" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D2" s="9">
         <f>LEN(C2)</f>
         <v>14</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="F2" s="9">
         <f>LEN(E2)</f>
         <v>10</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
     </row>
     <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A3" s="9" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D3" s="9">
         <f>LEN(C3)</f>
         <v>13</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="F3" s="9">
         <f>LEN(E3)</f>
         <v>11</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
     </row>
     <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A4" s="9" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D4" s="9">
         <f>LEN(C4)</f>
         <v>14</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F4" s="9">
         <f>LEN(E4)</f>
         <v>10</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
     </row>
     <row r="5" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A5" s="9" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D5" s="9">
         <f>LEN(C5)</f>
         <v>15</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F5" s="9">
         <f>LEN(E5)</f>
         <v>12</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
     <row r="6" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A6" s="9" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D6" s="9">
         <f>LEN(C6)</f>
         <v>13</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F6" s="9">
         <f>LEN(E6)</f>
         <v>10</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD249BB1-627E-4C4A-A5D0-6265702D61F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3908E836-0345-401F-898F-94A9B4F0AB93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -8148,14 +8148,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>밤 9시 후엔 주방 닫기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>한 숟갈마다 10초 쉬기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>숟가락을 놓고 쉬면 천천히 먹게 돼요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8253,6 +8245,14 @@
   </si>
   <si>
     <t>10-12 숫자로 구체화: 막연한 문구  사용자가 직접 셀 수 있는 숫자 표현으로 바꿈(예: 저녁 일찍 마치기 → 저녁은 7시 전에, 한 입에 30번 씹기)</t>
+  </si>
+  <si>
+    <t>9시 후엔 주방 닫기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한 입마다 10초 쉬기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -8823,7 +8823,7 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
   </sheetData>
@@ -9086,7 +9086,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>238</v>
@@ -9096,7 +9096,7 @@
         <v>12</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -9338,14 +9338,14 @@
         <v>220</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>662</v>
+        <v>687</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>244</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>90</v>
@@ -9506,7 +9506,7 @@
         <v>220</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>248</v>
@@ -9516,7 +9516,7 @@
         <v>11</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>27</v>
@@ -9884,7 +9884,7 @@
         <v>220</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>257</v>
@@ -9894,7 +9894,7 @@
         <v>12</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>11</v>
@@ -10808,7 +10808,7 @@
         <v>12</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>279</v>
@@ -10818,7 +10818,7 @@
         <v>12</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>43</v>
@@ -11060,7 +11060,7 @@
         <v>12</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>285</v>
@@ -11270,7 +11270,7 @@
         <v>7</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>290</v>
@@ -11280,7 +11280,7 @@
         <v>10</v>
       </c>
       <c r="I58" s="7" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>49</v>
@@ -11564,7 +11564,7 @@
         <v>146</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="G65" s="5" t="s">
         <v>296</v>
@@ -11574,7 +11574,7 @@
         <v>10</v>
       </c>
       <c r="I65" s="7" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>147</v>
@@ -11648,7 +11648,7 @@
         <v>146</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>299</v>
@@ -11658,7 +11658,7 @@
         <v>12</v>
       </c>
       <c r="I67" s="7" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J67" s="3" t="s">
         <v>151</v>
@@ -12404,7 +12404,7 @@
         <v>146</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="G85" s="5" t="s">
         <v>332</v>
@@ -12414,7 +12414,7 @@
         <v>11</v>
       </c>
       <c r="I85" s="7" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="J85" s="3" t="s">
         <v>187</v>
@@ -12782,7 +12782,7 @@
         <v>146</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="G94" s="5" t="s">
         <v>346</v>
@@ -12792,7 +12792,7 @@
         <v>12</v>
       </c>
       <c r="I94" s="7" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>198</v>
@@ -12824,17 +12824,17 @@
         <v>146</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>663</v>
+        <v>688</v>
       </c>
       <c r="G95" s="5" t="s">
         <v>347</v>
       </c>
       <c r="H95" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I95" s="7" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="J95" s="3" t="s">
         <v>200</v>
@@ -13202,7 +13202,7 @@
         <v>146</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="G104" s="5" t="s">
         <v>362</v>
@@ -13212,7 +13212,7 @@
         <v>9</v>
       </c>
       <c r="I104" s="7" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="J104" s="3" t="s">
         <v>210</v>
@@ -13454,7 +13454,7 @@
         <v>146</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="G110" s="5" t="s">
         <v>462</v>
@@ -13464,7 +13464,7 @@
         <v>10</v>
       </c>
       <c r="I110" s="7" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="J110" s="3" t="s">
         <v>216</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3908E836-0345-401F-898F-94A9B4F0AB93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E34DA0-97F9-4BBB-98D8-D185EAF3A241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="기존 문구 수정" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'추가 문구'!$A$1:$O$207</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'추가 문구'!$A$1:$O$177</definedName>
   </definedNames>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2142" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1827" uniqueCount="630">
   <si>
     <t>—</t>
   </si>
@@ -7533,105 +7533,18 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>아침 추천: 누룽지</t>
-  </si>
-  <si>
     <t>따뜻한 누룽지는 아침에 부담 없이 먹기 좋아요.</t>
   </si>
   <si>
     <t>오전(04~10시)</t>
   </si>
   <si>
-    <t>아침 추천: 찐 고구마</t>
-  </si>
-  <si>
-    <t>찐 고구마는 든든하고 준비가 간단해요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 달걀말이</t>
-  </si>
-  <si>
-    <t>달걀말이로 아침 단백질을 챙길 수 있어요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 두부부침</t>
-  </si>
-  <si>
-    <t>두부부침은 부드러운 단백질 반찬이에요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 두유</t>
-  </si>
-  <si>
-    <t>두유 한 잔으로 간편하게 단백질을 더해요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 시금치국</t>
-  </si>
-  <si>
-    <t>시금치국으로 아침에도 채소를 먹어요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 비빔밥</t>
-  </si>
-  <si>
-    <t>비빔밥은 나물을 넉넉히 먹을 수 있어요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 맑은 국</t>
-  </si>
-  <si>
     <t>맑은 국은 찌개보다 덜 짜서 아침에 좋아요.</t>
   </si>
   <si>
-    <t>저녁 추천: 고등어구이</t>
-  </si>
-  <si>
-    <t>고등어구이는 튀김보다 기름이 덜 들어가요.</t>
-  </si>
-  <si>
     <t>오후(12~17시)</t>
   </si>
   <si>
-    <t>저녁 추천: 수육</t>
-  </si>
-  <si>
-    <t>삶은 수육은 구운 고기보다 기름이 덜해요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 닭백숙</t>
-  </si>
-  <si>
-    <t>저녁 추천: 두부조림</t>
-  </si>
-  <si>
-    <t>두부조림은 손쉬운 단백질 반찬이에요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 달걀찜</t>
-  </si>
-  <si>
-    <t>달걀찜은 부드럽고 기름 없이 만들어요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 쌈밥</t>
-  </si>
-  <si>
-    <t>쌈밥은 채소를 듬뿍 먹을 수 있어요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 나물 반찬</t>
-  </si>
-  <si>
-    <t>나물 반찬 하나로 저녁 채소가 채워져요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 생선찜</t>
-  </si>
-  <si>
-    <t>생선찜은 찌개보다 국물이 적고 덜 짜요.</t>
-  </si>
-  <si>
     <t>아침엔 누룽지 한 그릇</t>
   </si>
   <si>
@@ -7746,513 +7659,425 @@
     <t>작은 공기에 담으면 양을 가늠하기 쉬워요.</t>
   </si>
   <si>
+    <t>10-12 상황 전제 규칙(편의점·외식)에 걸린 4개 수정 · 6차 새 표현 20개 · 7차 끼니 추천 16개(아침 추천 8은 04~10시, 저녁 추천 8은 12~17시 — 있는 시간 조건만 사용) 추가. 합계 154개</t>
+  </si>
+  <si>
+    <t>끼니 추천</t>
+  </si>
+  <si>
+    <t>묶음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁·새벽 문구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입문 보강</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부담 줄이기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새 표현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10-12 끼니 추천 확대: 아침 추천 (04~10시) · 저녁 추천 (12~17시). 「묶음」 열은 검수할 때 신경 쓰지 않아도 되는 분류. 합계 206개</t>
+  </si>
+  <si>
+    <t>한 입에 30번 씹기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>꼭꼭 씹으면 천천히 먹게 되고 배부름도 빨리 느껴요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>언제나(낮 포함)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아니오</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입맛 있을 때 먹어 두기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입맛이 돌 때 먹어 두면 하루 식사를 채우기 쉬워요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁은 7시 전에</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁을 일찍 마치면 속이 편하게 잠들 수 있어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁 8시까지 마치기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>늦은 시간까지 먹지 않으면 속이 편해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밥은 15분 넘게 먹기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15분 넘게 먹으면 배부름을 느낄 시간이 생겨요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>숟가락을 놓고 쉬면 천천히 먹게 돼요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>점심 채소 반찬 2가지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>채소 반찬을 두 가지로 늘리면 한 끼 채소가 넉넉해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주 3일 단 음료 쉬기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쉬는 날을 정하면 단 음료를 줄이기 쉬워요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁은 매일 7시쯤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4시간마다 끼니 챙기기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>끼니 사이가 너무 길지 않으면 과식을 막기 쉬워요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>점심 알림 12시로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>알림을 맞춰 두면 바쁜 날에도 점심을 놓치지 않아요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소스는 한 번만 찍기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한 번만 찍어도 맛은 충분해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>샐러드 소스 1스푼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소스를 한 스푼만 쓰면 기름과 염분이 줄어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밤 11시 전 잠자리에</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일찍 자면 야식 생각이 줄어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제철 채소 2가지 사기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제철 채소는 맛있고 값도 부담이 적어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주 2회 생선 먹기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생선은 일주일에 두 번쯤 먹기를 권해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달걀 한 판 사 두기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달걀이 있으면 끼니마다 단백질을 챙기기 쉬워요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국에 두부 반 모</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>두부를 넣으면 국 한 그릇에 단백질이 더해져요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10-12 숫자로 구체화: 막연한 문구  사용자가 직접 셀 수 있는 숫자 표현으로 바꿈(예: 저녁 일찍 마치기 → 저녁은 7시 전에, 한 입에 30번 씹기)</t>
+  </si>
+  <si>
+    <t>9시 후엔 주방 닫기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한 입마다 10초 쉬기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>국수는 천천히 후루룩</t>
-  </si>
-  <si>
-    <t>면은 천천히 먹어야 배부름을 느끼기 쉬워요.</t>
-  </si>
-  <si>
-    <t>10-12 상황 전제 규칙(편의점·외식)에 걸린 4개 수정 · 6차 새 표현 20개 · 7차 끼니 추천 16개(아침 추천 8은 04~10시, 저녁 추천 8은 12~17시 — 있는 시간 조건만 사용) 추가. 합계 154개</t>
-  </si>
-  <si>
-    <t>끼니 추천</t>
-  </si>
-  <si>
-    <t>아침 추천: 달걀죽</t>
-  </si>
-  <si>
-    <t>부드러운 달걀죽은 아침에 넘기기 편해요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 채소죽</t>
-  </si>
-  <si>
-    <t>채소죽 한 그릇이면 아침과 채소를 함께 챙겨요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 전복죽</t>
-  </si>
-  <si>
-    <t>전복죽은 속이 편한 든든한 아침이에요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 오트밀</t>
-  </si>
-  <si>
-    <t>오트밀은 금방 만들 수 있는 아침이에요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 잡곡밥</t>
-  </si>
-  <si>
-    <t>잡곡밥은 오래 든든한 아침이에요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 현미밥</t>
-  </si>
-  <si>
-    <t>현미밥은 천천히 소화돼 든든해요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 통밀빵</t>
-  </si>
-  <si>
-    <t>통밀빵은 흰 빵보다 오래 든든해요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 미역국</t>
-  </si>
-  <si>
-    <t>미역국으로 아침에 해조류를 더해요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 콩나물국</t>
-  </si>
-  <si>
-    <t>콩나물국으로 아침에도 채소를 먹어요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 배춧국</t>
-  </si>
-  <si>
-    <t>배춧국은 부드러워 아침에 먹기 좋아요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 아욱국</t>
-  </si>
-  <si>
-    <t>아욱국으로 아침 채소를 챙겨요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 뭇국</t>
-  </si>
-  <si>
-    <t>뭇국은 담백해서 아침에 부담이 없어요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 두부된장국</t>
-  </si>
-  <si>
-    <t>두부와 채소를 한 그릇에 챙겨요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 브로콜리</t>
-  </si>
-  <si>
-    <t>데친 브로콜리 한 줌으로 채소를 더해요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 나물무침</t>
-  </si>
-  <si>
-    <t>나물 한 가지로 아침 채소를 챙겨요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 북엇국</t>
-  </si>
-  <si>
-    <t>북엇국은 가볍고 단백질이 많은 국이에요.</t>
-  </si>
-  <si>
-    <t>단백질 메뉴 — 증량 성격으로 표시하면 신장질환 사용자에게는 안 나옴</t>
-  </si>
-  <si>
-    <t>아침 추천: 달걀국</t>
-  </si>
-  <si>
-    <t>달걀국으로 간단히 단백질을 더해요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 달걀찜</t>
-  </si>
-  <si>
-    <t>달걀찜은 부드러운 아침 단백질이에요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 삶은 달걀</t>
-  </si>
-  <si>
-    <t>삶은 달걀 하나로 아침 단백질을 챙겨요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 순두부</t>
-  </si>
-  <si>
-    <t>순두부는 부드러워 아침에 먹기 좋아요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 연두부</t>
-  </si>
-  <si>
-    <t>연두부는 데우기만 하면 되는 단백질이에요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 그릭요거트</t>
-  </si>
-  <si>
-    <t>그릭요거트는 단백질이 많고 달지 않아요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 우유</t>
-  </si>
-  <si>
-    <t>우유 한 잔으로 아침 단백질을 더해요.</t>
-  </si>
-  <si>
-    <t>아침 추천: 생선구이</t>
-  </si>
-  <si>
-    <t>생선구이는 기름을 덜 쓰는 아침 반찬이에요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 갈치구이</t>
-  </si>
-  <si>
-    <t>갈치구이는 튀김보다 기름이 덜 들어가요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 삼치구이</t>
-  </si>
-  <si>
-    <t>삼치구이로 기름 적은 저녁을 먹어요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 조기구이</t>
-  </si>
-  <si>
-    <t>조기구이는 담백한 저녁 반찬이에요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 보쌈</t>
-  </si>
-  <si>
-    <t>삶은 보쌈은 구운 고기보다 기름이 덜해요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 문어숙회</t>
-  </si>
-  <si>
-    <t>데친 문어는 기름 없이 먹는 반찬이에요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 오징어숙회</t>
-  </si>
-  <si>
-    <t>숙회는 튀김옷 없이 데쳐 기름이 적어요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 연어구이</t>
-  </si>
-  <si>
-    <t>연어구이로 저녁 단백질을 챙겨요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 두부구이</t>
-  </si>
-  <si>
-    <t>두부구이는 손쉬운 단백질 반찬이에요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 닭가슴살</t>
-  </si>
-  <si>
-    <t>닭가슴살은 기름 적은 단백질이에요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 닭안심구이</t>
-  </si>
-  <si>
-    <t>닭안심은 부드럽고 기름이 적어요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 닭곰탕</t>
-  </si>
-  <si>
-    <t>닭곰탕은 담백한 단백질 한 그릇이에요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 연두부찜</t>
-  </si>
-  <si>
-    <t>연두부찜은 부드러운 단백질 반찬이에요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 콩국수</t>
-  </si>
-  <si>
-    <t>콩국수로 식물성 단백질을 챙겨요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 소고기뭇국</t>
-  </si>
-  <si>
-    <t>살코기와 무로 담백하게 단백질을 챙겨요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 버섯된장국</t>
-  </si>
-  <si>
-    <t>버섯을 듬뿍 넣어 저녁 채소를 챙겨요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 샤브샤브</t>
-  </si>
-  <si>
-    <t>채소를 듬뿍 데쳐 먹을 수 있어요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 월남쌈</t>
-  </si>
-  <si>
-    <t>월남쌈은 채소를 듬뿍 싸 먹을 수 있어요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 버섯구이</t>
-  </si>
-  <si>
-    <t>버섯구이는 기름 없이 즐기는 채소 반찬이에요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 가지구이</t>
-  </si>
-  <si>
-    <t>가지구이로 저녁 채소를 더해요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 애호박나물</t>
-  </si>
-  <si>
-    <t>애호박나물은 부드러운 채소 반찬이에요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 시금치무침</t>
-  </si>
-  <si>
-    <t>시금치무침 하나로 저녁 채소가 채워져요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 콩나물무침</t>
-  </si>
-  <si>
-    <t>콩나물무침은 기름을 거의 쓰지 않아요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 숙주나물</t>
-  </si>
-  <si>
-    <t>숙주나물은 아삭하고 담백한 채소 반찬이에요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 오이무침</t>
-  </si>
-  <si>
-    <t>오이무침으로 상큼하게 채소를 더해요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 잡곡밥</t>
-  </si>
-  <si>
-    <t>잡곡밥은 저녁까지 든든하게 해 줘요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 대구맑은탕</t>
-  </si>
-  <si>
-    <t>맑은 대구탕은 빨간 탕보다 덜 짜요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 콩나물국</t>
-  </si>
-  <si>
-    <t>맑은 콩나물국은 찌개보다 덜 짜요.</t>
-  </si>
-  <si>
-    <t>저녁 추천: 미역냉국</t>
-  </si>
-  <si>
-    <t>미역냉국은 싱겁게 만들기 쉬워요.</t>
-  </si>
-  <si>
-    <t>묶음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>저녁·새벽 문구</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>입문 보강</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>부담 줄이기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>끼니 추천</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>새 표현</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10-12 끼니 추천 확대: 아침 추천 (04~10시) · 저녁 추천 (12~17시). 「묶음」 열은 검수할 때 신경 쓰지 않아도 되는 분류. 합계 206개</t>
-  </si>
-  <si>
-    <t>한 입에 30번 씹기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>꼭꼭 씹으면 천천히 먹게 되고 배부름도 빨리 느껴요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>언제나(낮 포함)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아니오</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>입맛 있을 때 먹어 두기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>입맛이 돌 때 먹어 두면 하루 식사를 채우기 쉬워요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>저녁은 7시 전에</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>저녁을 일찍 마치면 속이 편하게 잠들 수 있어요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>저녁 8시까지 마치기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>늦은 시간까지 먹지 않으면 속이 편해요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>밥은 15분 넘게 먹기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15분 넘게 먹으면 배부름을 느낄 시간이 생겨요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>숟가락을 놓고 쉬면 천천히 먹게 돼요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>점심 채소 반찬 2가지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>채소 반찬을 두 가지로 늘리면 한 끼 채소가 넉넉해요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>주 3일 단 음료 쉬기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>쉬는 날을 정하면 단 음료를 줄이기 쉬워요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>저녁은 매일 7시쯤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4시간마다 끼니 챙기기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>끼니 사이가 너무 길지 않으면 과식을 막기 쉬워요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>점심 알림 12시로</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>알림을 맞춰 두면 바쁜 날에도 점심을 놓치지 않아요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>소스는 한 번만 찍기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>한 번만 찍어도 맛은 충분해요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>샐러드 소스 1스푼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>소스를 한 스푼만 쓰면 기름과 염분이 줄어요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>밤 11시 전 잠자리에</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>일찍 자면 야식 생각이 줄어요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>제철 채소 2가지 사기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>제철 채소는 맛있고 값도 부담이 적어요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>주 2회 생선 먹기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>생선은 일주일에 두 번쯤 먹기를 권해요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>달걀 한 판 사 두기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>달걀이 있으면 끼니마다 단백질을 챙기기 쉬워요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>국에 두부 반 모</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>두부를 넣으면 국 한 그릇에 단백질이 더해져요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10-12 숫자로 구체화: 막연한 문구  사용자가 직접 셀 수 있는 숫자 표현으로 바꿈(예: 저녁 일찍 마치기 → 저녁은 7시 전에, 한 입에 30번 씹기)</t>
-  </si>
-  <si>
-    <t>9시 후엔 주방 닫기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>한 입마다 10초 쉬기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>면은 꼭꼭 씹어 먹기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>면도 꼭꼭 씹으면 천천히 먹고 배부름을 느끼기 쉬워요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아메추: 달걀죽/누룽지</t>
+  </si>
+  <si>
+    <t>속이 편한 죽이나 누룽지로 아침을 시작해요.</t>
+  </si>
+  <si>
+    <t>아메추: 잡곡밥/현미밥</t>
+  </si>
+  <si>
+    <t>잡곡밥이나 현미밥은 오래 든든해요.</t>
+  </si>
+  <si>
+    <t>아메추: 오트밀/통밀빵</t>
+  </si>
+  <si>
+    <t>금방 준비할 수 있는 든든한 아침이에요.</t>
+  </si>
+  <si>
+    <t>아메추: 고구마/누룽지</t>
+  </si>
+  <si>
+    <t>찐 고구마나 누룽지는 준비가 간단해요.</t>
+  </si>
+  <si>
+    <t>아메추: 전복죽/채소죽</t>
+  </si>
+  <si>
+    <t>부드러운 죽은 아침에 넘기기 편해요.</t>
+  </si>
+  <si>
+    <t>아메추: 미역국/뭇국</t>
+  </si>
+  <si>
+    <t>담백한 국으로 아침에도 채소를 먹어요.</t>
+  </si>
+  <si>
+    <t>아메추: 콩나물국/뭇국</t>
+  </si>
+  <si>
+    <t>맑은 국으로 아침 채소를 챙겨요.</t>
+  </si>
+  <si>
+    <t>아메추: 아욱국/배춧국</t>
+  </si>
+  <si>
+    <t>부드러운 채소국은 아침에 먹기 좋아요.</t>
+  </si>
+  <si>
+    <t>아메추: 비빔밥/쌈밥</t>
+  </si>
+  <si>
+    <t>나물이나 쌈으로 채소를 넉넉히 먹어요.</t>
+  </si>
+  <si>
+    <t>아메추: 브로콜리/나물</t>
+  </si>
+  <si>
+    <t>데친 채소 한 가지로 아침 채소를 더해요.</t>
+  </si>
+  <si>
+    <t>아메추: 달걀찜/달걀국</t>
+  </si>
+  <si>
+    <t>달걀로 간단히 아침 단백질을 챙겨요.</t>
+  </si>
+  <si>
+    <t>아메추: 순두부/연두부</t>
+  </si>
+  <si>
+    <t>부드러운 두부는 아침에 먹기 좋아요.</t>
+  </si>
+  <si>
+    <t>아메추: 두유/우유</t>
+  </si>
+  <si>
+    <t>한 잔으로 간편하게 단백질을 더해요.</t>
+  </si>
+  <si>
+    <t>아메추: 달걀/두유</t>
+  </si>
+  <si>
+    <t>바쁜 아침에도 단백질을 챙길 수 있어요.</t>
+  </si>
+  <si>
+    <t>아메추: 두부/달걀말이</t>
+  </si>
+  <si>
+    <t>손쉬운 단백질 반찬으로 아침을 채워요.</t>
+  </si>
+  <si>
+    <t>아메추: 북엇국/달걀국</t>
+  </si>
+  <si>
+    <t>가벼운 국으로 단백질을 더해요.</t>
+  </si>
+  <si>
+    <t>아메추: 생선구이/두부</t>
+  </si>
+  <si>
+    <t>기름을 덜 쓰는 반찬으로 아침을 먹어요.</t>
+  </si>
+  <si>
+    <t>아메추: 맑은 국/계란국</t>
+  </si>
+  <si>
+    <t>저메추: 생선구이/수육</t>
+  </si>
+  <si>
+    <t>구이와 수육은 튀김보다 기름이 덜해요.</t>
+  </si>
+  <si>
+    <t>저메추: 수육/보쌈</t>
+  </si>
+  <si>
+    <t>삶은 고기는 구운 고기보다 기름이 덜해요.</t>
+  </si>
+  <si>
+    <t>저메추: 닭백숙/닭곰탕</t>
+  </si>
+  <si>
+    <t>저메추: 문어숙회/수육</t>
+  </si>
+  <si>
+    <t>데친 요리는 기름 없이 먹을 수 있어요.</t>
+  </si>
+  <si>
+    <t>저메추: 고등어/갈치</t>
+  </si>
+  <si>
+    <t>구운 생선은 튀김보다 기름이 덜 들어가요.</t>
+  </si>
+  <si>
+    <t>저메추: 삼치/조기구이</t>
+  </si>
+  <si>
+    <t>담백한 생선구이로 저녁을 먹어요.</t>
+  </si>
+  <si>
+    <t>저메추: 두부/달걀찜</t>
+  </si>
+  <si>
+    <t>부드러운 단백질 반찬으로 저녁을 채워요.</t>
+  </si>
+  <si>
+    <t>저메추: 연어/닭가슴살</t>
+  </si>
+  <si>
+    <t>기름 적은 단백질로 저녁을 챙겨요.</t>
+  </si>
+  <si>
+    <t>저메추: 닭안심/두부</t>
+  </si>
+  <si>
+    <t>담백한 단백질 반찬이에요.</t>
+  </si>
+  <si>
+    <t>저메추: 콩국수/닭곰탕</t>
+  </si>
+  <si>
+    <t>든든한 한 그릇으로 단백질을 챙겨요.</t>
+  </si>
+  <si>
+    <t>저메추: 두부조림/생선</t>
+  </si>
+  <si>
+    <t>손쉬운 두부 반찬으로 단백질을 더해요.</t>
+  </si>
+  <si>
+    <t>저메추: 쌈밥/샤브샤브</t>
+  </si>
+  <si>
+    <t>채소를 듬뿍 먹을 수 있는 저녁이에요.</t>
+  </si>
+  <si>
+    <t>저메추: 월남쌈/쌈밥</t>
+  </si>
+  <si>
+    <t>채소를 싸 먹으면 자연스럽게 많이 먹어요.</t>
+  </si>
+  <si>
+    <t>저메추: 가지/버섯구이</t>
+  </si>
+  <si>
+    <t>기름 없이 구운 채소 반찬이에요.</t>
+  </si>
+  <si>
+    <t>저메추: 나물/오이무침</t>
+  </si>
+  <si>
+    <t>무침 반찬 하나로 저녁 채소가 채워져요.</t>
+  </si>
+  <si>
+    <t>저메추: 숙주/시금치</t>
+  </si>
+  <si>
+    <t>나물 한 가지로 저녁 채소를 더해요.</t>
+  </si>
+  <si>
+    <t>저메추: 버섯된장국/쌈</t>
+  </si>
+  <si>
+    <t>버섯국과 쌈으로 채소를 넉넉히 먹어요.</t>
+  </si>
+  <si>
+    <t>저메추: 북엇국/생선찜</t>
+  </si>
+  <si>
+    <t>맑은 국과 찜은 찌개보다 덜 짜요.</t>
+  </si>
+  <si>
+    <t>저메추: 미역냉국/뭇국</t>
+  </si>
+  <si>
+    <t>담백한 국은 싱겁게 만들기 쉬워요.</t>
+  </si>
+  <si>
+    <t>저메추: 잡곡밥/현미밥</t>
+  </si>
+  <si>
+    <t>잡곡밥이나 현미밥은 저녁까지 든든해요.</t>
+  </si>
+  <si>
+    <t>10-12 끼니 추천을 「아메추: A/B」 · 「저메추: A/B」 두 가지 고르기로 바꿈(아침 18 · 저녁 20). 한 가지씩이던 아침·저녁 추천  지움. 국수는 천천히 후루룩 → 면은 꼭꼭 씹어 먹기. 합계 176개</t>
   </si>
 </sst>
 </file>
@@ -8739,7 +8564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F51797-492B-40AC-833D-E19CEF6E9FA5}">
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="120.58203125" style="1" customWidth="1"/>
@@ -8813,17 +8638,22 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>536</v>
+        <v>505</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>649</v>
+        <v>512</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>686</v>
+        <v>549</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A18" s="1" t="s">
+        <v>629</v>
       </c>
     </row>
   </sheetData>
@@ -8834,7 +8664,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{243C8A1C-2FBA-4873-BD31-7545635970F1}">
-  <dimension ref="A1:O207"/>
+  <dimension ref="A1:O177"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6.58203125" style="1" customWidth="1"/>
@@ -8859,7 +8689,7 @@
         <v>53</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>643</v>
+        <v>507</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>54</v>
@@ -8906,7 +8736,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -8948,7 +8778,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -8990,7 +8820,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -9032,7 +8862,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -9074,7 +8904,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -9086,7 +8916,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>663</v>
+        <v>526</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>238</v>
@@ -9096,7 +8926,7 @@
         <v>12</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>664</v>
+        <v>527</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -9116,7 +8946,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -9158,7 +8988,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -9200,7 +9030,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -9242,7 +9072,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -9284,7 +9114,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -9326,7 +9156,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -9338,7 +9168,7 @@
         <v>220</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>687</v>
+        <v>550</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>244</v>
@@ -9368,7 +9198,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -9410,7 +9240,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -9452,7 +9282,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -9494,7 +9324,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -9506,7 +9336,7 @@
         <v>220</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>682</v>
+        <v>545</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>248</v>
@@ -9516,7 +9346,7 @@
         <v>11</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>683</v>
+        <v>546</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>27</v>
@@ -9536,7 +9366,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -9578,7 +9408,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -9620,7 +9450,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>31</v>
@@ -9662,7 +9492,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>31</v>
@@ -9704,7 +9534,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>31</v>
@@ -9746,7 +9576,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1</v>
@@ -9788,7 +9618,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>1</v>
@@ -9830,7 +9660,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>1</v>
@@ -9872,7 +9702,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>1</v>
@@ -9884,7 +9714,7 @@
         <v>220</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>678</v>
+        <v>541</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>257</v>
@@ -9894,7 +9724,7 @@
         <v>12</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>679</v>
+        <v>542</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>11</v>
@@ -9914,7 +9744,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>1</v>
@@ -9956,7 +9786,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>1</v>
@@ -9998,7 +9828,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>1</v>
@@ -10040,7 +9870,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>1</v>
@@ -10082,7 +9912,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>1</v>
@@ -10094,7 +9924,7 @@
         <v>12</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>658</v>
+        <v>521</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>262</v>
@@ -10104,7 +9934,7 @@
         <v>11</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>659</v>
+        <v>522</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>8</v>
@@ -10124,7 +9954,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>1</v>
@@ -10166,7 +9996,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>1</v>
@@ -10178,7 +10008,7 @@
         <v>220</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>650</v>
+        <v>513</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>264</v>
@@ -10188,16 +10018,16 @@
         <v>11</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>651</v>
+        <v>514</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>652</v>
+        <v>515</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>653</v>
+        <v>516</v>
       </c>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
@@ -10208,7 +10038,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>1</v>
@@ -10250,7 +10080,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>1</v>
@@ -10292,7 +10122,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>1</v>
@@ -10334,7 +10164,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>1</v>
@@ -10376,7 +10206,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>1</v>
@@ -10418,7 +10248,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>31</v>
@@ -10430,7 +10260,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>654</v>
+        <v>517</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>270</v>
@@ -10440,7 +10270,7 @@
         <v>13</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>655</v>
+        <v>518</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>32</v>
@@ -10460,7 +10290,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>31</v>
@@ -10502,7 +10332,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>1</v>
@@ -10544,7 +10374,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>1</v>
@@ -10586,7 +10416,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>1</v>
@@ -10628,7 +10458,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>1</v>
@@ -10670,7 +10500,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>1</v>
@@ -10712,7 +10542,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>1</v>
@@ -10754,7 +10584,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>1</v>
@@ -10796,7 +10626,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>1</v>
@@ -10808,7 +10638,7 @@
         <v>12</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>665</v>
+        <v>528</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>279</v>
@@ -10818,7 +10648,7 @@
         <v>12</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>666</v>
+        <v>529</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>43</v>
@@ -10838,7 +10668,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>1</v>
@@ -10880,7 +10710,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>1</v>
@@ -10922,7 +10752,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>1</v>
@@ -10964,7 +10794,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>1</v>
@@ -11006,7 +10836,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>1</v>
@@ -11018,7 +10848,7 @@
         <v>7</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>656</v>
+        <v>519</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>284</v>
@@ -11028,7 +10858,7 @@
         <v>9</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>657</v>
+        <v>520</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>46</v>
@@ -11048,7 +10878,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>1</v>
@@ -11060,7 +10890,7 @@
         <v>12</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>667</v>
+        <v>530</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>285</v>
@@ -11090,7 +10920,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>1</v>
@@ -11102,7 +10932,7 @@
         <v>3</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>660</v>
+        <v>523</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>286</v>
@@ -11112,7 +10942,7 @@
         <v>12</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>661</v>
+        <v>524</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>23</v>
@@ -11132,7 +10962,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>1</v>
@@ -11174,7 +11004,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>1</v>
@@ -11216,7 +11046,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>1</v>
@@ -11258,7 +11088,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>1</v>
@@ -11270,7 +11100,7 @@
         <v>7</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>680</v>
+        <v>543</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>290</v>
@@ -11280,7 +11110,7 @@
         <v>10</v>
       </c>
       <c r="I58" s="7" t="s">
-        <v>681</v>
+        <v>544</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>49</v>
@@ -11300,7 +11130,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>1</v>
@@ -11342,7 +11172,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>1</v>
@@ -11384,7 +11214,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>1</v>
@@ -11426,7 +11256,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>1</v>
@@ -11468,7 +11298,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>31</v>
@@ -11510,7 +11340,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>644</v>
+        <v>508</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>31</v>
@@ -11552,7 +11382,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>144</v>
@@ -11564,7 +11394,7 @@
         <v>146</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>670</v>
+        <v>533</v>
       </c>
       <c r="G65" s="5" t="s">
         <v>296</v>
@@ -11574,7 +11404,7 @@
         <v>10</v>
       </c>
       <c r="I65" s="7" t="s">
-        <v>671</v>
+        <v>534</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>147</v>
@@ -11594,7 +11424,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>144</v>
@@ -11636,7 +11466,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>144</v>
@@ -11648,7 +11478,7 @@
         <v>146</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>668</v>
+        <v>531</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>299</v>
@@ -11658,7 +11488,7 @@
         <v>12</v>
       </c>
       <c r="I67" s="7" t="s">
-        <v>669</v>
+        <v>532</v>
       </c>
       <c r="J67" s="3" t="s">
         <v>151</v>
@@ -11678,7 +11508,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>144</v>
@@ -11720,7 +11550,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>144</v>
@@ -11762,7 +11592,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>144</v>
@@ -11804,7 +11634,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>144</v>
@@ -11846,7 +11676,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>144</v>
@@ -11888,7 +11718,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>144</v>
@@ -11930,7 +11760,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>144</v>
@@ -11972,7 +11802,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>144</v>
@@ -12014,7 +11844,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>144</v>
@@ -12056,7 +11886,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>144</v>
@@ -12098,7 +11928,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>144</v>
@@ -12140,7 +11970,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>144</v>
@@ -12182,7 +12012,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>144</v>
@@ -12224,7 +12054,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>144</v>
@@ -12266,7 +12096,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>144</v>
@@ -12308,7 +12138,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>144</v>
@@ -12350,7 +12180,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>144</v>
@@ -12392,7 +12222,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>144</v>
@@ -12404,7 +12234,7 @@
         <v>146</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>672</v>
+        <v>535</v>
       </c>
       <c r="G85" s="5" t="s">
         <v>332</v>
@@ -12414,7 +12244,7 @@
         <v>11</v>
       </c>
       <c r="I85" s="7" t="s">
-        <v>673</v>
+        <v>536</v>
       </c>
       <c r="J85" s="3" t="s">
         <v>187</v>
@@ -12434,7 +12264,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>144</v>
@@ -12476,7 +12306,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>144</v>
@@ -12518,7 +12348,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>144</v>
@@ -12560,7 +12390,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>144</v>
@@ -12602,7 +12432,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>144</v>
@@ -12644,7 +12474,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>144</v>
@@ -12686,7 +12516,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>144</v>
@@ -12728,7 +12558,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>144</v>
@@ -12770,7 +12600,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>144</v>
@@ -12782,7 +12612,7 @@
         <v>146</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>676</v>
+        <v>539</v>
       </c>
       <c r="G94" s="5" t="s">
         <v>346</v>
@@ -12792,7 +12622,7 @@
         <v>12</v>
       </c>
       <c r="I94" s="7" t="s">
-        <v>677</v>
+        <v>540</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>198</v>
@@ -12812,7 +12642,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>144</v>
@@ -12824,7 +12654,7 @@
         <v>146</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>688</v>
+        <v>551</v>
       </c>
       <c r="G95" s="5" t="s">
         <v>347</v>
@@ -12834,7 +12664,7 @@
         <v>12</v>
       </c>
       <c r="I95" s="7" t="s">
-        <v>662</v>
+        <v>525</v>
       </c>
       <c r="J95" s="3" t="s">
         <v>200</v>
@@ -12854,7 +12684,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>144</v>
@@ -12896,7 +12726,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>144</v>
@@ -12938,7 +12768,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>144</v>
@@ -12980,7 +12810,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>144</v>
@@ -13022,7 +12852,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>144</v>
@@ -13064,7 +12894,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>144</v>
@@ -13106,7 +12936,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>144</v>
@@ -13148,7 +12978,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>144</v>
@@ -13190,7 +13020,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>144</v>
@@ -13202,7 +13032,7 @@
         <v>146</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>684</v>
+        <v>547</v>
       </c>
       <c r="G104" s="5" t="s">
         <v>362</v>
@@ -13212,7 +13042,7 @@
         <v>9</v>
       </c>
       <c r="I104" s="7" t="s">
-        <v>685</v>
+        <v>548</v>
       </c>
       <c r="J104" s="3" t="s">
         <v>210</v>
@@ -13232,7 +13062,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>144</v>
@@ -13274,7 +13104,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>144</v>
@@ -13316,7 +13146,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>144</v>
@@ -13358,7 +13188,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>144</v>
@@ -13400,7 +13230,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>144</v>
@@ -13442,7 +13272,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>144</v>
@@ -13454,7 +13284,7 @@
         <v>146</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>674</v>
+        <v>537</v>
       </c>
       <c r="G110" s="5" t="s">
         <v>462</v>
@@ -13464,7 +13294,7 @@
         <v>10</v>
       </c>
       <c r="I110" s="7" t="s">
-        <v>675</v>
+        <v>538</v>
       </c>
       <c r="J110" s="3" t="s">
         <v>216</v>
@@ -13484,7 +13314,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>144</v>
@@ -13526,7 +13356,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>144</v>
@@ -13568,7 +13398,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C113" s="7" t="s">
         <v>144</v>
@@ -13610,7 +13440,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C114" s="7" t="s">
         <v>144</v>
@@ -13652,7 +13482,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C115" s="7" t="s">
         <v>144</v>
@@ -13694,7 +13524,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C116" s="7" t="s">
         <v>144</v>
@@ -13736,7 +13566,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C117" s="7" t="s">
         <v>144</v>
@@ -13778,7 +13608,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>645</v>
+        <v>509</v>
       </c>
       <c r="C118" s="7" t="s">
         <v>144</v>
@@ -13820,7 +13650,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>646</v>
+        <v>510</v>
       </c>
       <c r="C119" s="7" t="s">
         <v>386</v>
@@ -13838,7 +13668,7 @@
         <v>0</v>
       </c>
       <c r="H119" s="7">
-        <f t="shared" ref="H119:H155" si="4">LEN(F119)</f>
+        <f t="shared" ref="H119:H139" si="4">LEN(F119)</f>
         <v>10</v>
       </c>
       <c r="I119" s="7" t="s">
@@ -13862,7 +13692,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>647</v>
+        <v>511</v>
       </c>
       <c r="C120" s="7" t="s">
         <v>144</v>
@@ -13874,23 +13704,23 @@
         <v>146</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="G120" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H120" s="7">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I120" s="7" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J120" s="7" t="s">
         <v>155</v>
       </c>
       <c r="K120" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="L120" s="7" t="s">
         <v>149</v>
@@ -13904,7 +13734,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>647</v>
+        <v>511</v>
       </c>
       <c r="C121" s="7" t="s">
         <v>144</v>
@@ -13916,7 +13746,7 @@
         <v>146</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="G121" s="7" t="s">
         <v>0</v>
@@ -13926,13 +13756,13 @@
         <v>12</v>
       </c>
       <c r="I121" s="7" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="J121" s="7" t="s">
         <v>155</v>
       </c>
       <c r="K121" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="L121" s="7" t="s">
         <v>149</v>
@@ -13946,19 +13776,19 @@
         <v>121</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>647</v>
+        <v>511</v>
       </c>
       <c r="C122" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D122" s="7" t="s">
-        <v>208</v>
+        <v>159</v>
       </c>
       <c r="E122" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="G122" s="7" t="s">
         <v>0</v>
@@ -13968,13 +13798,13 @@
         <v>11</v>
       </c>
       <c r="I122" s="7" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="J122" s="7" t="s">
-        <v>210</v>
+        <v>163</v>
       </c>
       <c r="K122" s="7" t="s">
-        <v>465</v>
+        <v>148</v>
       </c>
       <c r="L122" s="7" t="s">
         <v>149</v>
@@ -13988,35 +13818,35 @@
         <v>122</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>647</v>
+        <v>511</v>
       </c>
       <c r="C123" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D123" s="7" t="s">
-        <v>208</v>
+        <v>159</v>
       </c>
       <c r="E123" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="G123" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H123" s="7">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I123" s="7" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="J123" s="7" t="s">
-        <v>210</v>
+        <v>161</v>
       </c>
       <c r="K123" s="7" t="s">
-        <v>465</v>
+        <v>148</v>
       </c>
       <c r="L123" s="7" t="s">
         <v>149</v>
@@ -14030,35 +13860,35 @@
         <v>123</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>647</v>
+        <v>511</v>
       </c>
       <c r="C124" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D124" s="7" t="s">
-        <v>208</v>
+        <v>159</v>
       </c>
       <c r="E124" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="G124" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H124" s="7">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I124" s="7" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="J124" s="7" t="s">
-        <v>210</v>
+        <v>161</v>
       </c>
       <c r="K124" s="7" t="s">
-        <v>465</v>
+        <v>148</v>
       </c>
       <c r="L124" s="7" t="s">
         <v>149</v>
@@ -14072,35 +13902,35 @@
         <v>124</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>647</v>
+        <v>511</v>
       </c>
       <c r="C125" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D125" s="7" t="s">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="E125" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="G125" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H125" s="7">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I125" s="7" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="J125" s="7" t="s">
-        <v>161</v>
+        <v>210</v>
       </c>
       <c r="K125" s="7" t="s">
-        <v>465</v>
+        <v>148</v>
       </c>
       <c r="L125" s="7" t="s">
         <v>149</v>
@@ -14114,35 +13944,35 @@
         <v>125</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>647</v>
+        <v>511</v>
       </c>
       <c r="C126" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D126" s="7" t="s">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="E126" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="G126" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H126" s="7">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I126" s="7" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="J126" s="7" t="s">
-        <v>161</v>
+        <v>210</v>
       </c>
       <c r="K126" s="7" t="s">
-        <v>465</v>
+        <v>148</v>
       </c>
       <c r="L126" s="7" t="s">
         <v>149</v>
@@ -14156,35 +13986,35 @@
         <v>126</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>647</v>
+        <v>511</v>
       </c>
       <c r="C127" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D127" s="7" t="s">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="E127" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="G127" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H127" s="7">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I127" s="7" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="J127" s="7" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="K127" s="7" t="s">
-        <v>465</v>
+        <v>148</v>
       </c>
       <c r="L127" s="7" t="s">
         <v>149</v>
@@ -14198,35 +14028,35 @@
         <v>127</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>647</v>
+        <v>511</v>
       </c>
       <c r="C128" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D128" s="7" t="s">
-        <v>214</v>
+        <v>169</v>
       </c>
       <c r="E128" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="G128" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H128" s="7">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I128" s="7" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J128" s="7" t="s">
-        <v>215</v>
+        <v>171</v>
       </c>
       <c r="K128" s="7" t="s">
-        <v>482</v>
+        <v>148</v>
       </c>
       <c r="L128" s="7" t="s">
         <v>149</v>
@@ -14240,19 +14070,19 @@
         <v>128</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>647</v>
+        <v>511</v>
       </c>
       <c r="C129" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D129" s="7" t="s">
-        <v>214</v>
+        <v>169</v>
       </c>
       <c r="E129" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G129" s="7" t="s">
         <v>0</v>
@@ -14262,13 +14092,13 @@
         <v>9</v>
       </c>
       <c r="I129" s="7" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J129" s="7" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
       <c r="K129" s="7" t="s">
-        <v>482</v>
+        <v>148</v>
       </c>
       <c r="L129" s="7" t="s">
         <v>149</v>
@@ -14282,35 +14112,35 @@
         <v>129</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>647</v>
+        <v>511</v>
       </c>
       <c r="C130" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D130" s="7" t="s">
-        <v>214</v>
+        <v>169</v>
       </c>
       <c r="E130" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F130" s="7" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G130" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H130" s="7">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I130" s="7" t="s">
-        <v>227</v>
+        <v>487</v>
       </c>
       <c r="J130" s="7" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
       <c r="K130" s="7" t="s">
-        <v>482</v>
+        <v>148</v>
       </c>
       <c r="L130" s="7" t="s">
         <v>149</v>
@@ -14324,35 +14154,35 @@
         <v>130</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>647</v>
+        <v>511</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D131" s="7" t="s">
-        <v>208</v>
+        <v>181</v>
       </c>
       <c r="E131" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F131" s="7" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="G131" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H131" s="7">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I131" s="7" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="J131" s="7" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="K131" s="7" t="s">
-        <v>482</v>
+        <v>148</v>
       </c>
       <c r="L131" s="7" t="s">
         <v>149</v>
@@ -14366,35 +14196,35 @@
         <v>131</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>647</v>
+        <v>511</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D132" s="7" t="s">
-        <v>208</v>
+        <v>181</v>
       </c>
       <c r="E132" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G132" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H132" s="7">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I132" s="7" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="J132" s="7" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="K132" s="7" t="s">
-        <v>482</v>
+        <v>148</v>
       </c>
       <c r="L132" s="7" t="s">
         <v>149</v>
@@ -14408,35 +14238,35 @@
         <v>132</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>647</v>
+        <v>511</v>
       </c>
       <c r="C133" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D133" s="7" t="s">
-        <v>159</v>
+        <v>214</v>
       </c>
       <c r="E133" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F133" s="7" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="G133" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H133" s="7">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I133" s="7" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="J133" s="7" t="s">
-        <v>163</v>
+        <v>215</v>
       </c>
       <c r="K133" s="7" t="s">
-        <v>482</v>
+        <v>148</v>
       </c>
       <c r="L133" s="7" t="s">
         <v>149</v>
@@ -14450,35 +14280,35 @@
         <v>133</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>647</v>
+        <v>511</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D134" s="7" t="s">
-        <v>159</v>
+        <v>214</v>
       </c>
       <c r="E134" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F134" s="7" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="G134" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H134" s="7">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I134" s="7" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="J134" s="7" t="s">
-        <v>161</v>
+        <v>215</v>
       </c>
       <c r="K134" s="7" t="s">
-        <v>482</v>
+        <v>148</v>
       </c>
       <c r="L134" s="7" t="s">
         <v>149</v>
@@ -14492,38 +14322,38 @@
         <v>134</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>647</v>
+        <v>511</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D135" s="7" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="E135" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="G135" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H135" s="7">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I135" s="7" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="J135" s="7" t="s">
-        <v>187</v>
+        <v>498</v>
       </c>
       <c r="K135" s="7" t="s">
-        <v>482</v>
+        <v>156</v>
       </c>
       <c r="L135" s="7" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="M135" s="3"/>
       <c r="N135" s="3"/>
@@ -14534,38 +14364,38 @@
         <v>135</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>648</v>
+        <v>511</v>
       </c>
       <c r="C136" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D136" s="7" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="E136" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="G136" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H136" s="7">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I136" s="7" t="s">
-        <v>464</v>
+        <v>500</v>
       </c>
       <c r="J136" s="7" t="s">
-        <v>155</v>
+        <v>498</v>
       </c>
       <c r="K136" s="7" t="s">
-        <v>465</v>
+        <v>156</v>
       </c>
       <c r="L136" s="7" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="M136" s="3"/>
       <c r="N136" s="3"/>
@@ -14576,19 +14406,19 @@
         <v>136</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>648</v>
+        <v>511</v>
       </c>
       <c r="C137" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D137" s="7" t="s">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="E137" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="G137" s="7" t="s">
         <v>0</v>
@@ -14598,13 +14428,13 @@
         <v>12</v>
       </c>
       <c r="I137" s="7" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="J137" s="7" t="s">
-        <v>155</v>
+        <v>200</v>
       </c>
       <c r="K137" s="7" t="s">
-        <v>465</v>
+        <v>148</v>
       </c>
       <c r="L137" s="7" t="s">
         <v>149</v>
@@ -14618,32 +14448,32 @@
         <v>137</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>648</v>
+        <v>511</v>
       </c>
       <c r="C138" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D138" s="7" t="s">
-        <v>159</v>
+        <v>199</v>
       </c>
       <c r="E138" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="G138" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H138" s="7">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I138" s="7" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="J138" s="7" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="K138" s="7" t="s">
         <v>148</v>
@@ -14655,37 +14485,37 @@
       <c r="N138" s="3"/>
       <c r="O138" s="3"/>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A139" s="7">
         <v>138</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>648</v>
+        <v>511</v>
       </c>
       <c r="C139" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D139" s="7" t="s">
-        <v>159</v>
+        <v>199</v>
       </c>
       <c r="E139" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>501</v>
+        <v>553</v>
       </c>
       <c r="G139" s="7" t="s">
-        <v>0</v>
+        <v>552</v>
       </c>
       <c r="H139" s="7">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I139" s="7" t="s">
-        <v>502</v>
+        <v>554</v>
       </c>
       <c r="J139" s="7" t="s">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="K139" s="7" t="s">
         <v>148</v>
@@ -14702,35 +14532,35 @@
         <v>139</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>648</v>
+        <v>506</v>
       </c>
       <c r="C140" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D140" s="7" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="E140" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>503</v>
+        <v>555</v>
       </c>
       <c r="G140" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H140" s="7">
-        <f t="shared" si="4"/>
-        <v>11</v>
+        <f>LEN(F140)</f>
+        <v>12</v>
       </c>
       <c r="I140" s="7" t="s">
-        <v>504</v>
+        <v>556</v>
       </c>
       <c r="J140" s="7" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="K140" s="7" t="s">
-        <v>148</v>
+        <v>464</v>
       </c>
       <c r="L140" s="7" t="s">
         <v>149</v>
@@ -14744,35 +14574,35 @@
         <v>140</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>648</v>
+        <v>506</v>
       </c>
       <c r="C141" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D141" s="7" t="s">
-        <v>208</v>
+        <v>145</v>
       </c>
       <c r="E141" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>505</v>
+        <v>557</v>
       </c>
       <c r="G141" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H141" s="7">
-        <f t="shared" si="4"/>
-        <v>9</v>
+        <f>LEN(F141)</f>
+        <v>12</v>
       </c>
       <c r="I141" s="7" t="s">
-        <v>506</v>
+        <v>558</v>
       </c>
       <c r="J141" s="7" t="s">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="K141" s="7" t="s">
-        <v>148</v>
+        <v>464</v>
       </c>
       <c r="L141" s="7" t="s">
         <v>149</v>
@@ -14786,35 +14616,35 @@
         <v>141</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>648</v>
+        <v>506</v>
       </c>
       <c r="C142" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D142" s="7" t="s">
-        <v>208</v>
+        <v>145</v>
       </c>
       <c r="E142" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>507</v>
+        <v>559</v>
       </c>
       <c r="G142" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H142" s="7">
-        <f t="shared" si="4"/>
-        <v>11</v>
+        <f>LEN(F142)</f>
+        <v>12</v>
       </c>
       <c r="I142" s="7" t="s">
-        <v>508</v>
+        <v>560</v>
       </c>
       <c r="J142" s="7" t="s">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="K142" s="7" t="s">
-        <v>148</v>
+        <v>464</v>
       </c>
       <c r="L142" s="7" t="s">
         <v>149</v>
@@ -14828,35 +14658,35 @@
         <v>142</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>648</v>
+        <v>506</v>
       </c>
       <c r="C143" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D143" s="7" t="s">
-        <v>208</v>
+        <v>145</v>
       </c>
       <c r="E143" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>509</v>
+        <v>561</v>
       </c>
       <c r="G143" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H143" s="7">
-        <f t="shared" si="4"/>
-        <v>10</v>
+        <f>LEN(F143)</f>
+        <v>12</v>
       </c>
       <c r="I143" s="7" t="s">
-        <v>510</v>
+        <v>562</v>
       </c>
       <c r="J143" s="7" t="s">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="K143" s="7" t="s">
-        <v>148</v>
+        <v>464</v>
       </c>
       <c r="L143" s="7" t="s">
         <v>149</v>
@@ -14870,35 +14700,35 @@
         <v>143</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>648</v>
+        <v>506</v>
       </c>
       <c r="C144" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D144" s="7" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="E144" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>511</v>
+        <v>563</v>
       </c>
       <c r="G144" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H144" s="7">
-        <f t="shared" si="4"/>
-        <v>9</v>
+        <f>LEN(F144)</f>
+        <v>12</v>
       </c>
       <c r="I144" s="7" t="s">
-        <v>512</v>
+        <v>564</v>
       </c>
       <c r="J144" s="7" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="K144" s="7" t="s">
-        <v>148</v>
+        <v>464</v>
       </c>
       <c r="L144" s="7" t="s">
         <v>149</v>
@@ -14912,35 +14742,35 @@
         <v>144</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>648</v>
+        <v>506</v>
       </c>
       <c r="C145" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D145" s="7" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E145" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>513</v>
+        <v>565</v>
       </c>
       <c r="G145" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H145" s="7">
-        <f t="shared" si="4"/>
-        <v>9</v>
+        <f>LEN(F145)</f>
+        <v>11</v>
       </c>
       <c r="I145" s="7" t="s">
-        <v>514</v>
+        <v>566</v>
       </c>
       <c r="J145" s="7" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="K145" s="7" t="s">
-        <v>148</v>
+        <v>464</v>
       </c>
       <c r="L145" s="7" t="s">
         <v>149</v>
@@ -14954,35 +14784,35 @@
         <v>145</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>648</v>
+        <v>506</v>
       </c>
       <c r="C146" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D146" s="7" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E146" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>515</v>
+        <v>567</v>
       </c>
       <c r="G146" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H146" s="7">
-        <f t="shared" si="4"/>
-        <v>11</v>
+        <f>LEN(F146)</f>
+        <v>12</v>
       </c>
       <c r="I146" s="7" t="s">
-        <v>516</v>
+        <v>568</v>
       </c>
       <c r="J146" s="7" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="K146" s="7" t="s">
-        <v>148</v>
+        <v>464</v>
       </c>
       <c r="L146" s="7" t="s">
         <v>149</v>
@@ -14996,35 +14826,35 @@
         <v>146</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>648</v>
+        <v>506</v>
       </c>
       <c r="C147" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D147" s="7" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="E147" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>517</v>
+        <v>569</v>
       </c>
       <c r="G147" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H147" s="7">
-        <f t="shared" si="4"/>
-        <v>9</v>
+        <f>LEN(F147)</f>
+        <v>12</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>518</v>
+        <v>570</v>
       </c>
       <c r="J147" s="7" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="K147" s="7" t="s">
-        <v>148</v>
+        <v>464</v>
       </c>
       <c r="L147" s="7" t="s">
         <v>149</v>
@@ -15038,35 +14868,35 @@
         <v>147</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>648</v>
+        <v>506</v>
       </c>
       <c r="C148" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D148" s="7" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="E148" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>519</v>
+        <v>571</v>
       </c>
       <c r="G148" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H148" s="7">
-        <f t="shared" si="4"/>
-        <v>8</v>
+        <f>LEN(F148)</f>
+        <v>11</v>
       </c>
       <c r="I148" s="7" t="s">
-        <v>520</v>
+        <v>572</v>
       </c>
       <c r="J148" s="7" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="K148" s="7" t="s">
-        <v>148</v>
+        <v>464</v>
       </c>
       <c r="L148" s="7" t="s">
         <v>149</v>
@@ -15080,35 +14910,35 @@
         <v>148</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>648</v>
+        <v>506</v>
       </c>
       <c r="C149" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D149" s="7" t="s">
-        <v>214</v>
+        <v>159</v>
       </c>
       <c r="E149" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>521</v>
+        <v>573</v>
       </c>
       <c r="G149" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H149" s="7">
-        <f t="shared" si="4"/>
-        <v>11</v>
+        <f>LEN(F149)</f>
+        <v>12</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>522</v>
+        <v>574</v>
       </c>
       <c r="J149" s="7" t="s">
-        <v>215</v>
+        <v>161</v>
       </c>
       <c r="K149" s="7" t="s">
-        <v>148</v>
+        <v>464</v>
       </c>
       <c r="L149" s="7" t="s">
         <v>149</v>
@@ -15122,35 +14952,35 @@
         <v>149</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>648</v>
+        <v>506</v>
       </c>
       <c r="C150" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D150" s="7" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="E150" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>523</v>
+        <v>575</v>
       </c>
       <c r="G150" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H150" s="7">
-        <f t="shared" si="4"/>
-        <v>9</v>
+        <f>LEN(F150)</f>
+        <v>12</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>524</v>
+        <v>576</v>
       </c>
       <c r="J150" s="7" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K150" s="7" t="s">
-        <v>148</v>
+        <v>464</v>
       </c>
       <c r="L150" s="7" t="s">
         <v>149</v>
@@ -15164,38 +14994,38 @@
         <v>150</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>648</v>
+        <v>506</v>
       </c>
       <c r="C151" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D151" s="7" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="E151" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>525</v>
+        <v>577</v>
       </c>
       <c r="G151" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H151" s="7">
-        <f t="shared" si="4"/>
-        <v>11</v>
+        <f>LEN(F151)</f>
+        <v>12</v>
       </c>
       <c r="I151" s="7" t="s">
-        <v>526</v>
+        <v>578</v>
       </c>
       <c r="J151" s="7" t="s">
-        <v>527</v>
+        <v>210</v>
       </c>
       <c r="K151" s="7" t="s">
-        <v>156</v>
+        <v>464</v>
       </c>
       <c r="L151" s="7" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="M151" s="3"/>
       <c r="N151" s="3"/>
@@ -15206,38 +15036,38 @@
         <v>151</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>648</v>
+        <v>506</v>
       </c>
       <c r="C152" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D152" s="7" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="E152" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>528</v>
+        <v>579</v>
       </c>
       <c r="G152" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H152" s="7">
-        <f t="shared" si="4"/>
-        <v>11</v>
+        <f>LEN(F152)</f>
+        <v>10</v>
       </c>
       <c r="I152" s="7" t="s">
-        <v>529</v>
+        <v>580</v>
       </c>
       <c r="J152" s="7" t="s">
-        <v>527</v>
+        <v>210</v>
       </c>
       <c r="K152" s="7" t="s">
-        <v>156</v>
+        <v>464</v>
       </c>
       <c r="L152" s="7" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="M152" s="3"/>
       <c r="N152" s="3"/>
@@ -15248,35 +15078,35 @@
         <v>152</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>648</v>
+        <v>506</v>
       </c>
       <c r="C153" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D153" s="7" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="E153" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>530</v>
+        <v>581</v>
       </c>
       <c r="G153" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H153" s="7">
-        <f t="shared" si="4"/>
-        <v>12</v>
+        <f>LEN(F153)</f>
+        <v>10</v>
       </c>
       <c r="I153" s="7" t="s">
-        <v>531</v>
+        <v>582</v>
       </c>
       <c r="J153" s="7" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="K153" s="7" t="s">
-        <v>148</v>
+        <v>464</v>
       </c>
       <c r="L153" s="7" t="s">
         <v>149</v>
@@ -15290,35 +15120,35 @@
         <v>153</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>648</v>
+        <v>506</v>
       </c>
       <c r="C154" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D154" s="7" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="E154" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>532</v>
+        <v>583</v>
       </c>
       <c r="G154" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H154" s="7">
-        <f t="shared" si="4"/>
-        <v>9</v>
+        <f>LEN(F154)</f>
+        <v>12</v>
       </c>
       <c r="I154" s="7" t="s">
-        <v>533</v>
+        <v>584</v>
       </c>
       <c r="J154" s="7" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="K154" s="7" t="s">
-        <v>148</v>
+        <v>464</v>
       </c>
       <c r="L154" s="7" t="s">
         <v>149</v>
@@ -15332,35 +15162,35 @@
         <v>154</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>648</v>
+        <v>506</v>
       </c>
       <c r="C155" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D155" s="7" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="E155" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>534</v>
+        <v>585</v>
       </c>
       <c r="G155" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H155" s="7">
-        <f t="shared" si="4"/>
-        <v>11</v>
+        <f>LEN(F155)</f>
+        <v>12</v>
       </c>
       <c r="I155" s="7" t="s">
-        <v>535</v>
+        <v>586</v>
       </c>
       <c r="J155" s="7" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="K155" s="7" t="s">
-        <v>148</v>
+        <v>464</v>
       </c>
       <c r="L155" s="7" t="s">
         <v>149</v>
@@ -15374,35 +15204,35 @@
         <v>155</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="C156" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D156" s="7" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="E156" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>538</v>
+        <v>587</v>
       </c>
       <c r="G156" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H156" s="7">
-        <f t="shared" ref="H156:H187" si="5">LEN(F156)</f>
-        <v>10</v>
+        <f>LEN(F156)</f>
+        <v>12</v>
       </c>
       <c r="I156" s="7" t="s">
-        <v>539</v>
+        <v>588</v>
       </c>
       <c r="J156" s="7" t="s">
-        <v>155</v>
+        <v>215</v>
       </c>
       <c r="K156" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="L156" s="7" t="s">
         <v>149</v>
@@ -15416,35 +15246,35 @@
         <v>156</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="C157" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D157" s="7" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="E157" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>540</v>
+        <v>589</v>
       </c>
       <c r="G157" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H157" s="7">
-        <f t="shared" si="5"/>
-        <v>10</v>
+        <f>LEN(F157)</f>
+        <v>13</v>
       </c>
       <c r="I157" s="7" t="s">
-        <v>541</v>
+        <v>465</v>
       </c>
       <c r="J157" s="7" t="s">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="K157" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="L157" s="7" t="s">
         <v>149</v>
@@ -15458,35 +15288,35 @@
         <v>157</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="C158" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D158" s="7" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="E158" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>542</v>
+        <v>590</v>
       </c>
       <c r="G158" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H158" s="7">
-        <f t="shared" si="5"/>
-        <v>10</v>
+        <f>LEN(F158)</f>
+        <v>12</v>
       </c>
       <c r="I158" s="7" t="s">
-        <v>543</v>
+        <v>591</v>
       </c>
       <c r="J158" s="7" t="s">
-        <v>155</v>
+        <v>215</v>
       </c>
       <c r="K158" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L158" s="7" t="s">
         <v>149</v>
@@ -15500,35 +15330,35 @@
         <v>158</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="C159" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D159" s="7" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="E159" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>544</v>
+        <v>592</v>
       </c>
       <c r="G159" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H159" s="7">
-        <f t="shared" si="5"/>
+        <f>LEN(F159)</f>
         <v>10</v>
       </c>
       <c r="I159" s="7" t="s">
-        <v>545</v>
+        <v>593</v>
       </c>
       <c r="J159" s="7" t="s">
-        <v>155</v>
+        <v>215</v>
       </c>
       <c r="K159" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L159" s="7" t="s">
         <v>149</v>
@@ -15542,35 +15372,35 @@
         <v>159</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="C160" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D160" s="7" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="E160" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>546</v>
+        <v>594</v>
       </c>
       <c r="G160" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H160" s="7">
-        <f t="shared" si="5"/>
-        <v>10</v>
+        <f>LEN(F160)</f>
+        <v>12</v>
       </c>
       <c r="I160" s="7" t="s">
-        <v>547</v>
+        <v>227</v>
       </c>
       <c r="J160" s="7" t="s">
-        <v>155</v>
+        <v>215</v>
       </c>
       <c r="K160" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L160" s="7" t="s">
         <v>149</v>
@@ -15584,35 +15414,35 @@
         <v>160</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="C161" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="E161" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>548</v>
+        <v>595</v>
       </c>
       <c r="G161" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H161" s="7">
-        <f t="shared" si="5"/>
-        <v>10</v>
+        <f>LEN(F161)</f>
+        <v>12</v>
       </c>
       <c r="I161" s="7" t="s">
-        <v>549</v>
+        <v>596</v>
       </c>
       <c r="J161" s="7" t="s">
-        <v>155</v>
+        <v>215</v>
       </c>
       <c r="K161" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L161" s="7" t="s">
         <v>149</v>
@@ -15626,35 +15456,35 @@
         <v>161</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="C162" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D162" s="7" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="E162" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>550</v>
+        <v>597</v>
       </c>
       <c r="G162" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H162" s="7">
-        <f t="shared" si="5"/>
-        <v>10</v>
+        <f>LEN(F162)</f>
+        <v>11</v>
       </c>
       <c r="I162" s="7" t="s">
-        <v>551</v>
+        <v>598</v>
       </c>
       <c r="J162" s="7" t="s">
-        <v>155</v>
+        <v>215</v>
       </c>
       <c r="K162" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L162" s="7" t="s">
         <v>149</v>
@@ -15668,35 +15498,35 @@
         <v>162</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="C163" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>159</v>
+        <v>214</v>
       </c>
       <c r="E163" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>552</v>
+        <v>599</v>
       </c>
       <c r="G163" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H163" s="7">
-        <f t="shared" si="5"/>
-        <v>10</v>
+        <f>LEN(F163)</f>
+        <v>12</v>
       </c>
       <c r="I163" s="7" t="s">
-        <v>553</v>
+        <v>600</v>
       </c>
       <c r="J163" s="7" t="s">
-        <v>161</v>
+        <v>215</v>
       </c>
       <c r="K163" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L163" s="7" t="s">
         <v>149</v>
@@ -15710,35 +15540,35 @@
         <v>163</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="C164" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D164" s="7" t="s">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="E164" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G164" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H164" s="7">
-        <f t="shared" si="5"/>
+        <f>LEN(F164)</f>
         <v>11</v>
       </c>
       <c r="I164" s="7" t="s">
-        <v>555</v>
+        <v>602</v>
       </c>
       <c r="J164" s="7" t="s">
-        <v>161</v>
+        <v>210</v>
       </c>
       <c r="K164" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L164" s="7" t="s">
         <v>149</v>
@@ -15752,35 +15582,35 @@
         <v>164</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="C165" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D165" s="7" t="s">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="E165" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>556</v>
+        <v>603</v>
       </c>
       <c r="G165" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H165" s="7">
-        <f t="shared" si="5"/>
-        <v>10</v>
+        <f>LEN(F165)</f>
+        <v>12</v>
       </c>
       <c r="I165" s="7" t="s">
-        <v>557</v>
+        <v>604</v>
       </c>
       <c r="J165" s="7" t="s">
-        <v>161</v>
+        <v>210</v>
       </c>
       <c r="K165" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L165" s="7" t="s">
         <v>149</v>
@@ -15794,35 +15624,35 @@
         <v>165</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="C166" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D166" s="7" t="s">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="E166" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>558</v>
+        <v>605</v>
       </c>
       <c r="G166" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H166" s="7">
-        <f t="shared" si="5"/>
-        <v>10</v>
+        <f>LEN(F166)</f>
+        <v>11</v>
       </c>
       <c r="I166" s="7" t="s">
-        <v>559</v>
+        <v>606</v>
       </c>
       <c r="J166" s="7" t="s">
-        <v>161</v>
+        <v>210</v>
       </c>
       <c r="K166" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L166" s="7" t="s">
         <v>149</v>
@@ -15836,35 +15666,35 @@
         <v>166</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="C167" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D167" s="7" t="s">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="E167" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>560</v>
+        <v>607</v>
       </c>
       <c r="G167" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H167" s="7">
-        <f t="shared" si="5"/>
-        <v>9</v>
+        <f>LEN(F167)</f>
+        <v>12</v>
       </c>
       <c r="I167" s="7" t="s">
-        <v>561</v>
+        <v>608</v>
       </c>
       <c r="J167" s="7" t="s">
-        <v>161</v>
+        <v>210</v>
       </c>
       <c r="K167" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L167" s="7" t="s">
         <v>149</v>
@@ -15878,35 +15708,35 @@
         <v>167</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="C168" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D168" s="7" t="s">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="E168" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>562</v>
+        <v>609</v>
       </c>
       <c r="G168" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H168" s="7">
-        <f t="shared" si="5"/>
+        <f>LEN(F168)</f>
         <v>12</v>
       </c>
       <c r="I168" s="7" t="s">
-        <v>563</v>
+        <v>610</v>
       </c>
       <c r="J168" s="7" t="s">
-        <v>161</v>
+        <v>210</v>
       </c>
       <c r="K168" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L168" s="7" t="s">
         <v>149</v>
@@ -15920,7 +15750,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="C169" s="7" t="s">
         <v>144</v>
@@ -15932,23 +15762,23 @@
         <v>146</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>564</v>
+        <v>611</v>
       </c>
       <c r="G169" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H169" s="7">
-        <f t="shared" si="5"/>
-        <v>11</v>
+        <f>LEN(F169)</f>
+        <v>12</v>
       </c>
       <c r="I169" s="7" t="s">
-        <v>565</v>
+        <v>612</v>
       </c>
       <c r="J169" s="7" t="s">
         <v>161</v>
       </c>
       <c r="K169" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L169" s="7" t="s">
         <v>149</v>
@@ -15962,7 +15792,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="C170" s="7" t="s">
         <v>144</v>
@@ -15974,23 +15804,23 @@
         <v>146</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>566</v>
+        <v>613</v>
       </c>
       <c r="G170" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H170" s="7">
-        <f t="shared" si="5"/>
+        <f>LEN(F170)</f>
         <v>11</v>
       </c>
       <c r="I170" s="7" t="s">
-        <v>567</v>
+        <v>614</v>
       </c>
       <c r="J170" s="7" t="s">
         <v>161</v>
       </c>
       <c r="K170" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L170" s="7" t="s">
         <v>149</v>
@@ -15999,1597 +15829,305 @@
       <c r="N170" s="3"/>
       <c r="O170" s="3"/>
     </row>
-    <row r="171" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A171" s="7">
         <v>170</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="C171" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D171" s="7" t="s">
-        <v>208</v>
+        <v>159</v>
       </c>
       <c r="E171" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>568</v>
+        <v>615</v>
       </c>
       <c r="G171" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H171" s="7">
-        <f t="shared" si="5"/>
-        <v>10</v>
+        <f>LEN(F171)</f>
+        <v>12</v>
       </c>
       <c r="I171" s="7" t="s">
-        <v>569</v>
+        <v>616</v>
       </c>
       <c r="J171" s="7" t="s">
-        <v>210</v>
+        <v>161</v>
       </c>
       <c r="K171" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L171" s="7" t="s">
         <v>149</v>
       </c>
       <c r="M171" s="3"/>
-      <c r="N171" s="3" t="s">
-        <v>570</v>
-      </c>
+      <c r="N171" s="3"/>
       <c r="O171" s="3"/>
     </row>
-    <row r="172" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A172" s="7">
         <v>171</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="C172" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D172" s="7" t="s">
-        <v>208</v>
+        <v>159</v>
       </c>
       <c r="E172" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>571</v>
+        <v>617</v>
       </c>
       <c r="G172" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H172" s="7">
-        <f t="shared" si="5"/>
-        <v>10</v>
+        <f>LEN(F172)</f>
+        <v>12</v>
       </c>
       <c r="I172" s="7" t="s">
-        <v>572</v>
+        <v>618</v>
       </c>
       <c r="J172" s="7" t="s">
-        <v>210</v>
+        <v>161</v>
       </c>
       <c r="K172" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L172" s="7" t="s">
         <v>149</v>
       </c>
       <c r="M172" s="3"/>
-      <c r="N172" s="3" t="s">
-        <v>570</v>
-      </c>
+      <c r="N172" s="3"/>
       <c r="O172" s="3"/>
     </row>
-    <row r="173" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A173" s="7">
         <v>172</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="C173" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D173" s="7" t="s">
-        <v>208</v>
+        <v>159</v>
       </c>
       <c r="E173" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>573</v>
+        <v>619</v>
       </c>
       <c r="G173" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H173" s="7">
-        <f t="shared" si="5"/>
-        <v>10</v>
+        <f>LEN(F173)</f>
+        <v>11</v>
       </c>
       <c r="I173" s="7" t="s">
-        <v>574</v>
+        <v>620</v>
       </c>
       <c r="J173" s="7" t="s">
-        <v>210</v>
+        <v>161</v>
       </c>
       <c r="K173" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L173" s="7" t="s">
         <v>149</v>
       </c>
       <c r="M173" s="3"/>
-      <c r="N173" s="3" t="s">
-        <v>570</v>
-      </c>
+      <c r="N173" s="3"/>
       <c r="O173" s="3"/>
     </row>
-    <row r="174" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A174" s="7">
         <v>173</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="C174" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D174" s="7" t="s">
-        <v>208</v>
+        <v>159</v>
       </c>
       <c r="E174" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>575</v>
+        <v>621</v>
       </c>
       <c r="G174" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H174" s="7">
-        <f t="shared" si="5"/>
+        <f>LEN(F174)</f>
         <v>12</v>
       </c>
       <c r="I174" s="7" t="s">
-        <v>576</v>
+        <v>622</v>
       </c>
       <c r="J174" s="7" t="s">
-        <v>210</v>
+        <v>161</v>
       </c>
       <c r="K174" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L174" s="7" t="s">
         <v>149</v>
       </c>
       <c r="M174" s="3"/>
-      <c r="N174" s="3" t="s">
-        <v>570</v>
-      </c>
+      <c r="N174" s="3"/>
       <c r="O174" s="3"/>
     </row>
-    <row r="175" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A175" s="7">
         <v>174</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="C175" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D175" s="7" t="s">
-        <v>208</v>
+        <v>181</v>
       </c>
       <c r="E175" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>577</v>
+        <v>623</v>
       </c>
       <c r="G175" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H175" s="7">
-        <f t="shared" si="5"/>
-        <v>10</v>
+        <f>LEN(F175)</f>
+        <v>12</v>
       </c>
       <c r="I175" s="7" t="s">
-        <v>578</v>
+        <v>624</v>
       </c>
       <c r="J175" s="7" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="K175" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L175" s="7" t="s">
         <v>149</v>
       </c>
       <c r="M175" s="3"/>
-      <c r="N175" s="3" t="s">
-        <v>570</v>
-      </c>
+      <c r="N175" s="3"/>
       <c r="O175" s="3"/>
     </row>
-    <row r="176" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A176" s="7">
         <v>175</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="C176" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D176" s="7" t="s">
-        <v>208</v>
+        <v>181</v>
       </c>
       <c r="E176" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>579</v>
+        <v>625</v>
       </c>
       <c r="G176" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H176" s="7">
-        <f t="shared" si="5"/>
-        <v>10</v>
+        <f>LEN(F176)</f>
+        <v>12</v>
       </c>
       <c r="I176" s="7" t="s">
-        <v>580</v>
+        <v>626</v>
       </c>
       <c r="J176" s="7" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="K176" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L176" s="7" t="s">
         <v>149</v>
       </c>
       <c r="M176" s="3"/>
-      <c r="N176" s="3" t="s">
-        <v>570</v>
-      </c>
+      <c r="N176" s="3"/>
       <c r="O176" s="3"/>
     </row>
-    <row r="177" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A177" s="7">
         <v>176</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="C177" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D177" s="7" t="s">
-        <v>208</v>
+        <v>145</v>
       </c>
       <c r="E177" s="7" t="s">
         <v>146</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>581</v>
+        <v>627</v>
       </c>
       <c r="G177" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H177" s="7">
-        <f t="shared" si="5"/>
+        <f>LEN(F177)</f>
         <v>12</v>
       </c>
       <c r="I177" s="7" t="s">
-        <v>582</v>
+        <v>628</v>
       </c>
       <c r="J177" s="7" t="s">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="K177" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L177" s="7" t="s">
         <v>149</v>
       </c>
       <c r="M177" s="3"/>
-      <c r="N177" s="3" t="s">
-        <v>570</v>
-      </c>
+      <c r="N177" s="3"/>
       <c r="O177" s="3"/>
     </row>
-    <row r="178" spans="1:15" ht="25" x14ac:dyDescent="0.45">
-      <c r="A178" s="7">
-        <v>177</v>
-      </c>
-      <c r="B178" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C178" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D178" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="E178" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F178" s="7" t="s">
-        <v>583</v>
-      </c>
-      <c r="G178" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H178" s="7">
-        <f t="shared" si="5"/>
-        <v>9</v>
-      </c>
-      <c r="I178" s="7" t="s">
-        <v>584</v>
-      </c>
-      <c r="J178" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="K178" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="L178" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M178" s="3"/>
-      <c r="N178" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="O178" s="3"/>
-    </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A179" s="7">
-        <v>178</v>
-      </c>
-      <c r="B179" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C179" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D179" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="E179" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F179" s="7" t="s">
-        <v>585</v>
-      </c>
-      <c r="G179" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H179" s="7">
-        <f t="shared" si="5"/>
-        <v>11</v>
-      </c>
-      <c r="I179" s="7" t="s">
-        <v>586</v>
-      </c>
-      <c r="J179" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="K179" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="L179" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M179" s="3"/>
-      <c r="N179" s="3"/>
-      <c r="O179" s="3"/>
-    </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A180" s="7">
-        <v>179</v>
-      </c>
-      <c r="B180" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C180" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D180" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="E180" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F180" s="7" t="s">
-        <v>587</v>
-      </c>
-      <c r="G180" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H180" s="7">
-        <f t="shared" si="5"/>
-        <v>11</v>
-      </c>
-      <c r="I180" s="7" t="s">
-        <v>588</v>
-      </c>
-      <c r="J180" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="K180" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L180" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M180" s="3"/>
-      <c r="N180" s="3"/>
-      <c r="O180" s="3"/>
-    </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A181" s="7">
-        <v>180</v>
-      </c>
-      <c r="B181" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C181" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D181" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="E181" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F181" s="7" t="s">
-        <v>589</v>
-      </c>
-      <c r="G181" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H181" s="7">
-        <f t="shared" si="5"/>
-        <v>11</v>
-      </c>
-      <c r="I181" s="7" t="s">
-        <v>590</v>
-      </c>
-      <c r="J181" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="K181" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L181" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M181" s="3"/>
-      <c r="N181" s="3"/>
-      <c r="O181" s="3"/>
-    </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A182" s="7">
-        <v>181</v>
-      </c>
-      <c r="B182" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C182" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D182" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="E182" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F182" s="7" t="s">
-        <v>591</v>
-      </c>
-      <c r="G182" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H182" s="7">
-        <f t="shared" si="5"/>
-        <v>11</v>
-      </c>
-      <c r="I182" s="7" t="s">
-        <v>592</v>
-      </c>
-      <c r="J182" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="K182" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L182" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M182" s="3"/>
-      <c r="N182" s="3"/>
-      <c r="O182" s="3"/>
-    </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A183" s="7">
-        <v>182</v>
-      </c>
-      <c r="B183" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C183" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D183" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="E183" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F183" s="7" t="s">
-        <v>593</v>
-      </c>
-      <c r="G183" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H183" s="7">
-        <f t="shared" si="5"/>
-        <v>9</v>
-      </c>
-      <c r="I183" s="7" t="s">
-        <v>594</v>
-      </c>
-      <c r="J183" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="K183" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L183" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M183" s="3"/>
-      <c r="N183" s="3"/>
-      <c r="O183" s="3"/>
-    </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A184" s="7">
-        <v>183</v>
-      </c>
-      <c r="B184" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C184" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D184" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="E184" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F184" s="7" t="s">
-        <v>595</v>
-      </c>
-      <c r="G184" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H184" s="7">
-        <f t="shared" si="5"/>
-        <v>11</v>
-      </c>
-      <c r="I184" s="7" t="s">
-        <v>596</v>
-      </c>
-      <c r="J184" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="K184" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L184" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M184" s="3"/>
-      <c r="N184" s="3"/>
-      <c r="O184" s="3"/>
-    </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A185" s="7">
-        <v>184</v>
-      </c>
-      <c r="B185" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C185" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D185" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="E185" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F185" s="7" t="s">
-        <v>597</v>
-      </c>
-      <c r="G185" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H185" s="7">
-        <f t="shared" si="5"/>
-        <v>12</v>
-      </c>
-      <c r="I185" s="7" t="s">
-        <v>598</v>
-      </c>
-      <c r="J185" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="K185" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L185" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M185" s="3"/>
-      <c r="N185" s="3"/>
-      <c r="O185" s="3"/>
-    </row>
-    <row r="186" spans="1:15" ht="25" x14ac:dyDescent="0.45">
-      <c r="A186" s="7">
-        <v>185</v>
-      </c>
-      <c r="B186" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C186" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D186" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="E186" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F186" s="7" t="s">
-        <v>599</v>
-      </c>
-      <c r="G186" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H186" s="7">
-        <f t="shared" si="5"/>
-        <v>11</v>
-      </c>
-      <c r="I186" s="7" t="s">
-        <v>600</v>
-      </c>
-      <c r="J186" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="K186" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L186" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M186" s="3"/>
-      <c r="N186" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="O186" s="3"/>
-    </row>
-    <row r="187" spans="1:15" ht="25" x14ac:dyDescent="0.45">
-      <c r="A187" s="7">
-        <v>186</v>
-      </c>
-      <c r="B187" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C187" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D187" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="E187" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F187" s="7" t="s">
-        <v>601</v>
-      </c>
-      <c r="G187" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H187" s="7">
-        <f t="shared" si="5"/>
-        <v>11</v>
-      </c>
-      <c r="I187" s="7" t="s">
-        <v>602</v>
-      </c>
-      <c r="J187" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="K187" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L187" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M187" s="3"/>
-      <c r="N187" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="O187" s="3"/>
-    </row>
-    <row r="188" spans="1:15" ht="25" x14ac:dyDescent="0.45">
-      <c r="A188" s="7">
-        <v>187</v>
-      </c>
-      <c r="B188" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C188" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D188" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="E188" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F188" s="7" t="s">
-        <v>603</v>
-      </c>
-      <c r="G188" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H188" s="7">
-        <f t="shared" ref="H188:H207" si="6">LEN(F188)</f>
-        <v>11</v>
-      </c>
-      <c r="I188" s="7" t="s">
-        <v>604</v>
-      </c>
-      <c r="J188" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="K188" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L188" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M188" s="3"/>
-      <c r="N188" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="O188" s="3"/>
-    </row>
-    <row r="189" spans="1:15" ht="25" x14ac:dyDescent="0.45">
-      <c r="A189" s="7">
-        <v>188</v>
-      </c>
-      <c r="B189" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C189" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D189" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="E189" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F189" s="7" t="s">
-        <v>605</v>
-      </c>
-      <c r="G189" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H189" s="7">
-        <f t="shared" si="6"/>
-        <v>12</v>
-      </c>
-      <c r="I189" s="7" t="s">
-        <v>606</v>
-      </c>
-      <c r="J189" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="K189" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L189" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M189" s="3"/>
-      <c r="N189" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="O189" s="3"/>
-    </row>
-    <row r="190" spans="1:15" ht="25" x14ac:dyDescent="0.45">
-      <c r="A190" s="7">
-        <v>189</v>
-      </c>
-      <c r="B190" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C190" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D190" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="E190" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F190" s="7" t="s">
-        <v>607</v>
-      </c>
-      <c r="G190" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H190" s="7">
-        <f t="shared" si="6"/>
-        <v>10</v>
-      </c>
-      <c r="I190" s="7" t="s">
-        <v>608</v>
-      </c>
-      <c r="J190" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="K190" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L190" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M190" s="3"/>
-      <c r="N190" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="O190" s="3"/>
-    </row>
-    <row r="191" spans="1:15" ht="25" x14ac:dyDescent="0.45">
-      <c r="A191" s="7">
-        <v>190</v>
-      </c>
-      <c r="B191" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C191" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D191" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="E191" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F191" s="7" t="s">
-        <v>609</v>
-      </c>
-      <c r="G191" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H191" s="7">
-        <f t="shared" si="6"/>
-        <v>11</v>
-      </c>
-      <c r="I191" s="7" t="s">
-        <v>610</v>
-      </c>
-      <c r="J191" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="K191" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L191" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M191" s="3"/>
-      <c r="N191" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="O191" s="3"/>
-    </row>
-    <row r="192" spans="1:15" ht="25" x14ac:dyDescent="0.45">
-      <c r="A192" s="7">
-        <v>191</v>
-      </c>
-      <c r="B192" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C192" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D192" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="E192" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F192" s="7" t="s">
-        <v>611</v>
-      </c>
-      <c r="G192" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H192" s="7">
-        <f t="shared" si="6"/>
-        <v>10</v>
-      </c>
-      <c r="I192" s="7" t="s">
-        <v>612</v>
-      </c>
-      <c r="J192" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="K192" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L192" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M192" s="3"/>
-      <c r="N192" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="O192" s="3"/>
-    </row>
-    <row r="193" spans="1:15" ht="25" x14ac:dyDescent="0.45">
-      <c r="A193" s="7">
-        <v>192</v>
-      </c>
-      <c r="B193" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C193" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D193" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="E193" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F193" s="7" t="s">
-        <v>613</v>
-      </c>
-      <c r="G193" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H193" s="7">
-        <f t="shared" si="6"/>
-        <v>12</v>
-      </c>
-      <c r="I193" s="7" t="s">
-        <v>614</v>
-      </c>
-      <c r="J193" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="K193" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L193" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M193" s="3"/>
-      <c r="N193" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="O193" s="3"/>
-    </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A194" s="7">
-        <v>193</v>
-      </c>
-      <c r="B194" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C194" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D194" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E194" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F194" s="7" t="s">
-        <v>615</v>
-      </c>
-      <c r="G194" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H194" s="7">
-        <f t="shared" si="6"/>
-        <v>12</v>
-      </c>
-      <c r="I194" s="7" t="s">
-        <v>616</v>
-      </c>
-      <c r="J194" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="K194" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L194" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M194" s="3"/>
-      <c r="N194" s="3"/>
-      <c r="O194" s="3"/>
-    </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A195" s="7">
-        <v>194</v>
-      </c>
-      <c r="B195" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C195" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D195" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E195" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F195" s="7" t="s">
-        <v>617</v>
-      </c>
-      <c r="G195" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H195" s="7">
-        <f t="shared" si="6"/>
-        <v>11</v>
-      </c>
-      <c r="I195" s="7" t="s">
-        <v>618</v>
-      </c>
-      <c r="J195" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="K195" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L195" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M195" s="3"/>
-      <c r="N195" s="3"/>
-      <c r="O195" s="3"/>
-    </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A196" s="7">
-        <v>195</v>
-      </c>
-      <c r="B196" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C196" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D196" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E196" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F196" s="7" t="s">
-        <v>619</v>
-      </c>
-      <c r="G196" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H196" s="7">
-        <f t="shared" si="6"/>
-        <v>10</v>
-      </c>
-      <c r="I196" s="7" t="s">
-        <v>620</v>
-      </c>
-      <c r="J196" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="K196" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L196" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M196" s="3"/>
-      <c r="N196" s="3"/>
-      <c r="O196" s="3"/>
-    </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A197" s="7">
-        <v>196</v>
-      </c>
-      <c r="B197" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C197" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D197" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E197" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F197" s="7" t="s">
-        <v>621</v>
-      </c>
-      <c r="G197" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H197" s="7">
-        <f t="shared" si="6"/>
-        <v>11</v>
-      </c>
-      <c r="I197" s="7" t="s">
-        <v>622</v>
-      </c>
-      <c r="J197" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="K197" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L197" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M197" s="3"/>
-      <c r="N197" s="3"/>
-      <c r="O197" s="3"/>
-    </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A198" s="7">
-        <v>197</v>
-      </c>
-      <c r="B198" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C198" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D198" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E198" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F198" s="7" t="s">
-        <v>623</v>
-      </c>
-      <c r="G198" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H198" s="7">
-        <f t="shared" si="6"/>
-        <v>11</v>
-      </c>
-      <c r="I198" s="7" t="s">
-        <v>624</v>
-      </c>
-      <c r="J198" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="K198" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L198" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M198" s="3"/>
-      <c r="N198" s="3"/>
-      <c r="O198" s="3"/>
-    </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A199" s="7">
-        <v>198</v>
-      </c>
-      <c r="B199" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C199" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D199" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E199" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F199" s="7" t="s">
-        <v>625</v>
-      </c>
-      <c r="G199" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H199" s="7">
-        <f t="shared" si="6"/>
-        <v>12</v>
-      </c>
-      <c r="I199" s="7" t="s">
-        <v>626</v>
-      </c>
-      <c r="J199" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="K199" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L199" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M199" s="3"/>
-      <c r="N199" s="3"/>
-      <c r="O199" s="3"/>
-    </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A200" s="7">
-        <v>199</v>
-      </c>
-      <c r="B200" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C200" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D200" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E200" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F200" s="7" t="s">
-        <v>627</v>
-      </c>
-      <c r="G200" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H200" s="7">
-        <f t="shared" si="6"/>
-        <v>12</v>
-      </c>
-      <c r="I200" s="7" t="s">
-        <v>628</v>
-      </c>
-      <c r="J200" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="K200" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L200" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M200" s="3"/>
-      <c r="N200" s="3"/>
-      <c r="O200" s="3"/>
-    </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A201" s="7">
-        <v>200</v>
-      </c>
-      <c r="B201" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C201" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D201" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E201" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F201" s="7" t="s">
-        <v>629</v>
-      </c>
-      <c r="G201" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H201" s="7">
-        <f t="shared" si="6"/>
-        <v>12</v>
-      </c>
-      <c r="I201" s="7" t="s">
-        <v>630</v>
-      </c>
-      <c r="J201" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="K201" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L201" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M201" s="3"/>
-      <c r="N201" s="3"/>
-      <c r="O201" s="3"/>
-    </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A202" s="7">
-        <v>201</v>
-      </c>
-      <c r="B202" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C202" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D202" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E202" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F202" s="7" t="s">
-        <v>631</v>
-      </c>
-      <c r="G202" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H202" s="7">
-        <f t="shared" si="6"/>
-        <v>11</v>
-      </c>
-      <c r="I202" s="7" t="s">
-        <v>632</v>
-      </c>
-      <c r="J202" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="K202" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L202" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M202" s="3"/>
-      <c r="N202" s="3"/>
-      <c r="O202" s="3"/>
-    </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A203" s="7">
-        <v>202</v>
-      </c>
-      <c r="B203" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C203" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D203" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E203" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F203" s="7" t="s">
-        <v>633</v>
-      </c>
-      <c r="G203" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H203" s="7">
-        <f t="shared" si="6"/>
-        <v>11</v>
-      </c>
-      <c r="I203" s="7" t="s">
-        <v>634</v>
-      </c>
-      <c r="J203" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="K203" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L203" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M203" s="3"/>
-      <c r="N203" s="3"/>
-      <c r="O203" s="3"/>
-    </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A204" s="7">
-        <v>203</v>
-      </c>
-      <c r="B204" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C204" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D204" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="E204" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F204" s="7" t="s">
-        <v>635</v>
-      </c>
-      <c r="G204" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H204" s="7">
-        <f t="shared" si="6"/>
-        <v>10</v>
-      </c>
-      <c r="I204" s="7" t="s">
-        <v>636</v>
-      </c>
-      <c r="J204" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="K204" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L204" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M204" s="3"/>
-      <c r="N204" s="3"/>
-      <c r="O204" s="3"/>
-    </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A205" s="7">
-        <v>204</v>
-      </c>
-      <c r="B205" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C205" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D205" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E205" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F205" s="7" t="s">
-        <v>637</v>
-      </c>
-      <c r="G205" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H205" s="7">
-        <f t="shared" si="6"/>
-        <v>12</v>
-      </c>
-      <c r="I205" s="7" t="s">
-        <v>638</v>
-      </c>
-      <c r="J205" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="K205" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L205" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M205" s="3"/>
-      <c r="N205" s="3"/>
-      <c r="O205" s="3"/>
-    </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A206" s="7">
-        <v>205</v>
-      </c>
-      <c r="B206" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C206" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D206" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E206" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F206" s="7" t="s">
-        <v>639</v>
-      </c>
-      <c r="G206" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H206" s="7">
-        <f t="shared" si="6"/>
-        <v>11</v>
-      </c>
-      <c r="I206" s="7" t="s">
-        <v>640</v>
-      </c>
-      <c r="J206" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="K206" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L206" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M206" s="3"/>
-      <c r="N206" s="3"/>
-      <c r="O206" s="3"/>
-    </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A207" s="7">
-        <v>206</v>
-      </c>
-      <c r="B207" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="C207" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D207" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E207" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F207" s="7" t="s">
-        <v>641</v>
-      </c>
-      <c r="G207" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H207" s="7">
-        <f t="shared" si="6"/>
-        <v>11</v>
-      </c>
-      <c r="I207" s="7" t="s">
-        <v>642</v>
-      </c>
-      <c r="J207" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="K207" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="L207" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M207" s="3"/>
-      <c r="N207" s="3"/>
-      <c r="O207" s="3"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O207" xr:uid="{243C8A1C-2FBA-4873-BD31-7545635970F1}"/>
+  <autoFilter ref="A1:O177" xr:uid="{243C8A1C-2FBA-4873-BD31-7545635970F1}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M207" xr:uid="{29F577E0-A9A7-4D3D-B3E7-99484ADFB535}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M177" xr:uid="{29F577E0-A9A7-4D3D-B3E7-99484ADFB535}">
       <formula1>"승인,수정,제외"</formula1>
     </dataValidation>
   </dataValidations>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E34DA0-97F9-4BBB-98D8-D185EAF3A241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF63781-0D58-4224-A8A8-F458BEECFF74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -7957,9 +7957,6 @@
     <t>기름을 덜 쓰는 반찬으로 아침을 먹어요.</t>
   </si>
   <si>
-    <t>아메추: 맑은 국/계란국</t>
-  </si>
-  <si>
     <t>저메추: 생선구이/수육</t>
   </si>
   <si>
@@ -8078,6 +8075,10 @@
   </si>
   <si>
     <t>10-12 끼니 추천을 「아메추: A/B」 · 「저메추: A/B」 두 가지 고르기로 바꿈(아침 18 · 저녁 20). 한 가지씩이던 아침·저녁 추천  지움. 국수는 천천히 후루룩 → 면은 꼭꼭 씹어 먹기. 합계 176개</t>
+  </si>
+  <si>
+    <t>아메추: 맑은 국/뭇국</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -8653,7 +8654,7 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
   </sheetData>
@@ -14550,7 +14551,7 @@
         <v>0</v>
       </c>
       <c r="H140" s="7">
-        <f>LEN(F140)</f>
+        <f t="shared" ref="H140:H177" si="5">LEN(F140)</f>
         <v>12</v>
       </c>
       <c r="I140" s="7" t="s">
@@ -14592,7 +14593,7 @@
         <v>0</v>
       </c>
       <c r="H141" s="7">
-        <f>LEN(F141)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I141" s="7" t="s">
@@ -14634,7 +14635,7 @@
         <v>0</v>
       </c>
       <c r="H142" s="7">
-        <f>LEN(F142)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I142" s="7" t="s">
@@ -14676,7 +14677,7 @@
         <v>0</v>
       </c>
       <c r="H143" s="7">
-        <f>LEN(F143)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I143" s="7" t="s">
@@ -14718,7 +14719,7 @@
         <v>0</v>
       </c>
       <c r="H144" s="7">
-        <f>LEN(F144)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I144" s="7" t="s">
@@ -14760,7 +14761,7 @@
         <v>0</v>
       </c>
       <c r="H145" s="7">
-        <f>LEN(F145)</f>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="I145" s="7" t="s">
@@ -14802,7 +14803,7 @@
         <v>0</v>
       </c>
       <c r="H146" s="7">
-        <f>LEN(F146)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I146" s="7" t="s">
@@ -14844,7 +14845,7 @@
         <v>0</v>
       </c>
       <c r="H147" s="7">
-        <f>LEN(F147)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I147" s="7" t="s">
@@ -14886,7 +14887,7 @@
         <v>0</v>
       </c>
       <c r="H148" s="7">
-        <f>LEN(F148)</f>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="I148" s="7" t="s">
@@ -14928,7 +14929,7 @@
         <v>0</v>
       </c>
       <c r="H149" s="7">
-        <f>LEN(F149)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I149" s="7" t="s">
@@ -14970,7 +14971,7 @@
         <v>0</v>
       </c>
       <c r="H150" s="7">
-        <f>LEN(F150)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I150" s="7" t="s">
@@ -15012,7 +15013,7 @@
         <v>0</v>
       </c>
       <c r="H151" s="7">
-        <f>LEN(F151)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I151" s="7" t="s">
@@ -15054,7 +15055,7 @@
         <v>0</v>
       </c>
       <c r="H152" s="7">
-        <f>LEN(F152)</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="I152" s="7" t="s">
@@ -15096,7 +15097,7 @@
         <v>0</v>
       </c>
       <c r="H153" s="7">
-        <f>LEN(F153)</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="I153" s="7" t="s">
@@ -15138,7 +15139,7 @@
         <v>0</v>
       </c>
       <c r="H154" s="7">
-        <f>LEN(F154)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I154" s="7" t="s">
@@ -15180,7 +15181,7 @@
         <v>0</v>
       </c>
       <c r="H155" s="7">
-        <f>LEN(F155)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I155" s="7" t="s">
@@ -15222,7 +15223,7 @@
         <v>0</v>
       </c>
       <c r="H156" s="7">
-        <f>LEN(F156)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I156" s="7" t="s">
@@ -15258,14 +15259,14 @@
         <v>146</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>589</v>
+        <v>629</v>
       </c>
       <c r="G157" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H157" s="7">
-        <f>LEN(F157)</f>
-        <v>13</v>
+        <f t="shared" si="5"/>
+        <v>12</v>
       </c>
       <c r="I157" s="7" t="s">
         <v>465</v>
@@ -15300,17 +15301,17 @@
         <v>146</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G158" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H158" s="7">
-        <f>LEN(F158)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I158" s="7" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="J158" s="7" t="s">
         <v>215</v>
@@ -15342,17 +15343,17 @@
         <v>146</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G159" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H159" s="7">
-        <f>LEN(F159)</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="I159" s="7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="J159" s="7" t="s">
         <v>215</v>
@@ -15384,13 +15385,13 @@
         <v>146</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G160" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H160" s="7">
-        <f>LEN(F160)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I160" s="7" t="s">
@@ -15426,17 +15427,17 @@
         <v>146</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G161" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H161" s="7">
-        <f>LEN(F161)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I161" s="7" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="J161" s="7" t="s">
         <v>215</v>
@@ -15468,17 +15469,17 @@
         <v>146</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G162" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H162" s="7">
-        <f>LEN(F162)</f>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="I162" s="7" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J162" s="7" t="s">
         <v>215</v>
@@ -15510,17 +15511,17 @@
         <v>146</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G163" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H163" s="7">
-        <f>LEN(F163)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I163" s="7" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J163" s="7" t="s">
         <v>215</v>
@@ -15552,17 +15553,17 @@
         <v>146</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G164" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H164" s="7">
-        <f>LEN(F164)</f>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="I164" s="7" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J164" s="7" t="s">
         <v>210</v>
@@ -15594,17 +15595,17 @@
         <v>146</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G165" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H165" s="7">
-        <f>LEN(F165)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I165" s="7" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="J165" s="7" t="s">
         <v>210</v>
@@ -15636,17 +15637,17 @@
         <v>146</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G166" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H166" s="7">
-        <f>LEN(F166)</f>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="I166" s="7" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="J166" s="7" t="s">
         <v>210</v>
@@ -15678,17 +15679,17 @@
         <v>146</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="G167" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H167" s="7">
-        <f>LEN(F167)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I167" s="7" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="J167" s="7" t="s">
         <v>210</v>
@@ -15720,17 +15721,17 @@
         <v>146</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G168" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H168" s="7">
-        <f>LEN(F168)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I168" s="7" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="J168" s="7" t="s">
         <v>210</v>
@@ -15762,17 +15763,17 @@
         <v>146</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G169" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H169" s="7">
-        <f>LEN(F169)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I169" s="7" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="J169" s="7" t="s">
         <v>161</v>
@@ -15804,17 +15805,17 @@
         <v>146</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G170" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H170" s="7">
-        <f>LEN(F170)</f>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="I170" s="7" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J170" s="7" t="s">
         <v>161</v>
@@ -15846,17 +15847,17 @@
         <v>146</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="G171" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H171" s="7">
-        <f>LEN(F171)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I171" s="7" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="J171" s="7" t="s">
         <v>161</v>
@@ -15888,17 +15889,17 @@
         <v>146</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G172" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H172" s="7">
-        <f>LEN(F172)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I172" s="7" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="J172" s="7" t="s">
         <v>161</v>
@@ -15930,17 +15931,17 @@
         <v>146</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="G173" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H173" s="7">
-        <f>LEN(F173)</f>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="I173" s="7" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="J173" s="7" t="s">
         <v>161</v>
@@ -15972,17 +15973,17 @@
         <v>146</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="G174" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H174" s="7">
-        <f>LEN(F174)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I174" s="7" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="J174" s="7" t="s">
         <v>161</v>
@@ -16014,17 +16015,17 @@
         <v>146</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G175" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H175" s="7">
-        <f>LEN(F175)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I175" s="7" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="J175" s="7" t="s">
         <v>187</v>
@@ -16056,17 +16057,17 @@
         <v>146</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="G176" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H176" s="7">
-        <f>LEN(F176)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I176" s="7" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="J176" s="7" t="s">
         <v>187</v>
@@ -16098,17 +16099,17 @@
         <v>146</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G177" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H177" s="7">
-        <f>LEN(F177)</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I177" s="7" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J177" s="7" t="s">
         <v>155</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF63781-0D58-4224-A8A8-F458BEECFF74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5EB0D1C-B913-4FCF-A4A0-6E991FA8B8B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -7704,10 +7704,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>입맛 있을 때 먹어 두기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>입맛이 돌 때 먹어 두면 하루 식사를 채우기 쉬워요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8078,6 +8074,10 @@
   </si>
   <si>
     <t>아메추: 맑은 국/뭇국</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입맛 돌 때 먹어 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8649,12 +8649,12 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
   </sheetData>
@@ -8917,7 +8917,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>238</v>
@@ -8927,7 +8927,7 @@
         <v>12</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -9169,7 +9169,7 @@
         <v>220</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>244</v>
@@ -9337,7 +9337,7 @@
         <v>220</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>248</v>
@@ -9347,7 +9347,7 @@
         <v>11</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>27</v>
@@ -9715,7 +9715,7 @@
         <v>220</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>257</v>
@@ -9725,7 +9725,7 @@
         <v>12</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>11</v>
@@ -9925,7 +9925,7 @@
         <v>12</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>262</v>
@@ -9935,7 +9935,7 @@
         <v>11</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>8</v>
@@ -10261,17 +10261,17 @@
         <v>0</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>517</v>
+        <v>629</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>270</v>
       </c>
       <c r="H38" s="3">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>32</v>
@@ -10639,7 +10639,7 @@
         <v>12</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>279</v>
@@ -10649,7 +10649,7 @@
         <v>12</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>43</v>
@@ -10849,7 +10849,7 @@
         <v>7</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>284</v>
@@ -10859,7 +10859,7 @@
         <v>9</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>46</v>
@@ -10891,7 +10891,7 @@
         <v>12</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>285</v>
@@ -10933,7 +10933,7 @@
         <v>3</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>286</v>
@@ -10943,7 +10943,7 @@
         <v>12</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>23</v>
@@ -11101,7 +11101,7 @@
         <v>7</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>290</v>
@@ -11111,7 +11111,7 @@
         <v>10</v>
       </c>
       <c r="I58" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>49</v>
@@ -11395,7 +11395,7 @@
         <v>146</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="G65" s="5" t="s">
         <v>296</v>
@@ -11405,7 +11405,7 @@
         <v>10</v>
       </c>
       <c r="I65" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>147</v>
@@ -11479,7 +11479,7 @@
         <v>146</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>299</v>
@@ -11489,7 +11489,7 @@
         <v>12</v>
       </c>
       <c r="I67" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="J67" s="3" t="s">
         <v>151</v>
@@ -12235,7 +12235,7 @@
         <v>146</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="G85" s="5" t="s">
         <v>332</v>
@@ -12245,7 +12245,7 @@
         <v>11</v>
       </c>
       <c r="I85" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="J85" s="3" t="s">
         <v>187</v>
@@ -12613,7 +12613,7 @@
         <v>146</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="G94" s="5" t="s">
         <v>346</v>
@@ -12623,7 +12623,7 @@
         <v>12</v>
       </c>
       <c r="I94" s="7" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>198</v>
@@ -12655,7 +12655,7 @@
         <v>146</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G95" s="5" t="s">
         <v>347</v>
@@ -12665,7 +12665,7 @@
         <v>12</v>
       </c>
       <c r="I95" s="7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J95" s="3" t="s">
         <v>200</v>
@@ -13033,7 +13033,7 @@
         <v>146</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G104" s="5" t="s">
         <v>362</v>
@@ -13043,7 +13043,7 @@
         <v>9</v>
       </c>
       <c r="I104" s="7" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="J104" s="3" t="s">
         <v>210</v>
@@ -13285,7 +13285,7 @@
         <v>146</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G110" s="5" t="s">
         <v>462</v>
@@ -13295,7 +13295,7 @@
         <v>10</v>
       </c>
       <c r="I110" s="7" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="J110" s="3" t="s">
         <v>216</v>
@@ -14503,17 +14503,17 @@
         <v>146</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G139" s="7" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H139" s="7">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="I139" s="7" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="J139" s="7" t="s">
         <v>200</v>
@@ -14545,7 +14545,7 @@
         <v>146</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G140" s="7" t="s">
         <v>0</v>
@@ -14555,7 +14555,7 @@
         <v>12</v>
       </c>
       <c r="I140" s="7" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="J140" s="7" t="s">
         <v>155</v>
@@ -14587,7 +14587,7 @@
         <v>146</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G141" s="7" t="s">
         <v>0</v>
@@ -14597,7 +14597,7 @@
         <v>12</v>
       </c>
       <c r="I141" s="7" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="J141" s="7" t="s">
         <v>155</v>
@@ -14629,7 +14629,7 @@
         <v>146</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G142" s="7" t="s">
         <v>0</v>
@@ -14639,7 +14639,7 @@
         <v>12</v>
       </c>
       <c r="I142" s="7" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="J142" s="7" t="s">
         <v>155</v>
@@ -14671,7 +14671,7 @@
         <v>146</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G143" s="7" t="s">
         <v>0</v>
@@ -14681,7 +14681,7 @@
         <v>12</v>
       </c>
       <c r="I143" s="7" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="J143" s="7" t="s">
         <v>155</v>
@@ -14713,7 +14713,7 @@
         <v>146</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G144" s="7" t="s">
         <v>0</v>
@@ -14723,7 +14723,7 @@
         <v>12</v>
       </c>
       <c r="I144" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="J144" s="7" t="s">
         <v>155</v>
@@ -14755,7 +14755,7 @@
         <v>146</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G145" s="7" t="s">
         <v>0</v>
@@ -14765,7 +14765,7 @@
         <v>11</v>
       </c>
       <c r="I145" s="7" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="J145" s="7" t="s">
         <v>161</v>
@@ -14797,7 +14797,7 @@
         <v>146</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G146" s="7" t="s">
         <v>0</v>
@@ -14807,7 +14807,7 @@
         <v>12</v>
       </c>
       <c r="I146" s="7" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="J146" s="7" t="s">
         <v>161</v>
@@ -14839,7 +14839,7 @@
         <v>146</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G147" s="7" t="s">
         <v>0</v>
@@ -14849,7 +14849,7 @@
         <v>12</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="J147" s="7" t="s">
         <v>161</v>
@@ -14881,7 +14881,7 @@
         <v>146</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G148" s="7" t="s">
         <v>0</v>
@@ -14891,7 +14891,7 @@
         <v>11</v>
       </c>
       <c r="I148" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="J148" s="7" t="s">
         <v>161</v>
@@ -14923,7 +14923,7 @@
         <v>146</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G149" s="7" t="s">
         <v>0</v>
@@ -14933,7 +14933,7 @@
         <v>12</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="J149" s="7" t="s">
         <v>161</v>
@@ -14965,7 +14965,7 @@
         <v>146</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="G150" s="7" t="s">
         <v>0</v>
@@ -14975,7 +14975,7 @@
         <v>12</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="J150" s="7" t="s">
         <v>210</v>
@@ -15007,7 +15007,7 @@
         <v>146</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="G151" s="7" t="s">
         <v>0</v>
@@ -15017,7 +15017,7 @@
         <v>12</v>
       </c>
       <c r="I151" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J151" s="7" t="s">
         <v>210</v>
@@ -15049,7 +15049,7 @@
         <v>146</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G152" s="7" t="s">
         <v>0</v>
@@ -15059,7 +15059,7 @@
         <v>10</v>
       </c>
       <c r="I152" s="7" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="J152" s="7" t="s">
         <v>210</v>
@@ -15091,7 +15091,7 @@
         <v>146</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G153" s="7" t="s">
         <v>0</v>
@@ -15101,7 +15101,7 @@
         <v>10</v>
       </c>
       <c r="I153" s="7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="J153" s="7" t="s">
         <v>210</v>
@@ -15133,7 +15133,7 @@
         <v>146</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="G154" s="7" t="s">
         <v>0</v>
@@ -15143,7 +15143,7 @@
         <v>12</v>
       </c>
       <c r="I154" s="7" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="J154" s="7" t="s">
         <v>210</v>
@@ -15175,7 +15175,7 @@
         <v>146</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="G155" s="7" t="s">
         <v>0</v>
@@ -15185,7 +15185,7 @@
         <v>12</v>
       </c>
       <c r="I155" s="7" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J155" s="7" t="s">
         <v>210</v>
@@ -15217,7 +15217,7 @@
         <v>146</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="G156" s="7" t="s">
         <v>0</v>
@@ -15227,7 +15227,7 @@
         <v>12</v>
       </c>
       <c r="I156" s="7" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="J156" s="7" t="s">
         <v>215</v>
@@ -15259,7 +15259,7 @@
         <v>146</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="G157" s="7" t="s">
         <v>0</v>
@@ -15301,7 +15301,7 @@
         <v>146</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G158" s="7" t="s">
         <v>0</v>
@@ -15311,7 +15311,7 @@
         <v>12</v>
       </c>
       <c r="I158" s="7" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J158" s="7" t="s">
         <v>215</v>
@@ -15343,7 +15343,7 @@
         <v>146</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G159" s="7" t="s">
         <v>0</v>
@@ -15353,7 +15353,7 @@
         <v>10</v>
       </c>
       <c r="I159" s="7" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="J159" s="7" t="s">
         <v>215</v>
@@ -15385,7 +15385,7 @@
         <v>146</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G160" s="7" t="s">
         <v>0</v>
@@ -15427,7 +15427,7 @@
         <v>146</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G161" s="7" t="s">
         <v>0</v>
@@ -15437,7 +15437,7 @@
         <v>12</v>
       </c>
       <c r="I161" s="7" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="J161" s="7" t="s">
         <v>215</v>
@@ -15469,7 +15469,7 @@
         <v>146</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G162" s="7" t="s">
         <v>0</v>
@@ -15479,7 +15479,7 @@
         <v>11</v>
       </c>
       <c r="I162" s="7" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="J162" s="7" t="s">
         <v>215</v>
@@ -15511,7 +15511,7 @@
         <v>146</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G163" s="7" t="s">
         <v>0</v>
@@ -15521,7 +15521,7 @@
         <v>12</v>
       </c>
       <c r="I163" s="7" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J163" s="7" t="s">
         <v>215</v>
@@ -15553,7 +15553,7 @@
         <v>146</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G164" s="7" t="s">
         <v>0</v>
@@ -15563,7 +15563,7 @@
         <v>11</v>
       </c>
       <c r="I164" s="7" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J164" s="7" t="s">
         <v>210</v>
@@ -15595,7 +15595,7 @@
         <v>146</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G165" s="7" t="s">
         <v>0</v>
@@ -15605,7 +15605,7 @@
         <v>12</v>
       </c>
       <c r="I165" s="7" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J165" s="7" t="s">
         <v>210</v>
@@ -15637,7 +15637,7 @@
         <v>146</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G166" s="7" t="s">
         <v>0</v>
@@ -15647,7 +15647,7 @@
         <v>11</v>
       </c>
       <c r="I166" s="7" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="J166" s="7" t="s">
         <v>210</v>
@@ -15679,7 +15679,7 @@
         <v>146</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G167" s="7" t="s">
         <v>0</v>
@@ -15689,7 +15689,7 @@
         <v>12</v>
       </c>
       <c r="I167" s="7" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="J167" s="7" t="s">
         <v>210</v>
@@ -15721,7 +15721,7 @@
         <v>146</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G168" s="7" t="s">
         <v>0</v>
@@ -15731,7 +15731,7 @@
         <v>12</v>
       </c>
       <c r="I168" s="7" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="J168" s="7" t="s">
         <v>210</v>
@@ -15763,7 +15763,7 @@
         <v>146</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="G169" s="7" t="s">
         <v>0</v>
@@ -15773,7 +15773,7 @@
         <v>12</v>
       </c>
       <c r="I169" s="7" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="J169" s="7" t="s">
         <v>161</v>
@@ -15805,7 +15805,7 @@
         <v>146</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G170" s="7" t="s">
         <v>0</v>
@@ -15815,7 +15815,7 @@
         <v>11</v>
       </c>
       <c r="I170" s="7" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J170" s="7" t="s">
         <v>161</v>
@@ -15847,7 +15847,7 @@
         <v>146</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G171" s="7" t="s">
         <v>0</v>
@@ -15857,7 +15857,7 @@
         <v>12</v>
       </c>
       <c r="I171" s="7" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="J171" s="7" t="s">
         <v>161</v>
@@ -15889,7 +15889,7 @@
         <v>146</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G172" s="7" t="s">
         <v>0</v>
@@ -15899,7 +15899,7 @@
         <v>12</v>
       </c>
       <c r="I172" s="7" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="J172" s="7" t="s">
         <v>161</v>
@@ -15931,7 +15931,7 @@
         <v>146</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G173" s="7" t="s">
         <v>0</v>
@@ -15941,7 +15941,7 @@
         <v>11</v>
       </c>
       <c r="I173" s="7" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="J173" s="7" t="s">
         <v>161</v>
@@ -15973,7 +15973,7 @@
         <v>146</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G174" s="7" t="s">
         <v>0</v>
@@ -15983,7 +15983,7 @@
         <v>12</v>
       </c>
       <c r="I174" s="7" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="J174" s="7" t="s">
         <v>161</v>
@@ -16015,7 +16015,7 @@
         <v>146</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="G175" s="7" t="s">
         <v>0</v>
@@ -16025,7 +16025,7 @@
         <v>12</v>
       </c>
       <c r="I175" s="7" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J175" s="7" t="s">
         <v>187</v>
@@ -16057,7 +16057,7 @@
         <v>146</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G176" s="7" t="s">
         <v>0</v>
@@ -16067,7 +16067,7 @@
         <v>12</v>
       </c>
       <c r="I176" s="7" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="J176" s="7" t="s">
         <v>187</v>
@@ -16099,7 +16099,7 @@
         <v>146</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G177" s="7" t="s">
         <v>0</v>
@@ -16109,7 +16109,7 @@
         <v>12</v>
       </c>
       <c r="I177" s="7" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J177" s="7" t="s">
         <v>155</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5EB0D1C-B913-4FCF-A4A0-6E991FA8B8B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC54100-FA2D-4177-86A9-42655A3ACD09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1827" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1828" uniqueCount="631">
   <si>
     <t>—</t>
   </si>
@@ -7851,234 +7851,274 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>아메추: 달걀죽/누룽지</t>
-  </si>
-  <si>
     <t>속이 편한 죽이나 누룽지로 아침을 시작해요.</t>
   </si>
   <si>
-    <t>아메추: 잡곡밥/현미밥</t>
-  </si>
-  <si>
     <t>잡곡밥이나 현미밥은 오래 든든해요.</t>
   </si>
   <si>
-    <t>아메추: 오트밀/통밀빵</t>
-  </si>
-  <si>
     <t>금방 준비할 수 있는 든든한 아침이에요.</t>
   </si>
   <si>
-    <t>아메추: 고구마/누룽지</t>
-  </si>
-  <si>
     <t>찐 고구마나 누룽지는 준비가 간단해요.</t>
   </si>
   <si>
-    <t>아메추: 전복죽/채소죽</t>
-  </si>
-  <si>
     <t>부드러운 죽은 아침에 넘기기 편해요.</t>
   </si>
   <si>
-    <t>아메추: 미역국/뭇국</t>
-  </si>
-  <si>
     <t>담백한 국으로 아침에도 채소를 먹어요.</t>
   </si>
   <si>
-    <t>아메추: 콩나물국/뭇국</t>
-  </si>
-  <si>
     <t>맑은 국으로 아침 채소를 챙겨요.</t>
   </si>
   <si>
-    <t>아메추: 아욱국/배춧국</t>
-  </si>
-  <si>
     <t>부드러운 채소국은 아침에 먹기 좋아요.</t>
   </si>
   <si>
-    <t>아메추: 비빔밥/쌈밥</t>
-  </si>
-  <si>
     <t>나물이나 쌈으로 채소를 넉넉히 먹어요.</t>
   </si>
   <si>
-    <t>아메추: 브로콜리/나물</t>
-  </si>
-  <si>
     <t>데친 채소 한 가지로 아침 채소를 더해요.</t>
   </si>
   <si>
-    <t>아메추: 달걀찜/달걀국</t>
-  </si>
-  <si>
     <t>달걀로 간단히 아침 단백질을 챙겨요.</t>
   </si>
   <si>
-    <t>아메추: 순두부/연두부</t>
-  </si>
-  <si>
     <t>부드러운 두부는 아침에 먹기 좋아요.</t>
   </si>
   <si>
-    <t>아메추: 두유/우유</t>
-  </si>
-  <si>
     <t>한 잔으로 간편하게 단백질을 더해요.</t>
   </si>
   <si>
-    <t>아메추: 달걀/두유</t>
-  </si>
-  <si>
     <t>바쁜 아침에도 단백질을 챙길 수 있어요.</t>
   </si>
   <si>
-    <t>아메추: 두부/달걀말이</t>
-  </si>
-  <si>
     <t>손쉬운 단백질 반찬으로 아침을 채워요.</t>
   </si>
   <si>
-    <t>아메추: 북엇국/달걀국</t>
-  </si>
-  <si>
     <t>가벼운 국으로 단백질을 더해요.</t>
   </si>
   <si>
-    <t>아메추: 생선구이/두부</t>
-  </si>
-  <si>
     <t>기름을 덜 쓰는 반찬으로 아침을 먹어요.</t>
   </si>
   <si>
-    <t>저메추: 생선구이/수육</t>
-  </si>
-  <si>
     <t>구이와 수육은 튀김보다 기름이 덜해요.</t>
   </si>
   <si>
-    <t>저메추: 수육/보쌈</t>
-  </si>
-  <si>
     <t>삶은 고기는 구운 고기보다 기름이 덜해요.</t>
   </si>
   <si>
-    <t>저메추: 닭백숙/닭곰탕</t>
-  </si>
-  <si>
-    <t>저메추: 문어숙회/수육</t>
-  </si>
-  <si>
     <t>데친 요리는 기름 없이 먹을 수 있어요.</t>
   </si>
   <si>
-    <t>저메추: 고등어/갈치</t>
-  </si>
-  <si>
     <t>구운 생선은 튀김보다 기름이 덜 들어가요.</t>
   </si>
   <si>
-    <t>저메추: 삼치/조기구이</t>
-  </si>
-  <si>
     <t>담백한 생선구이로 저녁을 먹어요.</t>
   </si>
   <si>
-    <t>저메추: 두부/달걀찜</t>
-  </si>
-  <si>
     <t>부드러운 단백질 반찬으로 저녁을 채워요.</t>
   </si>
   <si>
-    <t>저메추: 연어/닭가슴살</t>
-  </si>
-  <si>
     <t>기름 적은 단백질로 저녁을 챙겨요.</t>
   </si>
   <si>
-    <t>저메추: 닭안심/두부</t>
-  </si>
-  <si>
     <t>담백한 단백질 반찬이에요.</t>
   </si>
   <si>
-    <t>저메추: 콩국수/닭곰탕</t>
-  </si>
-  <si>
     <t>든든한 한 그릇으로 단백질을 챙겨요.</t>
   </si>
   <si>
-    <t>저메추: 두부조림/생선</t>
-  </si>
-  <si>
     <t>손쉬운 두부 반찬으로 단백질을 더해요.</t>
   </si>
   <si>
-    <t>저메추: 쌈밥/샤브샤브</t>
-  </si>
-  <si>
     <t>채소를 듬뿍 먹을 수 있는 저녁이에요.</t>
   </si>
   <si>
-    <t>저메추: 월남쌈/쌈밥</t>
-  </si>
-  <si>
     <t>채소를 싸 먹으면 자연스럽게 많이 먹어요.</t>
   </si>
   <si>
-    <t>저메추: 가지/버섯구이</t>
-  </si>
-  <si>
     <t>기름 없이 구운 채소 반찬이에요.</t>
   </si>
   <si>
-    <t>저메추: 나물/오이무침</t>
-  </si>
-  <si>
     <t>무침 반찬 하나로 저녁 채소가 채워져요.</t>
   </si>
   <si>
-    <t>저메추: 숙주/시금치</t>
-  </si>
-  <si>
     <t>나물 한 가지로 저녁 채소를 더해요.</t>
   </si>
   <si>
-    <t>저메추: 버섯된장국/쌈</t>
-  </si>
-  <si>
     <t>버섯국과 쌈으로 채소를 넉넉히 먹어요.</t>
   </si>
   <si>
-    <t>저메추: 북엇국/생선찜</t>
-  </si>
-  <si>
     <t>맑은 국과 찜은 찌개보다 덜 짜요.</t>
   </si>
   <si>
-    <t>저메추: 미역냉국/뭇국</t>
-  </si>
-  <si>
     <t>담백한 국은 싱겁게 만들기 쉬워요.</t>
   </si>
   <si>
-    <t>저메추: 잡곡밥/현미밥</t>
-  </si>
-  <si>
     <t>잡곡밥이나 현미밥은 저녁까지 든든해요.</t>
   </si>
   <si>
     <t>10-12 끼니 추천을 「아메추: A/B」 · 「저메추: A/B」 두 가지 고르기로 바꿈(아침 18 · 저녁 20). 한 가지씩이던 아침·저녁 추천  지움. 국수는 천천히 후루룩 → 면은 꼭꼭 씹어 먹기. 합계 176개</t>
   </si>
   <si>
-    <t>아메추: 맑은 국/뭇국</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>입맛 돌 때 먹어 두기</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 죽/누룽지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 잡곡밥/죽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 오트밀/감자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 고구마/죽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 전복죽/쌀죽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 미역국/뭇국</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 뭇국/배춧국</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 아욱국/쑥국</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 비빔밥/쌈밥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 나물/샐러드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 달걀찜/두부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 순두부/두유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 두유/우유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 달걀/두유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 연두부/달걀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 북엇국/두부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 생선/달걀찜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 맑은 국/죽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 생선/수육</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 수육/보쌈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 백숙/닭곰탕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 숙회/수육</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 고등어/갈치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 삼치/조기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 두부/달걀찜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 연어/닭안심</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 닭안심/두부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 콩국수/백숙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 두부/생선찜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 샤브샤브/쌈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 월남쌈/쌈밥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 가지/버섯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 나물/생채</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 숙주/시금치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 된장국/쌈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 생선찜/냉국</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 미역국/뭇국</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 잡곡밥/쌈밥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10-12 끼니 추천 머리말을 「아침추천: 」 · 「저녁추천: 」으로 바꿈(누구나 알아보게). 머리말이 6자라 메뉴 짝은 6자 이내로 다시 고름</t>
   </si>
 </sst>
 </file>
@@ -8565,7 +8605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F51797-492B-40AC-833D-E19CEF6E9FA5}">
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="120.58203125" style="1" customWidth="1"/>
@@ -8654,7 +8694,12 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>627</v>
+        <v>590</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
+        <v>630</v>
       </c>
     </row>
   </sheetData>
@@ -10261,7 +10306,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>629</v>
+        <v>591</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>270</v>
@@ -14545,17 +14590,17 @@
         <v>146</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>554</v>
+        <v>592</v>
       </c>
       <c r="G140" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H140" s="7">
         <f t="shared" ref="H140:H177" si="5">LEN(F140)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I140" s="7" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J140" s="7" t="s">
         <v>155</v>
@@ -14587,17 +14632,17 @@
         <v>146</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>556</v>
+        <v>593</v>
       </c>
       <c r="G141" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H141" s="7">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I141" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="J141" s="7" t="s">
         <v>155</v>
@@ -14629,7 +14674,7 @@
         <v>146</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>558</v>
+        <v>594</v>
       </c>
       <c r="G142" s="7" t="s">
         <v>0</v>
@@ -14639,7 +14684,7 @@
         <v>12</v>
       </c>
       <c r="I142" s="7" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="J142" s="7" t="s">
         <v>155</v>
@@ -14671,17 +14716,17 @@
         <v>146</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>560</v>
+        <v>595</v>
       </c>
       <c r="G143" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H143" s="7">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I143" s="7" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="J143" s="7" t="s">
         <v>155</v>
@@ -14713,7 +14758,7 @@
         <v>146</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>562</v>
+        <v>596</v>
       </c>
       <c r="G144" s="7" t="s">
         <v>0</v>
@@ -14723,7 +14768,7 @@
         <v>12</v>
       </c>
       <c r="I144" s="7" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="J144" s="7" t="s">
         <v>155</v>
@@ -14755,17 +14800,17 @@
         <v>146</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>564</v>
+        <v>597</v>
       </c>
       <c r="G145" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H145" s="7">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I145" s="7" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="J145" s="7" t="s">
         <v>161</v>
@@ -14797,7 +14842,7 @@
         <v>146</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>566</v>
+        <v>598</v>
       </c>
       <c r="G146" s="7" t="s">
         <v>0</v>
@@ -14807,7 +14852,7 @@
         <v>12</v>
       </c>
       <c r="I146" s="7" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="J146" s="7" t="s">
         <v>161</v>
@@ -14839,7 +14884,7 @@
         <v>146</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>568</v>
+        <v>599</v>
       </c>
       <c r="G147" s="7" t="s">
         <v>0</v>
@@ -14849,7 +14894,7 @@
         <v>12</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="J147" s="7" t="s">
         <v>161</v>
@@ -14881,17 +14926,17 @@
         <v>146</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>570</v>
+        <v>600</v>
       </c>
       <c r="G148" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H148" s="7">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I148" s="7" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="J148" s="7" t="s">
         <v>161</v>
@@ -14923,7 +14968,7 @@
         <v>146</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>572</v>
+        <v>601</v>
       </c>
       <c r="G149" s="7" t="s">
         <v>0</v>
@@ -14933,7 +14978,7 @@
         <v>12</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="J149" s="7" t="s">
         <v>161</v>
@@ -14965,7 +15010,7 @@
         <v>146</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>574</v>
+        <v>602</v>
       </c>
       <c r="G150" s="7" t="s">
         <v>0</v>
@@ -14975,7 +15020,7 @@
         <v>12</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="J150" s="7" t="s">
         <v>210</v>
@@ -15007,7 +15052,7 @@
         <v>146</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="G151" s="7" t="s">
         <v>0</v>
@@ -15017,7 +15062,7 @@
         <v>12</v>
       </c>
       <c r="I151" s="7" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="J151" s="7" t="s">
         <v>210</v>
@@ -15049,17 +15094,17 @@
         <v>146</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>578</v>
+        <v>604</v>
       </c>
       <c r="G152" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H152" s="7">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I152" s="7" t="s">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="J152" s="7" t="s">
         <v>210</v>
@@ -15091,17 +15136,17 @@
         <v>146</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>580</v>
+        <v>605</v>
       </c>
       <c r="G153" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H153" s="7">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I153" s="7" t="s">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="J153" s="7" t="s">
         <v>210</v>
@@ -15133,7 +15178,7 @@
         <v>146</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="G154" s="7" t="s">
         <v>0</v>
@@ -15143,7 +15188,7 @@
         <v>12</v>
       </c>
       <c r="I154" s="7" t="s">
-        <v>583</v>
+        <v>568</v>
       </c>
       <c r="J154" s="7" t="s">
         <v>210</v>
@@ -15175,7 +15220,7 @@
         <v>146</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>584</v>
+        <v>607</v>
       </c>
       <c r="G155" s="7" t="s">
         <v>0</v>
@@ -15185,7 +15230,7 @@
         <v>12</v>
       </c>
       <c r="I155" s="7" t="s">
-        <v>585</v>
+        <v>569</v>
       </c>
       <c r="J155" s="7" t="s">
         <v>210</v>
@@ -15217,7 +15262,7 @@
         <v>146</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>586</v>
+        <v>608</v>
       </c>
       <c r="G156" s="7" t="s">
         <v>0</v>
@@ -15227,7 +15272,7 @@
         <v>12</v>
       </c>
       <c r="I156" s="7" t="s">
-        <v>587</v>
+        <v>570</v>
       </c>
       <c r="J156" s="7" t="s">
         <v>215</v>
@@ -15259,7 +15304,7 @@
         <v>146</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>628</v>
+        <v>609</v>
       </c>
       <c r="G157" s="7" t="s">
         <v>0</v>
@@ -15301,17 +15346,17 @@
         <v>146</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>588</v>
+        <v>610</v>
       </c>
       <c r="G158" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H158" s="7">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I158" s="7" t="s">
-        <v>589</v>
+        <v>571</v>
       </c>
       <c r="J158" s="7" t="s">
         <v>215</v>
@@ -15343,17 +15388,17 @@
         <v>146</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>590</v>
+        <v>611</v>
       </c>
       <c r="G159" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H159" s="7">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I159" s="7" t="s">
-        <v>591</v>
+        <v>572</v>
       </c>
       <c r="J159" s="7" t="s">
         <v>215</v>
@@ -15385,7 +15430,7 @@
         <v>146</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>592</v>
+        <v>612</v>
       </c>
       <c r="G160" s="7" t="s">
         <v>0</v>
@@ -15427,17 +15472,17 @@
         <v>146</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>593</v>
+        <v>613</v>
       </c>
       <c r="G161" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H161" s="7">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I161" s="7" t="s">
-        <v>594</v>
+        <v>573</v>
       </c>
       <c r="J161" s="7" t="s">
         <v>215</v>
@@ -15469,17 +15514,17 @@
         <v>146</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>595</v>
+        <v>614</v>
       </c>
       <c r="G162" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H162" s="7">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I162" s="7" t="s">
-        <v>596</v>
+        <v>574</v>
       </c>
       <c r="J162" s="7" t="s">
         <v>215</v>
@@ -15511,17 +15556,17 @@
         <v>146</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>597</v>
+        <v>615</v>
       </c>
       <c r="G163" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H163" s="7">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I163" s="7" t="s">
-        <v>598</v>
+        <v>575</v>
       </c>
       <c r="J163" s="7" t="s">
         <v>215</v>
@@ -15553,17 +15598,17 @@
         <v>146</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>599</v>
+        <v>616</v>
       </c>
       <c r="G164" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H164" s="7">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I164" s="7" t="s">
-        <v>600</v>
+        <v>576</v>
       </c>
       <c r="J164" s="7" t="s">
         <v>210</v>
@@ -15595,7 +15640,7 @@
         <v>146</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>601</v>
+        <v>617</v>
       </c>
       <c r="G165" s="7" t="s">
         <v>0</v>
@@ -15605,7 +15650,7 @@
         <v>12</v>
       </c>
       <c r="I165" s="7" t="s">
-        <v>602</v>
+        <v>577</v>
       </c>
       <c r="J165" s="7" t="s">
         <v>210</v>
@@ -15637,17 +15682,17 @@
         <v>146</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>603</v>
+        <v>618</v>
       </c>
       <c r="G166" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H166" s="7">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I166" s="7" t="s">
-        <v>604</v>
+        <v>578</v>
       </c>
       <c r="J166" s="7" t="s">
         <v>210</v>
@@ -15679,7 +15724,7 @@
         <v>146</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>605</v>
+        <v>619</v>
       </c>
       <c r="G167" s="7" t="s">
         <v>0</v>
@@ -15689,7 +15734,7 @@
         <v>12</v>
       </c>
       <c r="I167" s="7" t="s">
-        <v>606</v>
+        <v>579</v>
       </c>
       <c r="J167" s="7" t="s">
         <v>210</v>
@@ -15721,7 +15766,7 @@
         <v>146</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>607</v>
+        <v>620</v>
       </c>
       <c r="G168" s="7" t="s">
         <v>0</v>
@@ -15731,7 +15776,7 @@
         <v>12</v>
       </c>
       <c r="I168" s="7" t="s">
-        <v>608</v>
+        <v>580</v>
       </c>
       <c r="J168" s="7" t="s">
         <v>210</v>
@@ -15763,7 +15808,7 @@
         <v>146</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="G169" s="7" t="s">
         <v>0</v>
@@ -15773,7 +15818,7 @@
         <v>12</v>
       </c>
       <c r="I169" s="7" t="s">
-        <v>610</v>
+        <v>581</v>
       </c>
       <c r="J169" s="7" t="s">
         <v>161</v>
@@ -15805,17 +15850,17 @@
         <v>146</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>611</v>
+        <v>622</v>
       </c>
       <c r="G170" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H170" s="7">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I170" s="7" t="s">
-        <v>612</v>
+        <v>582</v>
       </c>
       <c r="J170" s="7" t="s">
         <v>161</v>
@@ -15847,17 +15892,17 @@
         <v>146</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
       <c r="G171" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H171" s="7">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I171" s="7" t="s">
-        <v>614</v>
+        <v>583</v>
       </c>
       <c r="J171" s="7" t="s">
         <v>161</v>
@@ -15889,17 +15934,17 @@
         <v>146</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="G172" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H172" s="7">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I172" s="7" t="s">
-        <v>616</v>
+        <v>584</v>
       </c>
       <c r="J172" s="7" t="s">
         <v>161</v>
@@ -15931,17 +15976,17 @@
         <v>146</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="G173" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H173" s="7">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I173" s="7" t="s">
-        <v>618</v>
+        <v>585</v>
       </c>
       <c r="J173" s="7" t="s">
         <v>161</v>
@@ -15973,17 +16018,17 @@
         <v>146</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="G174" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H174" s="7">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I174" s="7" t="s">
-        <v>620</v>
+        <v>586</v>
       </c>
       <c r="J174" s="7" t="s">
         <v>161</v>
@@ -16015,7 +16060,7 @@
         <v>146</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="G175" s="7" t="s">
         <v>0</v>
@@ -16025,7 +16070,7 @@
         <v>12</v>
       </c>
       <c r="I175" s="7" t="s">
-        <v>622</v>
+        <v>587</v>
       </c>
       <c r="J175" s="7" t="s">
         <v>187</v>
@@ -16057,7 +16102,7 @@
         <v>146</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="G176" s="7" t="s">
         <v>0</v>
@@ -16067,7 +16112,7 @@
         <v>12</v>
       </c>
       <c r="I176" s="7" t="s">
-        <v>624</v>
+        <v>588</v>
       </c>
       <c r="J176" s="7" t="s">
         <v>187</v>
@@ -16099,7 +16144,7 @@
         <v>146</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="G177" s="7" t="s">
         <v>0</v>
@@ -16109,7 +16154,7 @@
         <v>12</v>
       </c>
       <c r="I177" s="7" t="s">
-        <v>626</v>
+        <v>589</v>
       </c>
       <c r="J177" s="7" t="s">
         <v>155</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC54100-FA2D-4177-86A9-42655A3ACD09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{586B0DAC-F9CE-4CB1-A1E1-63B959181494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="기존 문구 수정" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'추가 문구'!$A$1:$O$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'추가 문구'!$A$1:$O$198</definedName>
   </definedNames>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1828" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2039" uniqueCount="673">
   <si>
     <t>—</t>
   </si>
@@ -8119,6 +8119,132 @@
   </si>
   <si>
     <t>10-12 끼니 추천 머리말을 「아침추천: 」 · 「저녁추천: 」으로 바꿈(누구나 알아보게). 머리말이 6자라 메뉴 짝은 6자 이내로 다시 고름</t>
+  </si>
+  <si>
+    <t>저녁추천: 닭찜/수육</t>
+  </si>
+  <si>
+    <t>찜이나 수육은 튀김보다 기름이 덜해요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 가자미/조기</t>
+  </si>
+  <si>
+    <t>구운 흰살생선은 담백하고 기름이 적어요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 임연수/삼치</t>
+  </si>
+  <si>
+    <t>생선구이로 기름 적은 저녁을 먹어요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 닭구이/수육</t>
+  </si>
+  <si>
+    <t>구이와 수육은 튀긴 고기보다 기름이 덜해요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 새우/오징어</t>
+  </si>
+  <si>
+    <t>데친 해산물은 기름 없이 먹을 수 있어요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 살코기/생선</t>
+  </si>
+  <si>
+    <t>기름 적은 고기나 생선으로 단백질을 챙겨요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 조개/생선</t>
+  </si>
+  <si>
+    <t>조개나 생선으로 담백하게 단백질을 더해요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 두부/닭찜</t>
+  </si>
+  <si>
+    <t>두부나 닭찜으로 부드럽게 단백질을 챙겨요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 곤드레밥/쌈</t>
+  </si>
+  <si>
+    <t>나물밥이나 쌈으로 채소를 넉넉히 먹어요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 버섯밥/쌈</t>
+  </si>
+  <si>
+    <t>버섯밥과 쌈으로 저녁 채소를 챙겨요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 가지/호박</t>
+  </si>
+  <si>
+    <t>구운 가지나 호박으로 채소를 더해요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 샐러드/쌈</t>
+  </si>
+  <si>
+    <t>생채소로 저녁 채소를 넉넉히 먹어요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 청경채/버섯</t>
+  </si>
+  <si>
+    <t>데친 채소 한 가지로 저녁 채소를 더해요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 브로콜리/쌈</t>
+  </si>
+  <si>
+    <t>데친 브로콜리나 쌈으로 채소를 챙겨요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 양배추/나물</t>
+  </si>
+  <si>
+    <t>양배추쌈이나 나물로 채소를 더해요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 미나리/숙주</t>
+  </si>
+  <si>
+    <t>향긋한 나물로 저녁 채소를 챙겨요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 상추쌈/나물</t>
+  </si>
+  <si>
+    <t>쌈 한 접시로 채소를 듬뿍 먹어요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 지리/생선찜</t>
+  </si>
+  <si>
+    <t>맑은 지리와 찜은 빨간 탕보다 덜 짜요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 백김치/쌈</t>
+  </si>
+  <si>
+    <t>백김치와 쌈은 짠 반찬보다 염분이 적어요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 맑은 국/찜</t>
+  </si>
+  <si>
+    <t>저녁추천: 보리밥/쌈밥</t>
+  </si>
+  <si>
+    <t>든든한 밥 한 그릇으로 저녁을 챙겨요.</t>
+  </si>
+  <si>
+    <t>10-12 저녁추천 확대: 모두 . 합계 197개</t>
   </si>
 </sst>
 </file>
@@ -8605,7 +8731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F51797-492B-40AC-833D-E19CEF6E9FA5}">
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="120.58203125" style="1" customWidth="1"/>
@@ -8702,6 +8828,11 @@
         <v>630</v>
       </c>
     </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="s">
+        <v>672</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8710,7 +8841,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{243C8A1C-2FBA-4873-BD31-7545635970F1}">
-  <dimension ref="A1:O177"/>
+  <dimension ref="A1:O198"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6.58203125" style="1" customWidth="1"/>
@@ -16169,11 +16300,893 @@
       <c r="N177" s="3"/>
       <c r="O177" s="3"/>
     </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A178" s="7">
+        <v>177</v>
+      </c>
+      <c r="B178" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C178" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D178" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="E178" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F178" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="G178" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H178" s="7">
+        <f>LEN(F178)</f>
+        <v>11</v>
+      </c>
+      <c r="I178" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="J178" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K178" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L178" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M178" s="3"/>
+      <c r="N178" s="3"/>
+      <c r="O178" s="3"/>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A179" s="7">
+        <v>178</v>
+      </c>
+      <c r="B179" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C179" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D179" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="E179" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F179" s="7" t="s">
+        <v>633</v>
+      </c>
+      <c r="G179" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H179" s="7">
+        <f>LEN(F179)</f>
+        <v>12</v>
+      </c>
+      <c r="I179" s="7" t="s">
+        <v>634</v>
+      </c>
+      <c r="J179" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K179" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L179" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M179" s="3"/>
+      <c r="N179" s="3"/>
+      <c r="O179" s="3"/>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A180" s="7">
+        <v>179</v>
+      </c>
+      <c r="B180" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C180" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D180" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="E180" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F180" s="7" t="s">
+        <v>635</v>
+      </c>
+      <c r="G180" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H180" s="7">
+        <f>LEN(F180)</f>
+        <v>12</v>
+      </c>
+      <c r="I180" s="7" t="s">
+        <v>636</v>
+      </c>
+      <c r="J180" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K180" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L180" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M180" s="3"/>
+      <c r="N180" s="3"/>
+      <c r="O180" s="3"/>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A181" s="7">
+        <v>180</v>
+      </c>
+      <c r="B181" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C181" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D181" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="E181" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F181" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="G181" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H181" s="7">
+        <f>LEN(F181)</f>
+        <v>12</v>
+      </c>
+      <c r="I181" s="7" t="s">
+        <v>638</v>
+      </c>
+      <c r="J181" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K181" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L181" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M181" s="3"/>
+      <c r="N181" s="3"/>
+      <c r="O181" s="3"/>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A182" s="7">
+        <v>181</v>
+      </c>
+      <c r="B182" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C182" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D182" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="E182" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F182" s="7" t="s">
+        <v>639</v>
+      </c>
+      <c r="G182" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H182" s="7">
+        <f>LEN(F182)</f>
+        <v>12</v>
+      </c>
+      <c r="I182" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="J182" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K182" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L182" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M182" s="3"/>
+      <c r="N182" s="3"/>
+      <c r="O182" s="3"/>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A183" s="7">
+        <v>182</v>
+      </c>
+      <c r="B183" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C183" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D183" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="E183" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F183" s="7" t="s">
+        <v>641</v>
+      </c>
+      <c r="G183" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H183" s="7">
+        <f>LEN(F183)</f>
+        <v>12</v>
+      </c>
+      <c r="I183" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="J183" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="K183" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L183" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M183" s="3"/>
+      <c r="N183" s="3"/>
+      <c r="O183" s="3"/>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A184" s="7">
+        <v>183</v>
+      </c>
+      <c r="B184" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C184" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D184" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="E184" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F184" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="G184" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H184" s="7">
+        <f>LEN(F184)</f>
+        <v>11</v>
+      </c>
+      <c r="I184" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="J184" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="K184" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L184" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M184" s="3"/>
+      <c r="N184" s="3"/>
+      <c r="O184" s="3"/>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A185" s="7">
+        <v>184</v>
+      </c>
+      <c r="B185" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C185" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D185" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="E185" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F185" s="7" t="s">
+        <v>645</v>
+      </c>
+      <c r="G185" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H185" s="7">
+        <f>LEN(F185)</f>
+        <v>11</v>
+      </c>
+      <c r="I185" s="7" t="s">
+        <v>646</v>
+      </c>
+      <c r="J185" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="K185" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L185" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M185" s="3"/>
+      <c r="N185" s="3"/>
+      <c r="O185" s="3"/>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A186" s="7">
+        <v>185</v>
+      </c>
+      <c r="B186" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C186" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D186" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E186" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F186" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="G186" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H186" s="7">
+        <f>LEN(F186)</f>
+        <v>12</v>
+      </c>
+      <c r="I186" s="7" t="s">
+        <v>648</v>
+      </c>
+      <c r="J186" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="K186" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L186" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M186" s="3"/>
+      <c r="N186" s="3"/>
+      <c r="O186" s="3"/>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A187" s="7">
+        <v>186</v>
+      </c>
+      <c r="B187" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C187" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D187" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E187" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F187" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="G187" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H187" s="7">
+        <f>LEN(F187)</f>
+        <v>11</v>
+      </c>
+      <c r="I187" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="J187" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="K187" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L187" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M187" s="3"/>
+      <c r="N187" s="3"/>
+      <c r="O187" s="3"/>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A188" s="7">
+        <v>187</v>
+      </c>
+      <c r="B188" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C188" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D188" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E188" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F188" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="G188" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H188" s="7">
+        <f>LEN(F188)</f>
+        <v>11</v>
+      </c>
+      <c r="I188" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="J188" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="K188" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L188" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M188" s="3"/>
+      <c r="N188" s="3"/>
+      <c r="O188" s="3"/>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A189" s="7">
+        <v>188</v>
+      </c>
+      <c r="B189" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C189" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D189" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E189" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F189" s="7" t="s">
+        <v>653</v>
+      </c>
+      <c r="G189" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H189" s="7">
+        <f>LEN(F189)</f>
+        <v>11</v>
+      </c>
+      <c r="I189" s="7" t="s">
+        <v>654</v>
+      </c>
+      <c r="J189" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="K189" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L189" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M189" s="3"/>
+      <c r="N189" s="3"/>
+      <c r="O189" s="3"/>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A190" s="7">
+        <v>189</v>
+      </c>
+      <c r="B190" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D190" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E190" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F190" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="G190" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H190" s="7">
+        <f>LEN(F190)</f>
+        <v>12</v>
+      </c>
+      <c r="I190" s="7" t="s">
+        <v>656</v>
+      </c>
+      <c r="J190" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="K190" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L190" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M190" s="3"/>
+      <c r="N190" s="3"/>
+      <c r="O190" s="3"/>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A191" s="7">
+        <v>190</v>
+      </c>
+      <c r="B191" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C191" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D191" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E191" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F191" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="G191" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H191" s="7">
+        <f>LEN(F191)</f>
+        <v>12</v>
+      </c>
+      <c r="I191" s="7" t="s">
+        <v>658</v>
+      </c>
+      <c r="J191" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="K191" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L191" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M191" s="3"/>
+      <c r="N191" s="3"/>
+      <c r="O191" s="3"/>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A192" s="7">
+        <v>191</v>
+      </c>
+      <c r="B192" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C192" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D192" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E192" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F192" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="G192" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H192" s="7">
+        <f>LEN(F192)</f>
+        <v>12</v>
+      </c>
+      <c r="I192" s="7" t="s">
+        <v>660</v>
+      </c>
+      <c r="J192" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="K192" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L192" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M192" s="3"/>
+      <c r="N192" s="3"/>
+      <c r="O192" s="3"/>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A193" s="7">
+        <v>192</v>
+      </c>
+      <c r="B193" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C193" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D193" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E193" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F193" s="7" t="s">
+        <v>661</v>
+      </c>
+      <c r="G193" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H193" s="7">
+        <f>LEN(F193)</f>
+        <v>12</v>
+      </c>
+      <c r="I193" s="7" t="s">
+        <v>662</v>
+      </c>
+      <c r="J193" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="K193" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L193" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M193" s="3"/>
+      <c r="N193" s="3"/>
+      <c r="O193" s="3"/>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A194" s="7">
+        <v>193</v>
+      </c>
+      <c r="B194" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C194" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D194" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E194" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F194" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="G194" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H194" s="7">
+        <f>LEN(F194)</f>
+        <v>12</v>
+      </c>
+      <c r="I194" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="J194" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="K194" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L194" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M194" s="3"/>
+      <c r="N194" s="3"/>
+      <c r="O194" s="3"/>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A195" s="7">
+        <v>194</v>
+      </c>
+      <c r="B195" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C195" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D195" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="E195" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F195" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="G195" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H195" s="7">
+        <f>LEN(F195)</f>
+        <v>12</v>
+      </c>
+      <c r="I195" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J195" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K195" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L195" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M195" s="3"/>
+      <c r="N195" s="3"/>
+      <c r="O195" s="3"/>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A196" s="7">
+        <v>195</v>
+      </c>
+      <c r="B196" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C196" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D196" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="E196" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F196" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="G196" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H196" s="7">
+        <f>LEN(F196)</f>
+        <v>11</v>
+      </c>
+      <c r="I196" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="J196" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K196" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L196" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M196" s="3"/>
+      <c r="N196" s="3"/>
+      <c r="O196" s="3"/>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A197" s="7">
+        <v>196</v>
+      </c>
+      <c r="B197" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C197" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D197" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="E197" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F197" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="G197" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H197" s="7">
+        <f>LEN(F197)</f>
+        <v>12</v>
+      </c>
+      <c r="I197" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="J197" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K197" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L197" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M197" s="3"/>
+      <c r="N197" s="3"/>
+      <c r="O197" s="3"/>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A198" s="7">
+        <v>197</v>
+      </c>
+      <c r="B198" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C198" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D198" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E198" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F198" s="7" t="s">
+        <v>670</v>
+      </c>
+      <c r="G198" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H198" s="7">
+        <f>LEN(F198)</f>
+        <v>12</v>
+      </c>
+      <c r="I198" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="J198" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="K198" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L198" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M198" s="3"/>
+      <c r="N198" s="3"/>
+      <c r="O198" s="3"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O177" xr:uid="{243C8A1C-2FBA-4873-BD31-7545635970F1}"/>
+  <autoFilter ref="A1:O198" xr:uid="{243C8A1C-2FBA-4873-BD31-7545635970F1}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M177" xr:uid="{29F577E0-A9A7-4D3D-B3E7-99484ADFB535}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M198" xr:uid="{29F577E0-A9A7-4D3D-B3E7-99484ADFB535}">
       <formula1>"승인,수정,제외"</formula1>
     </dataValidation>
   </dataValidations>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{586B0DAC-F9CE-4CB1-A1E1-63B959181494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61CA15F1-467C-4ED5-A03A-8854338E32AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="기존 문구 수정" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'추가 문구'!$A$1:$O$198</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'추가 문구'!$A$1:$O$212</definedName>
   </definedNames>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2039" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2180" uniqueCount="699">
   <si>
     <t>—</t>
   </si>
@@ -8245,6 +8245,84 @@
   </si>
   <si>
     <t>10-12 저녁추천 확대: 모두 . 합계 197개</t>
+  </si>
+  <si>
+    <t>아침추천: 감자/옥수수</t>
+  </si>
+  <si>
+    <t>찐 감자나 옥수수는 준비가 간단해요.</t>
+  </si>
+  <si>
+    <t>아침추천: 주먹밥/죽</t>
+  </si>
+  <si>
+    <t>주먹밥이나 죽으로 간단히 아침을 먹어요.</t>
+  </si>
+  <si>
+    <t>아침추천: 호박죽/쌀죽</t>
+  </si>
+  <si>
+    <t>아침추천: 통밀빵/감자</t>
+  </si>
+  <si>
+    <t>통밀빵이나 감자로 아침을 든든하게 해요.</t>
+  </si>
+  <si>
+    <t>아침추천: 시금치국/쌈</t>
+  </si>
+  <si>
+    <t>채소국이나 쌈으로 아침 채소를 챙겨요.</t>
+  </si>
+  <si>
+    <t>아침추천: 샐러드/나물</t>
+  </si>
+  <si>
+    <t>생채소나 나물로 아침 채소를 더해요.</t>
+  </si>
+  <si>
+    <t>아침추천: 비빔밥/나물</t>
+  </si>
+  <si>
+    <t>나물을 곁들이면 아침 채소가 넉넉해요.</t>
+  </si>
+  <si>
+    <t>아침추천: 요거트/두유</t>
+  </si>
+  <si>
+    <t>달지 않은 요거트나 두유로 단백질을 더해요.</t>
+  </si>
+  <si>
+    <t>아침추천: 우유/달걀</t>
+  </si>
+  <si>
+    <t>한 잔이나 한 알로 아침 단백질을 챙겨요.</t>
+  </si>
+  <si>
+    <t>아침추천: 북엇국/달걀</t>
+  </si>
+  <si>
+    <t>가벼운 국으로 아침 단백질을 더해요.</t>
+  </si>
+  <si>
+    <t>아침추천: 생선/두부</t>
+  </si>
+  <si>
+    <t>아침추천: 달걀찜/생선</t>
+  </si>
+  <si>
+    <t>찜이나 구이로 기름 적은 아침을 먹어요.</t>
+  </si>
+  <si>
+    <t>아침추천: 미역국/쑥국</t>
+  </si>
+  <si>
+    <t>아침추천: 백김치/나물</t>
+  </si>
+  <si>
+    <t>백김치와 나물은 짠 반찬보다 염분이 적어요.</t>
+  </si>
+  <si>
+    <t>10-12 아침추천 확대: 모두 . 합계 211개</t>
   </si>
 </sst>
 </file>
@@ -8731,7 +8809,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F51797-492B-40AC-833D-E19CEF6E9FA5}">
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="120.58203125" style="1" customWidth="1"/>
@@ -8833,6 +8911,11 @@
         <v>672</v>
       </c>
     </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A21" s="1" t="s">
+        <v>698</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8841,7 +8924,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{243C8A1C-2FBA-4873-BD31-7545635970F1}">
-  <dimension ref="A1:O198"/>
+  <dimension ref="A1:O212"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6.58203125" style="1" customWidth="1"/>
@@ -16323,7 +16406,7 @@
         <v>0</v>
       </c>
       <c r="H178" s="7">
-        <f>LEN(F178)</f>
+        <f t="shared" ref="H178:H198" si="6">LEN(F178)</f>
         <v>11</v>
       </c>
       <c r="I178" s="7" t="s">
@@ -16365,7 +16448,7 @@
         <v>0</v>
       </c>
       <c r="H179" s="7">
-        <f>LEN(F179)</f>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="I179" s="7" t="s">
@@ -16407,7 +16490,7 @@
         <v>0</v>
       </c>
       <c r="H180" s="7">
-        <f>LEN(F180)</f>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="I180" s="7" t="s">
@@ -16449,7 +16532,7 @@
         <v>0</v>
       </c>
       <c r="H181" s="7">
-        <f>LEN(F181)</f>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="I181" s="7" t="s">
@@ -16491,7 +16574,7 @@
         <v>0</v>
       </c>
       <c r="H182" s="7">
-        <f>LEN(F182)</f>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="I182" s="7" t="s">
@@ -16533,7 +16616,7 @@
         <v>0</v>
       </c>
       <c r="H183" s="7">
-        <f>LEN(F183)</f>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="I183" s="7" t="s">
@@ -16575,7 +16658,7 @@
         <v>0</v>
       </c>
       <c r="H184" s="7">
-        <f>LEN(F184)</f>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="I184" s="7" t="s">
@@ -16617,7 +16700,7 @@
         <v>0</v>
       </c>
       <c r="H185" s="7">
-        <f>LEN(F185)</f>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="I185" s="7" t="s">
@@ -16659,7 +16742,7 @@
         <v>0</v>
       </c>
       <c r="H186" s="7">
-        <f>LEN(F186)</f>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="I186" s="7" t="s">
@@ -16701,7 +16784,7 @@
         <v>0</v>
       </c>
       <c r="H187" s="7">
-        <f>LEN(F187)</f>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="I187" s="7" t="s">
@@ -16743,7 +16826,7 @@
         <v>0</v>
       </c>
       <c r="H188" s="7">
-        <f>LEN(F188)</f>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="I188" s="7" t="s">
@@ -16785,7 +16868,7 @@
         <v>0</v>
       </c>
       <c r="H189" s="7">
-        <f>LEN(F189)</f>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="I189" s="7" t="s">
@@ -16827,7 +16910,7 @@
         <v>0</v>
       </c>
       <c r="H190" s="7">
-        <f>LEN(F190)</f>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="I190" s="7" t="s">
@@ -16869,7 +16952,7 @@
         <v>0</v>
       </c>
       <c r="H191" s="7">
-        <f>LEN(F191)</f>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="I191" s="7" t="s">
@@ -16911,7 +16994,7 @@
         <v>0</v>
       </c>
       <c r="H192" s="7">
-        <f>LEN(F192)</f>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="I192" s="7" t="s">
@@ -16953,7 +17036,7 @@
         <v>0</v>
       </c>
       <c r="H193" s="7">
-        <f>LEN(F193)</f>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="I193" s="7" t="s">
@@ -16995,7 +17078,7 @@
         <v>0</v>
       </c>
       <c r="H194" s="7">
-        <f>LEN(F194)</f>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="I194" s="7" t="s">
@@ -17037,7 +17120,7 @@
         <v>0</v>
       </c>
       <c r="H195" s="7">
-        <f>LEN(F195)</f>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="I195" s="7" t="s">
@@ -17079,7 +17162,7 @@
         <v>0</v>
       </c>
       <c r="H196" s="7">
-        <f>LEN(F196)</f>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="I196" s="7" t="s">
@@ -17121,7 +17204,7 @@
         <v>0</v>
       </c>
       <c r="H197" s="7">
-        <f>LEN(F197)</f>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="I197" s="7" t="s">
@@ -17163,7 +17246,7 @@
         <v>0</v>
       </c>
       <c r="H198" s="7">
-        <f>LEN(F198)</f>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="I198" s="7" t="s">
@@ -17182,11 +17265,599 @@
       <c r="N198" s="3"/>
       <c r="O198" s="3"/>
     </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A199" s="7">
+        <v>198</v>
+      </c>
+      <c r="B199" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C199" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D199" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E199" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F199" s="7" t="s">
+        <v>673</v>
+      </c>
+      <c r="G199" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H199" s="7">
+        <f>LEN(F199)</f>
+        <v>12</v>
+      </c>
+      <c r="I199" s="7" t="s">
+        <v>674</v>
+      </c>
+      <c r="J199" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="K199" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L199" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M199" s="3"/>
+      <c r="N199" s="3"/>
+      <c r="O199" s="3"/>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A200" s="7">
+        <v>199</v>
+      </c>
+      <c r="B200" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C200" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D200" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E200" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F200" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="G200" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H200" s="7">
+        <f>LEN(F200)</f>
+        <v>11</v>
+      </c>
+      <c r="I200" s="7" t="s">
+        <v>676</v>
+      </c>
+      <c r="J200" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="K200" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L200" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M200" s="3"/>
+      <c r="N200" s="3"/>
+      <c r="O200" s="3"/>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A201" s="7">
+        <v>200</v>
+      </c>
+      <c r="B201" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C201" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D201" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E201" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F201" s="7" t="s">
+        <v>677</v>
+      </c>
+      <c r="G201" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H201" s="7">
+        <f>LEN(F201)</f>
+        <v>12</v>
+      </c>
+      <c r="I201" s="7" t="s">
+        <v>558</v>
+      </c>
+      <c r="J201" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="K201" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L201" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M201" s="3"/>
+      <c r="N201" s="3"/>
+      <c r="O201" s="3"/>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A202" s="7">
+        <v>201</v>
+      </c>
+      <c r="B202" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C202" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D202" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E202" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F202" s="7" t="s">
+        <v>678</v>
+      </c>
+      <c r="G202" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H202" s="7">
+        <f>LEN(F202)</f>
+        <v>12</v>
+      </c>
+      <c r="I202" s="7" t="s">
+        <v>679</v>
+      </c>
+      <c r="J202" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="K202" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L202" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M202" s="3"/>
+      <c r="N202" s="3"/>
+      <c r="O202" s="3"/>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A203" s="7">
+        <v>202</v>
+      </c>
+      <c r="B203" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C203" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D203" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E203" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F203" s="7" t="s">
+        <v>680</v>
+      </c>
+      <c r="G203" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H203" s="7">
+        <f>LEN(F203)</f>
+        <v>12</v>
+      </c>
+      <c r="I203" s="7" t="s">
+        <v>681</v>
+      </c>
+      <c r="J203" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="K203" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L203" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M203" s="3"/>
+      <c r="N203" s="3"/>
+      <c r="O203" s="3"/>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A204" s="7">
+        <v>203</v>
+      </c>
+      <c r="B204" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C204" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D204" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E204" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F204" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="G204" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H204" s="7">
+        <f>LEN(F204)</f>
+        <v>12</v>
+      </c>
+      <c r="I204" s="7" t="s">
+        <v>683</v>
+      </c>
+      <c r="J204" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="K204" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L204" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M204" s="3"/>
+      <c r="N204" s="3"/>
+      <c r="O204" s="3"/>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A205" s="7">
+        <v>204</v>
+      </c>
+      <c r="B205" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C205" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D205" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E205" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F205" s="7" t="s">
+        <v>684</v>
+      </c>
+      <c r="G205" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H205" s="7">
+        <f>LEN(F205)</f>
+        <v>12</v>
+      </c>
+      <c r="I205" s="7" t="s">
+        <v>685</v>
+      </c>
+      <c r="J205" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="K205" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L205" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M205" s="3"/>
+      <c r="N205" s="3"/>
+      <c r="O205" s="3"/>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A206" s="7">
+        <v>205</v>
+      </c>
+      <c r="B206" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C206" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D206" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="E206" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F206" s="7" t="s">
+        <v>686</v>
+      </c>
+      <c r="G206" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H206" s="7">
+        <f>LEN(F206)</f>
+        <v>12</v>
+      </c>
+      <c r="I206" s="7" t="s">
+        <v>687</v>
+      </c>
+      <c r="J206" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="K206" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L206" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M206" s="3"/>
+      <c r="N206" s="3"/>
+      <c r="O206" s="3"/>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A207" s="7">
+        <v>206</v>
+      </c>
+      <c r="B207" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C207" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D207" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="E207" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F207" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="G207" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H207" s="7">
+        <f>LEN(F207)</f>
+        <v>11</v>
+      </c>
+      <c r="I207" s="7" t="s">
+        <v>689</v>
+      </c>
+      <c r="J207" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="K207" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L207" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M207" s="3"/>
+      <c r="N207" s="3"/>
+      <c r="O207" s="3"/>
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A208" s="7">
+        <v>207</v>
+      </c>
+      <c r="B208" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C208" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D208" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="E208" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F208" s="7" t="s">
+        <v>690</v>
+      </c>
+      <c r="G208" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H208" s="7">
+        <f>LEN(F208)</f>
+        <v>12</v>
+      </c>
+      <c r="I208" s="7" t="s">
+        <v>691</v>
+      </c>
+      <c r="J208" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="K208" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L208" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M208" s="3"/>
+      <c r="N208" s="3"/>
+      <c r="O208" s="3"/>
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A209" s="7">
+        <v>208</v>
+      </c>
+      <c r="B209" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C209" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D209" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="E209" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F209" s="7" t="s">
+        <v>692</v>
+      </c>
+      <c r="G209" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H209" s="7">
+        <f>LEN(F209)</f>
+        <v>11</v>
+      </c>
+      <c r="I209" s="7" t="s">
+        <v>570</v>
+      </c>
+      <c r="J209" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K209" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L209" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M209" s="3"/>
+      <c r="N209" s="3"/>
+      <c r="O209" s="3"/>
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A210" s="7">
+        <v>209</v>
+      </c>
+      <c r="B210" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C210" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D210" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="E210" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F210" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="G210" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H210" s="7">
+        <f>LEN(F210)</f>
+        <v>12</v>
+      </c>
+      <c r="I210" s="7" t="s">
+        <v>694</v>
+      </c>
+      <c r="J210" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K210" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L210" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M210" s="3"/>
+      <c r="N210" s="3"/>
+      <c r="O210" s="3"/>
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A211" s="7">
+        <v>210</v>
+      </c>
+      <c r="B211" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C211" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D211" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="E211" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F211" s="7" t="s">
+        <v>695</v>
+      </c>
+      <c r="G211" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H211" s="7">
+        <f>LEN(F211)</f>
+        <v>12</v>
+      </c>
+      <c r="I211" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="J211" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K211" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L211" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M211" s="3"/>
+      <c r="N211" s="3"/>
+      <c r="O211" s="3"/>
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A212" s="7">
+        <v>211</v>
+      </c>
+      <c r="B212" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C212" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D212" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="E212" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F212" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="G212" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H212" s="7">
+        <f>LEN(F212)</f>
+        <v>12</v>
+      </c>
+      <c r="I212" s="7" t="s">
+        <v>697</v>
+      </c>
+      <c r="J212" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K212" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L212" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M212" s="3"/>
+      <c r="N212" s="3"/>
+      <c r="O212" s="3"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O198" xr:uid="{243C8A1C-2FBA-4873-BD31-7545635970F1}"/>
+  <autoFilter ref="A1:O212" xr:uid="{243C8A1C-2FBA-4873-BD31-7545635970F1}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M198" xr:uid="{29F577E0-A9A7-4D3D-B3E7-99484ADFB535}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M212" xr:uid="{29F577E0-A9A7-4D3D-B3E7-99484ADFB535}">
       <formula1>"승인,수정,제외"</formula1>
     </dataValidation>
   </dataValidations>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61CA15F1-467C-4ED5-A03A-8854338E32AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B090D9B2-35F7-46B3-B66F-10D09C224F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="기존 문구 수정" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'추가 문구'!$A$1:$O$212</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'추가 문구'!$A$1:$O$220</definedName>
   </definedNames>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2180" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2261" uniqueCount="716">
   <si>
     <t>—</t>
   </si>
@@ -8323,6 +8323,57 @@
   </si>
   <si>
     <t>10-12 아침추천 확대: 모두 . 합계 211개</t>
+  </si>
+  <si>
+    <t>아침추천: 옥수수/죽</t>
+  </si>
+  <si>
+    <t>찐 옥수수나 죽으로 간단히 아침을 먹어요.</t>
+  </si>
+  <si>
+    <t>아침추천: 현미밥/감자</t>
+  </si>
+  <si>
+    <t>든든한 현미밥이나 감자로 아침을 시작해요.</t>
+  </si>
+  <si>
+    <t>아침추천: 콩나물국/쌈</t>
+  </si>
+  <si>
+    <t>맑은 국이나 쌈으로 아침에도 채소를 먹어요.</t>
+  </si>
+  <si>
+    <t>아침추천: 호박국/나물</t>
+  </si>
+  <si>
+    <t>부드러운 채소 반찬으로 아침을 채워요.</t>
+  </si>
+  <si>
+    <t>아침추천: 양배추/오이</t>
+  </si>
+  <si>
+    <t>아삭한 채소 한 가지로 아침 채소를 더해요.</t>
+  </si>
+  <si>
+    <t>아침추천: 달걀/요거트</t>
+  </si>
+  <si>
+    <t>달걀이나 요거트로 아침 단백질을 더해요.</t>
+  </si>
+  <si>
+    <t>아침추천: 두부/달걀찜</t>
+  </si>
+  <si>
+    <t>부드러운 반찬으로 아침 단백질을 챙겨요.</t>
+  </si>
+  <si>
+    <t>아침추천: 달걀말이/죽</t>
+  </si>
+  <si>
+    <t>달걀말이를 곁들이면 아침이 든든해져요.</t>
+  </si>
+  <si>
+    <t>10-12 아침추천 확대: 모두 . 합계 219개</t>
   </si>
 </sst>
 </file>
@@ -8809,7 +8860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F51797-492B-40AC-833D-E19CEF6E9FA5}">
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="120.58203125" style="1" customWidth="1"/>
@@ -8916,6 +8967,11 @@
         <v>698</v>
       </c>
     </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A22" s="1" t="s">
+        <v>715</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8924,7 +8980,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{243C8A1C-2FBA-4873-BD31-7545635970F1}">
-  <dimension ref="A1:O212"/>
+  <dimension ref="A1:O220"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6.58203125" style="1" customWidth="1"/>
@@ -17288,7 +17344,7 @@
         <v>0</v>
       </c>
       <c r="H199" s="7">
-        <f>LEN(F199)</f>
+        <f t="shared" ref="H199:H212" si="7">LEN(F199)</f>
         <v>12</v>
       </c>
       <c r="I199" s="7" t="s">
@@ -17330,7 +17386,7 @@
         <v>0</v>
       </c>
       <c r="H200" s="7">
-        <f>LEN(F200)</f>
+        <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="I200" s="7" t="s">
@@ -17372,7 +17428,7 @@
         <v>0</v>
       </c>
       <c r="H201" s="7">
-        <f>LEN(F201)</f>
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I201" s="7" t="s">
@@ -17414,7 +17470,7 @@
         <v>0</v>
       </c>
       <c r="H202" s="7">
-        <f>LEN(F202)</f>
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I202" s="7" t="s">
@@ -17456,7 +17512,7 @@
         <v>0</v>
       </c>
       <c r="H203" s="7">
-        <f>LEN(F203)</f>
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I203" s="7" t="s">
@@ -17498,7 +17554,7 @@
         <v>0</v>
       </c>
       <c r="H204" s="7">
-        <f>LEN(F204)</f>
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I204" s="7" t="s">
@@ -17540,7 +17596,7 @@
         <v>0</v>
       </c>
       <c r="H205" s="7">
-        <f>LEN(F205)</f>
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I205" s="7" t="s">
@@ -17582,7 +17638,7 @@
         <v>0</v>
       </c>
       <c r="H206" s="7">
-        <f>LEN(F206)</f>
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I206" s="7" t="s">
@@ -17624,7 +17680,7 @@
         <v>0</v>
       </c>
       <c r="H207" s="7">
-        <f>LEN(F207)</f>
+        <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="I207" s="7" t="s">
@@ -17666,7 +17722,7 @@
         <v>0</v>
       </c>
       <c r="H208" s="7">
-        <f>LEN(F208)</f>
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I208" s="7" t="s">
@@ -17708,7 +17764,7 @@
         <v>0</v>
       </c>
       <c r="H209" s="7">
-        <f>LEN(F209)</f>
+        <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="I209" s="7" t="s">
@@ -17750,7 +17806,7 @@
         <v>0</v>
       </c>
       <c r="H210" s="7">
-        <f>LEN(F210)</f>
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I210" s="7" t="s">
@@ -17792,7 +17848,7 @@
         <v>0</v>
       </c>
       <c r="H211" s="7">
-        <f>LEN(F211)</f>
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I211" s="7" t="s">
@@ -17834,7 +17890,7 @@
         <v>0</v>
       </c>
       <c r="H212" s="7">
-        <f>LEN(F212)</f>
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I212" s="7" t="s">
@@ -17853,11 +17909,347 @@
       <c r="N212" s="3"/>
       <c r="O212" s="3"/>
     </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A213" s="7">
+        <v>212</v>
+      </c>
+      <c r="B213" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C213" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D213" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E213" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F213" s="7" t="s">
+        <v>699</v>
+      </c>
+      <c r="G213" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H213" s="7">
+        <f>LEN(F213)</f>
+        <v>11</v>
+      </c>
+      <c r="I213" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="J213" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="K213" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L213" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M213" s="3"/>
+      <c r="N213" s="3"/>
+      <c r="O213" s="3"/>
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A214" s="7">
+        <v>213</v>
+      </c>
+      <c r="B214" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C214" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D214" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E214" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F214" s="7" t="s">
+        <v>701</v>
+      </c>
+      <c r="G214" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H214" s="7">
+        <f>LEN(F214)</f>
+        <v>12</v>
+      </c>
+      <c r="I214" s="7" t="s">
+        <v>702</v>
+      </c>
+      <c r="J214" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="K214" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L214" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M214" s="3"/>
+      <c r="N214" s="3"/>
+      <c r="O214" s="3"/>
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A215" s="7">
+        <v>214</v>
+      </c>
+      <c r="B215" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C215" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D215" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E215" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F215" s="7" t="s">
+        <v>703</v>
+      </c>
+      <c r="G215" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H215" s="7">
+        <f>LEN(F215)</f>
+        <v>12</v>
+      </c>
+      <c r="I215" s="7" t="s">
+        <v>704</v>
+      </c>
+      <c r="J215" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="K215" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L215" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M215" s="3"/>
+      <c r="N215" s="3"/>
+      <c r="O215" s="3"/>
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A216" s="7">
+        <v>215</v>
+      </c>
+      <c r="B216" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C216" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D216" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E216" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F216" s="7" t="s">
+        <v>705</v>
+      </c>
+      <c r="G216" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H216" s="7">
+        <f>LEN(F216)</f>
+        <v>12</v>
+      </c>
+      <c r="I216" s="7" t="s">
+        <v>706</v>
+      </c>
+      <c r="J216" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="K216" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L216" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M216" s="3"/>
+      <c r="N216" s="3"/>
+      <c r="O216" s="3"/>
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A217" s="7">
+        <v>216</v>
+      </c>
+      <c r="B217" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C217" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D217" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E217" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F217" s="7" t="s">
+        <v>707</v>
+      </c>
+      <c r="G217" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H217" s="7">
+        <f>LEN(F217)</f>
+        <v>12</v>
+      </c>
+      <c r="I217" s="7" t="s">
+        <v>708</v>
+      </c>
+      <c r="J217" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="K217" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L217" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M217" s="3"/>
+      <c r="N217" s="3"/>
+      <c r="O217" s="3"/>
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A218" s="7">
+        <v>217</v>
+      </c>
+      <c r="B218" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C218" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D218" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="E218" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F218" s="7" t="s">
+        <v>709</v>
+      </c>
+      <c r="G218" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H218" s="7">
+        <f>LEN(F218)</f>
+        <v>12</v>
+      </c>
+      <c r="I218" s="7" t="s">
+        <v>710</v>
+      </c>
+      <c r="J218" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="K218" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L218" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M218" s="3"/>
+      <c r="N218" s="3"/>
+      <c r="O218" s="3"/>
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A219" s="7">
+        <v>218</v>
+      </c>
+      <c r="B219" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C219" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D219" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="E219" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F219" s="7" t="s">
+        <v>711</v>
+      </c>
+      <c r="G219" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H219" s="7">
+        <f>LEN(F219)</f>
+        <v>12</v>
+      </c>
+      <c r="I219" s="7" t="s">
+        <v>712</v>
+      </c>
+      <c r="J219" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="K219" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L219" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M219" s="3"/>
+      <c r="N219" s="3"/>
+      <c r="O219" s="3"/>
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A220" s="7">
+        <v>219</v>
+      </c>
+      <c r="B220" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C220" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D220" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="E220" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F220" s="7" t="s">
+        <v>713</v>
+      </c>
+      <c r="G220" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H220" s="7">
+        <f>LEN(F220)</f>
+        <v>12</v>
+      </c>
+      <c r="I220" s="7" t="s">
+        <v>714</v>
+      </c>
+      <c r="J220" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="K220" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L220" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M220" s="3"/>
+      <c r="N220" s="3"/>
+      <c r="O220" s="3"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O212" xr:uid="{243C8A1C-2FBA-4873-BD31-7545635970F1}"/>
+  <autoFilter ref="A1:O220" xr:uid="{243C8A1C-2FBA-4873-BD31-7545635970F1}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M212" xr:uid="{29F577E0-A9A7-4D3D-B3E7-99484ADFB535}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M220" xr:uid="{29F577E0-A9A7-4D3D-B3E7-99484ADFB535}">
       <formula1>"승인,수정,제외"</formula1>
     </dataValidation>
   </dataValidations>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B090D9B2-35F7-46B3-B66F-10D09C224F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7A2472-6D0D-4DA3-B07F-A682C2D47E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2261" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2262" uniqueCount="732">
   <si>
     <t>—</t>
   </si>
@@ -7854,15 +7854,9 @@
     <t>속이 편한 죽이나 누룽지로 아침을 시작해요.</t>
   </si>
   <si>
-    <t>잡곡밥이나 현미밥은 오래 든든해요.</t>
-  </si>
-  <si>
     <t>금방 준비할 수 있는 든든한 아침이에요.</t>
   </si>
   <si>
-    <t>찐 고구마나 누룽지는 준비가 간단해요.</t>
-  </si>
-  <si>
     <t>부드러운 죽은 아침에 넘기기 편해요.</t>
   </si>
   <si>
@@ -7893,9 +7887,6 @@
     <t>바쁜 아침에도 단백질을 챙길 수 있어요.</t>
   </si>
   <si>
-    <t>손쉬운 단백질 반찬으로 아침을 채워요.</t>
-  </si>
-  <si>
     <t>가벼운 국으로 단백질을 더해요.</t>
   </si>
   <si>
@@ -8253,127 +8244,219 @@
     <t>찐 감자나 옥수수는 준비가 간단해요.</t>
   </si>
   <si>
+    <t>아침추천: 통밀빵/감자</t>
+  </si>
+  <si>
+    <t>통밀빵이나 감자로 아침을 든든하게 해요.</t>
+  </si>
+  <si>
+    <t>아침추천: 시금치국/쌈</t>
+  </si>
+  <si>
+    <t>채소국이나 쌈으로 아침 채소를 챙겨요.</t>
+  </si>
+  <si>
+    <t>아침추천: 샐러드/나물</t>
+  </si>
+  <si>
+    <t>생채소나 나물로 아침 채소를 더해요.</t>
+  </si>
+  <si>
+    <t>아침추천: 비빔밥/나물</t>
+  </si>
+  <si>
+    <t>나물을 곁들이면 아침 채소가 넉넉해요.</t>
+  </si>
+  <si>
+    <t>아침추천: 요거트/두유</t>
+  </si>
+  <si>
+    <t>달지 않은 요거트나 두유로 단백질을 더해요.</t>
+  </si>
+  <si>
+    <t>아침추천: 생선/두부</t>
+  </si>
+  <si>
+    <t>아침추천: 미역국/쑥국</t>
+  </si>
+  <si>
+    <t>아침추천: 백김치/나물</t>
+  </si>
+  <si>
+    <t>백김치와 나물은 짠 반찬보다 염분이 적어요.</t>
+  </si>
+  <si>
+    <t>10-12 아침추천 확대: 모두 . 합계 211개</t>
+  </si>
+  <si>
+    <t>아침추천: 현미밥/감자</t>
+  </si>
+  <si>
+    <t>든든한 현미밥이나 감자로 아침을 시작해요.</t>
+  </si>
+  <si>
+    <t>아침추천: 콩나물국/쌈</t>
+  </si>
+  <si>
+    <t>맑은 국이나 쌈으로 아침에도 채소를 먹어요.</t>
+  </si>
+  <si>
+    <t>아침추천: 호박국/나물</t>
+  </si>
+  <si>
+    <t>부드러운 채소 반찬으로 아침을 채워요.</t>
+  </si>
+  <si>
+    <t>아침추천: 양배추/오이</t>
+  </si>
+  <si>
+    <t>아삭한 채소 한 가지로 아침 채소를 더해요.</t>
+  </si>
+  <si>
+    <t>10-12 아침추천 확대: 모두 . 합계 219개</t>
+  </si>
+  <si>
+    <t>아침추천: 흑미밥/감자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흑미밥이나 감자로 든든하게 아침을 먹어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 고구마/밤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>찐 고구마나 밤은 준비가 간단한 아침이에요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>아침추천: 주먹밥/죽</t>
-  </si>
-  <si>
-    <t>주먹밥이나 죽으로 간단히 아침을 먹어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 김밥/주먹밥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김밥이나 주먹밥으로 간단히 아침을 챙겨요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>아침추천: 호박죽/쌀죽</t>
-  </si>
-  <si>
-    <t>아침추천: 통밀빵/감자</t>
-  </si>
-  <si>
-    <t>통밀빵이나 감자로 아침을 든든하게 해요.</t>
-  </si>
-  <si>
-    <t>아침추천: 시금치국/쌈</t>
-  </si>
-  <si>
-    <t>채소국이나 쌈으로 아침 채소를 챙겨요.</t>
-  </si>
-  <si>
-    <t>아침추천: 샐러드/나물</t>
-  </si>
-  <si>
-    <t>생채소나 나물로 아침 채소를 더해요.</t>
-  </si>
-  <si>
-    <t>아침추천: 비빔밥/나물</t>
-  </si>
-  <si>
-    <t>나물을 곁들이면 아침 채소가 넉넉해요.</t>
-  </si>
-  <si>
-    <t>아침추천: 요거트/두유</t>
-  </si>
-  <si>
-    <t>달지 않은 요거트나 두유로 단백질을 더해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 단호박/우유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>찐 단호박과 우유로 든든한 아침을 먹어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 옥수수/죽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 옥수수/두유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>찐 옥수수와 두유로 간단히 아침을 먹어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 달걀말이/죽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 닭안심/두부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>담백한 단백질로 아침을 든든하게 해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 연두부/두유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부드러운 두부나 두유로 단백질을 더해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 생선/나물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생선구이와 나물은 기름을 덜 쓰는 반찬이에요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>아침추천: 우유/달걀</t>
-  </si>
-  <si>
-    <t>한 잔이나 한 알로 아침 단백질을 챙겨요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 우유/요거트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한 잔이나 한 컵으로 아침 단백질을 챙겨요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>아침추천: 북엇국/달걀</t>
-  </si>
-  <si>
-    <t>가벼운 국으로 아침 단백질을 더해요.</t>
-  </si>
-  <si>
-    <t>아침추천: 생선/두부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 북엇국/두유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가벼운 국이나 두유로 아침 단백질을 더해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>아침추천: 달걀찜/생선</t>
-  </si>
-  <si>
-    <t>찜이나 구이로 기름 적은 아침을 먹어요.</t>
-  </si>
-  <si>
-    <t>아침추천: 미역국/쑥국</t>
-  </si>
-  <si>
-    <t>아침추천: 백김치/나물</t>
-  </si>
-  <si>
-    <t>백김치와 나물은 짠 반찬보다 염분이 적어요.</t>
-  </si>
-  <si>
-    <t>10-12 아침추천 확대: 모두 . 합계 211개</t>
-  </si>
-  <si>
-    <t>아침추천: 옥수수/죽</t>
-  </si>
-  <si>
-    <t>찐 옥수수나 죽으로 간단히 아침을 먹어요.</t>
-  </si>
-  <si>
-    <t>아침추천: 현미밥/감자</t>
-  </si>
-  <si>
-    <t>든든한 현미밥이나 감자로 아침을 시작해요.</t>
-  </si>
-  <si>
-    <t>아침추천: 콩나물국/쌈</t>
-  </si>
-  <si>
-    <t>맑은 국이나 쌈으로 아침에도 채소를 먹어요.</t>
-  </si>
-  <si>
-    <t>아침추천: 호박국/나물</t>
-  </si>
-  <si>
-    <t>부드러운 채소 반찬으로 아침을 채워요.</t>
-  </si>
-  <si>
-    <t>아침추천: 양배추/오이</t>
-  </si>
-  <si>
-    <t>아삭한 채소 한 가지로 아침 채소를 더해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 생선찜/두부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>찜과 두부는 기름을 덜 쓰는 반찬이에요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>아침추천: 달걀/요거트</t>
-  </si>
-  <si>
-    <t>달걀이나 요거트로 아침 단백질을 더해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 요거트/두부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달지 않은 요거트나 두부로 단백질을 더해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>아침추천: 두부/달걀찜</t>
-  </si>
-  <si>
-    <t>부드러운 반찬으로 아침 단백질을 챙겨요.</t>
-  </si>
-  <si>
-    <t>아침추천: 달걀말이/죽</t>
-  </si>
-  <si>
-    <t>달걀말이를 곁들이면 아침이 든든해져요.</t>
-  </si>
-  <si>
-    <t>10-12 아침추천 확대: 모두 . 합계 219개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 순두부/우유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부드러운 순두부나 우유로 단백질을 챙겨요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10-12 끼니 추천에서 죽·달걀이 몰린 짝  다른 메뉴로 바꿈(죽  · 달걀  남김)</t>
   </si>
 </sst>
 </file>
@@ -8860,7 +8943,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F51797-492B-40AC-833D-E19CEF6E9FA5}">
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="120.58203125" style="1" customWidth="1"/>
@@ -8949,27 +9032,32 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>698</v>
+        <v>686</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>715</v>
+        <v>695</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A23" s="1" t="s">
+        <v>731</v>
       </c>
     </row>
   </sheetData>
@@ -10576,7 +10664,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>270</v>
@@ -14860,7 +14948,7 @@
         <v>146</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="G140" s="7" t="s">
         <v>0</v>
@@ -14902,17 +14990,17 @@
         <v>146</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>593</v>
+        <v>696</v>
       </c>
       <c r="G141" s="7" t="s">
-        <v>0</v>
+        <v>590</v>
       </c>
       <c r="H141" s="7">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I141" s="7" t="s">
-        <v>555</v>
+        <v>697</v>
       </c>
       <c r="J141" s="7" t="s">
         <v>155</v>
@@ -14944,7 +15032,7 @@
         <v>146</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="G142" s="7" t="s">
         <v>0</v>
@@ -14954,7 +15042,7 @@
         <v>12</v>
       </c>
       <c r="I142" s="7" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="J142" s="7" t="s">
         <v>155</v>
@@ -14986,17 +15074,17 @@
         <v>146</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>595</v>
+        <v>698</v>
       </c>
       <c r="G143" s="7" t="s">
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="H143" s="7">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="I143" s="7" t="s">
-        <v>557</v>
+        <v>699</v>
       </c>
       <c r="J143" s="7" t="s">
         <v>155</v>
@@ -15028,7 +15116,7 @@
         <v>146</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="G144" s="7" t="s">
         <v>0</v>
@@ -15038,7 +15126,7 @@
         <v>12</v>
       </c>
       <c r="I144" s="7" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="J144" s="7" t="s">
         <v>155</v>
@@ -15070,7 +15158,7 @@
         <v>146</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="G145" s="7" t="s">
         <v>0</v>
@@ -15080,7 +15168,7 @@
         <v>12</v>
       </c>
       <c r="I145" s="7" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="J145" s="7" t="s">
         <v>161</v>
@@ -15112,7 +15200,7 @@
         <v>146</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="G146" s="7" t="s">
         <v>0</v>
@@ -15122,7 +15210,7 @@
         <v>12</v>
       </c>
       <c r="I146" s="7" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="J146" s="7" t="s">
         <v>161</v>
@@ -15154,7 +15242,7 @@
         <v>146</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="G147" s="7" t="s">
         <v>0</v>
@@ -15164,7 +15252,7 @@
         <v>12</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="J147" s="7" t="s">
         <v>161</v>
@@ -15196,7 +15284,7 @@
         <v>146</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="G148" s="7" t="s">
         <v>0</v>
@@ -15206,7 +15294,7 @@
         <v>12</v>
       </c>
       <c r="I148" s="7" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="J148" s="7" t="s">
         <v>161</v>
@@ -15238,7 +15326,7 @@
         <v>146</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="G149" s="7" t="s">
         <v>0</v>
@@ -15248,7 +15336,7 @@
         <v>12</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="J149" s="7" t="s">
         <v>161</v>
@@ -15280,7 +15368,7 @@
         <v>146</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="G150" s="7" t="s">
         <v>0</v>
@@ -15290,7 +15378,7 @@
         <v>12</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="J150" s="7" t="s">
         <v>210</v>
@@ -15322,7 +15410,7 @@
         <v>146</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="G151" s="7" t="s">
         <v>0</v>
@@ -15332,7 +15420,7 @@
         <v>12</v>
       </c>
       <c r="I151" s="7" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="J151" s="7" t="s">
         <v>210</v>
@@ -15364,7 +15452,7 @@
         <v>146</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="G152" s="7" t="s">
         <v>0</v>
@@ -15374,7 +15462,7 @@
         <v>11</v>
       </c>
       <c r="I152" s="7" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="J152" s="7" t="s">
         <v>210</v>
@@ -15406,7 +15494,7 @@
         <v>146</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="G153" s="7" t="s">
         <v>0</v>
@@ -15416,7 +15504,7 @@
         <v>11</v>
       </c>
       <c r="I153" s="7" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="J153" s="7" t="s">
         <v>210</v>
@@ -15448,17 +15536,17 @@
         <v>146</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>606</v>
+        <v>712</v>
       </c>
       <c r="G154" s="7" t="s">
-        <v>0</v>
+        <v>603</v>
       </c>
       <c r="H154" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I154" s="7" t="s">
-        <v>568</v>
+        <v>713</v>
       </c>
       <c r="J154" s="7" t="s">
         <v>210</v>
@@ -15490,7 +15578,7 @@
         <v>146</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G155" s="7" t="s">
         <v>0</v>
@@ -15500,7 +15588,7 @@
         <v>12</v>
       </c>
       <c r="I155" s="7" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="J155" s="7" t="s">
         <v>210</v>
@@ -15532,17 +15620,17 @@
         <v>146</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>608</v>
+        <v>714</v>
       </c>
       <c r="G156" s="7" t="s">
-        <v>0</v>
+        <v>605</v>
       </c>
       <c r="H156" s="7">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I156" s="7" t="s">
-        <v>570</v>
+        <v>715</v>
       </c>
       <c r="J156" s="7" t="s">
         <v>215</v>
@@ -15574,7 +15662,7 @@
         <v>146</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="G157" s="7" t="s">
         <v>0</v>
@@ -15616,7 +15704,7 @@
         <v>146</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="G158" s="7" t="s">
         <v>0</v>
@@ -15626,7 +15714,7 @@
         <v>11</v>
       </c>
       <c r="I158" s="7" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="J158" s="7" t="s">
         <v>215</v>
@@ -15658,7 +15746,7 @@
         <v>146</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="G159" s="7" t="s">
         <v>0</v>
@@ -15668,7 +15756,7 @@
         <v>11</v>
       </c>
       <c r="I159" s="7" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="J159" s="7" t="s">
         <v>215</v>
@@ -15700,7 +15788,7 @@
         <v>146</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="G160" s="7" t="s">
         <v>0</v>
@@ -15742,7 +15830,7 @@
         <v>146</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="G161" s="7" t="s">
         <v>0</v>
@@ -15752,7 +15840,7 @@
         <v>11</v>
       </c>
       <c r="I161" s="7" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="J161" s="7" t="s">
         <v>215</v>
@@ -15784,7 +15872,7 @@
         <v>146</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="G162" s="7" t="s">
         <v>0</v>
@@ -15794,7 +15882,7 @@
         <v>12</v>
       </c>
       <c r="I162" s="7" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="J162" s="7" t="s">
         <v>215</v>
@@ -15826,7 +15914,7 @@
         <v>146</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="G163" s="7" t="s">
         <v>0</v>
@@ -15836,7 +15924,7 @@
         <v>11</v>
       </c>
       <c r="I163" s="7" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="J163" s="7" t="s">
         <v>215</v>
@@ -15868,7 +15956,7 @@
         <v>146</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G164" s="7" t="s">
         <v>0</v>
@@ -15878,7 +15966,7 @@
         <v>12</v>
       </c>
       <c r="I164" s="7" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="J164" s="7" t="s">
         <v>210</v>
@@ -15910,7 +15998,7 @@
         <v>146</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="G165" s="7" t="s">
         <v>0</v>
@@ -15920,7 +16008,7 @@
         <v>12</v>
       </c>
       <c r="I165" s="7" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="J165" s="7" t="s">
         <v>210</v>
@@ -15952,7 +16040,7 @@
         <v>146</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="G166" s="7" t="s">
         <v>0</v>
@@ -15962,7 +16050,7 @@
         <v>12</v>
       </c>
       <c r="I166" s="7" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="J166" s="7" t="s">
         <v>210</v>
@@ -15994,7 +16082,7 @@
         <v>146</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="G167" s="7" t="s">
         <v>0</v>
@@ -16004,7 +16092,7 @@
         <v>12</v>
       </c>
       <c r="I167" s="7" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="J167" s="7" t="s">
         <v>210</v>
@@ -16036,7 +16124,7 @@
         <v>146</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="G168" s="7" t="s">
         <v>0</v>
@@ -16046,7 +16134,7 @@
         <v>12</v>
       </c>
       <c r="I168" s="7" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="J168" s="7" t="s">
         <v>210</v>
@@ -16078,7 +16166,7 @@
         <v>146</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="G169" s="7" t="s">
         <v>0</v>
@@ -16088,7 +16176,7 @@
         <v>12</v>
       </c>
       <c r="I169" s="7" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="J169" s="7" t="s">
         <v>161</v>
@@ -16120,7 +16208,7 @@
         <v>146</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="G170" s="7" t="s">
         <v>0</v>
@@ -16130,7 +16218,7 @@
         <v>12</v>
       </c>
       <c r="I170" s="7" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="J170" s="7" t="s">
         <v>161</v>
@@ -16162,7 +16250,7 @@
         <v>146</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="G171" s="7" t="s">
         <v>0</v>
@@ -16172,7 +16260,7 @@
         <v>11</v>
       </c>
       <c r="I171" s="7" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="J171" s="7" t="s">
         <v>161</v>
@@ -16204,7 +16292,7 @@
         <v>146</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="G172" s="7" t="s">
         <v>0</v>
@@ -16214,7 +16302,7 @@
         <v>11</v>
       </c>
       <c r="I172" s="7" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="J172" s="7" t="s">
         <v>161</v>
@@ -16246,7 +16334,7 @@
         <v>146</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="G173" s="7" t="s">
         <v>0</v>
@@ -16256,7 +16344,7 @@
         <v>12</v>
       </c>
       <c r="I173" s="7" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="J173" s="7" t="s">
         <v>161</v>
@@ -16288,7 +16376,7 @@
         <v>146</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="G174" s="7" t="s">
         <v>0</v>
@@ -16298,7 +16386,7 @@
         <v>11</v>
       </c>
       <c r="I174" s="7" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="J174" s="7" t="s">
         <v>161</v>
@@ -16330,7 +16418,7 @@
         <v>146</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="G175" s="7" t="s">
         <v>0</v>
@@ -16340,7 +16428,7 @@
         <v>12</v>
       </c>
       <c r="I175" s="7" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="J175" s="7" t="s">
         <v>187</v>
@@ -16372,7 +16460,7 @@
         <v>146</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="G176" s="7" t="s">
         <v>0</v>
@@ -16382,7 +16470,7 @@
         <v>12</v>
       </c>
       <c r="I176" s="7" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="J176" s="7" t="s">
         <v>187</v>
@@ -16414,7 +16502,7 @@
         <v>146</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="G177" s="7" t="s">
         <v>0</v>
@@ -16424,7 +16512,7 @@
         <v>12</v>
       </c>
       <c r="I177" s="7" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="J177" s="7" t="s">
         <v>155</v>
@@ -16456,7 +16544,7 @@
         <v>146</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="G178" s="7" t="s">
         <v>0</v>
@@ -16466,7 +16554,7 @@
         <v>11</v>
       </c>
       <c r="I178" s="7" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="J178" s="7" t="s">
         <v>215</v>
@@ -16498,7 +16586,7 @@
         <v>146</v>
       </c>
       <c r="F179" s="7" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="G179" s="7" t="s">
         <v>0</v>
@@ -16508,7 +16596,7 @@
         <v>12</v>
       </c>
       <c r="I179" s="7" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="J179" s="7" t="s">
         <v>215</v>
@@ -16540,7 +16628,7 @@
         <v>146</v>
       </c>
       <c r="F180" s="7" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="G180" s="7" t="s">
         <v>0</v>
@@ -16550,7 +16638,7 @@
         <v>12</v>
       </c>
       <c r="I180" s="7" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="J180" s="7" t="s">
         <v>215</v>
@@ -16582,7 +16670,7 @@
         <v>146</v>
       </c>
       <c r="F181" s="7" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G181" s="7" t="s">
         <v>0</v>
@@ -16592,7 +16680,7 @@
         <v>12</v>
       </c>
       <c r="I181" s="7" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="J181" s="7" t="s">
         <v>215</v>
@@ -16624,7 +16712,7 @@
         <v>146</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="G182" s="7" t="s">
         <v>0</v>
@@ -16634,7 +16722,7 @@
         <v>12</v>
       </c>
       <c r="I182" s="7" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="J182" s="7" t="s">
         <v>215</v>
@@ -16666,7 +16754,7 @@
         <v>146</v>
       </c>
       <c r="F183" s="7" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="G183" s="7" t="s">
         <v>0</v>
@@ -16676,7 +16764,7 @@
         <v>12</v>
       </c>
       <c r="I183" s="7" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="J183" s="7" t="s">
         <v>210</v>
@@ -16708,7 +16796,7 @@
         <v>146</v>
       </c>
       <c r="F184" s="7" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="G184" s="7" t="s">
         <v>0</v>
@@ -16718,7 +16806,7 @@
         <v>11</v>
       </c>
       <c r="I184" s="7" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="J184" s="7" t="s">
         <v>210</v>
@@ -16750,7 +16838,7 @@
         <v>146</v>
       </c>
       <c r="F185" s="7" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="G185" s="7" t="s">
         <v>0</v>
@@ -16760,7 +16848,7 @@
         <v>11</v>
       </c>
       <c r="I185" s="7" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="J185" s="7" t="s">
         <v>210</v>
@@ -16792,7 +16880,7 @@
         <v>146</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="G186" s="7" t="s">
         <v>0</v>
@@ -16802,7 +16890,7 @@
         <v>12</v>
       </c>
       <c r="I186" s="7" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="J186" s="7" t="s">
         <v>161</v>
@@ -16834,7 +16922,7 @@
         <v>146</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="G187" s="7" t="s">
         <v>0</v>
@@ -16844,7 +16932,7 @@
         <v>11</v>
       </c>
       <c r="I187" s="7" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="J187" s="7" t="s">
         <v>161</v>
@@ -16876,7 +16964,7 @@
         <v>146</v>
       </c>
       <c r="F188" s="7" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="G188" s="7" t="s">
         <v>0</v>
@@ -16886,7 +16974,7 @@
         <v>11</v>
       </c>
       <c r="I188" s="7" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="J188" s="7" t="s">
         <v>161</v>
@@ -16918,7 +17006,7 @@
         <v>146</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="G189" s="7" t="s">
         <v>0</v>
@@ -16928,7 +17016,7 @@
         <v>11</v>
       </c>
       <c r="I189" s="7" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="J189" s="7" t="s">
         <v>161</v>
@@ -16960,7 +17048,7 @@
         <v>146</v>
       </c>
       <c r="F190" s="7" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="G190" s="7" t="s">
         <v>0</v>
@@ -16970,7 +17058,7 @@
         <v>12</v>
       </c>
       <c r="I190" s="7" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="J190" s="7" t="s">
         <v>161</v>
@@ -17002,7 +17090,7 @@
         <v>146</v>
       </c>
       <c r="F191" s="7" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="G191" s="7" t="s">
         <v>0</v>
@@ -17012,7 +17100,7 @@
         <v>12</v>
       </c>
       <c r="I191" s="7" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="J191" s="7" t="s">
         <v>161</v>
@@ -17044,7 +17132,7 @@
         <v>146</v>
       </c>
       <c r="F192" s="7" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="G192" s="7" t="s">
         <v>0</v>
@@ -17054,7 +17142,7 @@
         <v>12</v>
       </c>
       <c r="I192" s="7" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="J192" s="7" t="s">
         <v>161</v>
@@ -17086,7 +17174,7 @@
         <v>146</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="G193" s="7" t="s">
         <v>0</v>
@@ -17096,7 +17184,7 @@
         <v>12</v>
       </c>
       <c r="I193" s="7" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="J193" s="7" t="s">
         <v>161</v>
@@ -17128,7 +17216,7 @@
         <v>146</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="G194" s="7" t="s">
         <v>0</v>
@@ -17138,7 +17226,7 @@
         <v>12</v>
       </c>
       <c r="I194" s="7" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="J194" s="7" t="s">
         <v>161</v>
@@ -17170,7 +17258,7 @@
         <v>146</v>
       </c>
       <c r="F195" s="7" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="G195" s="7" t="s">
         <v>0</v>
@@ -17180,7 +17268,7 @@
         <v>12</v>
       </c>
       <c r="I195" s="7" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="J195" s="7" t="s">
         <v>187</v>
@@ -17212,7 +17300,7 @@
         <v>146</v>
       </c>
       <c r="F196" s="7" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="G196" s="7" t="s">
         <v>0</v>
@@ -17222,7 +17310,7 @@
         <v>11</v>
       </c>
       <c r="I196" s="7" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="J196" s="7" t="s">
         <v>187</v>
@@ -17254,7 +17342,7 @@
         <v>146</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="G197" s="7" t="s">
         <v>0</v>
@@ -17264,7 +17352,7 @@
         <v>12</v>
       </c>
       <c r="I197" s="7" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="J197" s="7" t="s">
         <v>187</v>
@@ -17296,7 +17384,7 @@
         <v>146</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="G198" s="7" t="s">
         <v>0</v>
@@ -17306,7 +17394,7 @@
         <v>12</v>
       </c>
       <c r="I198" s="7" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="J198" s="7" t="s">
         <v>147</v>
@@ -17338,7 +17426,7 @@
         <v>146</v>
       </c>
       <c r="F199" s="7" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="G199" s="7" t="s">
         <v>0</v>
@@ -17348,7 +17436,7 @@
         <v>12</v>
       </c>
       <c r="I199" s="7" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="J199" s="7" t="s">
         <v>155</v>
@@ -17380,17 +17468,17 @@
         <v>146</v>
       </c>
       <c r="F200" s="7" t="s">
-        <v>675</v>
+        <v>701</v>
       </c>
       <c r="G200" s="7" t="s">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H200" s="7">
         <f t="shared" si="7"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I200" s="7" t="s">
-        <v>676</v>
+        <v>702</v>
       </c>
       <c r="J200" s="7" t="s">
         <v>155</v>
@@ -17422,17 +17510,17 @@
         <v>146</v>
       </c>
       <c r="F201" s="7" t="s">
-        <v>677</v>
+        <v>704</v>
       </c>
       <c r="G201" s="7" t="s">
-        <v>0</v>
+        <v>703</v>
       </c>
       <c r="H201" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I201" s="7" t="s">
-        <v>558</v>
+        <v>705</v>
       </c>
       <c r="J201" s="7" t="s">
         <v>155</v>
@@ -17464,7 +17552,7 @@
         <v>146</v>
       </c>
       <c r="F202" s="7" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="G202" s="7" t="s">
         <v>0</v>
@@ -17474,7 +17562,7 @@
         <v>12</v>
       </c>
       <c r="I202" s="7" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="J202" s="7" t="s">
         <v>155</v>
@@ -17506,7 +17594,7 @@
         <v>146</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="G203" s="7" t="s">
         <v>0</v>
@@ -17516,7 +17604,7 @@
         <v>12</v>
       </c>
       <c r="I203" s="7" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="J203" s="7" t="s">
         <v>161</v>
@@ -17548,7 +17636,7 @@
         <v>146</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="G204" s="7" t="s">
         <v>0</v>
@@ -17558,7 +17646,7 @@
         <v>12</v>
       </c>
       <c r="I204" s="7" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="J204" s="7" t="s">
         <v>161</v>
@@ -17590,7 +17678,7 @@
         <v>146</v>
       </c>
       <c r="F205" s="7" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="G205" s="7" t="s">
         <v>0</v>
@@ -17600,7 +17688,7 @@
         <v>12</v>
       </c>
       <c r="I205" s="7" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="J205" s="7" t="s">
         <v>161</v>
@@ -17632,7 +17720,7 @@
         <v>146</v>
       </c>
       <c r="F206" s="7" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="G206" s="7" t="s">
         <v>0</v>
@@ -17642,7 +17730,7 @@
         <v>12</v>
       </c>
       <c r="I206" s="7" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="J206" s="7" t="s">
         <v>210</v>
@@ -17674,17 +17762,17 @@
         <v>146</v>
       </c>
       <c r="F207" s="7" t="s">
-        <v>688</v>
+        <v>717</v>
       </c>
       <c r="G207" s="7" t="s">
-        <v>0</v>
+        <v>716</v>
       </c>
       <c r="H207" s="7">
         <f t="shared" si="7"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I207" s="7" t="s">
-        <v>689</v>
+        <v>718</v>
       </c>
       <c r="J207" s="7" t="s">
         <v>210</v>
@@ -17716,17 +17804,17 @@
         <v>146</v>
       </c>
       <c r="F208" s="7" t="s">
-        <v>690</v>
+        <v>720</v>
       </c>
       <c r="G208" s="7" t="s">
-        <v>0</v>
+        <v>719</v>
       </c>
       <c r="H208" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I208" s="7" t="s">
-        <v>691</v>
+        <v>721</v>
       </c>
       <c r="J208" s="7" t="s">
         <v>210</v>
@@ -17758,7 +17846,7 @@
         <v>146</v>
       </c>
       <c r="F209" s="7" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="G209" s="7" t="s">
         <v>0</v>
@@ -17768,7 +17856,7 @@
         <v>11</v>
       </c>
       <c r="I209" s="7" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="J209" s="7" t="s">
         <v>215</v>
@@ -17800,17 +17888,17 @@
         <v>146</v>
       </c>
       <c r="F210" s="7" t="s">
-        <v>693</v>
+        <v>723</v>
       </c>
       <c r="G210" s="7" t="s">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="H210" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I210" s="7" t="s">
-        <v>694</v>
+        <v>724</v>
       </c>
       <c r="J210" s="7" t="s">
         <v>215</v>
@@ -17842,7 +17930,7 @@
         <v>146</v>
       </c>
       <c r="F211" s="7" t="s">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="G211" s="7" t="s">
         <v>0</v>
@@ -17884,7 +17972,7 @@
         <v>146</v>
       </c>
       <c r="F212" s="7" t="s">
-        <v>696</v>
+        <v>684</v>
       </c>
       <c r="G212" s="7" t="s">
         <v>0</v>
@@ -17894,7 +17982,7 @@
         <v>12</v>
       </c>
       <c r="I212" s="7" t="s">
-        <v>697</v>
+        <v>685</v>
       </c>
       <c r="J212" s="7" t="s">
         <v>187</v>
@@ -17926,17 +18014,17 @@
         <v>146</v>
       </c>
       <c r="F213" s="7" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="G213" s="7" t="s">
-        <v>0</v>
+        <v>706</v>
       </c>
       <c r="H213" s="7">
-        <f>LEN(F213)</f>
-        <v>11</v>
+        <f t="shared" ref="H213:H220" si="8">LEN(F213)</f>
+        <v>12</v>
       </c>
       <c r="I213" s="7" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="J213" s="7" t="s">
         <v>155</v>
@@ -17968,17 +18056,17 @@
         <v>146</v>
       </c>
       <c r="F214" s="7" t="s">
-        <v>701</v>
+        <v>687</v>
       </c>
       <c r="G214" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H214" s="7">
-        <f>LEN(F214)</f>
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="I214" s="7" t="s">
-        <v>702</v>
+        <v>688</v>
       </c>
       <c r="J214" s="7" t="s">
         <v>155</v>
@@ -18010,17 +18098,17 @@
         <v>146</v>
       </c>
       <c r="F215" s="7" t="s">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="G215" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H215" s="7">
-        <f>LEN(F215)</f>
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="I215" s="7" t="s">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="J215" s="7" t="s">
         <v>161</v>
@@ -18052,17 +18140,17 @@
         <v>146</v>
       </c>
       <c r="F216" s="7" t="s">
-        <v>705</v>
+        <v>691</v>
       </c>
       <c r="G216" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H216" s="7">
-        <f>LEN(F216)</f>
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="I216" s="7" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="J216" s="7" t="s">
         <v>161</v>
@@ -18094,17 +18182,17 @@
         <v>146</v>
       </c>
       <c r="F217" s="7" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="G217" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H217" s="7">
-        <f>LEN(F217)</f>
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="I217" s="7" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="J217" s="7" t="s">
         <v>161</v>
@@ -18136,17 +18224,17 @@
         <v>146</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>709</v>
+        <v>726</v>
       </c>
       <c r="G218" s="7" t="s">
-        <v>0</v>
+        <v>725</v>
       </c>
       <c r="H218" s="7">
-        <f>LEN(F218)</f>
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="I218" s="7" t="s">
-        <v>710</v>
+        <v>727</v>
       </c>
       <c r="J218" s="7" t="s">
         <v>210</v>
@@ -18178,17 +18266,17 @@
         <v>146</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>711</v>
+        <v>729</v>
       </c>
       <c r="G219" s="7" t="s">
-        <v>0</v>
+        <v>728</v>
       </c>
       <c r="H219" s="7">
-        <f>LEN(F219)</f>
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="I219" s="7" t="s">
-        <v>712</v>
+        <v>730</v>
       </c>
       <c r="J219" s="7" t="s">
         <v>210</v>
@@ -18220,17 +18308,17 @@
         <v>146</v>
       </c>
       <c r="F220" s="7" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="G220" s="7" t="s">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="H220" s="7">
-        <f>LEN(F220)</f>
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="I220" s="7" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="J220" s="7" t="s">
         <v>210</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7A2472-6D0D-4DA3-B07F-A682C2D47E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233E7059-83B3-4459-AF67-56686B43E52A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2262" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2263" uniqueCount="734">
   <si>
     <t>—</t>
   </si>
@@ -8457,6 +8457,14 @@
   </si>
   <si>
     <t>10-12 끼니 추천에서 죽·달걀이 몰린 짝  다른 메뉴로 바꿈(죽  · 달걀  남김)</t>
+  </si>
+  <si>
+    <t>아침추천: 백김치/생채</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백김치와 생채는 짠 반찬보다 염분이 적어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -8943,7 +8951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F51797-492B-40AC-833D-E19CEF6E9FA5}">
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="120.58203125" style="1" customWidth="1"/>
@@ -9057,6 +9065,11 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A24" s="1" t="s">
         <v>731</v>
       </c>
     </row>
@@ -15662,17 +15675,17 @@
         <v>146</v>
       </c>
       <c r="F157" s="7" t="s">
+        <v>732</v>
+      </c>
+      <c r="G157" s="7" t="s">
         <v>606</v>
-      </c>
-      <c r="G157" s="7" t="s">
-        <v>0</v>
       </c>
       <c r="H157" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I157" s="7" t="s">
-        <v>465</v>
+        <v>733</v>
       </c>
       <c r="J157" s="7" t="s">
         <v>187</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233E7059-83B3-4459-AF67-56686B43E52A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E55493-6D33-45BE-A017-0AA308FC1CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2263" uniqueCount="734">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2264" uniqueCount="742">
   <si>
     <t>—</t>
   </si>
@@ -7851,15 +7851,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>속이 편한 죽이나 누룽지로 아침을 시작해요.</t>
-  </si>
-  <si>
-    <t>금방 준비할 수 있는 든든한 아침이에요.</t>
-  </si>
-  <si>
-    <t>부드러운 죽은 아침에 넘기기 편해요.</t>
-  </si>
-  <si>
     <t>담백한 국으로 아침에도 채소를 먹어요.</t>
   </si>
   <si>
@@ -7957,26 +7948,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>아침추천: 죽/누룽지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 잡곡밥/죽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 오트밀/감자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 고구마/죽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 전복죽/쌀죽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>아침추천: 미역국/뭇국</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8238,18 +8209,6 @@
     <t>10-12 저녁추천 확대: 모두 . 합계 197개</t>
   </si>
   <si>
-    <t>아침추천: 감자/옥수수</t>
-  </si>
-  <si>
-    <t>찐 감자나 옥수수는 준비가 간단해요.</t>
-  </si>
-  <si>
-    <t>아침추천: 통밀빵/감자</t>
-  </si>
-  <si>
-    <t>통밀빵이나 감자로 아침을 든든하게 해요.</t>
-  </si>
-  <si>
     <t>아침추천: 시금치국/쌈</t>
   </si>
   <si>
@@ -8289,12 +8248,6 @@
     <t>10-12 아침추천 확대: 모두 . 합계 211개</t>
   </si>
   <si>
-    <t>아침추천: 현미밥/감자</t>
-  </si>
-  <si>
-    <t>든든한 현미밥이나 감자로 아침을 시작해요.</t>
-  </si>
-  <si>
     <t>아침추천: 콩나물국/쌈</t>
   </si>
   <si>
@@ -8316,58 +8269,6 @@
     <t>10-12 아침추천 확대: 모두 . 합계 219개</t>
   </si>
   <si>
-    <t>아침추천: 흑미밥/감자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>흑미밥이나 감자로 든든하게 아침을 먹어요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 고구마/밤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>찐 고구마나 밤은 준비가 간단한 아침이에요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 주먹밥/죽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 김밥/주먹밥</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김밥이나 주먹밥으로 간단히 아침을 챙겨요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 호박죽/쌀죽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 단호박/우유</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>찐 단호박과 우유로 든든한 아침을 먹어요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 옥수수/죽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 옥수수/두유</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>찐 옥수수와 두유로 간단히 아침을 먹어요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>아침추천: 달걀말이/죽</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8465,6 +8366,145 @@
   <si>
     <t>백김치와 생채는 짠 반찬보다 염분이 적어요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 죽/누룽지 (탄수화물만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 현미밥+나물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현미밥에 나물을 곁들이면 혈당이 천천히 올라요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>식생활지침 「골고루 먹기」 · 당뇨병 식사요법(대한당뇨병학회)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 흑미밥/감자 (탄수화물만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 잡곡밥+두부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>잡곡밥에 두부를 곁들이면 오래 든든해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 오트밀/감자 (탄수화물만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 오트밀+우유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오트밀에 우유를 더하면 단백질도 함께 챙겨요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 고구마/밤 (탄수화물만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 고구마+두유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고구마에 두유를 곁들이면 단백질이 더해져요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 전복죽/쌀죽 (탄수화물만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 현미밥+생선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현미밥과 생선구이로 균형 잡힌 아침을 먹어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 감자/옥수수 (탄수화물만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 감자+요거트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>찐 감자에 요거트를 곁들이면 단백질이 더해져요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 김밥/주먹밥 (탄수화물만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 통밀빵+채소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통밀빵에 채소를 곁들이면 든든하고 가벼워요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 단호박/우유 (탄수화물만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 단호박+우유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>찐 단호박에 우유를 곁들여 든든하게 먹어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 통밀빵/감자 (탄수화물만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 흑미밥+나물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흑미밥에 나물을 곁들이면 아침 채소도 챙겨요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 옥수수/두유 (탄수화물만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 옥수수+두유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>찐 옥수수에 두유를 곁들이면 단백질이 더해져요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 현미밥/감자 (탄수화물만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 보리밥+나물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보리밥에 나물을 곁들이면 오래 든든해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10-12 끼니 추천 원칙 추가: 탄수화물만 있는 짝(죽·누룽지·김밥·주먹밥·감자/옥수수 등)  빼고, 밥·빵·고구마에 단백질이나 채소를 붙임. 「A+B」는 함께 먹기, 「A/B」는 둘 중 하나</t>
   </si>
 </sst>
 </file>
@@ -8951,7 +8991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F51797-492B-40AC-833D-E19CEF6E9FA5}">
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="120.58203125" style="1" customWidth="1"/>
@@ -9040,37 +9080,42 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>686</v>
+        <v>674</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>695</v>
+        <v>681</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>731</v>
+        <v>704</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>731</v>
+        <v>704</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A25" s="1" t="s">
+        <v>741</v>
       </c>
     </row>
   </sheetData>
@@ -10677,7 +10722,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>270</v>
@@ -14944,7 +14989,7 @@
       <c r="N139" s="3"/>
       <c r="O139" s="3"/>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A140" s="7">
         <v>139</v>
       </c>
@@ -14961,20 +15006,20 @@
         <v>146</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>589</v>
+        <v>708</v>
       </c>
       <c r="G140" s="7" t="s">
-        <v>0</v>
+        <v>707</v>
       </c>
       <c r="H140" s="7">
         <f t="shared" ref="H140:H177" si="5">LEN(F140)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I140" s="7" t="s">
-        <v>554</v>
+        <v>709</v>
       </c>
       <c r="J140" s="7" t="s">
-        <v>155</v>
+        <v>710</v>
       </c>
       <c r="K140" s="7" t="s">
         <v>464</v>
@@ -14986,7 +15031,7 @@
       <c r="N140" s="3"/>
       <c r="O140" s="3"/>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A141" s="7">
         <v>140</v>
       </c>
@@ -15003,20 +15048,20 @@
         <v>146</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>696</v>
+        <v>712</v>
       </c>
       <c r="G141" s="7" t="s">
-        <v>590</v>
+        <v>711</v>
       </c>
       <c r="H141" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I141" s="7" t="s">
-        <v>697</v>
+        <v>713</v>
       </c>
       <c r="J141" s="7" t="s">
-        <v>155</v>
+        <v>710</v>
       </c>
       <c r="K141" s="7" t="s">
         <v>464</v>
@@ -15028,7 +15073,7 @@
       <c r="N141" s="3"/>
       <c r="O141" s="3"/>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A142" s="7">
         <v>141</v>
       </c>
@@ -15045,20 +15090,20 @@
         <v>146</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>591</v>
+        <v>715</v>
       </c>
       <c r="G142" s="7" t="s">
-        <v>0</v>
+        <v>714</v>
       </c>
       <c r="H142" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I142" s="7" t="s">
-        <v>555</v>
+        <v>716</v>
       </c>
       <c r="J142" s="7" t="s">
-        <v>155</v>
+        <v>710</v>
       </c>
       <c r="K142" s="7" t="s">
         <v>464</v>
@@ -15070,7 +15115,7 @@
       <c r="N142" s="3"/>
       <c r="O142" s="3"/>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A143" s="7">
         <v>142</v>
       </c>
@@ -15087,20 +15132,20 @@
         <v>146</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>698</v>
+        <v>718</v>
       </c>
       <c r="G143" s="7" t="s">
-        <v>592</v>
+        <v>717</v>
       </c>
       <c r="H143" s="7">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I143" s="7" t="s">
-        <v>699</v>
+        <v>719</v>
       </c>
       <c r="J143" s="7" t="s">
-        <v>155</v>
+        <v>710</v>
       </c>
       <c r="K143" s="7" t="s">
         <v>464</v>
@@ -15112,7 +15157,7 @@
       <c r="N143" s="3"/>
       <c r="O143" s="3"/>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A144" s="7">
         <v>143</v>
       </c>
@@ -15129,20 +15174,20 @@
         <v>146</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>593</v>
+        <v>721</v>
       </c>
       <c r="G144" s="7" t="s">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="H144" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I144" s="7" t="s">
-        <v>556</v>
+        <v>722</v>
       </c>
       <c r="J144" s="7" t="s">
-        <v>155</v>
+        <v>710</v>
       </c>
       <c r="K144" s="7" t="s">
         <v>464</v>
@@ -15171,7 +15216,7 @@
         <v>146</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="G145" s="7" t="s">
         <v>0</v>
@@ -15181,7 +15226,7 @@
         <v>12</v>
       </c>
       <c r="I145" s="7" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="J145" s="7" t="s">
         <v>161</v>
@@ -15213,7 +15258,7 @@
         <v>146</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="G146" s="7" t="s">
         <v>0</v>
@@ -15223,7 +15268,7 @@
         <v>12</v>
       </c>
       <c r="I146" s="7" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="J146" s="7" t="s">
         <v>161</v>
@@ -15255,7 +15300,7 @@
         <v>146</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="G147" s="7" t="s">
         <v>0</v>
@@ -15265,7 +15310,7 @@
         <v>12</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="J147" s="7" t="s">
         <v>161</v>
@@ -15297,7 +15342,7 @@
         <v>146</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="G148" s="7" t="s">
         <v>0</v>
@@ -15307,7 +15352,7 @@
         <v>12</v>
       </c>
       <c r="I148" s="7" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="J148" s="7" t="s">
         <v>161</v>
@@ -15339,7 +15384,7 @@
         <v>146</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="G149" s="7" t="s">
         <v>0</v>
@@ -15349,7 +15394,7 @@
         <v>12</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="J149" s="7" t="s">
         <v>161</v>
@@ -15381,7 +15426,7 @@
         <v>146</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="G150" s="7" t="s">
         <v>0</v>
@@ -15391,7 +15436,7 @@
         <v>12</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="J150" s="7" t="s">
         <v>210</v>
@@ -15423,7 +15468,7 @@
         <v>146</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="G151" s="7" t="s">
         <v>0</v>
@@ -15433,7 +15478,7 @@
         <v>12</v>
       </c>
       <c r="I151" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="J151" s="7" t="s">
         <v>210</v>
@@ -15465,7 +15510,7 @@
         <v>146</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="G152" s="7" t="s">
         <v>0</v>
@@ -15475,7 +15520,7 @@
         <v>11</v>
       </c>
       <c r="I152" s="7" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="J152" s="7" t="s">
         <v>210</v>
@@ -15507,7 +15552,7 @@
         <v>146</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="G153" s="7" t="s">
         <v>0</v>
@@ -15517,7 +15562,7 @@
         <v>11</v>
       </c>
       <c r="I153" s="7" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="J153" s="7" t="s">
         <v>210</v>
@@ -15549,17 +15594,17 @@
         <v>146</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>712</v>
+        <v>685</v>
       </c>
       <c r="G154" s="7" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="H154" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I154" s="7" t="s">
-        <v>713</v>
+        <v>686</v>
       </c>
       <c r="J154" s="7" t="s">
         <v>210</v>
@@ -15591,7 +15636,7 @@
         <v>146</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="G155" s="7" t="s">
         <v>0</v>
@@ -15601,7 +15646,7 @@
         <v>12</v>
       </c>
       <c r="I155" s="7" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="J155" s="7" t="s">
         <v>210</v>
@@ -15633,17 +15678,17 @@
         <v>146</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>714</v>
+        <v>687</v>
       </c>
       <c r="G156" s="7" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="H156" s="7">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="I156" s="7" t="s">
-        <v>715</v>
+        <v>688</v>
       </c>
       <c r="J156" s="7" t="s">
         <v>215</v>
@@ -15675,17 +15720,17 @@
         <v>146</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>732</v>
+        <v>705</v>
       </c>
       <c r="G157" s="7" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="H157" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I157" s="7" t="s">
-        <v>733</v>
+        <v>706</v>
       </c>
       <c r="J157" s="7" t="s">
         <v>187</v>
@@ -15717,7 +15762,7 @@
         <v>146</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="G158" s="7" t="s">
         <v>0</v>
@@ -15727,7 +15772,7 @@
         <v>11</v>
       </c>
       <c r="I158" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="J158" s="7" t="s">
         <v>215</v>
@@ -15759,7 +15804,7 @@
         <v>146</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="G159" s="7" t="s">
         <v>0</v>
@@ -15769,7 +15814,7 @@
         <v>11</v>
       </c>
       <c r="I159" s="7" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="J159" s="7" t="s">
         <v>215</v>
@@ -15801,7 +15846,7 @@
         <v>146</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="G160" s="7" t="s">
         <v>0</v>
@@ -15843,7 +15888,7 @@
         <v>146</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="G161" s="7" t="s">
         <v>0</v>
@@ -15853,7 +15898,7 @@
         <v>11</v>
       </c>
       <c r="I161" s="7" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="J161" s="7" t="s">
         <v>215</v>
@@ -15885,7 +15930,7 @@
         <v>146</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="G162" s="7" t="s">
         <v>0</v>
@@ -15895,7 +15940,7 @@
         <v>12</v>
       </c>
       <c r="I162" s="7" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="J162" s="7" t="s">
         <v>215</v>
@@ -15927,7 +15972,7 @@
         <v>146</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="G163" s="7" t="s">
         <v>0</v>
@@ -15937,7 +15982,7 @@
         <v>11</v>
       </c>
       <c r="I163" s="7" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="J163" s="7" t="s">
         <v>215</v>
@@ -15969,7 +16014,7 @@
         <v>146</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="G164" s="7" t="s">
         <v>0</v>
@@ -15979,7 +16024,7 @@
         <v>12</v>
       </c>
       <c r="I164" s="7" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="J164" s="7" t="s">
         <v>210</v>
@@ -16011,7 +16056,7 @@
         <v>146</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="G165" s="7" t="s">
         <v>0</v>
@@ -16021,7 +16066,7 @@
         <v>12</v>
       </c>
       <c r="I165" s="7" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="J165" s="7" t="s">
         <v>210</v>
@@ -16053,7 +16098,7 @@
         <v>146</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="G166" s="7" t="s">
         <v>0</v>
@@ -16063,7 +16108,7 @@
         <v>12</v>
       </c>
       <c r="I166" s="7" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="J166" s="7" t="s">
         <v>210</v>
@@ -16095,7 +16140,7 @@
         <v>146</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="G167" s="7" t="s">
         <v>0</v>
@@ -16105,7 +16150,7 @@
         <v>12</v>
       </c>
       <c r="I167" s="7" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="J167" s="7" t="s">
         <v>210</v>
@@ -16137,7 +16182,7 @@
         <v>146</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="G168" s="7" t="s">
         <v>0</v>
@@ -16147,7 +16192,7 @@
         <v>12</v>
       </c>
       <c r="I168" s="7" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="J168" s="7" t="s">
         <v>210</v>
@@ -16179,7 +16224,7 @@
         <v>146</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="G169" s="7" t="s">
         <v>0</v>
@@ -16189,7 +16234,7 @@
         <v>12</v>
       </c>
       <c r="I169" s="7" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="J169" s="7" t="s">
         <v>161</v>
@@ -16221,7 +16266,7 @@
         <v>146</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="G170" s="7" t="s">
         <v>0</v>
@@ -16231,7 +16276,7 @@
         <v>12</v>
       </c>
       <c r="I170" s="7" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="J170" s="7" t="s">
         <v>161</v>
@@ -16263,7 +16308,7 @@
         <v>146</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="G171" s="7" t="s">
         <v>0</v>
@@ -16273,7 +16318,7 @@
         <v>11</v>
       </c>
       <c r="I171" s="7" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="J171" s="7" t="s">
         <v>161</v>
@@ -16305,7 +16350,7 @@
         <v>146</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="G172" s="7" t="s">
         <v>0</v>
@@ -16315,7 +16360,7 @@
         <v>11</v>
       </c>
       <c r="I172" s="7" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="J172" s="7" t="s">
         <v>161</v>
@@ -16347,7 +16392,7 @@
         <v>146</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="G173" s="7" t="s">
         <v>0</v>
@@ -16357,7 +16402,7 @@
         <v>12</v>
       </c>
       <c r="I173" s="7" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="J173" s="7" t="s">
         <v>161</v>
@@ -16389,7 +16434,7 @@
         <v>146</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="G174" s="7" t="s">
         <v>0</v>
@@ -16399,7 +16444,7 @@
         <v>11</v>
       </c>
       <c r="I174" s="7" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="J174" s="7" t="s">
         <v>161</v>
@@ -16431,7 +16476,7 @@
         <v>146</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="G175" s="7" t="s">
         <v>0</v>
@@ -16441,7 +16486,7 @@
         <v>12</v>
       </c>
       <c r="I175" s="7" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="J175" s="7" t="s">
         <v>187</v>
@@ -16473,7 +16518,7 @@
         <v>146</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="G176" s="7" t="s">
         <v>0</v>
@@ -16483,7 +16528,7 @@
         <v>12</v>
       </c>
       <c r="I176" s="7" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="J176" s="7" t="s">
         <v>187</v>
@@ -16515,7 +16560,7 @@
         <v>146</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="G177" s="7" t="s">
         <v>0</v>
@@ -16525,7 +16570,7 @@
         <v>12</v>
       </c>
       <c r="I177" s="7" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="J177" s="7" t="s">
         <v>155</v>
@@ -16557,7 +16602,7 @@
         <v>146</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="G178" s="7" t="s">
         <v>0</v>
@@ -16567,7 +16612,7 @@
         <v>11</v>
       </c>
       <c r="I178" s="7" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="J178" s="7" t="s">
         <v>215</v>
@@ -16599,7 +16644,7 @@
         <v>146</v>
       </c>
       <c r="F179" s="7" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="G179" s="7" t="s">
         <v>0</v>
@@ -16609,7 +16654,7 @@
         <v>12</v>
       </c>
       <c r="I179" s="7" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="J179" s="7" t="s">
         <v>215</v>
@@ -16641,7 +16686,7 @@
         <v>146</v>
       </c>
       <c r="F180" s="7" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="G180" s="7" t="s">
         <v>0</v>
@@ -16651,7 +16696,7 @@
         <v>12</v>
       </c>
       <c r="I180" s="7" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="J180" s="7" t="s">
         <v>215</v>
@@ -16683,7 +16728,7 @@
         <v>146</v>
       </c>
       <c r="F181" s="7" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="G181" s="7" t="s">
         <v>0</v>
@@ -16693,7 +16738,7 @@
         <v>12</v>
       </c>
       <c r="I181" s="7" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="J181" s="7" t="s">
         <v>215</v>
@@ -16725,7 +16770,7 @@
         <v>146</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="G182" s="7" t="s">
         <v>0</v>
@@ -16735,7 +16780,7 @@
         <v>12</v>
       </c>
       <c r="I182" s="7" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="J182" s="7" t="s">
         <v>215</v>
@@ -16767,7 +16812,7 @@
         <v>146</v>
       </c>
       <c r="F183" s="7" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="G183" s="7" t="s">
         <v>0</v>
@@ -16777,7 +16822,7 @@
         <v>12</v>
       </c>
       <c r="I183" s="7" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="J183" s="7" t="s">
         <v>210</v>
@@ -16809,7 +16854,7 @@
         <v>146</v>
       </c>
       <c r="F184" s="7" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="G184" s="7" t="s">
         <v>0</v>
@@ -16819,7 +16864,7 @@
         <v>11</v>
       </c>
       <c r="I184" s="7" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="J184" s="7" t="s">
         <v>210</v>
@@ -16851,7 +16896,7 @@
         <v>146</v>
       </c>
       <c r="F185" s="7" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="G185" s="7" t="s">
         <v>0</v>
@@ -16861,7 +16906,7 @@
         <v>11</v>
       </c>
       <c r="I185" s="7" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="J185" s="7" t="s">
         <v>210</v>
@@ -16893,7 +16938,7 @@
         <v>146</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="G186" s="7" t="s">
         <v>0</v>
@@ -16903,7 +16948,7 @@
         <v>12</v>
       </c>
       <c r="I186" s="7" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="J186" s="7" t="s">
         <v>161</v>
@@ -16935,7 +16980,7 @@
         <v>146</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="G187" s="7" t="s">
         <v>0</v>
@@ -16945,7 +16990,7 @@
         <v>11</v>
       </c>
       <c r="I187" s="7" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="J187" s="7" t="s">
         <v>161</v>
@@ -16977,7 +17022,7 @@
         <v>146</v>
       </c>
       <c r="F188" s="7" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="G188" s="7" t="s">
         <v>0</v>
@@ -16987,7 +17032,7 @@
         <v>11</v>
       </c>
       <c r="I188" s="7" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="J188" s="7" t="s">
         <v>161</v>
@@ -17019,7 +17064,7 @@
         <v>146</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="G189" s="7" t="s">
         <v>0</v>
@@ -17029,7 +17074,7 @@
         <v>11</v>
       </c>
       <c r="I189" s="7" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="J189" s="7" t="s">
         <v>161</v>
@@ -17061,7 +17106,7 @@
         <v>146</v>
       </c>
       <c r="F190" s="7" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="G190" s="7" t="s">
         <v>0</v>
@@ -17071,7 +17116,7 @@
         <v>12</v>
       </c>
       <c r="I190" s="7" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="J190" s="7" t="s">
         <v>161</v>
@@ -17103,7 +17148,7 @@
         <v>146</v>
       </c>
       <c r="F191" s="7" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="G191" s="7" t="s">
         <v>0</v>
@@ -17113,7 +17158,7 @@
         <v>12</v>
       </c>
       <c r="I191" s="7" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="J191" s="7" t="s">
         <v>161</v>
@@ -17145,7 +17190,7 @@
         <v>146</v>
       </c>
       <c r="F192" s="7" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="G192" s="7" t="s">
         <v>0</v>
@@ -17155,7 +17200,7 @@
         <v>12</v>
       </c>
       <c r="I192" s="7" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="J192" s="7" t="s">
         <v>161</v>
@@ -17187,7 +17232,7 @@
         <v>146</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="G193" s="7" t="s">
         <v>0</v>
@@ -17197,7 +17242,7 @@
         <v>12</v>
       </c>
       <c r="I193" s="7" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="J193" s="7" t="s">
         <v>161</v>
@@ -17229,7 +17274,7 @@
         <v>146</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="G194" s="7" t="s">
         <v>0</v>
@@ -17239,7 +17284,7 @@
         <v>12</v>
       </c>
       <c r="I194" s="7" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="J194" s="7" t="s">
         <v>161</v>
@@ -17271,7 +17316,7 @@
         <v>146</v>
       </c>
       <c r="F195" s="7" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="G195" s="7" t="s">
         <v>0</v>
@@ -17281,7 +17326,7 @@
         <v>12</v>
       </c>
       <c r="I195" s="7" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="J195" s="7" t="s">
         <v>187</v>
@@ -17313,7 +17358,7 @@
         <v>146</v>
       </c>
       <c r="F196" s="7" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="G196" s="7" t="s">
         <v>0</v>
@@ -17323,7 +17368,7 @@
         <v>11</v>
       </c>
       <c r="I196" s="7" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="J196" s="7" t="s">
         <v>187</v>
@@ -17355,7 +17400,7 @@
         <v>146</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="G197" s="7" t="s">
         <v>0</v>
@@ -17365,7 +17410,7 @@
         <v>12</v>
       </c>
       <c r="I197" s="7" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="J197" s="7" t="s">
         <v>187</v>
@@ -17397,7 +17442,7 @@
         <v>146</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="G198" s="7" t="s">
         <v>0</v>
@@ -17407,7 +17452,7 @@
         <v>12</v>
       </c>
       <c r="I198" s="7" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="J198" s="7" t="s">
         <v>147</v>
@@ -17422,7 +17467,7 @@
       <c r="N198" s="3"/>
       <c r="O198" s="3"/>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A199" s="7">
         <v>198</v>
       </c>
@@ -17439,20 +17484,20 @@
         <v>146</v>
       </c>
       <c r="F199" s="7" t="s">
-        <v>670</v>
+        <v>724</v>
       </c>
       <c r="G199" s="7" t="s">
-        <v>0</v>
+        <v>723</v>
       </c>
       <c r="H199" s="7">
         <f t="shared" ref="H199:H212" si="7">LEN(F199)</f>
         <v>12</v>
       </c>
       <c r="I199" s="7" t="s">
-        <v>671</v>
+        <v>725</v>
       </c>
       <c r="J199" s="7" t="s">
-        <v>155</v>
+        <v>710</v>
       </c>
       <c r="K199" s="7" t="s">
         <v>464</v>
@@ -17464,7 +17509,7 @@
       <c r="N199" s="3"/>
       <c r="O199" s="3"/>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A200" s="7">
         <v>199</v>
       </c>
@@ -17481,20 +17526,20 @@
         <v>146</v>
       </c>
       <c r="F200" s="7" t="s">
-        <v>701</v>
+        <v>727</v>
       </c>
       <c r="G200" s="7" t="s">
-        <v>700</v>
+        <v>726</v>
       </c>
       <c r="H200" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I200" s="7" t="s">
-        <v>702</v>
+        <v>728</v>
       </c>
       <c r="J200" s="7" t="s">
-        <v>155</v>
+        <v>710</v>
       </c>
       <c r="K200" s="7" t="s">
         <v>464</v>
@@ -17506,7 +17551,7 @@
       <c r="N200" s="3"/>
       <c r="O200" s="3"/>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A201" s="7">
         <v>200</v>
       </c>
@@ -17523,20 +17568,20 @@
         <v>146</v>
       </c>
       <c r="F201" s="7" t="s">
-        <v>704</v>
+        <v>730</v>
       </c>
       <c r="G201" s="7" t="s">
-        <v>703</v>
+        <v>729</v>
       </c>
       <c r="H201" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I201" s="7" t="s">
-        <v>705</v>
+        <v>731</v>
       </c>
       <c r="J201" s="7" t="s">
-        <v>155</v>
+        <v>710</v>
       </c>
       <c r="K201" s="7" t="s">
         <v>464</v>
@@ -17548,7 +17593,7 @@
       <c r="N201" s="3"/>
       <c r="O201" s="3"/>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A202" s="7">
         <v>201</v>
       </c>
@@ -17565,20 +17610,20 @@
         <v>146</v>
       </c>
       <c r="F202" s="7" t="s">
-        <v>672</v>
+        <v>733</v>
       </c>
       <c r="G202" s="7" t="s">
-        <v>0</v>
+        <v>732</v>
       </c>
       <c r="H202" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I202" s="7" t="s">
-        <v>673</v>
+        <v>734</v>
       </c>
       <c r="J202" s="7" t="s">
-        <v>155</v>
+        <v>710</v>
       </c>
       <c r="K202" s="7" t="s">
         <v>464</v>
@@ -17607,7 +17652,7 @@
         <v>146</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="G203" s="7" t="s">
         <v>0</v>
@@ -17617,7 +17662,7 @@
         <v>12</v>
       </c>
       <c r="I203" s="7" t="s">
-        <v>675</v>
+        <v>663</v>
       </c>
       <c r="J203" s="7" t="s">
         <v>161</v>
@@ -17649,7 +17694,7 @@
         <v>146</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>676</v>
+        <v>664</v>
       </c>
       <c r="G204" s="7" t="s">
         <v>0</v>
@@ -17659,7 +17704,7 @@
         <v>12</v>
       </c>
       <c r="I204" s="7" t="s">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="J204" s="7" t="s">
         <v>161</v>
@@ -17691,7 +17736,7 @@
         <v>146</v>
       </c>
       <c r="F205" s="7" t="s">
-        <v>678</v>
+        <v>666</v>
       </c>
       <c r="G205" s="7" t="s">
         <v>0</v>
@@ -17701,7 +17746,7 @@
         <v>12</v>
       </c>
       <c r="I205" s="7" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="J205" s="7" t="s">
         <v>161</v>
@@ -17733,7 +17778,7 @@
         <v>146</v>
       </c>
       <c r="F206" s="7" t="s">
-        <v>680</v>
+        <v>668</v>
       </c>
       <c r="G206" s="7" t="s">
         <v>0</v>
@@ -17743,7 +17788,7 @@
         <v>12</v>
       </c>
       <c r="I206" s="7" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
       <c r="J206" s="7" t="s">
         <v>210</v>
@@ -17775,17 +17820,17 @@
         <v>146</v>
       </c>
       <c r="F207" s="7" t="s">
-        <v>717</v>
+        <v>690</v>
       </c>
       <c r="G207" s="7" t="s">
-        <v>716</v>
+        <v>689</v>
       </c>
       <c r="H207" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I207" s="7" t="s">
-        <v>718</v>
+        <v>691</v>
       </c>
       <c r="J207" s="7" t="s">
         <v>210</v>
@@ -17817,17 +17862,17 @@
         <v>146</v>
       </c>
       <c r="F208" s="7" t="s">
-        <v>720</v>
+        <v>693</v>
       </c>
       <c r="G208" s="7" t="s">
-        <v>719</v>
+        <v>692</v>
       </c>
       <c r="H208" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I208" s="7" t="s">
-        <v>721</v>
+        <v>694</v>
       </c>
       <c r="J208" s="7" t="s">
         <v>210</v>
@@ -17859,7 +17904,7 @@
         <v>146</v>
       </c>
       <c r="F209" s="7" t="s">
-        <v>682</v>
+        <v>670</v>
       </c>
       <c r="G209" s="7" t="s">
         <v>0</v>
@@ -17869,7 +17914,7 @@
         <v>11</v>
       </c>
       <c r="I209" s="7" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="J209" s="7" t="s">
         <v>215</v>
@@ -17901,17 +17946,17 @@
         <v>146</v>
       </c>
       <c r="F210" s="7" t="s">
-        <v>723</v>
+        <v>696</v>
       </c>
       <c r="G210" s="7" t="s">
-        <v>722</v>
+        <v>695</v>
       </c>
       <c r="H210" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I210" s="7" t="s">
-        <v>724</v>
+        <v>697</v>
       </c>
       <c r="J210" s="7" t="s">
         <v>215</v>
@@ -17943,7 +17988,7 @@
         <v>146</v>
       </c>
       <c r="F211" s="7" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="G211" s="7" t="s">
         <v>0</v>
@@ -17985,7 +18030,7 @@
         <v>146</v>
       </c>
       <c r="F212" s="7" t="s">
-        <v>684</v>
+        <v>672</v>
       </c>
       <c r="G212" s="7" t="s">
         <v>0</v>
@@ -17995,7 +18040,7 @@
         <v>12</v>
       </c>
       <c r="I212" s="7" t="s">
-        <v>685</v>
+        <v>673</v>
       </c>
       <c r="J212" s="7" t="s">
         <v>187</v>
@@ -18010,7 +18055,7 @@
       <c r="N212" s="3"/>
       <c r="O212" s="3"/>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A213" s="7">
         <v>212</v>
       </c>
@@ -18027,20 +18072,20 @@
         <v>146</v>
       </c>
       <c r="F213" s="7" t="s">
-        <v>707</v>
+        <v>736</v>
       </c>
       <c r="G213" s="7" t="s">
-        <v>706</v>
+        <v>735</v>
       </c>
       <c r="H213" s="7">
         <f t="shared" ref="H213:H220" si="8">LEN(F213)</f>
         <v>12</v>
       </c>
       <c r="I213" s="7" t="s">
-        <v>708</v>
+        <v>737</v>
       </c>
       <c r="J213" s="7" t="s">
-        <v>155</v>
+        <v>710</v>
       </c>
       <c r="K213" s="7" t="s">
         <v>464</v>
@@ -18052,7 +18097,7 @@
       <c r="N213" s="3"/>
       <c r="O213" s="3"/>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A214" s="7">
         <v>213</v>
       </c>
@@ -18069,20 +18114,20 @@
         <v>146</v>
       </c>
       <c r="F214" s="7" t="s">
-        <v>687</v>
+        <v>739</v>
       </c>
       <c r="G214" s="7" t="s">
-        <v>0</v>
+        <v>738</v>
       </c>
       <c r="H214" s="7">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="I214" s="7" t="s">
-        <v>688</v>
+        <v>740</v>
       </c>
       <c r="J214" s="7" t="s">
-        <v>155</v>
+        <v>710</v>
       </c>
       <c r="K214" s="7" t="s">
         <v>464</v>
@@ -18111,7 +18156,7 @@
         <v>146</v>
       </c>
       <c r="F215" s="7" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="G215" s="7" t="s">
         <v>0</v>
@@ -18121,7 +18166,7 @@
         <v>12</v>
       </c>
       <c r="I215" s="7" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="J215" s="7" t="s">
         <v>161</v>
@@ -18153,7 +18198,7 @@
         <v>146</v>
       </c>
       <c r="F216" s="7" t="s">
-        <v>691</v>
+        <v>677</v>
       </c>
       <c r="G216" s="7" t="s">
         <v>0</v>
@@ -18163,7 +18208,7 @@
         <v>12</v>
       </c>
       <c r="I216" s="7" t="s">
-        <v>692</v>
+        <v>678</v>
       </c>
       <c r="J216" s="7" t="s">
         <v>161</v>
@@ -18195,7 +18240,7 @@
         <v>146</v>
       </c>
       <c r="F217" s="7" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="G217" s="7" t="s">
         <v>0</v>
@@ -18205,7 +18250,7 @@
         <v>12</v>
       </c>
       <c r="I217" s="7" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="J217" s="7" t="s">
         <v>161</v>
@@ -18237,17 +18282,17 @@
         <v>146</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>726</v>
+        <v>699</v>
       </c>
       <c r="G218" s="7" t="s">
-        <v>725</v>
+        <v>698</v>
       </c>
       <c r="H218" s="7">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="I218" s="7" t="s">
-        <v>727</v>
+        <v>700</v>
       </c>
       <c r="J218" s="7" t="s">
         <v>210</v>
@@ -18279,17 +18324,17 @@
         <v>146</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>729</v>
+        <v>702</v>
       </c>
       <c r="G219" s="7" t="s">
-        <v>728</v>
+        <v>701</v>
       </c>
       <c r="H219" s="7">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="I219" s="7" t="s">
-        <v>730</v>
+        <v>703</v>
       </c>
       <c r="J219" s="7" t="s">
         <v>210</v>
@@ -18321,17 +18366,17 @@
         <v>146</v>
       </c>
       <c r="F220" s="7" t="s">
-        <v>710</v>
+        <v>683</v>
       </c>
       <c r="G220" s="7" t="s">
-        <v>709</v>
+        <v>682</v>
       </c>
       <c r="H220" s="7">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="I220" s="7" t="s">
-        <v>711</v>
+        <v>684</v>
       </c>
       <c r="J220" s="7" t="s">
         <v>210</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E55493-6D33-45BE-A017-0AA308FC1CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB98C386-234F-424B-B9B1-8900907D5F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="기존 문구 수정" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'추가 문구'!$A$1:$O$220</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'추가 문구'!$A$1:$O$228</definedName>
   </definedNames>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2264" uniqueCount="742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2345" uniqueCount="763">
   <si>
     <t>—</t>
   </si>
@@ -7863,9 +7863,6 @@
     <t>나물이나 쌈으로 채소를 넉넉히 먹어요.</t>
   </si>
   <si>
-    <t>데친 채소 한 가지로 아침 채소를 더해요.</t>
-  </si>
-  <si>
     <t>달걀로 간단히 아침 단백질을 챙겨요.</t>
   </si>
   <si>
@@ -8149,362 +8146,436 @@
     <t>구운 가지나 호박으로 채소를 더해요.</t>
   </si>
   <si>
+    <t>저녁추천: 청경채/버섯</t>
+  </si>
+  <si>
+    <t>데친 채소 한 가지로 저녁 채소를 더해요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 브로콜리/쌈</t>
+  </si>
+  <si>
+    <t>데친 브로콜리나 쌈으로 채소를 챙겨요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 양배추/나물</t>
+  </si>
+  <si>
+    <t>양배추쌈이나 나물로 채소를 더해요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 미나리/숙주</t>
+  </si>
+  <si>
+    <t>향긋한 나물로 저녁 채소를 챙겨요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 상추쌈/나물</t>
+  </si>
+  <si>
+    <t>쌈 한 접시로 채소를 듬뿍 먹어요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 지리/생선찜</t>
+  </si>
+  <si>
+    <t>맑은 지리와 찜은 빨간 탕보다 덜 짜요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 백김치/쌈</t>
+  </si>
+  <si>
+    <t>백김치와 쌈은 짠 반찬보다 염분이 적어요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 맑은 국/찜</t>
+  </si>
+  <si>
+    <t>저녁추천: 보리밥/쌈밥</t>
+  </si>
+  <si>
+    <t>든든한 밥 한 그릇으로 저녁을 챙겨요.</t>
+  </si>
+  <si>
+    <t>10-12 저녁추천 확대: 모두 . 합계 197개</t>
+  </si>
+  <si>
+    <t>아침추천: 시금치국/쌈</t>
+  </si>
+  <si>
+    <t>채소국이나 쌈으로 아침 채소를 챙겨요.</t>
+  </si>
+  <si>
+    <t>아침추천: 비빔밥/나물</t>
+  </si>
+  <si>
+    <t>나물을 곁들이면 아침 채소가 넉넉해요.</t>
+  </si>
+  <si>
+    <t>아침추천: 요거트/두유</t>
+  </si>
+  <si>
+    <t>달지 않은 요거트나 두유로 단백질을 더해요.</t>
+  </si>
+  <si>
+    <t>아침추천: 생선/두부</t>
+  </si>
+  <si>
+    <t>아침추천: 미역국/쑥국</t>
+  </si>
+  <si>
+    <t>아침추천: 백김치/나물</t>
+  </si>
+  <si>
+    <t>백김치와 나물은 짠 반찬보다 염분이 적어요.</t>
+  </si>
+  <si>
+    <t>10-12 아침추천 확대: 모두 . 합계 211개</t>
+  </si>
+  <si>
+    <t>아침추천: 콩나물국/쌈</t>
+  </si>
+  <si>
+    <t>맑은 국이나 쌈으로 아침에도 채소를 먹어요.</t>
+  </si>
+  <si>
+    <t>아침추천: 호박국/나물</t>
+  </si>
+  <si>
+    <t>부드러운 채소 반찬으로 아침을 채워요.</t>
+  </si>
+  <si>
+    <t>아침추천: 양배추/오이</t>
+  </si>
+  <si>
+    <t>아삭한 채소 한 가지로 아침 채소를 더해요.</t>
+  </si>
+  <si>
+    <t>10-12 아침추천 확대: 모두 . 합계 219개</t>
+  </si>
+  <si>
+    <t>아침추천: 달걀말이/죽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 닭안심/두부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>담백한 단백질로 아침을 든든하게 해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 연두부/두유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부드러운 두부나 두유로 단백질을 더해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 생선/나물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생선구이와 나물은 기름을 덜 쓰는 반찬이에요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 우유/달걀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 우유/요거트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한 잔이나 한 컵으로 아침 단백질을 챙겨요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 북엇국/달걀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 북엇국/두유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가벼운 국이나 두유로 아침 단백질을 더해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 달걀찜/생선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 생선찜/두부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>찜과 두부는 기름을 덜 쓰는 반찬이에요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 달걀/요거트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 요거트/두부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달지 않은 요거트나 두부로 단백질을 더해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 두부/달걀찜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 순두부/우유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부드러운 순두부나 우유로 단백질을 챙겨요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10-12 끼니 추천에서 죽·달걀이 몰린 짝  다른 메뉴로 바꿈(죽  · 달걀  남김)</t>
+  </si>
+  <si>
+    <t>아침추천: 백김치/생채</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백김치와 생채는 짠 반찬보다 염분이 적어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 죽/누룽지 (탄수화물만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 현미밥+나물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현미밥에 나물을 곁들이면 혈당이 천천히 올라요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>식생활지침 「골고루 먹기」 · 당뇨병 식사요법(대한당뇨병학회)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 흑미밥/감자 (탄수화물만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 잡곡밥+두부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>잡곡밥에 두부를 곁들이면 오래 든든해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 오트밀/감자 (탄수화물만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 오트밀+우유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오트밀에 우유를 더하면 단백질도 함께 챙겨요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 고구마/밤 (탄수화물만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 고구마+두유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고구마에 두유를 곁들이면 단백질이 더해져요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 전복죽/쌀죽 (탄수화물만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 현미밥+생선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현미밥과 생선구이로 균형 잡힌 아침을 먹어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 감자/옥수수 (탄수화물만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 감자+요거트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>찐 감자에 요거트를 곁들이면 단백질이 더해져요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 김밥/주먹밥 (탄수화물만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 통밀빵+채소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통밀빵에 채소를 곁들이면 든든하고 가벼워요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 단호박/우유 (탄수화물만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 단호박+우유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>찐 단호박에 우유를 곁들여 든든하게 먹어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 통밀빵/감자 (탄수화물만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 흑미밥+나물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흑미밥에 나물을 곁들이면 아침 채소도 챙겨요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 옥수수/두유 (탄수화물만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 옥수수+두유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>찐 옥수수에 두유를 곁들이면 단백질이 더해져요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 현미밥/감자 (탄수화물만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 보리밥+나물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보리밥에 나물을 곁들이면 오래 든든해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10-12 끼니 추천 원칙 추가: 탄수화물만 있는 짝(죽·누룽지·김밥·주먹밥·감자/옥수수 등)  빼고, 밥·빵·고구마에 단백질이나 채소를 붙임. 「A+B」는 함께 먹기, 「A/B」는 둘 중 하나</t>
+  </si>
+  <si>
+    <t>아침추천: 두부샐러드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>두부를 올린 샐러드로 채소와 단백질을 함께 챙겨요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>저녁추천: 샐러드/쌈</t>
-  </si>
-  <si>
-    <t>생채소로 저녁 채소를 넉넉히 먹어요.</t>
-  </si>
-  <si>
-    <t>저녁추천: 청경채/버섯</t>
-  </si>
-  <si>
-    <t>데친 채소 한 가지로 저녁 채소를 더해요.</t>
-  </si>
-  <si>
-    <t>저녁추천: 브로콜리/쌈</t>
-  </si>
-  <si>
-    <t>데친 브로콜리나 쌈으로 채소를 챙겨요.</t>
-  </si>
-  <si>
-    <t>저녁추천: 양배추/나물</t>
-  </si>
-  <si>
-    <t>양배추쌈이나 나물로 채소를 더해요.</t>
-  </si>
-  <si>
-    <t>저녁추천: 미나리/숙주</t>
-  </si>
-  <si>
-    <t>향긋한 나물로 저녁 채소를 챙겨요.</t>
-  </si>
-  <si>
-    <t>저녁추천: 상추쌈/나물</t>
-  </si>
-  <si>
-    <t>쌈 한 접시로 채소를 듬뿍 먹어요.</t>
-  </si>
-  <si>
-    <t>저녁추천: 지리/생선찜</t>
-  </si>
-  <si>
-    <t>맑은 지리와 찜은 빨간 탕보다 덜 짜요.</t>
-  </si>
-  <si>
-    <t>저녁추천: 백김치/쌈</t>
-  </si>
-  <si>
-    <t>백김치와 쌈은 짠 반찬보다 염분이 적어요.</t>
-  </si>
-  <si>
-    <t>저녁추천: 맑은 국/찜</t>
-  </si>
-  <si>
-    <t>저녁추천: 보리밥/쌈밥</t>
-  </si>
-  <si>
-    <t>든든한 밥 한 그릇으로 저녁을 챙겨요.</t>
-  </si>
-  <si>
-    <t>10-12 저녁추천 확대: 모두 . 합계 197개</t>
-  </si>
-  <si>
-    <t>아침추천: 시금치국/쌈</t>
-  </si>
-  <si>
-    <t>채소국이나 쌈으로 아침 채소를 챙겨요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 연어샐러드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연어샐러드로 채소와 좋은 지방을 함께 먹어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>아침추천: 샐러드/나물</t>
-  </si>
-  <si>
-    <t>생채소나 나물로 아침 채소를 더해요.</t>
-  </si>
-  <si>
-    <t>아침추천: 비빔밥/나물</t>
-  </si>
-  <si>
-    <t>나물을 곁들이면 아침 채소가 넉넉해요.</t>
-  </si>
-  <si>
-    <t>아침추천: 요거트/두유</t>
-  </si>
-  <si>
-    <t>달지 않은 요거트나 두유로 단백질을 더해요.</t>
-  </si>
-  <si>
-    <t>아침추천: 생선/두부</t>
-  </si>
-  <si>
-    <t>아침추천: 미역국/쑥국</t>
-  </si>
-  <si>
-    <t>아침추천: 백김치/나물</t>
-  </si>
-  <si>
-    <t>백김치와 나물은 짠 반찬보다 염분이 적어요.</t>
-  </si>
-  <si>
-    <t>10-12 아침추천 확대: 모두 . 합계 211개</t>
-  </si>
-  <si>
-    <t>아침추천: 콩나물국/쌈</t>
-  </si>
-  <si>
-    <t>맑은 국이나 쌈으로 아침에도 채소를 먹어요.</t>
-  </si>
-  <si>
-    <t>아침추천: 호박국/나물</t>
-  </si>
-  <si>
-    <t>부드러운 채소 반찬으로 아침을 채워요.</t>
-  </si>
-  <si>
-    <t>아침추천: 양배추/오이</t>
-  </si>
-  <si>
-    <t>아삭한 채소 한 가지로 아침 채소를 더해요.</t>
-  </si>
-  <si>
-    <t>10-12 아침추천 확대: 모두 . 합계 219개</t>
-  </si>
-  <si>
-    <t>아침추천: 달걀말이/죽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 닭안심/두부</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>담백한 단백질로 아침을 든든하게 해요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 연두부/두유</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>부드러운 두부나 두유로 단백질을 더해요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 생선/나물</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>생선구이와 나물은 기름을 덜 쓰는 반찬이에요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 우유/달걀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 우유/요거트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>한 잔이나 한 컵으로 아침 단백질을 챙겨요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 북엇국/달걀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 북엇국/두유</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>가벼운 국이나 두유로 아침 단백질을 더해요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 달걀찜/생선</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 생선찜/두부</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>찜과 두부는 기름을 덜 쓰는 반찬이에요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 달걀/요거트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 요거트/두부</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>달지 않은 요거트나 두부로 단백질을 더해요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 두부/달걀찜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 순두부/우유</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>부드러운 순두부나 우유로 단백질을 챙겨요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10-12 끼니 추천에서 죽·달걀이 몰린 짝  다른 메뉴로 바꿈(죽  · 달걀  남김)</t>
-  </si>
-  <si>
-    <t>아침추천: 백김치/생채</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>백김치와 생채는 짠 반찬보다 염분이 적어요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 죽/누룽지 (탄수화물만)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 현미밥+나물</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>현미밥에 나물을 곁들이면 혈당이 천천히 올라요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>식생활지침 「골고루 먹기」 · 당뇨병 식사요법(대한당뇨병학회)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 흑미밥/감자 (탄수화물만)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 잡곡밥+두부</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>잡곡밥에 두부를 곁들이면 오래 든든해요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 오트밀/감자 (탄수화물만)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 오트밀+우유</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오트밀에 우유를 더하면 단백질도 함께 챙겨요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 고구마/밤 (탄수화물만)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 고구마+두유</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고구마에 두유를 곁들이면 단백질이 더해져요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 전복죽/쌀죽 (탄수화물만)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 현미밥+생선</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>현미밥과 생선구이로 균형 잡힌 아침을 먹어요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 감자/옥수수 (탄수화물만)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 감자+요거트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>찐 감자에 요거트를 곁들이면 단백질이 더해져요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 김밥/주먹밥 (탄수화물만)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 통밀빵+채소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>통밀빵에 채소를 곁들이면 든든하고 가벼워요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 단호박/우유 (탄수화물만)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 단호박+우유</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>찐 단호박에 우유를 곁들여 든든하게 먹어요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 통밀빵/감자 (탄수화물만)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 흑미밥+나물</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>흑미밥에 나물을 곁들이면 아침 채소도 챙겨요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 옥수수/두유 (탄수화물만)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 옥수수+두유</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>찐 옥수수에 두유를 곁들이면 단백질이 더해져요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 현미밥/감자 (탄수화물만)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 보리밥+나물</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>보리밥에 나물을 곁들이면 오래 든든해요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10-12 끼니 추천 원칙 추가: 탄수화물만 있는 짝(죽·누룽지·김밥·주먹밥·감자/옥수수 등)  빼고, 밥·빵·고구마에 단백질이나 채소를 붙임. 「A+B」는 함께 먹기, 「A/B」는 둘 중 하나</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 양배추샐러드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아삭한 양배추샐러드로 아침 채소를 더해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 오이샐러드</t>
+  </si>
+  <si>
+    <t>상큼한 오이샐러드로 아침 채소를 챙겨요.</t>
+  </si>
+  <si>
+    <t>식생활지침 「채소 충분히」 · WHO 채소 섭취 권고</t>
+  </si>
+  <si>
+    <t>아침추천: 연두부샐러드</t>
+  </si>
+  <si>
+    <t>연두부를 올리면 샐러드가 든든해져요.</t>
+  </si>
+  <si>
+    <t>아침추천: 버섯샐러드</t>
+  </si>
+  <si>
+    <t>구운 버섯을 올린 샐러드로 채소를 더해요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 버섯샐러드</t>
+  </si>
+  <si>
+    <t>구운 버섯샐러드는 기름 없이 즐기는 채소 요리예요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 닭샐러드</t>
+  </si>
+  <si>
+    <t>닭가슴살을 올린 샐러드로 채소와 단백질을 챙겨요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 새우샐러드</t>
+  </si>
+  <si>
+    <t>데친 새우를 올린 샐러드로 담백하게 먹어요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 리코타샐러드</t>
+  </si>
+  <si>
+    <t>리코타 치즈를 곁들이면 채소를 맛있게 먹을 수 있어요.</t>
+  </si>
+  <si>
+    <t>저녁추천: 두부샐러드</t>
+  </si>
+  <si>
+    <t>두부샐러드로 채소와 단백질을 함께 먹어요.</t>
+  </si>
+  <si>
+    <t>10-12 「샐러드」를 구체적인 샐러드 이름으로 바꿈() · 샐러드 추천  추가. 합계 227개</t>
   </si>
 </sst>
 </file>
@@ -8991,7 +9062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F51797-492B-40AC-833D-E19CEF6E9FA5}">
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="120.58203125" style="1" customWidth="1"/>
@@ -9080,42 +9151,47 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>741</v>
+        <v>736</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A26" s="1" t="s">
+        <v>762</v>
       </c>
     </row>
   </sheetData>
@@ -9126,7 +9202,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{243C8A1C-2FBA-4873-BD31-7545635970F1}">
-  <dimension ref="A1:O220"/>
+  <dimension ref="A1:O228"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6.58203125" style="1" customWidth="1"/>
@@ -10722,7 +10798,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>270</v>
@@ -15006,20 +15082,20 @@
         <v>146</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="G140" s="7" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="H140" s="7">
         <f t="shared" ref="H140:H177" si="5">LEN(F140)</f>
         <v>12</v>
       </c>
       <c r="I140" s="7" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="J140" s="7" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="K140" s="7" t="s">
         <v>464</v>
@@ -15048,20 +15124,20 @@
         <v>146</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="G141" s="7" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="H141" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I141" s="7" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="J141" s="7" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="K141" s="7" t="s">
         <v>464</v>
@@ -15090,20 +15166,20 @@
         <v>146</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="G142" s="7" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="H142" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I142" s="7" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="J142" s="7" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="K142" s="7" t="s">
         <v>464</v>
@@ -15132,20 +15208,20 @@
         <v>146</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="G143" s="7" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="H143" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I143" s="7" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="J143" s="7" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="K143" s="7" t="s">
         <v>464</v>
@@ -15174,20 +15250,20 @@
         <v>146</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="G144" s="7" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="H144" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I144" s="7" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="J144" s="7" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="K144" s="7" t="s">
         <v>464</v>
@@ -15216,7 +15292,7 @@
         <v>146</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G145" s="7" t="s">
         <v>0</v>
@@ -15258,7 +15334,7 @@
         <v>146</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="G146" s="7" t="s">
         <v>0</v>
@@ -15300,7 +15376,7 @@
         <v>146</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G147" s="7" t="s">
         <v>0</v>
@@ -15342,7 +15418,7 @@
         <v>146</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G148" s="7" t="s">
         <v>0</v>
@@ -15384,17 +15460,17 @@
         <v>146</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>590</v>
+        <v>737</v>
       </c>
       <c r="G149" s="7" t="s">
-        <v>0</v>
+        <v>589</v>
       </c>
       <c r="H149" s="7">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>558</v>
+        <v>738</v>
       </c>
       <c r="J149" s="7" t="s">
         <v>161</v>
@@ -15426,7 +15502,7 @@
         <v>146</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G150" s="7" t="s">
         <v>0</v>
@@ -15436,7 +15512,7 @@
         <v>12</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="J150" s="7" t="s">
         <v>210</v>
@@ -15468,7 +15544,7 @@
         <v>146</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G151" s="7" t="s">
         <v>0</v>
@@ -15478,7 +15554,7 @@
         <v>12</v>
       </c>
       <c r="I151" s="7" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="J151" s="7" t="s">
         <v>210</v>
@@ -15510,7 +15586,7 @@
         <v>146</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G152" s="7" t="s">
         <v>0</v>
@@ -15520,7 +15596,7 @@
         <v>11</v>
       </c>
       <c r="I152" s="7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="J152" s="7" t="s">
         <v>210</v>
@@ -15552,7 +15628,7 @@
         <v>146</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G153" s="7" t="s">
         <v>0</v>
@@ -15562,7 +15638,7 @@
         <v>11</v>
       </c>
       <c r="I153" s="7" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="J153" s="7" t="s">
         <v>210</v>
@@ -15594,17 +15670,17 @@
         <v>146</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="G154" s="7" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H154" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I154" s="7" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="J154" s="7" t="s">
         <v>210</v>
@@ -15636,7 +15712,7 @@
         <v>146</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G155" s="7" t="s">
         <v>0</v>
@@ -15646,7 +15722,7 @@
         <v>12</v>
       </c>
       <c r="I155" s="7" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="J155" s="7" t="s">
         <v>210</v>
@@ -15678,17 +15754,17 @@
         <v>146</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="G156" s="7" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H156" s="7">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="I156" s="7" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="J156" s="7" t="s">
         <v>215</v>
@@ -15720,17 +15796,17 @@
         <v>146</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="G157" s="7" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H157" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I157" s="7" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="J157" s="7" t="s">
         <v>187</v>
@@ -15762,7 +15838,7 @@
         <v>146</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G158" s="7" t="s">
         <v>0</v>
@@ -15772,7 +15848,7 @@
         <v>11</v>
       </c>
       <c r="I158" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="J158" s="7" t="s">
         <v>215</v>
@@ -15804,7 +15880,7 @@
         <v>146</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G159" s="7" t="s">
         <v>0</v>
@@ -15814,7 +15890,7 @@
         <v>11</v>
       </c>
       <c r="I159" s="7" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="J159" s="7" t="s">
         <v>215</v>
@@ -15846,7 +15922,7 @@
         <v>146</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G160" s="7" t="s">
         <v>0</v>
@@ -15888,7 +15964,7 @@
         <v>146</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G161" s="7" t="s">
         <v>0</v>
@@ -15898,7 +15974,7 @@
         <v>11</v>
       </c>
       <c r="I161" s="7" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="J161" s="7" t="s">
         <v>215</v>
@@ -15930,7 +16006,7 @@
         <v>146</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G162" s="7" t="s">
         <v>0</v>
@@ -15940,7 +16016,7 @@
         <v>12</v>
       </c>
       <c r="I162" s="7" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="J162" s="7" t="s">
         <v>215</v>
@@ -15972,7 +16048,7 @@
         <v>146</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G163" s="7" t="s">
         <v>0</v>
@@ -15982,7 +16058,7 @@
         <v>11</v>
       </c>
       <c r="I163" s="7" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="J163" s="7" t="s">
         <v>215</v>
@@ -16014,7 +16090,7 @@
         <v>146</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G164" s="7" t="s">
         <v>0</v>
@@ -16024,7 +16100,7 @@
         <v>12</v>
       </c>
       <c r="I164" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="J164" s="7" t="s">
         <v>210</v>
@@ -16056,7 +16132,7 @@
         <v>146</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G165" s="7" t="s">
         <v>0</v>
@@ -16066,7 +16142,7 @@
         <v>12</v>
       </c>
       <c r="I165" s="7" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="J165" s="7" t="s">
         <v>210</v>
@@ -16098,7 +16174,7 @@
         <v>146</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="G166" s="7" t="s">
         <v>0</v>
@@ -16108,7 +16184,7 @@
         <v>12</v>
       </c>
       <c r="I166" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="J166" s="7" t="s">
         <v>210</v>
@@ -16140,7 +16216,7 @@
         <v>146</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G167" s="7" t="s">
         <v>0</v>
@@ -16150,7 +16226,7 @@
         <v>12</v>
       </c>
       <c r="I167" s="7" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="J167" s="7" t="s">
         <v>210</v>
@@ -16182,7 +16258,7 @@
         <v>146</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G168" s="7" t="s">
         <v>0</v>
@@ -16192,7 +16268,7 @@
         <v>12</v>
       </c>
       <c r="I168" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="J168" s="7" t="s">
         <v>210</v>
@@ -16224,7 +16300,7 @@
         <v>146</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="G169" s="7" t="s">
         <v>0</v>
@@ -16234,7 +16310,7 @@
         <v>12</v>
       </c>
       <c r="I169" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="J169" s="7" t="s">
         <v>161</v>
@@ -16266,7 +16342,7 @@
         <v>146</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G170" s="7" t="s">
         <v>0</v>
@@ -16276,7 +16352,7 @@
         <v>12</v>
       </c>
       <c r="I170" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="J170" s="7" t="s">
         <v>161</v>
@@ -16308,7 +16384,7 @@
         <v>146</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G171" s="7" t="s">
         <v>0</v>
@@ -16318,7 +16394,7 @@
         <v>11</v>
       </c>
       <c r="I171" s="7" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="J171" s="7" t="s">
         <v>161</v>
@@ -16350,7 +16426,7 @@
         <v>146</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G172" s="7" t="s">
         <v>0</v>
@@ -16360,7 +16436,7 @@
         <v>11</v>
       </c>
       <c r="I172" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J172" s="7" t="s">
         <v>161</v>
@@ -16392,7 +16468,7 @@
         <v>146</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G173" s="7" t="s">
         <v>0</v>
@@ -16402,7 +16478,7 @@
         <v>12</v>
       </c>
       <c r="I173" s="7" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="J173" s="7" t="s">
         <v>161</v>
@@ -16434,7 +16510,7 @@
         <v>146</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="G174" s="7" t="s">
         <v>0</v>
@@ -16444,7 +16520,7 @@
         <v>11</v>
       </c>
       <c r="I174" s="7" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="J174" s="7" t="s">
         <v>161</v>
@@ -16476,7 +16552,7 @@
         <v>146</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G175" s="7" t="s">
         <v>0</v>
@@ -16486,7 +16562,7 @@
         <v>12</v>
       </c>
       <c r="I175" s="7" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="J175" s="7" t="s">
         <v>187</v>
@@ -16518,7 +16594,7 @@
         <v>146</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G176" s="7" t="s">
         <v>0</v>
@@ -16528,7 +16604,7 @@
         <v>12</v>
       </c>
       <c r="I176" s="7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="J176" s="7" t="s">
         <v>187</v>
@@ -16560,7 +16636,7 @@
         <v>146</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G177" s="7" t="s">
         <v>0</v>
@@ -16570,7 +16646,7 @@
         <v>12</v>
       </c>
       <c r="I177" s="7" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="J177" s="7" t="s">
         <v>155</v>
@@ -16602,7 +16678,7 @@
         <v>146</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G178" s="7" t="s">
         <v>0</v>
@@ -16612,7 +16688,7 @@
         <v>11</v>
       </c>
       <c r="I178" s="7" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="J178" s="7" t="s">
         <v>215</v>
@@ -16644,7 +16720,7 @@
         <v>146</v>
       </c>
       <c r="F179" s="7" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="G179" s="7" t="s">
         <v>0</v>
@@ -16654,7 +16730,7 @@
         <v>12</v>
       </c>
       <c r="I179" s="7" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J179" s="7" t="s">
         <v>215</v>
@@ -16686,7 +16762,7 @@
         <v>146</v>
       </c>
       <c r="F180" s="7" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G180" s="7" t="s">
         <v>0</v>
@@ -16696,7 +16772,7 @@
         <v>12</v>
       </c>
       <c r="I180" s="7" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="J180" s="7" t="s">
         <v>215</v>
@@ -16728,7 +16804,7 @@
         <v>146</v>
       </c>
       <c r="F181" s="7" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G181" s="7" t="s">
         <v>0</v>
@@ -16738,7 +16814,7 @@
         <v>12</v>
       </c>
       <c r="I181" s="7" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J181" s="7" t="s">
         <v>215</v>
@@ -16770,7 +16846,7 @@
         <v>146</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G182" s="7" t="s">
         <v>0</v>
@@ -16780,7 +16856,7 @@
         <v>12</v>
       </c>
       <c r="I182" s="7" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J182" s="7" t="s">
         <v>215</v>
@@ -16812,7 +16888,7 @@
         <v>146</v>
       </c>
       <c r="F183" s="7" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="G183" s="7" t="s">
         <v>0</v>
@@ -16822,7 +16898,7 @@
         <v>12</v>
       </c>
       <c r="I183" s="7" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="J183" s="7" t="s">
         <v>210</v>
@@ -16854,7 +16930,7 @@
         <v>146</v>
       </c>
       <c r="F184" s="7" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="G184" s="7" t="s">
         <v>0</v>
@@ -16864,7 +16940,7 @@
         <v>11</v>
       </c>
       <c r="I184" s="7" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="J184" s="7" t="s">
         <v>210</v>
@@ -16896,7 +16972,7 @@
         <v>146</v>
       </c>
       <c r="F185" s="7" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G185" s="7" t="s">
         <v>0</v>
@@ -16906,7 +16982,7 @@
         <v>11</v>
       </c>
       <c r="I185" s="7" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="J185" s="7" t="s">
         <v>210</v>
@@ -16938,7 +17014,7 @@
         <v>146</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G186" s="7" t="s">
         <v>0</v>
@@ -16948,7 +17024,7 @@
         <v>12</v>
       </c>
       <c r="I186" s="7" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="J186" s="7" t="s">
         <v>161</v>
@@ -16980,7 +17056,7 @@
         <v>146</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="G187" s="7" t="s">
         <v>0</v>
@@ -16990,7 +17066,7 @@
         <v>11</v>
       </c>
       <c r="I187" s="7" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="J187" s="7" t="s">
         <v>161</v>
@@ -17022,7 +17098,7 @@
         <v>146</v>
       </c>
       <c r="F188" s="7" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="G188" s="7" t="s">
         <v>0</v>
@@ -17032,7 +17108,7 @@
         <v>11</v>
       </c>
       <c r="I188" s="7" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="J188" s="7" t="s">
         <v>161</v>
@@ -17064,17 +17140,17 @@
         <v>146</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>642</v>
+        <v>740</v>
       </c>
       <c r="G189" s="7" t="s">
-        <v>0</v>
+        <v>739</v>
       </c>
       <c r="H189" s="7">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="I189" s="7" t="s">
-        <v>643</v>
+        <v>741</v>
       </c>
       <c r="J189" s="7" t="s">
         <v>161</v>
@@ -17106,7 +17182,7 @@
         <v>146</v>
       </c>
       <c r="F190" s="7" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="G190" s="7" t="s">
         <v>0</v>
@@ -17116,7 +17192,7 @@
         <v>12</v>
       </c>
       <c r="I190" s="7" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="J190" s="7" t="s">
         <v>161</v>
@@ -17148,7 +17224,7 @@
         <v>146</v>
       </c>
       <c r="F191" s="7" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="G191" s="7" t="s">
         <v>0</v>
@@ -17158,7 +17234,7 @@
         <v>12</v>
       </c>
       <c r="I191" s="7" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="J191" s="7" t="s">
         <v>161</v>
@@ -17190,7 +17266,7 @@
         <v>146</v>
       </c>
       <c r="F192" s="7" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="G192" s="7" t="s">
         <v>0</v>
@@ -17200,7 +17276,7 @@
         <v>12</v>
       </c>
       <c r="I192" s="7" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="J192" s="7" t="s">
         <v>161</v>
@@ -17232,7 +17308,7 @@
         <v>146</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="G193" s="7" t="s">
         <v>0</v>
@@ -17242,7 +17318,7 @@
         <v>12</v>
       </c>
       <c r="I193" s="7" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="J193" s="7" t="s">
         <v>161</v>
@@ -17274,7 +17350,7 @@
         <v>146</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="G194" s="7" t="s">
         <v>0</v>
@@ -17284,7 +17360,7 @@
         <v>12</v>
       </c>
       <c r="I194" s="7" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="J194" s="7" t="s">
         <v>161</v>
@@ -17316,7 +17392,7 @@
         <v>146</v>
       </c>
       <c r="F195" s="7" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="G195" s="7" t="s">
         <v>0</v>
@@ -17326,7 +17402,7 @@
         <v>12</v>
       </c>
       <c r="I195" s="7" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="J195" s="7" t="s">
         <v>187</v>
@@ -17358,7 +17434,7 @@
         <v>146</v>
       </c>
       <c r="F196" s="7" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G196" s="7" t="s">
         <v>0</v>
@@ -17368,7 +17444,7 @@
         <v>11</v>
       </c>
       <c r="I196" s="7" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="J196" s="7" t="s">
         <v>187</v>
@@ -17400,7 +17476,7 @@
         <v>146</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="G197" s="7" t="s">
         <v>0</v>
@@ -17410,7 +17486,7 @@
         <v>12</v>
       </c>
       <c r="I197" s="7" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="J197" s="7" t="s">
         <v>187</v>
@@ -17442,7 +17518,7 @@
         <v>146</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="G198" s="7" t="s">
         <v>0</v>
@@ -17452,7 +17528,7 @@
         <v>12</v>
       </c>
       <c r="I198" s="7" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="J198" s="7" t="s">
         <v>147</v>
@@ -17484,20 +17560,20 @@
         <v>146</v>
       </c>
       <c r="F199" s="7" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="G199" s="7" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="H199" s="7">
         <f t="shared" ref="H199:H212" si="7">LEN(F199)</f>
         <v>12</v>
       </c>
       <c r="I199" s="7" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="J199" s="7" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="K199" s="7" t="s">
         <v>464</v>
@@ -17526,20 +17602,20 @@
         <v>146</v>
       </c>
       <c r="F200" s="7" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="G200" s="7" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="H200" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I200" s="7" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="J200" s="7" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="K200" s="7" t="s">
         <v>464</v>
@@ -17568,20 +17644,20 @@
         <v>146</v>
       </c>
       <c r="F201" s="7" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="G201" s="7" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="H201" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I201" s="7" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="J201" s="7" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="K201" s="7" t="s">
         <v>464</v>
@@ -17610,20 +17686,20 @@
         <v>146</v>
       </c>
       <c r="F202" s="7" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="G202" s="7" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="H202" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I202" s="7" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="J202" s="7" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="K202" s="7" t="s">
         <v>464</v>
@@ -17652,7 +17728,7 @@
         <v>146</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="G203" s="7" t="s">
         <v>0</v>
@@ -17662,7 +17738,7 @@
         <v>12</v>
       </c>
       <c r="I203" s="7" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="J203" s="7" t="s">
         <v>161</v>
@@ -17694,17 +17770,17 @@
         <v>146</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>664</v>
+        <v>743</v>
       </c>
       <c r="G204" s="7" t="s">
-        <v>0</v>
+        <v>742</v>
       </c>
       <c r="H204" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I204" s="7" t="s">
-        <v>665</v>
+        <v>744</v>
       </c>
       <c r="J204" s="7" t="s">
         <v>161</v>
@@ -17736,7 +17812,7 @@
         <v>146</v>
       </c>
       <c r="F205" s="7" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="G205" s="7" t="s">
         <v>0</v>
@@ -17746,7 +17822,7 @@
         <v>12</v>
       </c>
       <c r="I205" s="7" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="J205" s="7" t="s">
         <v>161</v>
@@ -17778,7 +17854,7 @@
         <v>146</v>
       </c>
       <c r="F206" s="7" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="G206" s="7" t="s">
         <v>0</v>
@@ -17788,7 +17864,7 @@
         <v>12</v>
       </c>
       <c r="I206" s="7" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="J206" s="7" t="s">
         <v>210</v>
@@ -17820,17 +17896,17 @@
         <v>146</v>
       </c>
       <c r="F207" s="7" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="G207" s="7" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="H207" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I207" s="7" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="J207" s="7" t="s">
         <v>210</v>
@@ -17862,17 +17938,17 @@
         <v>146</v>
       </c>
       <c r="F208" s="7" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="G208" s="7" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="H208" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I208" s="7" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="J208" s="7" t="s">
         <v>210</v>
@@ -17904,7 +17980,7 @@
         <v>146</v>
       </c>
       <c r="F209" s="7" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="G209" s="7" t="s">
         <v>0</v>
@@ -17914,7 +17990,7 @@
         <v>11</v>
       </c>
       <c r="I209" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="J209" s="7" t="s">
         <v>215</v>
@@ -17946,17 +18022,17 @@
         <v>146</v>
       </c>
       <c r="F210" s="7" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="G210" s="7" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="H210" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I210" s="7" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="J210" s="7" t="s">
         <v>215</v>
@@ -17988,7 +18064,7 @@
         <v>146</v>
       </c>
       <c r="F211" s="7" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="G211" s="7" t="s">
         <v>0</v>
@@ -18030,7 +18106,7 @@
         <v>146</v>
       </c>
       <c r="F212" s="7" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="G212" s="7" t="s">
         <v>0</v>
@@ -18040,7 +18116,7 @@
         <v>12</v>
       </c>
       <c r="I212" s="7" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="J212" s="7" t="s">
         <v>187</v>
@@ -18072,20 +18148,20 @@
         <v>146</v>
       </c>
       <c r="F213" s="7" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="G213" s="7" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="H213" s="7">
         <f t="shared" ref="H213:H220" si="8">LEN(F213)</f>
         <v>12</v>
       </c>
       <c r="I213" s="7" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="J213" s="7" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="K213" s="7" t="s">
         <v>464</v>
@@ -18114,20 +18190,20 @@
         <v>146</v>
       </c>
       <c r="F214" s="7" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="G214" s="7" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="H214" s="7">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="I214" s="7" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="J214" s="7" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="K214" s="7" t="s">
         <v>464</v>
@@ -18156,7 +18232,7 @@
         <v>146</v>
       </c>
       <c r="F215" s="7" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="G215" s="7" t="s">
         <v>0</v>
@@ -18166,7 +18242,7 @@
         <v>12</v>
       </c>
       <c r="I215" s="7" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="J215" s="7" t="s">
         <v>161</v>
@@ -18198,7 +18274,7 @@
         <v>146</v>
       </c>
       <c r="F216" s="7" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="G216" s="7" t="s">
         <v>0</v>
@@ -18208,7 +18284,7 @@
         <v>12</v>
       </c>
       <c r="I216" s="7" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="J216" s="7" t="s">
         <v>161</v>
@@ -18240,7 +18316,7 @@
         <v>146</v>
       </c>
       <c r="F217" s="7" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="G217" s="7" t="s">
         <v>0</v>
@@ -18250,7 +18326,7 @@
         <v>12</v>
       </c>
       <c r="I217" s="7" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="J217" s="7" t="s">
         <v>161</v>
@@ -18282,17 +18358,17 @@
         <v>146</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="G218" s="7" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="H218" s="7">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="I218" s="7" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="J218" s="7" t="s">
         <v>210</v>
@@ -18324,17 +18400,17 @@
         <v>146</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="G219" s="7" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="H219" s="7">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="I219" s="7" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="J219" s="7" t="s">
         <v>210</v>
@@ -18366,17 +18442,17 @@
         <v>146</v>
       </c>
       <c r="F220" s="7" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="G220" s="7" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="H220" s="7">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="I220" s="7" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="J220" s="7" t="s">
         <v>210</v>
@@ -18391,11 +18467,347 @@
       <c r="N220" s="3"/>
       <c r="O220" s="3"/>
     </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A221" s="7">
+        <v>220</v>
+      </c>
+      <c r="B221" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C221" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D221" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E221" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F221" s="7" t="s">
+        <v>745</v>
+      </c>
+      <c r="G221" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H221" s="7">
+        <f>LEN(F221)</f>
+        <v>11</v>
+      </c>
+      <c r="I221" s="7" t="s">
+        <v>746</v>
+      </c>
+      <c r="J221" s="7" t="s">
+        <v>747</v>
+      </c>
+      <c r="K221" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L221" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M221" s="3"/>
+      <c r="N221" s="3"/>
+      <c r="O221" s="3"/>
+    </row>
+    <row r="222" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A222" s="7">
+        <v>221</v>
+      </c>
+      <c r="B222" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C222" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D222" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E222" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F222" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="G222" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H222" s="7">
+        <f>LEN(F222)</f>
+        <v>12</v>
+      </c>
+      <c r="I222" s="7" t="s">
+        <v>749</v>
+      </c>
+      <c r="J222" s="7" t="s">
+        <v>747</v>
+      </c>
+      <c r="K222" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L222" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M222" s="3"/>
+      <c r="N222" s="3"/>
+      <c r="O222" s="3"/>
+    </row>
+    <row r="223" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A223" s="7">
+        <v>222</v>
+      </c>
+      <c r="B223" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C223" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D223" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E223" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F223" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="G223" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H223" s="7">
+        <f>LEN(F223)</f>
+        <v>11</v>
+      </c>
+      <c r="I223" s="7" t="s">
+        <v>751</v>
+      </c>
+      <c r="J223" s="7" t="s">
+        <v>747</v>
+      </c>
+      <c r="K223" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L223" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M223" s="3"/>
+      <c r="N223" s="3"/>
+      <c r="O223" s="3"/>
+    </row>
+    <row r="224" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A224" s="7">
+        <v>223</v>
+      </c>
+      <c r="B224" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C224" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D224" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E224" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F224" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="G224" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H224" s="7">
+        <f>LEN(F224)</f>
+        <v>11</v>
+      </c>
+      <c r="I224" s="7" t="s">
+        <v>753</v>
+      </c>
+      <c r="J224" s="7" t="s">
+        <v>747</v>
+      </c>
+      <c r="K224" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L224" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M224" s="3"/>
+      <c r="N224" s="3"/>
+      <c r="O224" s="3"/>
+    </row>
+    <row r="225" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A225" s="7">
+        <v>224</v>
+      </c>
+      <c r="B225" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C225" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D225" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E225" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F225" s="7" t="s">
+        <v>754</v>
+      </c>
+      <c r="G225" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H225" s="7">
+        <f>LEN(F225)</f>
+        <v>10</v>
+      </c>
+      <c r="I225" s="7" t="s">
+        <v>755</v>
+      </c>
+      <c r="J225" s="7" t="s">
+        <v>747</v>
+      </c>
+      <c r="K225" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L225" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M225" s="3"/>
+      <c r="N225" s="3"/>
+      <c r="O225" s="3"/>
+    </row>
+    <row r="226" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A226" s="7">
+        <v>225</v>
+      </c>
+      <c r="B226" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C226" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D226" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E226" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F226" s="7" t="s">
+        <v>756</v>
+      </c>
+      <c r="G226" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H226" s="7">
+        <f>LEN(F226)</f>
+        <v>11</v>
+      </c>
+      <c r="I226" s="7" t="s">
+        <v>757</v>
+      </c>
+      <c r="J226" s="7" t="s">
+        <v>747</v>
+      </c>
+      <c r="K226" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L226" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M226" s="3"/>
+      <c r="N226" s="3"/>
+      <c r="O226" s="3"/>
+    </row>
+    <row r="227" spans="1:15" ht="25" x14ac:dyDescent="0.45">
+      <c r="A227" s="7">
+        <v>226</v>
+      </c>
+      <c r="B227" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C227" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D227" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E227" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F227" s="7" t="s">
+        <v>758</v>
+      </c>
+      <c r="G227" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H227" s="7">
+        <f>LEN(F227)</f>
+        <v>12</v>
+      </c>
+      <c r="I227" s="7" t="s">
+        <v>759</v>
+      </c>
+      <c r="J227" s="7" t="s">
+        <v>747</v>
+      </c>
+      <c r="K227" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L227" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M227" s="3"/>
+      <c r="N227" s="3"/>
+      <c r="O227" s="3"/>
+    </row>
+    <row r="228" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A228" s="7">
+        <v>227</v>
+      </c>
+      <c r="B228" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C228" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D228" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E228" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F228" s="7" t="s">
+        <v>760</v>
+      </c>
+      <c r="G228" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H228" s="7">
+        <f>LEN(F228)</f>
+        <v>11</v>
+      </c>
+      <c r="I228" s="7" t="s">
+        <v>761</v>
+      </c>
+      <c r="J228" s="7" t="s">
+        <v>747</v>
+      </c>
+      <c r="K228" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L228" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="M228" s="3"/>
+      <c r="N228" s="3"/>
+      <c r="O228" s="3"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O220" xr:uid="{243C8A1C-2FBA-4873-BD31-7545635970F1}"/>
+  <autoFilter ref="A1:O228" xr:uid="{243C8A1C-2FBA-4873-BD31-7545635970F1}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M220" xr:uid="{29F577E0-A9A7-4D3D-B3E7-99484ADFB535}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M228" xr:uid="{29F577E0-A9A7-4D3D-B3E7-99484ADFB535}">
       <formula1>"승인,수정,제외"</formula1>
     </dataValidation>
   </dataValidations>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB98C386-234F-424B-B9B1-8900907D5F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A76356-2ACA-4435-B22B-C9BDDC3BB665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -8496,10 +8496,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>두부를 올린 샐러드로 채소와 단백질을 함께 챙겨요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>저녁추천: 샐러드/쌈</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8508,10 +8504,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>연어샐러드로 채소와 좋은 지방을 함께 먹어요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>아침추천: 샐러드/나물</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8520,62 +8512,78 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>아삭한 양배추샐러드로 아침 채소를 더해요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>아침추천: 오이샐러드</t>
   </si>
   <si>
-    <t>상큼한 오이샐러드로 아침 채소를 챙겨요.</t>
-  </si>
-  <si>
     <t>식생활지침 「채소 충분히」 · WHO 채소 섭취 권고</t>
   </si>
   <si>
     <t>아침추천: 연두부샐러드</t>
   </si>
   <si>
-    <t>연두부를 올리면 샐러드가 든든해져요.</t>
-  </si>
-  <si>
     <t>아침추천: 버섯샐러드</t>
   </si>
   <si>
-    <t>구운 버섯을 올린 샐러드로 채소를 더해요.</t>
-  </si>
-  <si>
     <t>저녁추천: 버섯샐러드</t>
   </si>
   <si>
-    <t>구운 버섯샐러드는 기름 없이 즐기는 채소 요리예요.</t>
-  </si>
-  <si>
     <t>저녁추천: 닭샐러드</t>
   </si>
   <si>
-    <t>닭가슴살을 올린 샐러드로 채소와 단백질을 챙겨요.</t>
-  </si>
-  <si>
     <t>저녁추천: 새우샐러드</t>
   </si>
   <si>
-    <t>데친 새우를 올린 샐러드로 담백하게 먹어요.</t>
-  </si>
-  <si>
     <t>저녁추천: 리코타샐러드</t>
   </si>
   <si>
-    <t>리코타 치즈를 곁들이면 채소를 맛있게 먹을 수 있어요.</t>
-  </si>
-  <si>
     <t>저녁추천: 두부샐러드</t>
   </si>
   <si>
-    <t>두부샐러드로 채소와 단백질을 함께 먹어요.</t>
-  </si>
-  <si>
     <t>10-12 「샐러드」를 구체적인 샐러드 이름으로 바꿈() · 샐러드 추천  추가. 합계 227개</t>
+  </si>
+  <si>
+    <t>두부를 올린 샐러드로 채소와 단백질을 함께 챙겨요. 소스는 조금만 뿌려요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연어샐러드로 채소와 좋은 지방을 함께 먹어요. 소스는 조금만 뿌려요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아삭한 양배추샐러드로 아침 채소를 더해요. 소스는 조금만 뿌려요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상큼한 오이샐러드로 아침 채소를 챙겨요. 소스는 조금만 뿌려요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연두부를 올리면 샐러드가 든든해져요. 소스는 조금만 뿌려요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구운 버섯을 올린 샐러드로 채소를 더해요. 소스는 조금만 뿌려요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구운 버섯샐러드는 기름 없이 즐기는 채소 요리예요. 소스는 조금만 뿌려요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>닭가슴살을 올린 샐러드로 채소와 단백질을 챙겨요. 소스는 조금만 뿌려요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데친 새우를 올린 샐러드로 담백하게 먹어요. 소스는 조금만 뿌려요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리코타 치즈를 곁들이면 채소를 맛있게 먹을 수 있어요. 소스는 조금만 뿌려요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>두부샐러드로 채소와 단백질을 함께 먹어요. 소스는 조금만 뿌려요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -9191,7 +9199,7 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>762</v>
+        <v>751</v>
       </c>
     </row>
   </sheetData>
@@ -15443,7 +15451,7 @@
       <c r="N148" s="3"/>
       <c r="O148" s="3"/>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A149" s="7">
         <v>148</v>
       </c>
@@ -15470,7 +15478,7 @@
         <v>11</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>738</v>
+        <v>752</v>
       </c>
       <c r="J149" s="7" t="s">
         <v>161</v>
@@ -17123,7 +17131,7 @@
       <c r="N188" s="3"/>
       <c r="O188" s="3"/>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A189" s="7">
         <v>188</v>
       </c>
@@ -17140,17 +17148,17 @@
         <v>146</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="G189" s="7" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H189" s="7">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="I189" s="7" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
       <c r="J189" s="7" t="s">
         <v>161</v>
@@ -17753,7 +17761,7 @@
       <c r="N203" s="3"/>
       <c r="O203" s="3"/>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A204" s="7">
         <v>203</v>
       </c>
@@ -17770,17 +17778,17 @@
         <v>146</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="G204" s="7" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="H204" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I204" s="7" t="s">
-        <v>744</v>
+        <v>754</v>
       </c>
       <c r="J204" s="7" t="s">
         <v>161</v>
@@ -18467,7 +18475,7 @@
       <c r="N220" s="3"/>
       <c r="O220" s="3"/>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A221" s="7">
         <v>220</v>
       </c>
@@ -18484,20 +18492,20 @@
         <v>146</v>
       </c>
       <c r="F221" s="7" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="G221" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H221" s="7">
-        <f>LEN(F221)</f>
+        <f t="shared" ref="H221:H228" si="9">LEN(F221)</f>
         <v>11</v>
       </c>
       <c r="I221" s="7" t="s">
-        <v>746</v>
+        <v>755</v>
       </c>
       <c r="J221" s="7" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="K221" s="7" t="s">
         <v>464</v>
@@ -18509,7 +18517,7 @@
       <c r="N221" s="3"/>
       <c r="O221" s="3"/>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A222" s="7">
         <v>221</v>
       </c>
@@ -18526,20 +18534,20 @@
         <v>146</v>
       </c>
       <c r="F222" s="7" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="G222" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H222" s="7">
-        <f>LEN(F222)</f>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="I222" s="7" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="J222" s="7" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="K222" s="7" t="s">
         <v>464</v>
@@ -18551,7 +18559,7 @@
       <c r="N222" s="3"/>
       <c r="O222" s="3"/>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A223" s="7">
         <v>222</v>
       </c>
@@ -18568,20 +18576,20 @@
         <v>146</v>
       </c>
       <c r="F223" s="7" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="G223" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H223" s="7">
-        <f>LEN(F223)</f>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="I223" s="7" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="J223" s="7" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="K223" s="7" t="s">
         <v>464</v>
@@ -18593,7 +18601,7 @@
       <c r="N223" s="3"/>
       <c r="O223" s="3"/>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A224" s="7">
         <v>223</v>
       </c>
@@ -18610,20 +18618,20 @@
         <v>146</v>
       </c>
       <c r="F224" s="7" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="G224" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H224" s="7">
-        <f>LEN(F224)</f>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="I224" s="7" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="J224" s="7" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="K224" s="7" t="s">
         <v>466</v>
@@ -18635,7 +18643,7 @@
       <c r="N224" s="3"/>
       <c r="O224" s="3"/>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A225" s="7">
         <v>224</v>
       </c>
@@ -18652,20 +18660,20 @@
         <v>146</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="G225" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H225" s="7">
-        <f>LEN(F225)</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I225" s="7" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="J225" s="7" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="K225" s="7" t="s">
         <v>466</v>
@@ -18677,7 +18685,7 @@
       <c r="N225" s="3"/>
       <c r="O225" s="3"/>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A226" s="7">
         <v>225</v>
       </c>
@@ -18694,20 +18702,20 @@
         <v>146</v>
       </c>
       <c r="F226" s="7" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="G226" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H226" s="7">
-        <f>LEN(F226)</f>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="I226" s="7" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="J226" s="7" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="K226" s="7" t="s">
         <v>466</v>
@@ -18736,20 +18744,20 @@
         <v>146</v>
       </c>
       <c r="F227" s="7" t="s">
-        <v>758</v>
+        <v>749</v>
       </c>
       <c r="G227" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H227" s="7">
-        <f>LEN(F227)</f>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="I227" s="7" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="J227" s="7" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="K227" s="7" t="s">
         <v>466</v>
@@ -18761,7 +18769,7 @@
       <c r="N227" s="3"/>
       <c r="O227" s="3"/>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A228" s="7">
         <v>227</v>
       </c>
@@ -18778,20 +18786,20 @@
         <v>146</v>
       </c>
       <c r="F228" s="7" t="s">
-        <v>760</v>
+        <v>750</v>
       </c>
       <c r="G228" s="7" t="s">
         <v>0</v>
       </c>
       <c r="H228" s="7">
-        <f>LEN(F228)</f>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="I228" s="7" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="J228" s="7" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="K228" s="7" t="s">
         <v>466</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A76356-2ACA-4435-B22B-C9BDDC3BB665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59555251-7FAE-442C-8450-826B4DB84F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2345" uniqueCount="763">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2346" uniqueCount="772">
   <si>
     <t>—</t>
   </si>
@@ -7961,10 +7961,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>아침추천: 나물/샐러드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>아침추천: 달걀찜/두부</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8496,94 +8492,141 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>저녁추천: 샐러드/쌈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>저녁추천: 연어샐러드</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>아침추천: 샐러드/나물</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>아침추천: 양배추샐러드</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>식생활지침 「채소 충분히」 · WHO 채소 섭취 권고</t>
+  </si>
+  <si>
+    <t>10-12 「샐러드」를 구체적인 샐러드 이름으로 바꿈() · 샐러드 추천  추가. 합계 227개</t>
+  </si>
+  <si>
+    <t>소스 1/2 두부샐러드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>두부를 올린 샐러드로 채소와 단백질을 함께 챙겨요. 소스는 절반만 뿌려요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소스 1/2 연어샐러드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연어샐러드로 채소와 좋은 지방을 함께 먹어요. 소스는 절반만 뿌려요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소스 1/2 채소샐러드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아삭한 채소샐러드로 아침 채소를 더해요. 소스는 절반만 뿌려요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>아침추천: 오이샐러드</t>
-  </si>
-  <si>
-    <t>식생활지침 「채소 충분히」 · WHO 채소 섭취 권고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소스 1/2 오이샐러드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상큼한 오이샐러드로 아침 채소를 챙겨요. 소스는 절반만 뿌려요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>아침추천: 연두부샐러드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소스 1/2 콩샐러드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>콩을 곁들인 샐러드로 채소와 단백질을 챙겨요. 소스는 절반만 뿌려요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>아침추천: 버섯샐러드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소스 1/2 버섯샐러드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구운 버섯을 올린 샐러드로 채소를 더해요. 소스는 절반만 뿌려요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>저녁추천: 버섯샐러드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소스 1/2 가지샐러드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구운 가지샐러드로 저녁 채소를 더해요. 소스는 절반만 뿌려요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>저녁추천: 닭샐러드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소스 1/2 닭샐러드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>닭가슴살을 올린 샐러드로 채소와 단백질을 챙겨요. 소스는 절반만 뿌려요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>저녁추천: 새우샐러드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소스 1/2 새우샐러드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데친 새우를 올린 샐러드로 담백하게 먹어요. 소스는 절반만 뿌려요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>저녁추천: 리코타샐러드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소스 1/2 해초샐러드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해초샐러드로 저녁 채소를 가볍게 챙겨요. 소스는 절반만 뿌려요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>저녁추천: 두부샐러드</t>
-  </si>
-  <si>
-    <t>10-12 「샐러드」를 구체적인 샐러드 이름으로 바꿈() · 샐러드 추천  추가. 합계 227개</t>
-  </si>
-  <si>
-    <t>두부를 올린 샐러드로 채소와 단백질을 함께 챙겨요. 소스는 조금만 뿌려요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>연어샐러드로 채소와 좋은 지방을 함께 먹어요. 소스는 조금만 뿌려요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아삭한 양배추샐러드로 아침 채소를 더해요. 소스는 조금만 뿌려요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>상큼한 오이샐러드로 아침 채소를 챙겨요. 소스는 조금만 뿌려요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>연두부를 올리면 샐러드가 든든해져요. 소스는 조금만 뿌려요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>구운 버섯을 올린 샐러드로 채소를 더해요. 소스는 조금만 뿌려요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>구운 버섯샐러드는 기름 없이 즐기는 채소 요리예요. 소스는 조금만 뿌려요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>닭가슴살을 올린 샐러드로 채소와 단백질을 챙겨요. 소스는 조금만 뿌려요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>데친 새우를 올린 샐러드로 담백하게 먹어요. 소스는 조금만 뿌려요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>리코타 치즈를 곁들이면 채소를 맛있게 먹을 수 있어요. 소스는 조금만 뿌려요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>두부샐러드로 채소와 단백질을 함께 먹어요. 소스는 조금만 뿌려요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소스 1/2 참치샐러드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>참치를 올린 샐러드로 단백질을 함께 챙겨요. 소스는 절반만 뿌려요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10-12 샐러드 추천  「소스 1/2 ○○샐러드」로 바꿈(소스를 절반만 뿌리라는 뜻이 화면에 보이게). 12자 안에 넣느라 「아침추천: / 저녁추천:」 머리말은 빼고, 나오는 시간은 그대로</t>
   </si>
 </sst>
 </file>
@@ -9070,7 +9113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F51797-492B-40AC-833D-E19CEF6E9FA5}">
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="120.58203125" style="1" customWidth="1"/>
@@ -9164,42 +9207,47 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>751</v>
+        <v>740</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A27" s="1" t="s">
+        <v>771</v>
       </c>
     </row>
   </sheetData>
@@ -15090,20 +15138,20 @@
         <v>146</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="G140" s="7" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H140" s="7">
         <f t="shared" ref="H140:H177" si="5">LEN(F140)</f>
         <v>12</v>
       </c>
       <c r="I140" s="7" t="s">
+        <v>703</v>
+      </c>
+      <c r="J140" s="7" t="s">
         <v>704</v>
-      </c>
-      <c r="J140" s="7" t="s">
-        <v>705</v>
       </c>
       <c r="K140" s="7" t="s">
         <v>464</v>
@@ -15132,20 +15180,20 @@
         <v>146</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="G141" s="7" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H141" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I141" s="7" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="J141" s="7" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="K141" s="7" t="s">
         <v>464</v>
@@ -15174,20 +15222,20 @@
         <v>146</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="G142" s="7" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H142" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I142" s="7" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="J142" s="7" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="K142" s="7" t="s">
         <v>464</v>
@@ -15216,20 +15264,20 @@
         <v>146</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="G143" s="7" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H143" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I143" s="7" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="J143" s="7" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="K143" s="7" t="s">
         <v>464</v>
@@ -15258,20 +15306,20 @@
         <v>146</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="G144" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H144" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I144" s="7" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="J144" s="7" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="K144" s="7" t="s">
         <v>464</v>
@@ -15468,17 +15516,17 @@
         <v>146</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="G149" s="7" t="s">
-        <v>589</v>
+        <v>736</v>
       </c>
       <c r="H149" s="7">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>752</v>
+        <v>742</v>
       </c>
       <c r="J149" s="7" t="s">
         <v>161</v>
@@ -15510,7 +15558,7 @@
         <v>146</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G150" s="7" t="s">
         <v>0</v>
@@ -15552,7 +15600,7 @@
         <v>146</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G151" s="7" t="s">
         <v>0</v>
@@ -15594,7 +15642,7 @@
         <v>146</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G152" s="7" t="s">
         <v>0</v>
@@ -15636,7 +15684,7 @@
         <v>146</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G153" s="7" t="s">
         <v>0</v>
@@ -15678,17 +15726,17 @@
         <v>146</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G154" s="7" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H154" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I154" s="7" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="J154" s="7" t="s">
         <v>210</v>
@@ -15720,7 +15768,7 @@
         <v>146</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G155" s="7" t="s">
         <v>0</v>
@@ -15762,17 +15810,17 @@
         <v>146</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G156" s="7" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H156" s="7">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="I156" s="7" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="J156" s="7" t="s">
         <v>215</v>
@@ -15804,17 +15852,17 @@
         <v>146</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G157" s="7" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H157" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I157" s="7" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="J157" s="7" t="s">
         <v>187</v>
@@ -15846,7 +15894,7 @@
         <v>146</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G158" s="7" t="s">
         <v>0</v>
@@ -15888,7 +15936,7 @@
         <v>146</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G159" s="7" t="s">
         <v>0</v>
@@ -15930,7 +15978,7 @@
         <v>146</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G160" s="7" t="s">
         <v>0</v>
@@ -15972,7 +16020,7 @@
         <v>146</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G161" s="7" t="s">
         <v>0</v>
@@ -16014,7 +16062,7 @@
         <v>146</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G162" s="7" t="s">
         <v>0</v>
@@ -16056,7 +16104,7 @@
         <v>146</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G163" s="7" t="s">
         <v>0</v>
@@ -16098,7 +16146,7 @@
         <v>146</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G164" s="7" t="s">
         <v>0</v>
@@ -16140,7 +16188,7 @@
         <v>146</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G165" s="7" t="s">
         <v>0</v>
@@ -16182,7 +16230,7 @@
         <v>146</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G166" s="7" t="s">
         <v>0</v>
@@ -16224,7 +16272,7 @@
         <v>146</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="G167" s="7" t="s">
         <v>0</v>
@@ -16266,7 +16314,7 @@
         <v>146</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G168" s="7" t="s">
         <v>0</v>
@@ -16308,7 +16356,7 @@
         <v>146</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G169" s="7" t="s">
         <v>0</v>
@@ -16350,7 +16398,7 @@
         <v>146</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="G170" s="7" t="s">
         <v>0</v>
@@ -16392,7 +16440,7 @@
         <v>146</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G171" s="7" t="s">
         <v>0</v>
@@ -16434,7 +16482,7 @@
         <v>146</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G172" s="7" t="s">
         <v>0</v>
@@ -16476,7 +16524,7 @@
         <v>146</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G173" s="7" t="s">
         <v>0</v>
@@ -16518,7 +16566,7 @@
         <v>146</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G174" s="7" t="s">
         <v>0</v>
@@ -16560,7 +16608,7 @@
         <v>146</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="G175" s="7" t="s">
         <v>0</v>
@@ -16602,7 +16650,7 @@
         <v>146</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G176" s="7" t="s">
         <v>0</v>
@@ -16644,7 +16692,7 @@
         <v>146</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G177" s="7" t="s">
         <v>0</v>
@@ -16686,7 +16734,7 @@
         <v>146</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="G178" s="7" t="s">
         <v>0</v>
@@ -16696,7 +16744,7 @@
         <v>11</v>
       </c>
       <c r="I178" s="7" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="J178" s="7" t="s">
         <v>215</v>
@@ -16728,7 +16776,7 @@
         <v>146</v>
       </c>
       <c r="F179" s="7" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="G179" s="7" t="s">
         <v>0</v>
@@ -16738,7 +16786,7 @@
         <v>12</v>
       </c>
       <c r="I179" s="7" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="J179" s="7" t="s">
         <v>215</v>
@@ -16770,7 +16818,7 @@
         <v>146</v>
       </c>
       <c r="F180" s="7" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G180" s="7" t="s">
         <v>0</v>
@@ -16780,7 +16828,7 @@
         <v>12</v>
       </c>
       <c r="I180" s="7" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="J180" s="7" t="s">
         <v>215</v>
@@ -16812,7 +16860,7 @@
         <v>146</v>
       </c>
       <c r="F181" s="7" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="G181" s="7" t="s">
         <v>0</v>
@@ -16822,7 +16870,7 @@
         <v>12</v>
       </c>
       <c r="I181" s="7" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="J181" s="7" t="s">
         <v>215</v>
@@ -16854,7 +16902,7 @@
         <v>146</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G182" s="7" t="s">
         <v>0</v>
@@ -16864,7 +16912,7 @@
         <v>12</v>
       </c>
       <c r="I182" s="7" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J182" s="7" t="s">
         <v>215</v>
@@ -16896,7 +16944,7 @@
         <v>146</v>
       </c>
       <c r="F183" s="7" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="G183" s="7" t="s">
         <v>0</v>
@@ -16906,7 +16954,7 @@
         <v>12</v>
       </c>
       <c r="I183" s="7" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="J183" s="7" t="s">
         <v>210</v>
@@ -16938,7 +16986,7 @@
         <v>146</v>
       </c>
       <c r="F184" s="7" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G184" s="7" t="s">
         <v>0</v>
@@ -16948,7 +16996,7 @@
         <v>11</v>
       </c>
       <c r="I184" s="7" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="J184" s="7" t="s">
         <v>210</v>
@@ -16980,7 +17028,7 @@
         <v>146</v>
       </c>
       <c r="F185" s="7" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="G185" s="7" t="s">
         <v>0</v>
@@ -16990,7 +17038,7 @@
         <v>11</v>
       </c>
       <c r="I185" s="7" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="J185" s="7" t="s">
         <v>210</v>
@@ -17022,7 +17070,7 @@
         <v>146</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G186" s="7" t="s">
         <v>0</v>
@@ -17032,7 +17080,7 @@
         <v>12</v>
       </c>
       <c r="I186" s="7" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="J186" s="7" t="s">
         <v>161</v>
@@ -17064,7 +17112,7 @@
         <v>146</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G187" s="7" t="s">
         <v>0</v>
@@ -17074,7 +17122,7 @@
         <v>11</v>
       </c>
       <c r="I187" s="7" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="J187" s="7" t="s">
         <v>161</v>
@@ -17106,7 +17154,7 @@
         <v>146</v>
       </c>
       <c r="F188" s="7" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G188" s="7" t="s">
         <v>0</v>
@@ -17116,7 +17164,7 @@
         <v>11</v>
       </c>
       <c r="I188" s="7" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="J188" s="7" t="s">
         <v>161</v>
@@ -17148,17 +17196,17 @@
         <v>146</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="G189" s="7" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H189" s="7">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I189" s="7" t="s">
-        <v>753</v>
+        <v>744</v>
       </c>
       <c r="J189" s="7" t="s">
         <v>161</v>
@@ -17190,7 +17238,7 @@
         <v>146</v>
       </c>
       <c r="F190" s="7" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G190" s="7" t="s">
         <v>0</v>
@@ -17200,7 +17248,7 @@
         <v>12</v>
       </c>
       <c r="I190" s="7" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="J190" s="7" t="s">
         <v>161</v>
@@ -17232,7 +17280,7 @@
         <v>146</v>
       </c>
       <c r="F191" s="7" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G191" s="7" t="s">
         <v>0</v>
@@ -17242,7 +17290,7 @@
         <v>12</v>
       </c>
       <c r="I191" s="7" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="J191" s="7" t="s">
         <v>161</v>
@@ -17274,7 +17322,7 @@
         <v>146</v>
       </c>
       <c r="F192" s="7" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G192" s="7" t="s">
         <v>0</v>
@@ -17284,7 +17332,7 @@
         <v>12</v>
       </c>
       <c r="I192" s="7" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J192" s="7" t="s">
         <v>161</v>
@@ -17316,7 +17364,7 @@
         <v>146</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G193" s="7" t="s">
         <v>0</v>
@@ -17326,7 +17374,7 @@
         <v>12</v>
       </c>
       <c r="I193" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="J193" s="7" t="s">
         <v>161</v>
@@ -17358,7 +17406,7 @@
         <v>146</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G194" s="7" t="s">
         <v>0</v>
@@ -17368,7 +17416,7 @@
         <v>12</v>
       </c>
       <c r="I194" s="7" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="J194" s="7" t="s">
         <v>161</v>
@@ -17400,7 +17448,7 @@
         <v>146</v>
       </c>
       <c r="F195" s="7" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G195" s="7" t="s">
         <v>0</v>
@@ -17410,7 +17458,7 @@
         <v>12</v>
       </c>
       <c r="I195" s="7" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="J195" s="7" t="s">
         <v>187</v>
@@ -17442,7 +17490,7 @@
         <v>146</v>
       </c>
       <c r="F196" s="7" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G196" s="7" t="s">
         <v>0</v>
@@ -17452,7 +17500,7 @@
         <v>11</v>
       </c>
       <c r="I196" s="7" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="J196" s="7" t="s">
         <v>187</v>
@@ -17484,7 +17532,7 @@
         <v>146</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G197" s="7" t="s">
         <v>0</v>
@@ -17526,7 +17574,7 @@
         <v>146</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G198" s="7" t="s">
         <v>0</v>
@@ -17536,7 +17584,7 @@
         <v>12</v>
       </c>
       <c r="I198" s="7" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J198" s="7" t="s">
         <v>147</v>
@@ -17568,20 +17616,20 @@
         <v>146</v>
       </c>
       <c r="F199" s="7" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="G199" s="7" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H199" s="7">
         <f t="shared" ref="H199:H212" si="7">LEN(F199)</f>
         <v>12</v>
       </c>
       <c r="I199" s="7" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="J199" s="7" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="K199" s="7" t="s">
         <v>464</v>
@@ -17610,20 +17658,20 @@
         <v>146</v>
       </c>
       <c r="F200" s="7" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G200" s="7" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H200" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I200" s="7" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="J200" s="7" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="K200" s="7" t="s">
         <v>464</v>
@@ -17652,20 +17700,20 @@
         <v>146</v>
       </c>
       <c r="F201" s="7" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="G201" s="7" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H201" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I201" s="7" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="J201" s="7" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="K201" s="7" t="s">
         <v>464</v>
@@ -17694,20 +17742,20 @@
         <v>146</v>
       </c>
       <c r="F202" s="7" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="G202" s="7" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H202" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I202" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="J202" s="7" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="K202" s="7" t="s">
         <v>464</v>
@@ -17736,7 +17784,7 @@
         <v>146</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G203" s="7" t="s">
         <v>0</v>
@@ -17746,7 +17794,7 @@
         <v>12</v>
       </c>
       <c r="I203" s="7" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="J203" s="7" t="s">
         <v>161</v>
@@ -17778,17 +17826,17 @@
         <v>146</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="G204" s="7" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="H204" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I204" s="7" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="J204" s="7" t="s">
         <v>161</v>
@@ -17820,7 +17868,7 @@
         <v>146</v>
       </c>
       <c r="F205" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G205" s="7" t="s">
         <v>0</v>
@@ -17830,7 +17878,7 @@
         <v>12</v>
       </c>
       <c r="I205" s="7" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="J205" s="7" t="s">
         <v>161</v>
@@ -17862,7 +17910,7 @@
         <v>146</v>
       </c>
       <c r="F206" s="7" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G206" s="7" t="s">
         <v>0</v>
@@ -17872,7 +17920,7 @@
         <v>12</v>
       </c>
       <c r="I206" s="7" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="J206" s="7" t="s">
         <v>210</v>
@@ -17904,17 +17952,17 @@
         <v>146</v>
       </c>
       <c r="F207" s="7" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="G207" s="7" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H207" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I207" s="7" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="J207" s="7" t="s">
         <v>210</v>
@@ -17946,17 +17994,17 @@
         <v>146</v>
       </c>
       <c r="F208" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="G208" s="7" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H208" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I208" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J208" s="7" t="s">
         <v>210</v>
@@ -17988,7 +18036,7 @@
         <v>146</v>
       </c>
       <c r="F209" s="7" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G209" s="7" t="s">
         <v>0</v>
@@ -18030,17 +18078,17 @@
         <v>146</v>
       </c>
       <c r="F210" s="7" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G210" s="7" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H210" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I210" s="7" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J210" s="7" t="s">
         <v>215</v>
@@ -18072,7 +18120,7 @@
         <v>146</v>
       </c>
       <c r="F211" s="7" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G211" s="7" t="s">
         <v>0</v>
@@ -18114,7 +18162,7 @@
         <v>146</v>
       </c>
       <c r="F212" s="7" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G212" s="7" t="s">
         <v>0</v>
@@ -18124,7 +18172,7 @@
         <v>12</v>
       </c>
       <c r="I212" s="7" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="J212" s="7" t="s">
         <v>187</v>
@@ -18156,20 +18204,20 @@
         <v>146</v>
       </c>
       <c r="F213" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="G213" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H213" s="7">
         <f t="shared" ref="H213:H220" si="8">LEN(F213)</f>
         <v>12</v>
       </c>
       <c r="I213" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="J213" s="7" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="K213" s="7" t="s">
         <v>464</v>
@@ -18198,20 +18246,20 @@
         <v>146</v>
       </c>
       <c r="F214" s="7" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="G214" s="7" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H214" s="7">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="I214" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="J214" s="7" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="K214" s="7" t="s">
         <v>464</v>
@@ -18240,7 +18288,7 @@
         <v>146</v>
       </c>
       <c r="F215" s="7" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G215" s="7" t="s">
         <v>0</v>
@@ -18250,7 +18298,7 @@
         <v>12</v>
       </c>
       <c r="I215" s="7" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="J215" s="7" t="s">
         <v>161</v>
@@ -18282,7 +18330,7 @@
         <v>146</v>
       </c>
       <c r="F216" s="7" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="G216" s="7" t="s">
         <v>0</v>
@@ -18292,7 +18340,7 @@
         <v>12</v>
       </c>
       <c r="I216" s="7" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="J216" s="7" t="s">
         <v>161</v>
@@ -18324,7 +18372,7 @@
         <v>146</v>
       </c>
       <c r="F217" s="7" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G217" s="7" t="s">
         <v>0</v>
@@ -18334,7 +18382,7 @@
         <v>12</v>
       </c>
       <c r="I217" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="J217" s="7" t="s">
         <v>161</v>
@@ -18366,17 +18414,17 @@
         <v>146</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="G218" s="7" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H218" s="7">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="I218" s="7" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="J218" s="7" t="s">
         <v>210</v>
@@ -18408,17 +18456,17 @@
         <v>146</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="G219" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H219" s="7">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="I219" s="7" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="J219" s="7" t="s">
         <v>210</v>
@@ -18450,17 +18498,17 @@
         <v>146</v>
       </c>
       <c r="F220" s="7" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="G220" s="7" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H220" s="7">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="I220" s="7" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="J220" s="7" t="s">
         <v>210</v>
@@ -18492,20 +18540,20 @@
         <v>146</v>
       </c>
       <c r="F221" s="7" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="G221" s="7" t="s">
-        <v>0</v>
+        <v>747</v>
       </c>
       <c r="H221" s="7">
         <f t="shared" ref="H221:H228" si="9">LEN(F221)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I221" s="7" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="J221" s="7" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="K221" s="7" t="s">
         <v>464</v>
@@ -18534,20 +18582,20 @@
         <v>146</v>
       </c>
       <c r="F222" s="7" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="G222" s="7" t="s">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="H222" s="7">
         <f t="shared" si="9"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I222" s="7" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="J222" s="7" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="K222" s="7" t="s">
         <v>464</v>
@@ -18576,20 +18624,20 @@
         <v>146</v>
       </c>
       <c r="F223" s="7" t="s">
-        <v>745</v>
+        <v>754</v>
       </c>
       <c r="G223" s="7" t="s">
-        <v>0</v>
+        <v>753</v>
       </c>
       <c r="H223" s="7">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I223" s="7" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="J223" s="7" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="K223" s="7" t="s">
         <v>464</v>
@@ -18618,20 +18666,20 @@
         <v>146</v>
       </c>
       <c r="F224" s="7" t="s">
-        <v>746</v>
+        <v>757</v>
       </c>
       <c r="G224" s="7" t="s">
-        <v>0</v>
+        <v>756</v>
       </c>
       <c r="H224" s="7">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I224" s="7" t="s">
         <v>758</v>
       </c>
       <c r="J224" s="7" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="K224" s="7" t="s">
         <v>466</v>
@@ -18660,20 +18708,20 @@
         <v>146</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>747</v>
+        <v>760</v>
       </c>
       <c r="G225" s="7" t="s">
-        <v>0</v>
+        <v>759</v>
       </c>
       <c r="H225" s="7">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I225" s="7" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="J225" s="7" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="K225" s="7" t="s">
         <v>466</v>
@@ -18702,20 +18750,20 @@
         <v>146</v>
       </c>
       <c r="F226" s="7" t="s">
-        <v>748</v>
+        <v>763</v>
       </c>
       <c r="G226" s="7" t="s">
-        <v>0</v>
+        <v>762</v>
       </c>
       <c r="H226" s="7">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I226" s="7" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="J226" s="7" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="K226" s="7" t="s">
         <v>466</v>
@@ -18744,20 +18792,20 @@
         <v>146</v>
       </c>
       <c r="F227" s="7" t="s">
-        <v>749</v>
+        <v>766</v>
       </c>
       <c r="G227" s="7" t="s">
-        <v>0</v>
+        <v>765</v>
       </c>
       <c r="H227" s="7">
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="I227" s="7" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="J227" s="7" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="K227" s="7" t="s">
         <v>466</v>
@@ -18786,20 +18834,20 @@
         <v>146</v>
       </c>
       <c r="F228" s="7" t="s">
-        <v>750</v>
+        <v>769</v>
       </c>
       <c r="G228" s="7" t="s">
-        <v>0</v>
+        <v>768</v>
       </c>
       <c r="H228" s="7">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I228" s="7" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="J228" s="7" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="K228" s="7" t="s">
         <v>466</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59555251-7FAE-442C-8450-826B4DB84F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572DD75B-C924-4562-8EEA-9A878916327F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2346" uniqueCount="772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2347" uniqueCount="773">
   <si>
     <t>—</t>
   </si>
@@ -8506,26 +8506,14 @@
     <t>10-12 「샐러드」를 구체적인 샐러드 이름으로 바꿈() · 샐러드 추천  추가. 합계 227개</t>
   </si>
   <si>
-    <t>소스 1/2 두부샐러드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>두부를 올린 샐러드로 채소와 단백질을 함께 챙겨요. 소스는 절반만 뿌려요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>소스 1/2 연어샐러드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>연어샐러드로 채소와 좋은 지방을 함께 먹어요. 소스는 절반만 뿌려요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>소스 1/2 채소샐러드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>아삭한 채소샐러드로 아침 채소를 더해요. 소스는 절반만 뿌려요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8534,10 +8522,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>소스 1/2 오이샐러드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>상큼한 오이샐러드로 아침 채소를 챙겨요. 소스는 절반만 뿌려요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8546,10 +8530,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>소스 1/2 콩샐러드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>콩을 곁들인 샐러드로 채소와 단백질을 챙겨요. 소스는 절반만 뿌려요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8558,10 +8538,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>소스 1/2 버섯샐러드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>구운 버섯을 올린 샐러드로 채소를 더해요. 소스는 절반만 뿌려요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8570,10 +8546,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>소스 1/2 가지샐러드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>구운 가지샐러드로 저녁 채소를 더해요. 소스는 절반만 뿌려요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8582,10 +8554,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>소스 1/2 닭샐러드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>닭가슴살을 올린 샐러드로 채소와 단백질을 챙겨요. 소스는 절반만 뿌려요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8594,10 +8562,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>소스 1/2 새우샐러드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>데친 새우를 올린 샐러드로 담백하게 먹어요. 소스는 절반만 뿌려요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8606,10 +8570,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>소스 1/2 해초샐러드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>해초샐러드로 저녁 채소를 가볍게 챙겨요. 소스는 절반만 뿌려요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8618,15 +8578,58 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>소스 1/2 참치샐러드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>참치를 올린 샐러드로 단백질을 함께 챙겨요. 소스는 절반만 뿌려요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10-12 샐러드 추천  「소스 1/2 ○○샐러드」로 바꿈(소스를 절반만 뿌리라는 뜻이 화면에 보이게). 12자 안에 넣느라 「아침추천: / 저녁추천:」 머리말은 빼고, 나오는 시간은 그대로</t>
+  </si>
+  <si>
+    <t>두부샐러드+1/2소스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연어샐러드+1/2소스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>채소샐러드+1/2소스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오이샐러드+1/2소스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>콩샐러드+1/2소스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버섯샐러드+1/2소스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가지샐러드+1/2소스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>닭샐러드+1/2소스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새우샐러드+1/2소스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해초샐러드+1/2소스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>참치샐러드+1/2소스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10-12 샐러드 표기를 「○○샐러드+1/2소스」로 바꿈()</t>
   </si>
 </sst>
 </file>
@@ -9113,7 +9116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F51797-492B-40AC-833D-E19CEF6E9FA5}">
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="120.58203125" style="1" customWidth="1"/>
@@ -9247,7 +9250,12 @@
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>771</v>
+        <v>760</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A28" s="1" t="s">
+        <v>772</v>
       </c>
     </row>
   </sheetData>
@@ -15516,17 +15524,17 @@
         <v>146</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>741</v>
+        <v>761</v>
       </c>
       <c r="G149" s="7" t="s">
         <v>736</v>
       </c>
       <c r="H149" s="7">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="J149" s="7" t="s">
         <v>161</v>
@@ -17196,17 +17204,17 @@
         <v>146</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>743</v>
+        <v>762</v>
       </c>
       <c r="G189" s="7" t="s">
         <v>737</v>
       </c>
       <c r="H189" s="7">
         <f t="shared" si="6"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I189" s="7" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="J189" s="7" t="s">
         <v>161</v>
@@ -17826,17 +17834,17 @@
         <v>146</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>745</v>
+        <v>763</v>
       </c>
       <c r="G204" s="7" t="s">
         <v>738</v>
       </c>
       <c r="H204" s="7">
         <f t="shared" si="7"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I204" s="7" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="J204" s="7" t="s">
         <v>161</v>
@@ -18540,17 +18548,17 @@
         <v>146</v>
       </c>
       <c r="F221" s="7" t="s">
-        <v>748</v>
+        <v>764</v>
       </c>
       <c r="G221" s="7" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="H221" s="7">
         <f t="shared" ref="H221:H228" si="9">LEN(F221)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I221" s="7" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="J221" s="7" t="s">
         <v>739</v>
@@ -18582,17 +18590,17 @@
         <v>146</v>
       </c>
       <c r="F222" s="7" t="s">
-        <v>751</v>
+        <v>765</v>
       </c>
       <c r="G222" s="7" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="H222" s="7">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I222" s="7" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="J222" s="7" t="s">
         <v>739</v>
@@ -18624,17 +18632,17 @@
         <v>146</v>
       </c>
       <c r="F223" s="7" t="s">
-        <v>754</v>
+        <v>766</v>
       </c>
       <c r="G223" s="7" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="H223" s="7">
         <f t="shared" si="9"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I223" s="7" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="J223" s="7" t="s">
         <v>739</v>
@@ -18666,17 +18674,17 @@
         <v>146</v>
       </c>
       <c r="F224" s="7" t="s">
-        <v>757</v>
+        <v>767</v>
       </c>
       <c r="G224" s="7" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="H224" s="7">
         <f t="shared" si="9"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I224" s="7" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="J224" s="7" t="s">
         <v>739</v>
@@ -18708,17 +18716,17 @@
         <v>146</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="G225" s="7" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="H225" s="7">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I225" s="7" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="J225" s="7" t="s">
         <v>739</v>
@@ -18750,17 +18758,17 @@
         <v>146</v>
       </c>
       <c r="F226" s="7" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="G226" s="7" t="s">
-        <v>762</v>
+        <v>754</v>
       </c>
       <c r="H226" s="7">
         <f t="shared" si="9"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I226" s="7" t="s">
-        <v>764</v>
+        <v>755</v>
       </c>
       <c r="J226" s="7" t="s">
         <v>739</v>
@@ -18792,17 +18800,17 @@
         <v>146</v>
       </c>
       <c r="F227" s="7" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="G227" s="7" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="H227" s="7">
         <f t="shared" si="9"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I227" s="7" t="s">
-        <v>767</v>
+        <v>757</v>
       </c>
       <c r="J227" s="7" t="s">
         <v>739</v>
@@ -18834,17 +18842,17 @@
         <v>146</v>
       </c>
       <c r="F228" s="7" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="G228" s="7" t="s">
-        <v>768</v>
+        <v>758</v>
       </c>
       <c r="H228" s="7">
         <f t="shared" si="9"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I228" s="7" t="s">
-        <v>770</v>
+        <v>759</v>
       </c>
       <c r="J228" s="7" t="s">
         <v>739</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572DD75B-C924-4562-8EEA-9A878916327F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{561B99C4-5E49-4E4D-835F-9B681CF80B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -8514,10 +8514,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>아삭한 채소샐러드로 아침 채소를 더해요. 소스는 절반만 뿌려요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>아침추천: 오이샐러드</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8530,10 +8526,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>콩을 곁들인 샐러드로 채소와 단백질을 챙겨요. 소스는 절반만 뿌려요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>아침추천: 버섯샐러드</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8593,18 +8585,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>채소샐러드+1/2소스</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>오이샐러드+1/2소스</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>콩샐러드+1/2소스</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>버섯샐러드+1/2소스</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8630,6 +8614,22 @@
   </si>
   <si>
     <t>10-12 샐러드 표기를 「○○샐러드+1/2소스」로 바꿈()</t>
+  </si>
+  <si>
+    <t>양배추샐러드+1/2소스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아삭한 양배추샐러드로 아침 채소를 더해요. 소스는 절반만 뿌려요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연두부샐러드+1/2소스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연두부를 올리면 샐러드가 든든해져요. 소스는 절반만 뿌려요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -9250,12 +9250,12 @@
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
     </row>
   </sheetData>
@@ -15524,7 +15524,7 @@
         <v>146</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="G149" s="7" t="s">
         <v>736</v>
@@ -17204,7 +17204,7 @@
         <v>146</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="G189" s="7" t="s">
         <v>737</v>
@@ -17834,17 +17834,17 @@
         <v>146</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="G204" s="7" t="s">
         <v>738</v>
       </c>
       <c r="H204" s="7">
         <f t="shared" si="7"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I204" s="7" t="s">
-        <v>743</v>
+        <v>770</v>
       </c>
       <c r="J204" s="7" t="s">
         <v>161</v>
@@ -18548,17 +18548,17 @@
         <v>146</v>
       </c>
       <c r="F221" s="7" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="G221" s="7" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H221" s="7">
         <f t="shared" ref="H221:H228" si="9">LEN(F221)</f>
         <v>11</v>
       </c>
       <c r="I221" s="7" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="J221" s="7" t="s">
         <v>739</v>
@@ -18590,17 +18590,17 @@
         <v>146</v>
       </c>
       <c r="F222" s="7" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="G222" s="7" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H222" s="7">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I222" s="7" t="s">
-        <v>747</v>
+        <v>772</v>
       </c>
       <c r="J222" s="7" t="s">
         <v>739</v>
@@ -18632,17 +18632,17 @@
         <v>146</v>
       </c>
       <c r="F223" s="7" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="G223" s="7" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="H223" s="7">
         <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="I223" s="7" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="J223" s="7" t="s">
         <v>739</v>
@@ -18674,17 +18674,17 @@
         <v>146</v>
       </c>
       <c r="F224" s="7" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="G224" s="7" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="H224" s="7">
         <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="I224" s="7" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="J224" s="7" t="s">
         <v>739</v>
@@ -18716,17 +18716,17 @@
         <v>146</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="G225" s="7" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="H225" s="7">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I225" s="7" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="J225" s="7" t="s">
         <v>739</v>
@@ -18758,17 +18758,17 @@
         <v>146</v>
       </c>
       <c r="F226" s="7" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="G226" s="7" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="H226" s="7">
         <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="I226" s="7" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="J226" s="7" t="s">
         <v>739</v>
@@ -18800,17 +18800,17 @@
         <v>146</v>
       </c>
       <c r="F227" s="7" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="G227" s="7" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="H227" s="7">
         <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="I227" s="7" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="J227" s="7" t="s">
         <v>739</v>
@@ -18842,17 +18842,17 @@
         <v>146</v>
       </c>
       <c r="F228" s="7" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="G228" s="7" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="H228" s="7">
         <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="I228" s="7" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="J228" s="7" t="s">
         <v>739</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{561B99C4-5E49-4E4D-835F-9B681CF80B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C59402B-ACB9-4231-91E7-2EF613E4EB32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2347" uniqueCount="773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2348" uniqueCount="793">
   <si>
     <t>—</t>
   </si>
@@ -7539,9 +7539,6 @@
     <t>오전(04~10시)</t>
   </si>
   <si>
-    <t>맑은 국은 찌개보다 덜 짜서 아침에 좋아요.</t>
-  </si>
-  <si>
     <t>오후(12~17시)</t>
   </si>
   <si>
@@ -7851,15 +7848,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>담백한 국으로 아침에도 채소를 먹어요.</t>
-  </si>
-  <si>
-    <t>맑은 국으로 아침 채소를 챙겨요.</t>
-  </si>
-  <si>
-    <t>부드러운 채소국은 아침에 먹기 좋아요.</t>
-  </si>
-  <si>
     <t>나물이나 쌈으로 채소를 넉넉히 먹어요.</t>
   </si>
   <si>
@@ -7875,18 +7863,12 @@
     <t>바쁜 아침에도 단백질을 챙길 수 있어요.</t>
   </si>
   <si>
-    <t>가벼운 국으로 단백질을 더해요.</t>
-  </si>
-  <si>
     <t>기름을 덜 쓰는 반찬으로 아침을 먹어요.</t>
   </si>
   <si>
     <t>구이와 수육은 튀김보다 기름이 덜해요.</t>
   </si>
   <si>
-    <t>삶은 고기는 구운 고기보다 기름이 덜해요.</t>
-  </si>
-  <si>
     <t>데친 요리는 기름 없이 먹을 수 있어요.</t>
   </si>
   <si>
@@ -7905,9 +7887,6 @@
     <t>담백한 단백질 반찬이에요.</t>
   </si>
   <si>
-    <t>든든한 한 그릇으로 단백질을 챙겨요.</t>
-  </si>
-  <si>
     <t>손쉬운 두부 반찬으로 단백질을 더해요.</t>
   </si>
   <si>
@@ -7926,15 +7905,6 @@
     <t>나물 한 가지로 저녁 채소를 더해요.</t>
   </si>
   <si>
-    <t>버섯국과 쌈으로 채소를 넉넉히 먹어요.</t>
-  </si>
-  <si>
-    <t>맑은 국과 찜은 찌개보다 덜 짜요.</t>
-  </si>
-  <si>
-    <t>담백한 국은 싱겁게 만들기 쉬워요.</t>
-  </si>
-  <si>
     <t>잡곡밥이나 현미밥은 저녁까지 든든해요.</t>
   </si>
   <si>
@@ -7945,18 +7915,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>아침추천: 미역국/뭇국</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 뭇국/배춧국</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 아욱국/쑥국</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>아침추천: 비빔밥/쌈밥</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -7981,30 +7939,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>아침추천: 북엇국/두부</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>아침추천: 생선/달걀찜</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>아침추천: 맑은 국/죽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>저녁추천: 생선/수육</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>저녁추천: 수육/보쌈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>저녁추천: 백숙/닭곰탕</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>저녁추천: 숙회/수육</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8029,10 +7971,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>저녁추천: 콩국수/백숙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>저녁추천: 두부/생선찜</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8057,18 +7995,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>저녁추천: 된장국/쌈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>저녁추천: 생선찜/냉국</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>저녁추천: 미역국/뭇국</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>저녁추천: 잡곡밥/쌈밥</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8172,21 +8098,6 @@
     <t>쌈 한 접시로 채소를 듬뿍 먹어요.</t>
   </si>
   <si>
-    <t>저녁추천: 지리/생선찜</t>
-  </si>
-  <si>
-    <t>맑은 지리와 찜은 빨간 탕보다 덜 짜요.</t>
-  </si>
-  <si>
-    <t>저녁추천: 백김치/쌈</t>
-  </si>
-  <si>
-    <t>백김치와 쌈은 짠 반찬보다 염분이 적어요.</t>
-  </si>
-  <si>
-    <t>저녁추천: 맑은 국/찜</t>
-  </si>
-  <si>
     <t>저녁추천: 보리밥/쌈밥</t>
   </si>
   <si>
@@ -8196,12 +8107,6 @@
     <t>10-12 저녁추천 확대: 모두 . 합계 197개</t>
   </si>
   <si>
-    <t>아침추천: 시금치국/쌈</t>
-  </si>
-  <si>
-    <t>채소국이나 쌈으로 아침 채소를 챙겨요.</t>
-  </si>
-  <si>
     <t>아침추천: 비빔밥/나물</t>
   </si>
   <si>
@@ -8217,30 +8122,9 @@
     <t>아침추천: 생선/두부</t>
   </si>
   <si>
-    <t>아침추천: 미역국/쑥국</t>
-  </si>
-  <si>
-    <t>아침추천: 백김치/나물</t>
-  </si>
-  <si>
-    <t>백김치와 나물은 짠 반찬보다 염분이 적어요.</t>
-  </si>
-  <si>
     <t>10-12 아침추천 확대: 모두 . 합계 211개</t>
   </si>
   <si>
-    <t>아침추천: 콩나물국/쌈</t>
-  </si>
-  <si>
-    <t>맑은 국이나 쌈으로 아침에도 채소를 먹어요.</t>
-  </si>
-  <si>
-    <t>아침추천: 호박국/나물</t>
-  </si>
-  <si>
-    <t>부드러운 채소 반찬으로 아침을 채워요.</t>
-  </si>
-  <si>
     <t>아침추천: 양배추/오이</t>
   </si>
   <si>
@@ -8290,18 +8174,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>아침추천: 북엇국/달걀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침추천: 북엇국/두유</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>가벼운 국이나 두유로 아침 단백질을 더해요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>아침추천: 달걀찜/생선</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8341,14 +8213,6 @@
     <t>10-12 끼니 추천에서 죽·달걀이 몰린 짝  다른 메뉴로 바꿈(죽  · 달걀  남김)</t>
   </si>
   <si>
-    <t>아침추천: 백김치/생채</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>백김치와 생채는 짠 반찬보다 염분이 적어요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>아침추천: 죽/누룽지 (탄수화물만)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8630,6 +8494,245 @@
   <si>
     <t>연두부를 올리면 샐러드가 든든해져요. 소스는 절반만 뿌려요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 미역국/뭇국 (나트륨 높음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 시금치/오이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데친 시금치나 오이로 국물 없이 채소를 먹어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 뭇국/배춧국 (나트륨 높음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 배추쌈/오이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배추쌈이나 오이로 아삭하게 채소를 챙겨요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 아욱국/쑥국 (나트륨 높음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 애호박/가지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구운 애호박이나 가지로 채소를 더해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 북엇국/두부 (나트륨 높음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 연어/두부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연어나 두부로 국물 없이 단백질을 챙겨요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 백김치/생채 (나트륨 높음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 생채/샐러드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>절이지 않은 생채소라 염분이 적어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 수육/보쌈 (나트륨 높음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 수육/닭찜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삶거나 찐 고기는 기름과 양념이 적어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 백숙/닭곰탕 (나트륨 높음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 백숙/닭구이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삶거나 구운 닭은 기름이 적어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 콩국수/백숙 (나트륨 높음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 두부/백숙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>두부나 백숙으로 담백하게 단백질을 챙겨요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 된장국/쌈 (나트륨 높음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 쌈/나물무침</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쌈이나 나물로 국물 없이 채소를 먹어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 생선찜/냉국 (나트륨 높음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 생선찜/생채</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>찜과 생채는 양념이 적어 덜 짜요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 미역국/뭇국 (나트륨 높음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 두부찜/생채</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>찜과 생채는 찌개보다 훨씬 덜 짜요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 지리/생선찜 (나트륨 높음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 생선/두부찜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>양념이 적은 구이와 찜은 덜 짜요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 백김치/쌈 (나트륨 높음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 생채소/쌈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>절이지 않은 생채소는 염분이 거의 없어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 맑은 국/찜 (나트륨 높음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁추천: 생선찜/구이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>찜과 구이는 국물 요리보다 덜 짜요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 시금치국/쌈 (나트륨 높음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 시금치/쌈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국물 없이 채소를 먹을 수 있어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 북엇국/두유 (나트륨 높음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 닭안심/두유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 미역국/쑥국 (나트륨 높음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 오이/생채</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>절이지 않은 채소는 염분이 적어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 백김치/나물 (나트륨 높음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 무생채/나물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김치 대신 생채와 나물은 염분이 적어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 콩나물국/쌈 (나트륨 높음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 콩나물/쌈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>콩나물무침이나 쌈으로 채소를 챙겨요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 호박국/나물 (나트륨 높음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침추천: 호박/나물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호박이나 나물로 국물 없이 채소를 먹어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10-12 끼니 추천에서 나트륨이 높은 메뉴(국·탕·냉국·콩국수·닭곰탕·김치·보쌈)  국물 없는 메뉴로 바꿈. 국·찌개는 나트륨 주 공급원(국민건강영양조사)이라 끼니 추천에 넣지 않음</t>
   </si>
 </sst>
 </file>
@@ -9116,7 +9219,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F51797-492B-40AC-833D-E19CEF6E9FA5}">
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="120.58203125" style="1" customWidth="1"/>
@@ -9190,72 +9293,77 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>657</v>
+        <v>631</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>668</v>
+        <v>637</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>675</v>
+        <v>640</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>698</v>
+        <v>660</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>698</v>
+        <v>660</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>735</v>
+        <v>695</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>758</v>
+        <v>718</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>768</v>
+        <v>728</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A29" s="1" t="s">
+        <v>792</v>
       </c>
     </row>
   </sheetData>
@@ -9291,7 +9399,7 @@
         <v>53</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>54</v>
@@ -9338,7 +9446,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -9380,7 +9488,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -9422,7 +9530,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -9464,7 +9572,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -9506,7 +9614,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -9518,7 +9626,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>238</v>
@@ -9528,7 +9636,7 @@
         <v>12</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -9548,7 +9656,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -9590,7 +9698,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -9632,7 +9740,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -9674,7 +9782,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -9716,7 +9824,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -9758,7 +9866,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -9770,7 +9878,7 @@
         <v>220</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>244</v>
@@ -9800,7 +9908,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -9842,7 +9950,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -9884,7 +9992,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -9926,7 +10034,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -9938,7 +10046,7 @@
         <v>220</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>248</v>
@@ -9948,7 +10056,7 @@
         <v>11</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>27</v>
@@ -9968,7 +10076,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -10010,7 +10118,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -10052,7 +10160,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>31</v>
@@ -10094,7 +10202,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>31</v>
@@ -10136,7 +10244,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>31</v>
@@ -10178,7 +10286,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1</v>
@@ -10220,7 +10328,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>1</v>
@@ -10262,7 +10370,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>1</v>
@@ -10304,7 +10412,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>1</v>
@@ -10316,7 +10424,7 @@
         <v>220</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>257</v>
@@ -10326,7 +10434,7 @@
         <v>12</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>11</v>
@@ -10346,7 +10454,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>1</v>
@@ -10388,7 +10496,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>1</v>
@@ -10430,7 +10538,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>1</v>
@@ -10472,7 +10580,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>1</v>
@@ -10514,7 +10622,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>1</v>
@@ -10526,7 +10634,7 @@
         <v>12</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>262</v>
@@ -10536,7 +10644,7 @@
         <v>11</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>8</v>
@@ -10556,7 +10664,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>1</v>
@@ -10598,7 +10706,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>1</v>
@@ -10610,7 +10718,7 @@
         <v>220</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>264</v>
@@ -10620,16 +10728,16 @@
         <v>11</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K32" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="L32" s="7" t="s">
         <v>515</v>
-      </c>
-      <c r="L32" s="7" t="s">
-        <v>516</v>
       </c>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
@@ -10640,7 +10748,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>1</v>
@@ -10682,7 +10790,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>1</v>
@@ -10724,7 +10832,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>1</v>
@@ -10766,7 +10874,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>1</v>
@@ -10808,7 +10916,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>1</v>
@@ -10850,7 +10958,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>31</v>
@@ -10862,7 +10970,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>270</v>
@@ -10872,7 +10980,7 @@
         <v>12</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>32</v>
@@ -10892,7 +11000,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>31</v>
@@ -10934,7 +11042,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>1</v>
@@ -10976,7 +11084,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>1</v>
@@ -11018,7 +11126,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>1</v>
@@ -11060,7 +11168,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>1</v>
@@ -11102,7 +11210,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>1</v>
@@ -11144,7 +11252,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>1</v>
@@ -11186,7 +11294,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>1</v>
@@ -11228,7 +11336,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>1</v>
@@ -11240,7 +11348,7 @@
         <v>12</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>279</v>
@@ -11250,7 +11358,7 @@
         <v>12</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>43</v>
@@ -11270,7 +11378,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>1</v>
@@ -11312,7 +11420,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>1</v>
@@ -11354,7 +11462,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>1</v>
@@ -11396,7 +11504,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>1</v>
@@ -11438,7 +11546,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>1</v>
@@ -11450,7 +11558,7 @@
         <v>7</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>284</v>
@@ -11460,7 +11568,7 @@
         <v>9</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>46</v>
@@ -11480,7 +11588,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>1</v>
@@ -11492,7 +11600,7 @@
         <v>12</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>285</v>
@@ -11522,7 +11630,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>1</v>
@@ -11534,7 +11642,7 @@
         <v>3</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>286</v>
@@ -11544,7 +11652,7 @@
         <v>12</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>23</v>
@@ -11564,7 +11672,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>1</v>
@@ -11606,7 +11714,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>1</v>
@@ -11648,7 +11756,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>1</v>
@@ -11690,7 +11798,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>1</v>
@@ -11702,7 +11810,7 @@
         <v>7</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>290</v>
@@ -11712,7 +11820,7 @@
         <v>10</v>
       </c>
       <c r="I58" s="7" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>49</v>
@@ -11732,7 +11840,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>1</v>
@@ -11774,7 +11882,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>1</v>
@@ -11816,7 +11924,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>1</v>
@@ -11858,7 +11966,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>1</v>
@@ -11900,7 +12008,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>31</v>
@@ -11942,7 +12050,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>31</v>
@@ -11984,7 +12092,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>144</v>
@@ -11996,7 +12104,7 @@
         <v>146</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="G65" s="5" t="s">
         <v>296</v>
@@ -12006,7 +12114,7 @@
         <v>10</v>
       </c>
       <c r="I65" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>147</v>
@@ -12026,7 +12134,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>144</v>
@@ -12068,7 +12176,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>144</v>
@@ -12080,7 +12188,7 @@
         <v>146</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>299</v>
@@ -12090,7 +12198,7 @@
         <v>12</v>
       </c>
       <c r="I67" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="J67" s="3" t="s">
         <v>151</v>
@@ -12110,7 +12218,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>144</v>
@@ -12152,7 +12260,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>144</v>
@@ -12194,7 +12302,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>144</v>
@@ -12236,7 +12344,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>144</v>
@@ -12278,7 +12386,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>144</v>
@@ -12320,7 +12428,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>144</v>
@@ -12362,7 +12470,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>144</v>
@@ -12404,7 +12512,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>144</v>
@@ -12446,7 +12554,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>144</v>
@@ -12488,7 +12596,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>144</v>
@@ -12530,7 +12638,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>144</v>
@@ -12572,7 +12680,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>144</v>
@@ -12614,7 +12722,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>144</v>
@@ -12656,7 +12764,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>144</v>
@@ -12698,7 +12806,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>144</v>
@@ -12740,7 +12848,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>144</v>
@@ -12782,7 +12890,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>144</v>
@@ -12824,7 +12932,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>144</v>
@@ -12836,7 +12944,7 @@
         <v>146</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="G85" s="5" t="s">
         <v>332</v>
@@ -12846,7 +12954,7 @@
         <v>11</v>
       </c>
       <c r="I85" s="7" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="J85" s="3" t="s">
         <v>187</v>
@@ -12866,7 +12974,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>144</v>
@@ -12908,7 +13016,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>144</v>
@@ -12950,7 +13058,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>144</v>
@@ -12992,7 +13100,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>144</v>
@@ -13034,7 +13142,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>144</v>
@@ -13076,7 +13184,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>144</v>
@@ -13118,7 +13226,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>144</v>
@@ -13160,7 +13268,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>144</v>
@@ -13202,7 +13310,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>144</v>
@@ -13214,7 +13322,7 @@
         <v>146</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G94" s="5" t="s">
         <v>346</v>
@@ -13224,7 +13332,7 @@
         <v>12</v>
       </c>
       <c r="I94" s="7" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>198</v>
@@ -13244,7 +13352,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>144</v>
@@ -13256,7 +13364,7 @@
         <v>146</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G95" s="5" t="s">
         <v>347</v>
@@ -13266,7 +13374,7 @@
         <v>12</v>
       </c>
       <c r="I95" s="7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="J95" s="3" t="s">
         <v>200</v>
@@ -13286,7 +13394,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>144</v>
@@ -13328,7 +13436,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>144</v>
@@ -13370,7 +13478,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>144</v>
@@ -13412,7 +13520,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>144</v>
@@ -13454,7 +13562,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>144</v>
@@ -13496,7 +13604,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>144</v>
@@ -13538,7 +13646,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>144</v>
@@ -13580,7 +13688,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>144</v>
@@ -13622,7 +13730,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>144</v>
@@ -13634,7 +13742,7 @@
         <v>146</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G104" s="5" t="s">
         <v>362</v>
@@ -13644,7 +13752,7 @@
         <v>9</v>
       </c>
       <c r="I104" s="7" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="J104" s="3" t="s">
         <v>210</v>
@@ -13664,7 +13772,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>144</v>
@@ -13706,7 +13814,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>144</v>
@@ -13748,7 +13856,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>144</v>
@@ -13790,7 +13898,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>144</v>
@@ -13832,7 +13940,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>144</v>
@@ -13874,7 +13982,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>144</v>
@@ -13886,7 +13994,7 @@
         <v>146</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="G110" s="5" t="s">
         <v>462</v>
@@ -13896,7 +14004,7 @@
         <v>10</v>
       </c>
       <c r="I110" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="J110" s="3" t="s">
         <v>216</v>
@@ -13916,7 +14024,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>144</v>
@@ -13958,7 +14066,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>144</v>
@@ -14000,7 +14108,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C113" s="7" t="s">
         <v>144</v>
@@ -14042,7 +14150,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C114" s="7" t="s">
         <v>144</v>
@@ -14084,7 +14192,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C115" s="7" t="s">
         <v>144</v>
@@ -14126,7 +14234,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C116" s="7" t="s">
         <v>144</v>
@@ -14168,7 +14276,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C117" s="7" t="s">
         <v>144</v>
@@ -14210,7 +14318,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C118" s="7" t="s">
         <v>144</v>
@@ -14252,7 +14360,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C119" s="7" t="s">
         <v>386</v>
@@ -14294,7 +14402,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C120" s="7" t="s">
         <v>144</v>
@@ -14306,7 +14414,7 @@
         <v>146</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G120" s="7" t="s">
         <v>0</v>
@@ -14336,7 +14444,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C121" s="7" t="s">
         <v>144</v>
@@ -14348,7 +14456,7 @@
         <v>146</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G121" s="7" t="s">
         <v>0</v>
@@ -14358,7 +14466,7 @@
         <v>12</v>
       </c>
       <c r="I121" s="7" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="J121" s="7" t="s">
         <v>155</v>
@@ -14378,7 +14486,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C122" s="7" t="s">
         <v>144</v>
@@ -14390,7 +14498,7 @@
         <v>146</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G122" s="7" t="s">
         <v>0</v>
@@ -14400,7 +14508,7 @@
         <v>11</v>
       </c>
       <c r="I122" s="7" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="J122" s="7" t="s">
         <v>163</v>
@@ -14420,7 +14528,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C123" s="7" t="s">
         <v>144</v>
@@ -14432,7 +14540,7 @@
         <v>146</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G123" s="7" t="s">
         <v>0</v>
@@ -14442,7 +14550,7 @@
         <v>10</v>
       </c>
       <c r="I123" s="7" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="J123" s="7" t="s">
         <v>161</v>
@@ -14462,7 +14570,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C124" s="7" t="s">
         <v>144</v>
@@ -14474,7 +14582,7 @@
         <v>146</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G124" s="7" t="s">
         <v>0</v>
@@ -14484,7 +14592,7 @@
         <v>11</v>
       </c>
       <c r="I124" s="7" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="J124" s="7" t="s">
         <v>161</v>
@@ -14504,7 +14612,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C125" s="7" t="s">
         <v>144</v>
@@ -14516,7 +14624,7 @@
         <v>146</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G125" s="7" t="s">
         <v>0</v>
@@ -14526,7 +14634,7 @@
         <v>9</v>
       </c>
       <c r="I125" s="7" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J125" s="7" t="s">
         <v>210</v>
@@ -14546,7 +14654,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C126" s="7" t="s">
         <v>144</v>
@@ -14558,7 +14666,7 @@
         <v>146</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G126" s="7" t="s">
         <v>0</v>
@@ -14568,7 +14676,7 @@
         <v>11</v>
       </c>
       <c r="I126" s="7" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J126" s="7" t="s">
         <v>210</v>
@@ -14588,7 +14696,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C127" s="7" t="s">
         <v>144</v>
@@ -14600,7 +14708,7 @@
         <v>146</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G127" s="7" t="s">
         <v>0</v>
@@ -14610,7 +14718,7 @@
         <v>10</v>
       </c>
       <c r="I127" s="7" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="J127" s="7" t="s">
         <v>210</v>
@@ -14630,7 +14738,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C128" s="7" t="s">
         <v>144</v>
@@ -14642,7 +14750,7 @@
         <v>146</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G128" s="7" t="s">
         <v>0</v>
@@ -14652,7 +14760,7 @@
         <v>9</v>
       </c>
       <c r="I128" s="7" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="J128" s="7" t="s">
         <v>171</v>
@@ -14672,7 +14780,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C129" s="7" t="s">
         <v>144</v>
@@ -14684,7 +14792,7 @@
         <v>146</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G129" s="7" t="s">
         <v>0</v>
@@ -14694,7 +14802,7 @@
         <v>9</v>
       </c>
       <c r="I129" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="J129" s="7" t="s">
         <v>171</v>
@@ -14714,7 +14822,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C130" s="7" t="s">
         <v>144</v>
@@ -14726,7 +14834,7 @@
         <v>146</v>
       </c>
       <c r="F130" s="7" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G130" s="7" t="s">
         <v>0</v>
@@ -14736,7 +14844,7 @@
         <v>11</v>
       </c>
       <c r="I130" s="7" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="J130" s="7" t="s">
         <v>171</v>
@@ -14756,7 +14864,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>144</v>
@@ -14768,7 +14876,7 @@
         <v>146</v>
       </c>
       <c r="F131" s="7" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G131" s="7" t="s">
         <v>0</v>
@@ -14778,7 +14886,7 @@
         <v>9</v>
       </c>
       <c r="I131" s="7" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="J131" s="7" t="s">
         <v>187</v>
@@ -14798,7 +14906,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>144</v>
@@ -14810,7 +14918,7 @@
         <v>146</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G132" s="7" t="s">
         <v>0</v>
@@ -14820,7 +14928,7 @@
         <v>8</v>
       </c>
       <c r="I132" s="7" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J132" s="7" t="s">
         <v>187</v>
@@ -14840,7 +14948,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C133" s="7" t="s">
         <v>144</v>
@@ -14852,7 +14960,7 @@
         <v>146</v>
       </c>
       <c r="F133" s="7" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G133" s="7" t="s">
         <v>0</v>
@@ -14862,7 +14970,7 @@
         <v>11</v>
       </c>
       <c r="I133" s="7" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="J133" s="7" t="s">
         <v>215</v>
@@ -14882,7 +14990,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>144</v>
@@ -14894,7 +15002,7 @@
         <v>146</v>
       </c>
       <c r="F134" s="7" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G134" s="7" t="s">
         <v>0</v>
@@ -14904,7 +15012,7 @@
         <v>9</v>
       </c>
       <c r="I134" s="7" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="J134" s="7" t="s">
         <v>215</v>
@@ -14924,7 +15032,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>144</v>
@@ -14936,7 +15044,7 @@
         <v>146</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G135" s="7" t="s">
         <v>0</v>
@@ -14946,10 +15054,10 @@
         <v>11</v>
       </c>
       <c r="I135" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="J135" s="7" t="s">
         <v>497</v>
-      </c>
-      <c r="J135" s="7" t="s">
-        <v>498</v>
       </c>
       <c r="K135" s="7" t="s">
         <v>156</v>
@@ -14966,7 +15074,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C136" s="7" t="s">
         <v>144</v>
@@ -14978,7 +15086,7 @@
         <v>146</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G136" s="7" t="s">
         <v>0</v>
@@ -14988,10 +15096,10 @@
         <v>11</v>
       </c>
       <c r="I136" s="7" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="J136" s="7" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K136" s="7" t="s">
         <v>156</v>
@@ -15008,7 +15116,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C137" s="7" t="s">
         <v>144</v>
@@ -15020,7 +15128,7 @@
         <v>146</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G137" s="7" t="s">
         <v>0</v>
@@ -15030,7 +15138,7 @@
         <v>12</v>
       </c>
       <c r="I137" s="7" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="J137" s="7" t="s">
         <v>200</v>
@@ -15050,7 +15158,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C138" s="7" t="s">
         <v>144</v>
@@ -15062,7 +15170,7 @@
         <v>146</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G138" s="7" t="s">
         <v>0</v>
@@ -15072,7 +15180,7 @@
         <v>9</v>
       </c>
       <c r="I138" s="7" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="J138" s="7" t="s">
         <v>203</v>
@@ -15092,7 +15200,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C139" s="7" t="s">
         <v>144</v>
@@ -15104,17 +15212,17 @@
         <v>146</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G139" s="7" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H139" s="7">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="I139" s="7" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="J139" s="7" t="s">
         <v>200</v>
@@ -15134,7 +15242,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C140" s="7" t="s">
         <v>144</v>
@@ -15146,20 +15254,20 @@
         <v>146</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>702</v>
+        <v>662</v>
       </c>
       <c r="G140" s="7" t="s">
-        <v>701</v>
+        <v>661</v>
       </c>
       <c r="H140" s="7">
         <f t="shared" ref="H140:H177" si="5">LEN(F140)</f>
         <v>12</v>
       </c>
       <c r="I140" s="7" t="s">
-        <v>703</v>
+        <v>663</v>
       </c>
       <c r="J140" s="7" t="s">
-        <v>704</v>
+        <v>664</v>
       </c>
       <c r="K140" s="7" t="s">
         <v>464</v>
@@ -15176,7 +15284,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C141" s="7" t="s">
         <v>144</v>
@@ -15188,20 +15296,20 @@
         <v>146</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>706</v>
+        <v>666</v>
       </c>
       <c r="G141" s="7" t="s">
-        <v>705</v>
+        <v>665</v>
       </c>
       <c r="H141" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I141" s="7" t="s">
-        <v>707</v>
+        <v>667</v>
       </c>
       <c r="J141" s="7" t="s">
-        <v>704</v>
+        <v>664</v>
       </c>
       <c r="K141" s="7" t="s">
         <v>464</v>
@@ -15218,7 +15326,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C142" s="7" t="s">
         <v>144</v>
@@ -15230,20 +15338,20 @@
         <v>146</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>709</v>
+        <v>669</v>
       </c>
       <c r="G142" s="7" t="s">
-        <v>708</v>
+        <v>668</v>
       </c>
       <c r="H142" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I142" s="7" t="s">
-        <v>710</v>
+        <v>670</v>
       </c>
       <c r="J142" s="7" t="s">
-        <v>704</v>
+        <v>664</v>
       </c>
       <c r="K142" s="7" t="s">
         <v>464</v>
@@ -15260,7 +15368,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C143" s="7" t="s">
         <v>144</v>
@@ -15272,20 +15380,20 @@
         <v>146</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>712</v>
+        <v>672</v>
       </c>
       <c r="G143" s="7" t="s">
-        <v>711</v>
+        <v>671</v>
       </c>
       <c r="H143" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I143" s="7" t="s">
-        <v>713</v>
+        <v>673</v>
       </c>
       <c r="J143" s="7" t="s">
-        <v>704</v>
+        <v>664</v>
       </c>
       <c r="K143" s="7" t="s">
         <v>464</v>
@@ -15302,7 +15410,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C144" s="7" t="s">
         <v>144</v>
@@ -15314,20 +15422,20 @@
         <v>146</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>715</v>
+        <v>675</v>
       </c>
       <c r="G144" s="7" t="s">
-        <v>714</v>
+        <v>674</v>
       </c>
       <c r="H144" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I144" s="7" t="s">
-        <v>716</v>
+        <v>676</v>
       </c>
       <c r="J144" s="7" t="s">
-        <v>704</v>
+        <v>664</v>
       </c>
       <c r="K144" s="7" t="s">
         <v>464</v>
@@ -15339,12 +15447,12 @@
       <c r="N144" s="3"/>
       <c r="O144" s="3"/>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A145" s="7">
         <v>144</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C145" s="7" t="s">
         <v>144</v>
@@ -15356,17 +15464,17 @@
         <v>146</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>585</v>
+        <v>734</v>
       </c>
       <c r="G145" s="7" t="s">
-        <v>0</v>
+        <v>733</v>
       </c>
       <c r="H145" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I145" s="7" t="s">
-        <v>554</v>
+        <v>735</v>
       </c>
       <c r="J145" s="7" t="s">
         <v>161</v>
@@ -15381,12 +15489,12 @@
       <c r="N145" s="3"/>
       <c r="O145" s="3"/>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A146" s="7">
         <v>145</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C146" s="7" t="s">
         <v>144</v>
@@ -15398,17 +15506,17 @@
         <v>146</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>586</v>
+        <v>737</v>
       </c>
       <c r="G146" s="7" t="s">
-        <v>0</v>
+        <v>736</v>
       </c>
       <c r="H146" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I146" s="7" t="s">
-        <v>555</v>
+        <v>738</v>
       </c>
       <c r="J146" s="7" t="s">
         <v>161</v>
@@ -15423,12 +15531,12 @@
       <c r="N146" s="3"/>
       <c r="O146" s="3"/>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A147" s="7">
         <v>146</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C147" s="7" t="s">
         <v>144</v>
@@ -15440,17 +15548,17 @@
         <v>146</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>587</v>
+        <v>740</v>
       </c>
       <c r="G147" s="7" t="s">
-        <v>0</v>
+        <v>739</v>
       </c>
       <c r="H147" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>556</v>
+        <v>741</v>
       </c>
       <c r="J147" s="7" t="s">
         <v>161</v>
@@ -15470,7 +15578,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C148" s="7" t="s">
         <v>144</v>
@@ -15482,7 +15590,7 @@
         <v>146</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>588</v>
+        <v>575</v>
       </c>
       <c r="G148" s="7" t="s">
         <v>0</v>
@@ -15492,7 +15600,7 @@
         <v>12</v>
       </c>
       <c r="I148" s="7" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="J148" s="7" t="s">
         <v>161</v>
@@ -15512,7 +15620,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C149" s="7" t="s">
         <v>144</v>
@@ -15524,17 +15632,17 @@
         <v>146</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>759</v>
+        <v>719</v>
       </c>
       <c r="G149" s="7" t="s">
-        <v>736</v>
+        <v>696</v>
       </c>
       <c r="H149" s="7">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>741</v>
+        <v>701</v>
       </c>
       <c r="J149" s="7" t="s">
         <v>161</v>
@@ -15554,7 +15662,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C150" s="7" t="s">
         <v>144</v>
@@ -15566,7 +15674,7 @@
         <v>146</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="G150" s="7" t="s">
         <v>0</v>
@@ -15576,7 +15684,7 @@
         <v>12</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="J150" s="7" t="s">
         <v>210</v>
@@ -15596,7 +15704,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C151" s="7" t="s">
         <v>144</v>
@@ -15608,7 +15716,7 @@
         <v>146</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="G151" s="7" t="s">
         <v>0</v>
@@ -15618,7 +15726,7 @@
         <v>12</v>
       </c>
       <c r="I151" s="7" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="J151" s="7" t="s">
         <v>210</v>
@@ -15638,7 +15746,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C152" s="7" t="s">
         <v>144</v>
@@ -15650,7 +15758,7 @@
         <v>146</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>591</v>
+        <v>578</v>
       </c>
       <c r="G152" s="7" t="s">
         <v>0</v>
@@ -15660,7 +15768,7 @@
         <v>11</v>
       </c>
       <c r="I152" s="7" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="J152" s="7" t="s">
         <v>210</v>
@@ -15680,7 +15788,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C153" s="7" t="s">
         <v>144</v>
@@ -15692,7 +15800,7 @@
         <v>146</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>592</v>
+        <v>579</v>
       </c>
       <c r="G153" s="7" t="s">
         <v>0</v>
@@ -15702,7 +15810,7 @@
         <v>11</v>
       </c>
       <c r="I153" s="7" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="J153" s="7" t="s">
         <v>210</v>
@@ -15722,7 +15830,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C154" s="7" t="s">
         <v>144</v>
@@ -15734,17 +15842,17 @@
         <v>146</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>679</v>
+        <v>644</v>
       </c>
       <c r="G154" s="7" t="s">
-        <v>593</v>
+        <v>580</v>
       </c>
       <c r="H154" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I154" s="7" t="s">
-        <v>680</v>
+        <v>645</v>
       </c>
       <c r="J154" s="7" t="s">
         <v>210</v>
@@ -15759,12 +15867,12 @@
       <c r="N154" s="3"/>
       <c r="O154" s="3"/>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A155" s="7">
         <v>154</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C155" s="7" t="s">
         <v>144</v>
@@ -15776,17 +15884,17 @@
         <v>146</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>594</v>
+        <v>743</v>
       </c>
       <c r="G155" s="7" t="s">
-        <v>0</v>
+        <v>742</v>
       </c>
       <c r="H155" s="7">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I155" s="7" t="s">
-        <v>562</v>
+        <v>744</v>
       </c>
       <c r="J155" s="7" t="s">
         <v>210</v>
@@ -15806,7 +15914,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C156" s="7" t="s">
         <v>144</v>
@@ -15818,17 +15926,17 @@
         <v>146</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>681</v>
+        <v>646</v>
       </c>
       <c r="G156" s="7" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="H156" s="7">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="I156" s="7" t="s">
-        <v>682</v>
+        <v>647</v>
       </c>
       <c r="J156" s="7" t="s">
         <v>215</v>
@@ -15843,12 +15951,12 @@
       <c r="N156" s="3"/>
       <c r="O156" s="3"/>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A157" s="7">
         <v>156</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C157" s="7" t="s">
         <v>144</v>
@@ -15860,17 +15968,17 @@
         <v>146</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>699</v>
+        <v>746</v>
       </c>
       <c r="G157" s="7" t="s">
-        <v>596</v>
+        <v>745</v>
       </c>
       <c r="H157" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I157" s="7" t="s">
-        <v>700</v>
+        <v>747</v>
       </c>
       <c r="J157" s="7" t="s">
         <v>187</v>
@@ -15890,7 +15998,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C158" s="7" t="s">
         <v>144</v>
@@ -15902,7 +16010,7 @@
         <v>146</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>597</v>
+        <v>582</v>
       </c>
       <c r="G158" s="7" t="s">
         <v>0</v>
@@ -15912,13 +16020,13 @@
         <v>11</v>
       </c>
       <c r="I158" s="7" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="J158" s="7" t="s">
         <v>215</v>
       </c>
       <c r="K158" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L158" s="7" t="s">
         <v>149</v>
@@ -15932,7 +16040,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C159" s="7" t="s">
         <v>144</v>
@@ -15944,23 +16052,23 @@
         <v>146</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>598</v>
+        <v>749</v>
       </c>
       <c r="G159" s="7" t="s">
-        <v>0</v>
+        <v>748</v>
       </c>
       <c r="H159" s="7">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="I159" s="7" t="s">
-        <v>565</v>
+        <v>750</v>
       </c>
       <c r="J159" s="7" t="s">
         <v>215</v>
       </c>
       <c r="K159" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L159" s="7" t="s">
         <v>149</v>
@@ -15969,12 +16077,12 @@
       <c r="N159" s="3"/>
       <c r="O159" s="3"/>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A160" s="7">
         <v>159</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C160" s="7" t="s">
         <v>144</v>
@@ -15986,23 +16094,23 @@
         <v>146</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>599</v>
+        <v>752</v>
       </c>
       <c r="G160" s="7" t="s">
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="H160" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I160" s="7" t="s">
-        <v>227</v>
+        <v>753</v>
       </c>
       <c r="J160" s="7" t="s">
         <v>215</v>
       </c>
       <c r="K160" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L160" s="7" t="s">
         <v>149</v>
@@ -16016,7 +16124,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C161" s="7" t="s">
         <v>144</v>
@@ -16028,7 +16136,7 @@
         <v>146</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>600</v>
+        <v>583</v>
       </c>
       <c r="G161" s="7" t="s">
         <v>0</v>
@@ -16038,13 +16146,13 @@
         <v>11</v>
       </c>
       <c r="I161" s="7" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="J161" s="7" t="s">
         <v>215</v>
       </c>
       <c r="K161" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L161" s="7" t="s">
         <v>149</v>
@@ -16058,7 +16166,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C162" s="7" t="s">
         <v>144</v>
@@ -16070,7 +16178,7 @@
         <v>146</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>601</v>
+        <v>584</v>
       </c>
       <c r="G162" s="7" t="s">
         <v>0</v>
@@ -16080,13 +16188,13 @@
         <v>12</v>
       </c>
       <c r="I162" s="7" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="J162" s="7" t="s">
         <v>215</v>
       </c>
       <c r="K162" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L162" s="7" t="s">
         <v>149</v>
@@ -16100,7 +16208,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C163" s="7" t="s">
         <v>144</v>
@@ -16112,7 +16220,7 @@
         <v>146</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>602</v>
+        <v>585</v>
       </c>
       <c r="G163" s="7" t="s">
         <v>0</v>
@@ -16122,13 +16230,13 @@
         <v>11</v>
       </c>
       <c r="I163" s="7" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="J163" s="7" t="s">
         <v>215</v>
       </c>
       <c r="K163" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L163" s="7" t="s">
         <v>149</v>
@@ -16142,7 +16250,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C164" s="7" t="s">
         <v>144</v>
@@ -16154,7 +16262,7 @@
         <v>146</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="G164" s="7" t="s">
         <v>0</v>
@@ -16164,13 +16272,13 @@
         <v>12</v>
       </c>
       <c r="I164" s="7" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="J164" s="7" t="s">
         <v>210</v>
       </c>
       <c r="K164" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L164" s="7" t="s">
         <v>149</v>
@@ -16184,7 +16292,7 @@
         <v>164</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C165" s="7" t="s">
         <v>144</v>
@@ -16196,7 +16304,7 @@
         <v>146</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>604</v>
+        <v>587</v>
       </c>
       <c r="G165" s="7" t="s">
         <v>0</v>
@@ -16206,13 +16314,13 @@
         <v>12</v>
       </c>
       <c r="I165" s="7" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="J165" s="7" t="s">
         <v>210</v>
       </c>
       <c r="K165" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L165" s="7" t="s">
         <v>149</v>
@@ -16226,7 +16334,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C166" s="7" t="s">
         <v>144</v>
@@ -16238,7 +16346,7 @@
         <v>146</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="G166" s="7" t="s">
         <v>0</v>
@@ -16248,13 +16356,13 @@
         <v>12</v>
       </c>
       <c r="I166" s="7" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="J166" s="7" t="s">
         <v>210</v>
       </c>
       <c r="K166" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L166" s="7" t="s">
         <v>149</v>
@@ -16263,12 +16371,12 @@
       <c r="N166" s="3"/>
       <c r="O166" s="3"/>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A167" s="7">
         <v>166</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C167" s="7" t="s">
         <v>144</v>
@@ -16280,23 +16388,23 @@
         <v>146</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>606</v>
+        <v>755</v>
       </c>
       <c r="G167" s="7" t="s">
-        <v>0</v>
+        <v>754</v>
       </c>
       <c r="H167" s="7">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I167" s="7" t="s">
-        <v>572</v>
+        <v>756</v>
       </c>
       <c r="J167" s="7" t="s">
         <v>210</v>
       </c>
       <c r="K167" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L167" s="7" t="s">
         <v>149</v>
@@ -16310,7 +16418,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C168" s="7" t="s">
         <v>144</v>
@@ -16322,7 +16430,7 @@
         <v>146</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>607</v>
+        <v>589</v>
       </c>
       <c r="G168" s="7" t="s">
         <v>0</v>
@@ -16332,13 +16440,13 @@
         <v>12</v>
       </c>
       <c r="I168" s="7" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="J168" s="7" t="s">
         <v>210</v>
       </c>
       <c r="K168" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L168" s="7" t="s">
         <v>149</v>
@@ -16352,7 +16460,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C169" s="7" t="s">
         <v>144</v>
@@ -16364,7 +16472,7 @@
         <v>146</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>608</v>
+        <v>590</v>
       </c>
       <c r="G169" s="7" t="s">
         <v>0</v>
@@ -16374,13 +16482,13 @@
         <v>12</v>
       </c>
       <c r="I169" s="7" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="J169" s="7" t="s">
         <v>161</v>
       </c>
       <c r="K169" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L169" s="7" t="s">
         <v>149</v>
@@ -16394,7 +16502,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C170" s="7" t="s">
         <v>144</v>
@@ -16406,7 +16514,7 @@
         <v>146</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>609</v>
+        <v>591</v>
       </c>
       <c r="G170" s="7" t="s">
         <v>0</v>
@@ -16416,13 +16524,13 @@
         <v>12</v>
       </c>
       <c r="I170" s="7" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J170" s="7" t="s">
         <v>161</v>
       </c>
       <c r="K170" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L170" s="7" t="s">
         <v>149</v>
@@ -16436,7 +16544,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C171" s="7" t="s">
         <v>144</v>
@@ -16448,7 +16556,7 @@
         <v>146</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>610</v>
+        <v>592</v>
       </c>
       <c r="G171" s="7" t="s">
         <v>0</v>
@@ -16458,13 +16566,13 @@
         <v>11</v>
       </c>
       <c r="I171" s="7" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="J171" s="7" t="s">
         <v>161</v>
       </c>
       <c r="K171" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L171" s="7" t="s">
         <v>149</v>
@@ -16478,7 +16586,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C172" s="7" t="s">
         <v>144</v>
@@ -16490,7 +16598,7 @@
         <v>146</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>611</v>
+        <v>593</v>
       </c>
       <c r="G172" s="7" t="s">
         <v>0</v>
@@ -16500,13 +16608,13 @@
         <v>11</v>
       </c>
       <c r="I172" s="7" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="J172" s="7" t="s">
         <v>161</v>
       </c>
       <c r="K172" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L172" s="7" t="s">
         <v>149</v>
@@ -16520,7 +16628,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C173" s="7" t="s">
         <v>144</v>
@@ -16532,7 +16640,7 @@
         <v>146</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>612</v>
+        <v>594</v>
       </c>
       <c r="G173" s="7" t="s">
         <v>0</v>
@@ -16542,13 +16650,13 @@
         <v>12</v>
       </c>
       <c r="I173" s="7" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="J173" s="7" t="s">
         <v>161</v>
       </c>
       <c r="K173" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L173" s="7" t="s">
         <v>149</v>
@@ -16562,7 +16670,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C174" s="7" t="s">
         <v>144</v>
@@ -16574,23 +16682,23 @@
         <v>146</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>613</v>
+        <v>758</v>
       </c>
       <c r="G174" s="7" t="s">
-        <v>0</v>
+        <v>757</v>
       </c>
       <c r="H174" s="7">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I174" s="7" t="s">
-        <v>579</v>
+        <v>759</v>
       </c>
       <c r="J174" s="7" t="s">
         <v>161</v>
       </c>
       <c r="K174" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L174" s="7" t="s">
         <v>149</v>
@@ -16599,12 +16707,12 @@
       <c r="N174" s="3"/>
       <c r="O174" s="3"/>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A175" s="7">
         <v>174</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C175" s="7" t="s">
         <v>144</v>
@@ -16616,23 +16724,23 @@
         <v>146</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>614</v>
+        <v>761</v>
       </c>
       <c r="G175" s="7" t="s">
-        <v>0</v>
+        <v>760</v>
       </c>
       <c r="H175" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I175" s="7" t="s">
-        <v>580</v>
+        <v>762</v>
       </c>
       <c r="J175" s="7" t="s">
         <v>187</v>
       </c>
       <c r="K175" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L175" s="7" t="s">
         <v>149</v>
@@ -16641,12 +16749,12 @@
       <c r="N175" s="3"/>
       <c r="O175" s="3"/>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A176" s="7">
         <v>175</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C176" s="7" t="s">
         <v>144</v>
@@ -16658,23 +16766,23 @@
         <v>146</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>615</v>
+        <v>764</v>
       </c>
       <c r="G176" s="7" t="s">
-        <v>0</v>
+        <v>763</v>
       </c>
       <c r="H176" s="7">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="I176" s="7" t="s">
-        <v>581</v>
+        <v>765</v>
       </c>
       <c r="J176" s="7" t="s">
         <v>187</v>
       </c>
       <c r="K176" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L176" s="7" t="s">
         <v>149</v>
@@ -16688,7 +16796,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C177" s="7" t="s">
         <v>144</v>
@@ -16700,7 +16808,7 @@
         <v>146</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>616</v>
+        <v>595</v>
       </c>
       <c r="G177" s="7" t="s">
         <v>0</v>
@@ -16710,13 +16818,13 @@
         <v>12</v>
       </c>
       <c r="I177" s="7" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="J177" s="7" t="s">
         <v>155</v>
       </c>
       <c r="K177" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L177" s="7" t="s">
         <v>149</v>
@@ -16730,7 +16838,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C178" s="7" t="s">
         <v>144</v>
@@ -16742,7 +16850,7 @@
         <v>146</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
       <c r="G178" s="7" t="s">
         <v>0</v>
@@ -16752,13 +16860,13 @@
         <v>11</v>
       </c>
       <c r="I178" s="7" t="s">
-        <v>619</v>
+        <v>598</v>
       </c>
       <c r="J178" s="7" t="s">
         <v>215</v>
       </c>
       <c r="K178" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L178" s="7" t="s">
         <v>149</v>
@@ -16772,7 +16880,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C179" s="7" t="s">
         <v>144</v>
@@ -16784,7 +16892,7 @@
         <v>146</v>
       </c>
       <c r="F179" s="7" t="s">
-        <v>620</v>
+        <v>599</v>
       </c>
       <c r="G179" s="7" t="s">
         <v>0</v>
@@ -16794,13 +16902,13 @@
         <v>12</v>
       </c>
       <c r="I179" s="7" t="s">
-        <v>621</v>
+        <v>600</v>
       </c>
       <c r="J179" s="7" t="s">
         <v>215</v>
       </c>
       <c r="K179" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L179" s="7" t="s">
         <v>149</v>
@@ -16814,7 +16922,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C180" s="7" t="s">
         <v>144</v>
@@ -16826,7 +16934,7 @@
         <v>146</v>
       </c>
       <c r="F180" s="7" t="s">
-        <v>622</v>
+        <v>601</v>
       </c>
       <c r="G180" s="7" t="s">
         <v>0</v>
@@ -16836,13 +16944,13 @@
         <v>12</v>
       </c>
       <c r="I180" s="7" t="s">
-        <v>623</v>
+        <v>602</v>
       </c>
       <c r="J180" s="7" t="s">
         <v>215</v>
       </c>
       <c r="K180" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L180" s="7" t="s">
         <v>149</v>
@@ -16856,7 +16964,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C181" s="7" t="s">
         <v>144</v>
@@ -16868,7 +16976,7 @@
         <v>146</v>
       </c>
       <c r="F181" s="7" t="s">
-        <v>624</v>
+        <v>603</v>
       </c>
       <c r="G181" s="7" t="s">
         <v>0</v>
@@ -16878,13 +16986,13 @@
         <v>12</v>
       </c>
       <c r="I181" s="7" t="s">
-        <v>625</v>
+        <v>604</v>
       </c>
       <c r="J181" s="7" t="s">
         <v>215</v>
       </c>
       <c r="K181" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L181" s="7" t="s">
         <v>149</v>
@@ -16898,7 +17006,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C182" s="7" t="s">
         <v>144</v>
@@ -16910,7 +17018,7 @@
         <v>146</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>626</v>
+        <v>605</v>
       </c>
       <c r="G182" s="7" t="s">
         <v>0</v>
@@ -16920,13 +17028,13 @@
         <v>12</v>
       </c>
       <c r="I182" s="7" t="s">
-        <v>627</v>
+        <v>606</v>
       </c>
       <c r="J182" s="7" t="s">
         <v>215</v>
       </c>
       <c r="K182" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L182" s="7" t="s">
         <v>149</v>
@@ -16940,7 +17048,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C183" s="7" t="s">
         <v>144</v>
@@ -16952,7 +17060,7 @@
         <v>146</v>
       </c>
       <c r="F183" s="7" t="s">
-        <v>628</v>
+        <v>607</v>
       </c>
       <c r="G183" s="7" t="s">
         <v>0</v>
@@ -16962,13 +17070,13 @@
         <v>12</v>
       </c>
       <c r="I183" s="7" t="s">
-        <v>629</v>
+        <v>608</v>
       </c>
       <c r="J183" s="7" t="s">
         <v>210</v>
       </c>
       <c r="K183" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L183" s="7" t="s">
         <v>149</v>
@@ -16982,7 +17090,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C184" s="7" t="s">
         <v>144</v>
@@ -16994,7 +17102,7 @@
         <v>146</v>
       </c>
       <c r="F184" s="7" t="s">
-        <v>630</v>
+        <v>609</v>
       </c>
       <c r="G184" s="7" t="s">
         <v>0</v>
@@ -17004,13 +17112,13 @@
         <v>11</v>
       </c>
       <c r="I184" s="7" t="s">
-        <v>631</v>
+        <v>610</v>
       </c>
       <c r="J184" s="7" t="s">
         <v>210</v>
       </c>
       <c r="K184" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L184" s="7" t="s">
         <v>149</v>
@@ -17024,7 +17132,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C185" s="7" t="s">
         <v>144</v>
@@ -17036,7 +17144,7 @@
         <v>146</v>
       </c>
       <c r="F185" s="7" t="s">
-        <v>632</v>
+        <v>611</v>
       </c>
       <c r="G185" s="7" t="s">
         <v>0</v>
@@ -17046,13 +17154,13 @@
         <v>11</v>
       </c>
       <c r="I185" s="7" t="s">
-        <v>633</v>
+        <v>612</v>
       </c>
       <c r="J185" s="7" t="s">
         <v>210</v>
       </c>
       <c r="K185" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L185" s="7" t="s">
         <v>149</v>
@@ -17066,7 +17174,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C186" s="7" t="s">
         <v>144</v>
@@ -17078,7 +17186,7 @@
         <v>146</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>634</v>
+        <v>613</v>
       </c>
       <c r="G186" s="7" t="s">
         <v>0</v>
@@ -17088,13 +17196,13 @@
         <v>12</v>
       </c>
       <c r="I186" s="7" t="s">
-        <v>635</v>
+        <v>614</v>
       </c>
       <c r="J186" s="7" t="s">
         <v>161</v>
       </c>
       <c r="K186" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L186" s="7" t="s">
         <v>149</v>
@@ -17108,7 +17216,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C187" s="7" t="s">
         <v>144</v>
@@ -17120,7 +17228,7 @@
         <v>146</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>636</v>
+        <v>615</v>
       </c>
       <c r="G187" s="7" t="s">
         <v>0</v>
@@ -17130,13 +17238,13 @@
         <v>11</v>
       </c>
       <c r="I187" s="7" t="s">
-        <v>637</v>
+        <v>616</v>
       </c>
       <c r="J187" s="7" t="s">
         <v>161</v>
       </c>
       <c r="K187" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L187" s="7" t="s">
         <v>149</v>
@@ -17150,7 +17258,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C188" s="7" t="s">
         <v>144</v>
@@ -17162,7 +17270,7 @@
         <v>146</v>
       </c>
       <c r="F188" s="7" t="s">
-        <v>638</v>
+        <v>617</v>
       </c>
       <c r="G188" s="7" t="s">
         <v>0</v>
@@ -17172,13 +17280,13 @@
         <v>11</v>
       </c>
       <c r="I188" s="7" t="s">
-        <v>639</v>
+        <v>618</v>
       </c>
       <c r="J188" s="7" t="s">
         <v>161</v>
       </c>
       <c r="K188" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L188" s="7" t="s">
         <v>149</v>
@@ -17192,7 +17300,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C189" s="7" t="s">
         <v>144</v>
@@ -17204,23 +17312,23 @@
         <v>146</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>760</v>
+        <v>720</v>
       </c>
       <c r="G189" s="7" t="s">
-        <v>737</v>
+        <v>697</v>
       </c>
       <c r="H189" s="7">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="I189" s="7" t="s">
-        <v>742</v>
+        <v>702</v>
       </c>
       <c r="J189" s="7" t="s">
         <v>161</v>
       </c>
       <c r="K189" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L189" s="7" t="s">
         <v>149</v>
@@ -17234,7 +17342,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C190" s="7" t="s">
         <v>144</v>
@@ -17246,7 +17354,7 @@
         <v>146</v>
       </c>
       <c r="F190" s="7" t="s">
-        <v>640</v>
+        <v>619</v>
       </c>
       <c r="G190" s="7" t="s">
         <v>0</v>
@@ -17256,13 +17364,13 @@
         <v>12</v>
       </c>
       <c r="I190" s="7" t="s">
-        <v>641</v>
+        <v>620</v>
       </c>
       <c r="J190" s="7" t="s">
         <v>161</v>
       </c>
       <c r="K190" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L190" s="7" t="s">
         <v>149</v>
@@ -17276,7 +17384,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C191" s="7" t="s">
         <v>144</v>
@@ -17288,7 +17396,7 @@
         <v>146</v>
       </c>
       <c r="F191" s="7" t="s">
-        <v>642</v>
+        <v>621</v>
       </c>
       <c r="G191" s="7" t="s">
         <v>0</v>
@@ -17298,13 +17406,13 @@
         <v>12</v>
       </c>
       <c r="I191" s="7" t="s">
-        <v>643</v>
+        <v>622</v>
       </c>
       <c r="J191" s="7" t="s">
         <v>161</v>
       </c>
       <c r="K191" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L191" s="7" t="s">
         <v>149</v>
@@ -17318,7 +17426,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C192" s="7" t="s">
         <v>144</v>
@@ -17330,7 +17438,7 @@
         <v>146</v>
       </c>
       <c r="F192" s="7" t="s">
-        <v>644</v>
+        <v>623</v>
       </c>
       <c r="G192" s="7" t="s">
         <v>0</v>
@@ -17340,13 +17448,13 @@
         <v>12</v>
       </c>
       <c r="I192" s="7" t="s">
-        <v>645</v>
+        <v>624</v>
       </c>
       <c r="J192" s="7" t="s">
         <v>161</v>
       </c>
       <c r="K192" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L192" s="7" t="s">
         <v>149</v>
@@ -17360,7 +17468,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C193" s="7" t="s">
         <v>144</v>
@@ -17372,7 +17480,7 @@
         <v>146</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>646</v>
+        <v>625</v>
       </c>
       <c r="G193" s="7" t="s">
         <v>0</v>
@@ -17382,13 +17490,13 @@
         <v>12</v>
       </c>
       <c r="I193" s="7" t="s">
-        <v>647</v>
+        <v>626</v>
       </c>
       <c r="J193" s="7" t="s">
         <v>161</v>
       </c>
       <c r="K193" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L193" s="7" t="s">
         <v>149</v>
@@ -17402,7 +17510,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C194" s="7" t="s">
         <v>144</v>
@@ -17414,7 +17522,7 @@
         <v>146</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>648</v>
+        <v>627</v>
       </c>
       <c r="G194" s="7" t="s">
         <v>0</v>
@@ -17424,13 +17532,13 @@
         <v>12</v>
       </c>
       <c r="I194" s="7" t="s">
-        <v>649</v>
+        <v>628</v>
       </c>
       <c r="J194" s="7" t="s">
         <v>161</v>
       </c>
       <c r="K194" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L194" s="7" t="s">
         <v>149</v>
@@ -17439,12 +17547,12 @@
       <c r="N194" s="3"/>
       <c r="O194" s="3"/>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A195" s="7">
         <v>194</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C195" s="7" t="s">
         <v>144</v>
@@ -17456,23 +17564,23 @@
         <v>146</v>
       </c>
       <c r="F195" s="7" t="s">
-        <v>650</v>
+        <v>767</v>
       </c>
       <c r="G195" s="7" t="s">
-        <v>0</v>
+        <v>766</v>
       </c>
       <c r="H195" s="7">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="I195" s="7" t="s">
-        <v>651</v>
+        <v>768</v>
       </c>
       <c r="J195" s="7" t="s">
         <v>187</v>
       </c>
       <c r="K195" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L195" s="7" t="s">
         <v>149</v>
@@ -17486,7 +17594,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C196" s="7" t="s">
         <v>144</v>
@@ -17498,23 +17606,23 @@
         <v>146</v>
       </c>
       <c r="F196" s="7" t="s">
-        <v>652</v>
+        <v>770</v>
       </c>
       <c r="G196" s="7" t="s">
-        <v>0</v>
+        <v>769</v>
       </c>
       <c r="H196" s="7">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="I196" s="7" t="s">
-        <v>653</v>
+        <v>771</v>
       </c>
       <c r="J196" s="7" t="s">
         <v>187</v>
       </c>
       <c r="K196" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L196" s="7" t="s">
         <v>149</v>
@@ -17528,7 +17636,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C197" s="7" t="s">
         <v>144</v>
@@ -17540,23 +17648,23 @@
         <v>146</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>654</v>
+        <v>773</v>
       </c>
       <c r="G197" s="7" t="s">
-        <v>0</v>
+        <v>772</v>
       </c>
       <c r="H197" s="7">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="I197" s="7" t="s">
-        <v>580</v>
+        <v>774</v>
       </c>
       <c r="J197" s="7" t="s">
         <v>187</v>
       </c>
       <c r="K197" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L197" s="7" t="s">
         <v>149</v>
@@ -17570,7 +17678,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C198" s="7" t="s">
         <v>144</v>
@@ -17582,7 +17690,7 @@
         <v>146</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>655</v>
+        <v>629</v>
       </c>
       <c r="G198" s="7" t="s">
         <v>0</v>
@@ -17592,13 +17700,13 @@
         <v>12</v>
       </c>
       <c r="I198" s="7" t="s">
-        <v>656</v>
+        <v>630</v>
       </c>
       <c r="J198" s="7" t="s">
         <v>147</v>
       </c>
       <c r="K198" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L198" s="7" t="s">
         <v>149</v>
@@ -17612,7 +17720,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C199" s="7" t="s">
         <v>144</v>
@@ -17624,20 +17732,20 @@
         <v>146</v>
       </c>
       <c r="F199" s="7" t="s">
-        <v>718</v>
+        <v>678</v>
       </c>
       <c r="G199" s="7" t="s">
-        <v>717</v>
+        <v>677</v>
       </c>
       <c r="H199" s="7">
         <f t="shared" ref="H199:H212" si="7">LEN(F199)</f>
         <v>12</v>
       </c>
       <c r="I199" s="7" t="s">
-        <v>719</v>
+        <v>679</v>
       </c>
       <c r="J199" s="7" t="s">
-        <v>704</v>
+        <v>664</v>
       </c>
       <c r="K199" s="7" t="s">
         <v>464</v>
@@ -17654,7 +17762,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C200" s="7" t="s">
         <v>144</v>
@@ -17666,20 +17774,20 @@
         <v>146</v>
       </c>
       <c r="F200" s="7" t="s">
-        <v>721</v>
+        <v>681</v>
       </c>
       <c r="G200" s="7" t="s">
-        <v>720</v>
+        <v>680</v>
       </c>
       <c r="H200" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I200" s="7" t="s">
-        <v>722</v>
+        <v>682</v>
       </c>
       <c r="J200" s="7" t="s">
-        <v>704</v>
+        <v>664</v>
       </c>
       <c r="K200" s="7" t="s">
         <v>464</v>
@@ -17696,7 +17804,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C201" s="7" t="s">
         <v>144</v>
@@ -17708,20 +17816,20 @@
         <v>146</v>
       </c>
       <c r="F201" s="7" t="s">
-        <v>724</v>
+        <v>684</v>
       </c>
       <c r="G201" s="7" t="s">
-        <v>723</v>
+        <v>683</v>
       </c>
       <c r="H201" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I201" s="7" t="s">
-        <v>725</v>
+        <v>685</v>
       </c>
       <c r="J201" s="7" t="s">
-        <v>704</v>
+        <v>664</v>
       </c>
       <c r="K201" s="7" t="s">
         <v>464</v>
@@ -17738,7 +17846,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C202" s="7" t="s">
         <v>144</v>
@@ -17750,20 +17858,20 @@
         <v>146</v>
       </c>
       <c r="F202" s="7" t="s">
-        <v>727</v>
+        <v>687</v>
       </c>
       <c r="G202" s="7" t="s">
-        <v>726</v>
+        <v>686</v>
       </c>
       <c r="H202" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I202" s="7" t="s">
-        <v>728</v>
+        <v>688</v>
       </c>
       <c r="J202" s="7" t="s">
-        <v>704</v>
+        <v>664</v>
       </c>
       <c r="K202" s="7" t="s">
         <v>464</v>
@@ -17775,12 +17883,12 @@
       <c r="N202" s="3"/>
       <c r="O202" s="3"/>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A203" s="7">
         <v>202</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C203" s="7" t="s">
         <v>144</v>
@@ -17792,17 +17900,17 @@
         <v>146</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>658</v>
+        <v>776</v>
       </c>
       <c r="G203" s="7" t="s">
-        <v>0</v>
+        <v>775</v>
       </c>
       <c r="H203" s="7">
         <f t="shared" si="7"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I203" s="7" t="s">
-        <v>659</v>
+        <v>777</v>
       </c>
       <c r="J203" s="7" t="s">
         <v>161</v>
@@ -17822,7 +17930,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C204" s="7" t="s">
         <v>144</v>
@@ -17834,17 +17942,17 @@
         <v>146</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>769</v>
+        <v>729</v>
       </c>
       <c r="G204" s="7" t="s">
-        <v>738</v>
+        <v>698</v>
       </c>
       <c r="H204" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I204" s="7" t="s">
-        <v>770</v>
+        <v>730</v>
       </c>
       <c r="J204" s="7" t="s">
         <v>161</v>
@@ -17864,7 +17972,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C205" s="7" t="s">
         <v>144</v>
@@ -17876,7 +17984,7 @@
         <v>146</v>
       </c>
       <c r="F205" s="7" t="s">
-        <v>660</v>
+        <v>632</v>
       </c>
       <c r="G205" s="7" t="s">
         <v>0</v>
@@ -17886,7 +17994,7 @@
         <v>12</v>
       </c>
       <c r="I205" s="7" t="s">
-        <v>661</v>
+        <v>633</v>
       </c>
       <c r="J205" s="7" t="s">
         <v>161</v>
@@ -17906,7 +18014,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C206" s="7" t="s">
         <v>144</v>
@@ -17918,7 +18026,7 @@
         <v>146</v>
       </c>
       <c r="F206" s="7" t="s">
-        <v>662</v>
+        <v>634</v>
       </c>
       <c r="G206" s="7" t="s">
         <v>0</v>
@@ -17928,7 +18036,7 @@
         <v>12</v>
       </c>
       <c r="I206" s="7" t="s">
-        <v>663</v>
+        <v>635</v>
       </c>
       <c r="J206" s="7" t="s">
         <v>210</v>
@@ -17948,7 +18056,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C207" s="7" t="s">
         <v>144</v>
@@ -17960,17 +18068,17 @@
         <v>146</v>
       </c>
       <c r="F207" s="7" t="s">
-        <v>684</v>
+        <v>649</v>
       </c>
       <c r="G207" s="7" t="s">
-        <v>683</v>
+        <v>648</v>
       </c>
       <c r="H207" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I207" s="7" t="s">
-        <v>685</v>
+        <v>650</v>
       </c>
       <c r="J207" s="7" t="s">
         <v>210</v>
@@ -17985,12 +18093,12 @@
       <c r="N207" s="3"/>
       <c r="O207" s="3"/>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A208" s="7">
         <v>207</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C208" s="7" t="s">
         <v>144</v>
@@ -18002,17 +18110,17 @@
         <v>146</v>
       </c>
       <c r="F208" s="7" t="s">
-        <v>687</v>
+        <v>779</v>
       </c>
       <c r="G208" s="7" t="s">
-        <v>686</v>
+        <v>778</v>
       </c>
       <c r="H208" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I208" s="7" t="s">
-        <v>688</v>
+        <v>643</v>
       </c>
       <c r="J208" s="7" t="s">
         <v>210</v>
@@ -18032,7 +18140,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C209" s="7" t="s">
         <v>144</v>
@@ -18044,7 +18152,7 @@
         <v>146</v>
       </c>
       <c r="F209" s="7" t="s">
-        <v>664</v>
+        <v>636</v>
       </c>
       <c r="G209" s="7" t="s">
         <v>0</v>
@@ -18054,7 +18162,7 @@
         <v>11</v>
       </c>
       <c r="I209" s="7" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="J209" s="7" t="s">
         <v>215</v>
@@ -18074,7 +18182,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C210" s="7" t="s">
         <v>144</v>
@@ -18086,17 +18194,17 @@
         <v>146</v>
       </c>
       <c r="F210" s="7" t="s">
-        <v>690</v>
+        <v>652</v>
       </c>
       <c r="G210" s="7" t="s">
-        <v>689</v>
+        <v>651</v>
       </c>
       <c r="H210" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I210" s="7" t="s">
-        <v>691</v>
+        <v>653</v>
       </c>
       <c r="J210" s="7" t="s">
         <v>215</v>
@@ -18111,12 +18219,12 @@
       <c r="N210" s="3"/>
       <c r="O210" s="3"/>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A211" s="7">
         <v>210</v>
       </c>
       <c r="B211" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C211" s="7" t="s">
         <v>144</v>
@@ -18128,17 +18236,17 @@
         <v>146</v>
       </c>
       <c r="F211" s="7" t="s">
-        <v>665</v>
+        <v>781</v>
       </c>
       <c r="G211" s="7" t="s">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="H211" s="7">
         <f t="shared" si="7"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I211" s="7" t="s">
-        <v>465</v>
+        <v>782</v>
       </c>
       <c r="J211" s="7" t="s">
         <v>187</v>
@@ -18153,12 +18261,12 @@
       <c r="N211" s="3"/>
       <c r="O211" s="3"/>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A212" s="7">
         <v>211</v>
       </c>
       <c r="B212" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C212" s="7" t="s">
         <v>144</v>
@@ -18170,17 +18278,17 @@
         <v>146</v>
       </c>
       <c r="F212" s="7" t="s">
-        <v>666</v>
+        <v>784</v>
       </c>
       <c r="G212" s="7" t="s">
-        <v>0</v>
+        <v>783</v>
       </c>
       <c r="H212" s="7">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="I212" s="7" t="s">
-        <v>667</v>
+        <v>785</v>
       </c>
       <c r="J212" s="7" t="s">
         <v>187</v>
@@ -18200,7 +18308,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C213" s="7" t="s">
         <v>144</v>
@@ -18212,20 +18320,20 @@
         <v>146</v>
       </c>
       <c r="F213" s="7" t="s">
-        <v>730</v>
+        <v>690</v>
       </c>
       <c r="G213" s="7" t="s">
-        <v>729</v>
+        <v>689</v>
       </c>
       <c r="H213" s="7">
         <f t="shared" ref="H213:H220" si="8">LEN(F213)</f>
         <v>12</v>
       </c>
       <c r="I213" s="7" t="s">
-        <v>731</v>
+        <v>691</v>
       </c>
       <c r="J213" s="7" t="s">
-        <v>704</v>
+        <v>664</v>
       </c>
       <c r="K213" s="7" t="s">
         <v>464</v>
@@ -18242,7 +18350,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C214" s="7" t="s">
         <v>144</v>
@@ -18254,20 +18362,20 @@
         <v>146</v>
       </c>
       <c r="F214" s="7" t="s">
-        <v>733</v>
+        <v>693</v>
       </c>
       <c r="G214" s="7" t="s">
-        <v>732</v>
+        <v>692</v>
       </c>
       <c r="H214" s="7">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="I214" s="7" t="s">
-        <v>734</v>
+        <v>694</v>
       </c>
       <c r="J214" s="7" t="s">
-        <v>704</v>
+        <v>664</v>
       </c>
       <c r="K214" s="7" t="s">
         <v>464</v>
@@ -18279,12 +18387,12 @@
       <c r="N214" s="3"/>
       <c r="O214" s="3"/>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A215" s="7">
         <v>214</v>
       </c>
       <c r="B215" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C215" s="7" t="s">
         <v>144</v>
@@ -18296,17 +18404,17 @@
         <v>146</v>
       </c>
       <c r="F215" s="7" t="s">
-        <v>669</v>
+        <v>787</v>
       </c>
       <c r="G215" s="7" t="s">
-        <v>0</v>
+        <v>786</v>
       </c>
       <c r="H215" s="7">
         <f t="shared" si="8"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I215" s="7" t="s">
-        <v>670</v>
+        <v>788</v>
       </c>
       <c r="J215" s="7" t="s">
         <v>161</v>
@@ -18321,12 +18429,12 @@
       <c r="N215" s="3"/>
       <c r="O215" s="3"/>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A216" s="7">
         <v>215</v>
       </c>
       <c r="B216" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C216" s="7" t="s">
         <v>144</v>
@@ -18338,17 +18446,17 @@
         <v>146</v>
       </c>
       <c r="F216" s="7" t="s">
-        <v>671</v>
+        <v>790</v>
       </c>
       <c r="G216" s="7" t="s">
-        <v>0</v>
+        <v>789</v>
       </c>
       <c r="H216" s="7">
         <f t="shared" si="8"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I216" s="7" t="s">
-        <v>672</v>
+        <v>791</v>
       </c>
       <c r="J216" s="7" t="s">
         <v>161</v>
@@ -18368,7 +18476,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C217" s="7" t="s">
         <v>144</v>
@@ -18380,7 +18488,7 @@
         <v>146</v>
       </c>
       <c r="F217" s="7" t="s">
-        <v>673</v>
+        <v>638</v>
       </c>
       <c r="G217" s="7" t="s">
         <v>0</v>
@@ -18390,7 +18498,7 @@
         <v>12</v>
       </c>
       <c r="I217" s="7" t="s">
-        <v>674</v>
+        <v>639</v>
       </c>
       <c r="J217" s="7" t="s">
         <v>161</v>
@@ -18410,7 +18518,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C218" s="7" t="s">
         <v>144</v>
@@ -18422,17 +18530,17 @@
         <v>146</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>693</v>
+        <v>655</v>
       </c>
       <c r="G218" s="7" t="s">
-        <v>692</v>
+        <v>654</v>
       </c>
       <c r="H218" s="7">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="I218" s="7" t="s">
-        <v>694</v>
+        <v>656</v>
       </c>
       <c r="J218" s="7" t="s">
         <v>210</v>
@@ -18452,7 +18560,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C219" s="7" t="s">
         <v>144</v>
@@ -18464,17 +18572,17 @@
         <v>146</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>696</v>
+        <v>658</v>
       </c>
       <c r="G219" s="7" t="s">
-        <v>695</v>
+        <v>657</v>
       </c>
       <c r="H219" s="7">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="I219" s="7" t="s">
-        <v>697</v>
+        <v>659</v>
       </c>
       <c r="J219" s="7" t="s">
         <v>210</v>
@@ -18494,7 +18602,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C220" s="7" t="s">
         <v>144</v>
@@ -18506,17 +18614,17 @@
         <v>146</v>
       </c>
       <c r="F220" s="7" t="s">
-        <v>677</v>
+        <v>642</v>
       </c>
       <c r="G220" s="7" t="s">
-        <v>676</v>
+        <v>641</v>
       </c>
       <c r="H220" s="7">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="I220" s="7" t="s">
-        <v>678</v>
+        <v>643</v>
       </c>
       <c r="J220" s="7" t="s">
         <v>210</v>
@@ -18536,7 +18644,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C221" s="7" t="s">
         <v>144</v>
@@ -18548,20 +18656,20 @@
         <v>146</v>
       </c>
       <c r="F221" s="7" t="s">
-        <v>761</v>
+        <v>721</v>
       </c>
       <c r="G221" s="7" t="s">
-        <v>743</v>
+        <v>703</v>
       </c>
       <c r="H221" s="7">
         <f t="shared" ref="H221:H228" si="9">LEN(F221)</f>
         <v>11</v>
       </c>
       <c r="I221" s="7" t="s">
-        <v>744</v>
+        <v>704</v>
       </c>
       <c r="J221" s="7" t="s">
-        <v>739</v>
+        <v>699</v>
       </c>
       <c r="K221" s="7" t="s">
         <v>464</v>
@@ -18578,7 +18686,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C222" s="7" t="s">
         <v>144</v>
@@ -18590,20 +18698,20 @@
         <v>146</v>
       </c>
       <c r="F222" s="7" t="s">
-        <v>771</v>
+        <v>731</v>
       </c>
       <c r="G222" s="7" t="s">
-        <v>745</v>
+        <v>705</v>
       </c>
       <c r="H222" s="7">
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="I222" s="7" t="s">
-        <v>772</v>
+        <v>732</v>
       </c>
       <c r="J222" s="7" t="s">
-        <v>739</v>
+        <v>699</v>
       </c>
       <c r="K222" s="7" t="s">
         <v>464</v>
@@ -18620,7 +18728,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C223" s="7" t="s">
         <v>144</v>
@@ -18632,20 +18740,20 @@
         <v>146</v>
       </c>
       <c r="F223" s="7" t="s">
-        <v>762</v>
+        <v>722</v>
       </c>
       <c r="G223" s="7" t="s">
-        <v>746</v>
+        <v>706</v>
       </c>
       <c r="H223" s="7">
         <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="I223" s="7" t="s">
-        <v>747</v>
+        <v>707</v>
       </c>
       <c r="J223" s="7" t="s">
-        <v>739</v>
+        <v>699</v>
       </c>
       <c r="K223" s="7" t="s">
         <v>464</v>
@@ -18662,7 +18770,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C224" s="7" t="s">
         <v>144</v>
@@ -18674,23 +18782,23 @@
         <v>146</v>
       </c>
       <c r="F224" s="7" t="s">
-        <v>763</v>
+        <v>723</v>
       </c>
       <c r="G224" s="7" t="s">
-        <v>748</v>
+        <v>708</v>
       </c>
       <c r="H224" s="7">
         <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="I224" s="7" t="s">
-        <v>749</v>
+        <v>709</v>
       </c>
       <c r="J224" s="7" t="s">
-        <v>739</v>
+        <v>699</v>
       </c>
       <c r="K224" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L224" s="7" t="s">
         <v>149</v>
@@ -18704,7 +18812,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C225" s="7" t="s">
         <v>144</v>
@@ -18716,23 +18824,23 @@
         <v>146</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>764</v>
+        <v>724</v>
       </c>
       <c r="G225" s="7" t="s">
-        <v>750</v>
+        <v>710</v>
       </c>
       <c r="H225" s="7">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="I225" s="7" t="s">
-        <v>751</v>
+        <v>711</v>
       </c>
       <c r="J225" s="7" t="s">
-        <v>739</v>
+        <v>699</v>
       </c>
       <c r="K225" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L225" s="7" t="s">
         <v>149</v>
@@ -18746,7 +18854,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C226" s="7" t="s">
         <v>144</v>
@@ -18758,23 +18866,23 @@
         <v>146</v>
       </c>
       <c r="F226" s="7" t="s">
-        <v>765</v>
+        <v>725</v>
       </c>
       <c r="G226" s="7" t="s">
-        <v>752</v>
+        <v>712</v>
       </c>
       <c r="H226" s="7">
         <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="I226" s="7" t="s">
-        <v>753</v>
+        <v>713</v>
       </c>
       <c r="J226" s="7" t="s">
-        <v>739</v>
+        <v>699</v>
       </c>
       <c r="K226" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L226" s="7" t="s">
         <v>149</v>
@@ -18788,7 +18896,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C227" s="7" t="s">
         <v>144</v>
@@ -18800,23 +18908,23 @@
         <v>146</v>
       </c>
       <c r="F227" s="7" t="s">
-        <v>766</v>
+        <v>726</v>
       </c>
       <c r="G227" s="7" t="s">
-        <v>754</v>
+        <v>714</v>
       </c>
       <c r="H227" s="7">
         <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="I227" s="7" t="s">
-        <v>755</v>
+        <v>715</v>
       </c>
       <c r="J227" s="7" t="s">
-        <v>739</v>
+        <v>699</v>
       </c>
       <c r="K227" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L227" s="7" t="s">
         <v>149</v>
@@ -18830,7 +18938,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C228" s="7" t="s">
         <v>144</v>
@@ -18842,23 +18950,23 @@
         <v>146</v>
       </c>
       <c r="F228" s="7" t="s">
-        <v>767</v>
+        <v>727</v>
       </c>
       <c r="G228" s="7" t="s">
-        <v>756</v>
+        <v>716</v>
       </c>
       <c r="H228" s="7">
         <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="I228" s="7" t="s">
-        <v>757</v>
+        <v>717</v>
       </c>
       <c r="J228" s="7" t="s">
-        <v>739</v>
+        <v>699</v>
       </c>
       <c r="K228" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L228" s="7" t="s">
         <v>149</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C59402B-ACB9-4231-91E7-2EF613E4EB32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56F306D-D98B-4505-A258-B9812620B57F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2348" uniqueCount="793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2349" uniqueCount="796">
   <si>
     <t>—</t>
   </si>
@@ -8733,6 +8733,17 @@
   </si>
   <si>
     <t>10-12 끼니 추천에서 나트륨이 높은 메뉴(국·탕·냉국·콩국수·닭곰탕·김치·보쌈)  국물 없는 메뉴로 바꿈. 국·찌개는 나트륨 주 공급원(국민건강영양조사)이라 끼니 추천에 넣지 않음</t>
+  </si>
+  <si>
+    <t>언제나(낮 포함) · 저녁·새벽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10-13 회복 문구  시간 제한 없음으로 바꿈(낮에도 나오고, 식후 가능이라 저녁·새벽에도 나옴). 「내일은 죽 한 그릇」 「첫 끼 시간 정하기」는 내일을 말하는 문구라 저녁·새벽 그대로</t>
   </si>
 </sst>
 </file>
@@ -9219,7 +9230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F51797-492B-40AC-833D-E19CEF6E9FA5}">
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="120.58203125" style="1" customWidth="1"/>
@@ -9364,6 +9375,11 @@
     <row r="29" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
         <v>792</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A30" s="1" t="s">
+        <v>795</v>
       </c>
     </row>
   </sheetData>
@@ -10155,7 +10171,7 @@
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
     </row>
-    <row r="19" spans="1:15" ht="16" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -10187,17 +10203,17 @@
       <c r="J19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>5</v>
+      <c r="K19" s="7" t="s">
+        <v>793</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>6</v>
+        <v>794</v>
       </c>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
     </row>
-    <row r="20" spans="1:15" ht="16" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -10229,11 +10245,11 @@
       <c r="J20" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>5</v>
+      <c r="K20" s="7" t="s">
+        <v>793</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>6</v>
+        <v>794</v>
       </c>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
@@ -10953,7 +10969,7 @@
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
     </row>
-    <row r="38" spans="1:15" ht="16" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -10985,11 +11001,11 @@
       <c r="J38" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="K38" s="3" t="s">
-        <v>5</v>
+      <c r="K38" s="7" t="s">
+        <v>793</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>6</v>
+        <v>794</v>
       </c>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
@@ -12003,7 +12019,7 @@
       <c r="N62" s="3"/>
       <c r="O62" s="3"/>
     </row>
-    <row r="63" spans="1:15" ht="16" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -12035,17 +12051,17 @@
       <c r="J63" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="K63" s="3" t="s">
-        <v>5</v>
+      <c r="K63" s="7" t="s">
+        <v>793</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>6</v>
+        <v>794</v>
       </c>
       <c r="M63" s="3"/>
       <c r="N63" s="3"/>
       <c r="O63" s="3"/>
     </row>
-    <row r="64" spans="1:15" ht="16" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:15" ht="25" x14ac:dyDescent="0.45">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -12077,11 +12093,11 @@
       <c r="J64" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K64" s="3" t="s">
-        <v>5</v>
+      <c r="K64" s="7" t="s">
+        <v>793</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>6</v>
+        <v>794</v>
       </c>
       <c r="M64" s="3"/>
       <c r="N64" s="3"/>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40961F8C-709F-452A-9714-DD387A4B2A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDC31C6-DA28-4B52-A533-AB14C17BB6BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2821" uniqueCount="762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3048" uniqueCount="989">
   <si>
     <t>—</t>
   </si>
@@ -5983,132 +5983,1041 @@
     <t>성격 뜻 · 질환별 금지</t>
   </si>
   <si>
+    <t>국민 공통 식생활지침(보건복지부 2021) 2. 아침밥 꼭 먹기 · 규칙적인 식사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국민 공통 식생활지침(보건복지부 2021) 1. 채소 등 다양한 식품 골고루 · WHO 채소·과일 하루 400g 이상 권고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국민 공통 식생활지침(보건복지부 2021) 4. 덜 달게 · 5. 단 음료 대신 물 · WHO 유리당 하루 열량 10% 미만 권고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국민 공통 식생활지침(보건복지부 2021) 4. 덜 짜게 · WHO 나트륨 하루 2,000mg 미만 권고 · 국·찌개가 나트륨 주 공급원(국민건강영양조사)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국민 공통 식생활지침(보건복지부 2021) 3. 과식 피하기 · 위식도역류 생활수칙(대한소화기학회): 잠들기 전 식사 피하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국민 공통 식생활지침(보건복지부 2021) 3. 과식 피하기 · 천천히 먹기와 포만감(식사 속도 연구)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국민 공통 식생활지침(보건복지부 2021) 1. 다양한 식품 골고루 · 2020 한국인 영양소 섭취기준(단백질 끼니별 고른 섭취)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국민 공통 식생활지침(보건복지부 2021) 4. 덜 기름지게 · WHO 포화지방 하루 열량 10% 미만 권고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>식욕이 없을 때 식사 요령(대한영양사협회 · 국가암정보센터): 조금씩 자주, 먹기 편한 음식부터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미국심장협회(AHA): 생선 주 2회 권고 · 국민 공통 식생활지침(보건복지부 2021) 1. 다양한 식품 골고루</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수면위생 수칙(대한수면학회): 오후 이후 카페인 줄이기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국민 공통 식생활지침(보건복지부 2021) 1. 다양한 식품 골고루 · 당뇨병 식사요법(대한당뇨병학회): 탄수화물에 단백질·채소 곁들이기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제외</t>
+  </si>
+  <si>
+    <t>10-13 결정: 기존 문구는 그대로 둠</t>
+  </si>
+  <si>
+    <t>10-13 결정: 기존 데이터계약 문구는 바꾸지 않고 그대로 둠(12자 초과 5개 포함)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10-13 결정 반영</t>
+  </si>
+  <si>
+    <t>1) 영문: 외주업체 번역·검수 예정. 「영문」 열은 비워 둠</t>
+  </si>
+  <si>
+    <t>2) 근거: 근거 칸에 지침 이름과 항목 번호를 적음(국민 공통 식생활지침 2021 항목 · WHO 권고 · 한국인 영양소 섭취기준 · 대한당뇨병학회 · 대한소화기학회 · 대한수면학회 · AHA)</t>
+  </si>
+  <si>
+    <t>4) 기존 문구 수정 5개: 그대로 두기로 함(「기존 문구 수정」 시트 판정 제외)</t>
+  </si>
+  <si>
+    <t>—</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INCREASE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>증량 — 만성 신장질환 사용자에게는 안 나옴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REDUCE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>감량 — 당뇨병 · 만성 신장질환 사용자에게는 안 나옴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEXTURE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조리·식감 바꾸기 — 질환 금지 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FLUID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수분 — 만성 신장질환 사용자에게는 안 나옴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FAST</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>끊기·건너뛰기 — 당뇨병 사용자에게는 안 나옴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3) 성격 확정: 「성격(확정)」 열. 증량 36 · 감량 18 · 수분 7 · 끊기 4 · 조리 바꾸기 18 · 없음 144. 기존 데이터계약과 같은 기준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자기 전 야식을 건너뛰면 속이 편하고 잠도 잘 와요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>야식 없이 잠들기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>영문(외주 번역·검수 예정)</t>
-  </si>
-  <si>
-    <t>국민 공통 식생활지침(보건복지부 2021) 2. 아침밥 꼭 먹기 · 규칙적인 식사</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>국민 공통 식생활지침(보건복지부 2021) 1. 채소 등 다양한 식품 골고루 · WHO 채소·과일 하루 400g 이상 권고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>국민 공통 식생활지침(보건복지부 2021) 4. 덜 달게 · 5. 단 음료 대신 물 · WHO 유리당 하루 열량 10% 미만 권고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>국민 공통 식생활지침(보건복지부 2021) 4. 덜 짜게 · WHO 나트륨 하루 2,000mg 미만 권고 · 국·찌개가 나트륨 주 공급원(국민건강영양조사)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>국민 공통 식생활지침(보건복지부 2021) 3. 과식 피하기 · 위식도역류 생활수칙(대한소화기학회): 잠들기 전 식사 피하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>국민 공통 식생활지침(보건복지부 2021) 3. 과식 피하기 · 천천히 먹기와 포만감(식사 속도 연구)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>국민 공통 식생활지침(보건복지부 2021) 1. 다양한 식품 골고루 · 2020 한국인 영양소 섭취기준(단백질 끼니별 고른 섭취)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>국민 공통 식생활지침(보건복지부 2021) 4. 덜 기름지게 · WHO 포화지방 하루 열량 10% 미만 권고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>식욕이 없을 때 식사 요령(대한영양사협회 · 국가암정보센터): 조금씩 자주, 먹기 편한 음식부터</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>미국심장협회(AHA): 생선 주 2회 권고 · 국민 공통 식생활지침(보건복지부 2021) 1. 다양한 식품 골고루</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수면위생 수칙(대한수면학회): 오후 이후 카페인 줄이기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>국민 공통 식생활지침(보건복지부 2021) 1. 다양한 식품 골고루 · 당뇨병 식사요법(대한당뇨병학회): 탄수화물에 단백질·채소 곁들이기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>제외</t>
-  </si>
-  <si>
-    <t>10-13 결정: 기존 문구는 그대로 둠</t>
-  </si>
-  <si>
-    <t>10-13 결정: 기존 데이터계약 문구는 바꾸지 않고 그대로 둠(12자 초과 5개 포함)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10-13 결정 반영</t>
-  </si>
-  <si>
-    <t>1) 영문: 외주업체 번역·검수 예정. 「영문」 열은 비워 둠</t>
-  </si>
-  <si>
-    <t>2) 근거: 근거 칸에 지침 이름과 항목 번호를 적음(국민 공통 식생활지침 2021 항목 · WHO 권고 · 한국인 영양소 섭취기준 · 대한당뇨병학회 · 대한소화기학회 · 대한수면학회 · AHA)</t>
-  </si>
-  <si>
-    <t>4) 기존 문구 수정 5개: 그대로 두기로 함(「기존 문구 수정」 시트 판정 제외)</t>
-  </si>
-  <si>
-    <t>—</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INCREASE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>증량 — 만성 신장질환 사용자에게는 안 나옴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>REDUCE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>감량 — 당뇨병 · 만성 신장질환 사용자에게는 안 나옴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TEXTURE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>조리·식감 바꾸기 — 질환 금지 없음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FLUID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수분 — 만성 신장질환 사용자에게는 안 나옴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FAST</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>끊기·건너뛰기 — 당뇨병 사용자에게는 안 나옴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3) 성격 확정: 「성격(확정)」 열. 증량 36 · 감량 18 · 수분 7 · 끊기 4 · 조리 바꾸기 18 · 없음 144. 기존 데이터계약과 같은 기준</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>자기 전 야식을 건너뛰면 속이 편하고 잠도 잘 와요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>야식 없이 잠들기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plan tomorrow's breakfast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Write down your lunch time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Set out veggies for tomorrow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Make a veggie side ahead</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Two veggie sides at lunch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Put sweet snacks away</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Look back on today's drinks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use a smaller soup bowl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>List low-sodium products</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Set tomorrow's dinner time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Close the kitchen after 9 pm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reflect on how fast you ate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Set out a smaller plate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tofu stew side for tomorrow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buy a tray of eggs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grilled mackerel for tomorrow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Steamed eggs instead of fried</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Note the meals you ate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Note when eating feels easy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A bowl of rice porridge tomorrow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plan tomorrow's three meals</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Look back on skipped meals</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Look back on today's veggies</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buy two seasonal veggies</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bottled water instead of juice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Steamed sweet potato, not chips</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recall how much soup you had</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fresh slaw instead of pickles</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Finish dinner by 8 pm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Note when you had dinner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chew each bite 30 times</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Keep your phone off the table</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chicken salad for lunch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Look back on today's protein</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Greens instead of fritters</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Look back on fried food</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eat when your appetite returns</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Set your first meal time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buy breakfast basics</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Busy day? A kimbap roll</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Keep veggies front and center</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zucchini in tomorrow's soup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>One veggie side every day</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Check sugar on drink labels</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Don't stock sweet drinks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3 days a week, no sweet drinks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Put the salt shaker away</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eat the solids in soup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Compare sodium on labels</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Clear your snack spot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Have dinner before 7 pm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner around 7 pm daily</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Take 15+ minutes to eat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eat with the TV off</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plan a meal to share</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Set out eggs for breakfast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fish twice a week</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Make pan-fried tofu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Set out food to grill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Steamed potato, not fries</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Steamed fish, not pork ribs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Warm soup with rice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Write a line about your meal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Set a lunch alarm for noon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Add meal times to your calendar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eat every 4 hours</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bring a snack when you go out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Set out a breakfast bowl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Think of tomorrow's first meal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pick the veggie side first</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Add veggies to your ramen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Choose a veggie-packed kimbap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pack cucumber or carrot sticks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prep veggies for tomorrow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wash salad greens ahead</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Order coffee without syrup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Choose unsweetened drinks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pick a less sweet bread</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carry a water bottle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brew barley tea ahead</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shop without sweet snacks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eat soup solids first</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skip the extra salt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dip in sauce just once</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Make soup less salty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Clear bean sprout soup tomorrow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buy low-sodium soy sauce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Set a snack time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Set your dinner time ahead</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Make time for breakfast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eat at regular times</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Water instead of a late snack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Go to bed without a late snack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pause 10 seconds per bite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pause with a sip of water</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use your usual rice bowl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Check how hungry you are</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reflect on how full you got</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decide tomorrow's portions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pick a protein for lunch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bring a carton of soy milk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soy milk for breakfast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Half a block of tofu in soup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Slice tofu for breakfast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pack protein in your lunch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boiled pork, not pork belly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Greens instead of japchae</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Peel off the batter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 spoon of salad dressing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bean sprout side for tomorrow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boiled pork, not spicy stir-fry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grilled fish, not pork cutlet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Poached chicken, not fried</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Clear soup, not kimchi stew</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Black coffee, not instant mix</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yogurt instead of cake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bibimbap instead of jjajang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>No caffeine after noon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Toasted rice soup for breakfast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Busy morning? A boiled egg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A handful of sprouts in ramen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Load your bibimbap with greens</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Add chives to your omelet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Add an egg to your ramen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tuna or egg kimbap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Top your salad with an egg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Barley tea, not sweet rice drink</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Latte without syrup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Half a packet of instant coffee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use half the ramen seasoning</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Choose white (mild) kimchi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blanched squid, not fried</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oven-baked, not fried chicken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Warm tea instead of a snack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brush your teeth before bed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breathe after each spoonful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use a small rice bowl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chew noodles slowly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: brown rice + greens</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: grain rice + tofu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: oatmeal + milk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: sweet potato + soy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: brown rice + fish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: spinach or cucumber</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: cabbage wraps</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: zucchini or eggplant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: bibimbap or wraps</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tofu salad, half dressing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: steamed egg or tofu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: soft tofu or soy milk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: soy milk or milk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: egg or soy milk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: silken tofu or soy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: salmon or tofu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: fish or greens</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: fresh slaw or salad</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: fish or boiled pork</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: boiled pork or chicken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: poached or grilled chicken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: blanched squid or pork</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: mackerel or beltfish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: grilled white fish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: tofu or steamed egg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: salmon or chicken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: chicken or tofu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: tofu or poached chicken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: tofu or steamed fish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: shabu-shabu or wraps</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: rice paper rolls</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: eggplant or mushrooms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: greens or fresh slaw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: bean sprouts or spinach</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: lettuce wraps or greens</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: steamed fish + slaw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: steamed tofu + slaw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: grain rice + wraps</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: braised chicken or pork</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: flounder or croaker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: grilled mackerel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: grilled chicken or pork</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: shrimp or squid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: lean meat or fish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: clams or fish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: tofu or braised chicken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: greens rice + wraps</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: mushroom rice + wraps</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: eggplant or zucchini</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Salmon salad, half dressing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: bok choy or mushrooms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: broccoli or wraps</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: cabbage or greens</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: water parsley or sprouts</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: lettuce wraps + greens</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: fish or steamed tofu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: fresh veggie wraps</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: steamed or grilled fish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dinner: barley rice + wraps</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: potato + yogurt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: whole-wheat + veggies</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: squash + milk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: black rice + greens</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: spinach or wraps</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cabbage salad, half dressing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: bibimbap or greens</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: yogurt or soy milk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: milk or yogurt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: chicken or soy milk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: fish or tofu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: steamed fish or tofu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: cucumber or slaw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: radish slaw or greens</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: corn + soy milk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: barley rice + greens</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: sprouts or wraps</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: squash or greens</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: cabbage or cucumber</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: yogurt or tofu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: soft tofu or milk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakfast: chicken or tofu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cucumber salad, half dressing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Silken tofu salad, half dressing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mushroom salad, half dressing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eggplant salad, half dressing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chicken salad, half dressing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shrimp salad, half dressing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Seaweed salad, half dressing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tuna salad, half dressing</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6766,27 +7675,27 @@
     </row>
     <row r="32" spans="1:1" ht="13" x14ac:dyDescent="0.45">
       <c r="A32" s="12" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A33" s="11" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A34" s="11" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A35" s="11" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A36" s="11" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
   </sheetData>
@@ -6874,7 +7783,7 @@
         <v>727</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>728</v>
+        <v>761</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -6907,7 +7816,7 @@
         <v>36</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>4</v>
@@ -6919,12 +7828,14 @@
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
       <c r="P2" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R2" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>762</v>
+      </c>
     </row>
     <row r="3" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
@@ -6956,7 +7867,7 @@
         <v>38</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>4</v>
@@ -6968,12 +7879,14 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R3" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>763</v>
+      </c>
     </row>
     <row r="4" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
@@ -7005,7 +7918,7 @@
         <v>40</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>4</v>
@@ -7017,12 +7930,14 @@
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R4" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>764</v>
+      </c>
     </row>
     <row r="5" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
@@ -7054,7 +7969,7 @@
         <v>42</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>4</v>
@@ -7066,12 +7981,14 @@
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R5" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>765</v>
+      </c>
     </row>
     <row r="6" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
@@ -7103,7 +8020,7 @@
         <v>458</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>4</v>
@@ -7115,12 +8032,14 @@
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q6" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q6" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R6" s="3"/>
+      <c r="R6" s="3" t="s">
+        <v>766</v>
+      </c>
     </row>
     <row r="7" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
@@ -7152,7 +8071,7 @@
         <v>44</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>4</v>
@@ -7164,12 +8083,14 @@
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R7" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>767</v>
+      </c>
     </row>
     <row r="8" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
@@ -7201,7 +8122,7 @@
         <v>46</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>4</v>
@@ -7213,12 +8134,14 @@
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R8" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>768</v>
+      </c>
     </row>
     <row r="9" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
@@ -7250,7 +8173,7 @@
         <v>48</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>4</v>
@@ -7262,12 +8185,14 @@
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="Q9" s="7" t="s">
         <v>751</v>
       </c>
-      <c r="Q9" s="7" t="s">
-        <v>752</v>
-      </c>
-      <c r="R9" s="3"/>
+      <c r="R9" s="3" t="s">
+        <v>769</v>
+      </c>
     </row>
     <row r="10" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
@@ -7299,7 +8224,7 @@
         <v>50</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>4</v>
@@ -7311,12 +8236,14 @@
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R10" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>770</v>
+      </c>
     </row>
     <row r="11" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
@@ -7348,7 +8275,7 @@
         <v>52</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>4</v>
@@ -7360,12 +8287,14 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R11" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>771</v>
+      </c>
     </row>
     <row r="12" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
@@ -7397,7 +8326,7 @@
         <v>53</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>4</v>
@@ -7409,12 +8338,14 @@
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R12" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>772</v>
+      </c>
     </row>
     <row r="13" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
@@ -7446,7 +8377,7 @@
         <v>55</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>4</v>
@@ -7458,12 +8389,14 @@
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R13" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>773</v>
+      </c>
     </row>
     <row r="14" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
@@ -7495,7 +8428,7 @@
         <v>57</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
@@ -7507,12 +8440,14 @@
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="Q14" s="7" t="s">
         <v>751</v>
       </c>
-      <c r="Q14" s="7" t="s">
-        <v>752</v>
-      </c>
-      <c r="R14" s="3"/>
+      <c r="R14" s="3" t="s">
+        <v>774</v>
+      </c>
     </row>
     <row r="15" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
@@ -7544,7 +8479,7 @@
         <v>373</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>4</v>
@@ -7556,12 +8491,14 @@
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R15" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>775</v>
+      </c>
     </row>
     <row r="16" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
@@ -7593,7 +8530,7 @@
         <v>476</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>4</v>
@@ -7605,12 +8542,14 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q16" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q16" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R16" s="3"/>
+      <c r="R16" s="3" t="s">
+        <v>776</v>
+      </c>
     </row>
     <row r="17" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A17" s="3">
@@ -7642,7 +8581,7 @@
         <v>349</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>4</v>
@@ -7654,12 +8593,14 @@
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="Q17" s="7" t="s">
         <v>753</v>
       </c>
-      <c r="Q17" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="R17" s="3"/>
+      <c r="R17" s="3" t="s">
+        <v>777</v>
+      </c>
     </row>
     <row r="18" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A18" s="3">
@@ -7691,7 +8632,7 @@
         <v>351</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>4</v>
@@ -7703,12 +8644,14 @@
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="Q18" s="7" t="s">
         <v>753</v>
       </c>
-      <c r="Q18" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="R18" s="3"/>
+      <c r="R18" s="3" t="s">
+        <v>778</v>
+      </c>
     </row>
     <row r="19" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A19" s="3">
@@ -7740,7 +8683,7 @@
         <v>59</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="K19" s="7" t="s">
         <v>723</v>
@@ -7752,12 +8695,14 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R19" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>779</v>
+      </c>
     </row>
     <row r="20" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A20" s="3">
@@ -7789,7 +8734,7 @@
         <v>61</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="K20" s="7" t="s">
         <v>723</v>
@@ -7801,12 +8746,14 @@
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R20" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>780</v>
+      </c>
     </row>
     <row r="21" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A21" s="3">
@@ -7838,7 +8785,7 @@
         <v>383</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
@@ -7850,12 +8797,14 @@
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q21" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q21" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R21" s="3"/>
+      <c r="R21" s="3" t="s">
+        <v>781</v>
+      </c>
     </row>
     <row r="22" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A22" s="3">
@@ -7887,7 +8836,7 @@
         <v>63</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>4</v>
@@ -7899,12 +8848,14 @@
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R22" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>782</v>
+      </c>
     </row>
     <row r="23" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A23" s="3">
@@ -7936,7 +8887,7 @@
         <v>65</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>4</v>
@@ -7948,12 +8899,14 @@
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R23" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>783</v>
+      </c>
     </row>
     <row r="24" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A24" s="3">
@@ -7985,7 +8938,7 @@
         <v>67</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>4</v>
@@ -7997,12 +8950,14 @@
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
       <c r="P24" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R24" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>784</v>
+      </c>
     </row>
     <row r="25" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A25" s="3">
@@ -8034,7 +8989,7 @@
         <v>472</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>4</v>
@@ -8046,12 +9001,14 @@
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
       <c r="P25" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q25" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q25" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R25" s="3"/>
+      <c r="R25" s="3" t="s">
+        <v>785</v>
+      </c>
     </row>
     <row r="26" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A26" s="3">
@@ -8083,7 +9040,7 @@
         <v>377</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>4</v>
@@ -8095,12 +9052,14 @@
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="7" t="s">
+        <v>754</v>
+      </c>
+      <c r="Q26" s="7" t="s">
         <v>755</v>
       </c>
-      <c r="Q26" s="7" t="s">
-        <v>756</v>
-      </c>
-      <c r="R26" s="3"/>
+      <c r="R26" s="3" t="s">
+        <v>786</v>
+      </c>
     </row>
     <row r="27" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A27" s="3">
@@ -8132,7 +9091,7 @@
         <v>379</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>4</v>
@@ -8144,12 +9103,14 @@
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
       <c r="P27" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R27" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>787</v>
+      </c>
     </row>
     <row r="28" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A28" s="3">
@@ -8181,7 +9142,7 @@
         <v>69</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K28" s="3" t="s">
         <v>4</v>
@@ -8193,12 +9154,14 @@
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
       <c r="P28" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q28" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R28" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R28" s="3" t="s">
+        <v>788</v>
+      </c>
     </row>
     <row r="29" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A29" s="3">
@@ -8230,7 +9193,7 @@
         <v>365</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>4</v>
@@ -8242,12 +9205,14 @@
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
       <c r="P29" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R29" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>789</v>
+      </c>
     </row>
     <row r="30" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A30" s="3">
@@ -8279,7 +9244,7 @@
         <v>453</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>4</v>
@@ -8291,12 +9256,14 @@
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
       <c r="P30" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q30" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R30" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R30" s="3" t="s">
+        <v>790</v>
+      </c>
     </row>
     <row r="31" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A31" s="3">
@@ -8328,7 +9295,7 @@
         <v>71</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K31" s="3" t="s">
         <v>4</v>
@@ -8340,12 +9307,14 @@
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
       <c r="P31" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q31" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R31" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R31" s="3" t="s">
+        <v>791</v>
+      </c>
     </row>
     <row r="32" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A32" s="3">
@@ -8377,7 +9346,7 @@
         <v>446</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="K32" s="7" t="s">
         <v>447</v>
@@ -8389,12 +9358,14 @@
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
       <c r="P32" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q32" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R32" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>792</v>
+      </c>
     </row>
     <row r="33" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A33" s="3">
@@ -8426,7 +9397,7 @@
         <v>73</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>4</v>
@@ -8438,12 +9409,14 @@
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
       <c r="P33" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R33" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>793</v>
+      </c>
     </row>
     <row r="34" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A34" s="3">
@@ -8475,7 +9448,7 @@
         <v>375</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>4</v>
@@ -8487,12 +9460,14 @@
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
       <c r="P34" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q34" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R34" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R34" s="3" t="s">
+        <v>794</v>
+      </c>
     </row>
     <row r="35" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A35" s="3">
@@ -8524,7 +9499,7 @@
         <v>75</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>4</v>
@@ -8536,12 +9511,14 @@
       <c r="N35" s="3"/>
       <c r="O35" s="3"/>
       <c r="P35" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q35" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R35" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>795</v>
+      </c>
     </row>
     <row r="36" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A36" s="3">
@@ -8573,7 +9550,7 @@
         <v>353</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K36" s="3" t="s">
         <v>4</v>
@@ -8585,12 +9562,14 @@
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
       <c r="P36" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="Q36" s="7" t="s">
         <v>753</v>
       </c>
-      <c r="Q36" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="R36" s="3"/>
+      <c r="R36" s="3" t="s">
+        <v>796</v>
+      </c>
     </row>
     <row r="37" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A37" s="3">
@@ -8622,7 +9601,7 @@
         <v>46</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K37" s="3" t="s">
         <v>4</v>
@@ -8634,12 +9613,14 @@
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
       <c r="P37" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q37" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R37" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R37" s="3" t="s">
+        <v>797</v>
+      </c>
     </row>
     <row r="38" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A38" s="3">
@@ -8671,7 +9652,7 @@
         <v>449</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="K38" s="7" t="s">
         <v>723</v>
@@ -8683,12 +9664,14 @@
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
       <c r="P38" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q38" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q38" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R38" s="3"/>
+      <c r="R38" s="3" t="s">
+        <v>798</v>
+      </c>
     </row>
     <row r="39" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A39" s="3">
@@ -8720,7 +9703,7 @@
         <v>78</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="K39" s="3" t="s">
         <v>4</v>
@@ -8732,12 +9715,14 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q39" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R39" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R39" s="3" t="s">
+        <v>799</v>
+      </c>
     </row>
     <row r="40" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A40" s="3">
@@ -8769,7 +9754,7 @@
         <v>80</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K40" s="3" t="s">
         <v>4</v>
@@ -8781,12 +9766,14 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q40" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R40" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R40" s="3" t="s">
+        <v>800</v>
+      </c>
     </row>
     <row r="41" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A41" s="3">
@@ -8818,7 +9805,7 @@
         <v>367</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>4</v>
@@ -8830,12 +9817,14 @@
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
       <c r="P41" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q41" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R41" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>801</v>
+      </c>
     </row>
     <row r="42" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A42" s="3">
@@ -8867,7 +9856,7 @@
         <v>82</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>4</v>
@@ -8879,12 +9868,14 @@
       <c r="N42" s="3"/>
       <c r="O42" s="3"/>
       <c r="P42" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q42" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R42" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>802</v>
+      </c>
     </row>
     <row r="43" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A43" s="3">
@@ -8916,7 +9907,7 @@
         <v>369</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
@@ -8928,12 +9919,14 @@
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
       <c r="P43" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q43" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R43" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>803</v>
+      </c>
     </row>
     <row r="44" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A44" s="3">
@@ -8965,7 +9958,7 @@
         <v>371</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>4</v>
@@ -8977,12 +9970,14 @@
       <c r="N44" s="3"/>
       <c r="O44" s="3"/>
       <c r="P44" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q44" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R44" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>804</v>
+      </c>
     </row>
     <row r="45" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A45" s="3">
@@ -9014,7 +10009,7 @@
         <v>84</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>4</v>
@@ -9026,12 +10021,14 @@
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q45" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R45" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>805</v>
+      </c>
     </row>
     <row r="46" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A46" s="3">
@@ -9063,7 +10060,7 @@
         <v>86</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>4</v>
@@ -9075,12 +10072,14 @@
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
       <c r="P46" s="7" t="s">
+        <v>756</v>
+      </c>
+      <c r="Q46" s="7" t="s">
         <v>757</v>
       </c>
-      <c r="Q46" s="7" t="s">
-        <v>758</v>
-      </c>
-      <c r="R46" s="3"/>
+      <c r="R46" s="3" t="s">
+        <v>806</v>
+      </c>
     </row>
     <row r="47" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A47" s="3">
@@ -9112,7 +10111,7 @@
         <v>460</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>4</v>
@@ -9124,12 +10123,14 @@
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
       <c r="P47" s="7" t="s">
+        <v>756</v>
+      </c>
+      <c r="Q47" s="7" t="s">
         <v>757</v>
       </c>
-      <c r="Q47" s="7" t="s">
-        <v>758</v>
-      </c>
-      <c r="R47" s="3"/>
+      <c r="R47" s="3" t="s">
+        <v>807</v>
+      </c>
     </row>
     <row r="48" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A48" s="3">
@@ -9161,7 +10162,7 @@
         <v>88</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>4</v>
@@ -9173,12 +10174,14 @@
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
       <c r="P48" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q48" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R48" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>808</v>
+      </c>
     </row>
     <row r="49" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A49" s="3">
@@ -9210,7 +10213,7 @@
         <v>90</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>4</v>
@@ -9222,12 +10225,14 @@
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
       <c r="P49" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q49" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R49" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>809</v>
+      </c>
     </row>
     <row r="50" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A50" s="3">
@@ -9259,7 +10264,7 @@
         <v>92</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>4</v>
@@ -9271,12 +10276,14 @@
       <c r="N50" s="3"/>
       <c r="O50" s="3"/>
       <c r="P50" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q50" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R50" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R50" s="3" t="s">
+        <v>810</v>
+      </c>
     </row>
     <row r="51" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A51" s="3">
@@ -9308,7 +10315,7 @@
         <v>94</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="K51" s="3" t="s">
         <v>4</v>
@@ -9320,12 +10327,14 @@
       <c r="N51" s="3"/>
       <c r="O51" s="3"/>
       <c r="P51" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q51" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R51" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R51" s="3" t="s">
+        <v>811</v>
+      </c>
     </row>
     <row r="52" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A52" s="3">
@@ -9357,7 +10366,7 @@
         <v>451</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>4</v>
@@ -9369,12 +10378,14 @@
       <c r="N52" s="3"/>
       <c r="O52" s="3"/>
       <c r="P52" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q52" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R52" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>812</v>
+      </c>
     </row>
     <row r="53" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A53" s="3">
@@ -9406,7 +10417,7 @@
         <v>95</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="K53" s="3" t="s">
         <v>4</v>
@@ -9418,12 +10429,14 @@
       <c r="N53" s="3"/>
       <c r="O53" s="3"/>
       <c r="P53" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q53" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R53" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R53" s="3" t="s">
+        <v>813</v>
+      </c>
     </row>
     <row r="54" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A54" s="3">
@@ -9455,7 +10468,7 @@
         <v>455</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>4</v>
@@ -9467,12 +10480,14 @@
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q54" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R54" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>814</v>
+      </c>
     </row>
     <row r="55" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A55" s="3">
@@ -9504,7 +10519,7 @@
         <v>97</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="K55" s="3" t="s">
         <v>4</v>
@@ -9516,12 +10531,14 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q55" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R55" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R55" s="3" t="s">
+        <v>815</v>
+      </c>
     </row>
     <row r="56" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A56" s="3">
@@ -9553,7 +10570,7 @@
         <v>99</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="K56" s="3" t="s">
         <v>4</v>
@@ -9565,12 +10582,14 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q56" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R56" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R56" s="3" t="s">
+        <v>816</v>
+      </c>
     </row>
     <row r="57" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A57" s="3">
@@ -9602,7 +10621,7 @@
         <v>101</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>4</v>
@@ -9614,12 +10633,14 @@
       <c r="N57" s="3"/>
       <c r="O57" s="3"/>
       <c r="P57" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q57" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R57" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>817</v>
+      </c>
     </row>
     <row r="58" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A58" s="3">
@@ -9651,7 +10672,7 @@
         <v>474</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>4</v>
@@ -9663,12 +10684,14 @@
       <c r="N58" s="3"/>
       <c r="O58" s="3"/>
       <c r="P58" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q58" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R58" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>818</v>
+      </c>
     </row>
     <row r="59" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A59" s="3">
@@ -9700,7 +10723,7 @@
         <v>381</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>4</v>
@@ -9712,12 +10735,14 @@
       <c r="N59" s="3"/>
       <c r="O59" s="3"/>
       <c r="P59" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q59" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R59" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>819</v>
+      </c>
     </row>
     <row r="60" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A60" s="3">
@@ -9749,7 +10774,7 @@
         <v>103</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>4</v>
@@ -9761,12 +10786,14 @@
       <c r="N60" s="3"/>
       <c r="O60" s="3"/>
       <c r="P60" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q60" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R60" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>820</v>
+      </c>
     </row>
     <row r="61" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A61" s="3">
@@ -9798,7 +10825,7 @@
         <v>355</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K61" s="3" t="s">
         <v>4</v>
@@ -9810,12 +10837,14 @@
       <c r="N61" s="3"/>
       <c r="O61" s="3"/>
       <c r="P61" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="Q61" s="7" t="s">
         <v>753</v>
       </c>
-      <c r="Q61" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="R61" s="3"/>
+      <c r="R61" s="3" t="s">
+        <v>821</v>
+      </c>
     </row>
     <row r="62" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A62" s="3">
@@ -9847,7 +10876,7 @@
         <v>389</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>4</v>
@@ -9859,12 +10888,14 @@
       <c r="N62" s="3"/>
       <c r="O62" s="3"/>
       <c r="P62" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="Q62" s="7" t="s">
         <v>753</v>
       </c>
-      <c r="Q62" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="R62" s="3"/>
+      <c r="R62" s="3" t="s">
+        <v>822</v>
+      </c>
     </row>
     <row r="63" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A63" s="3">
@@ -9896,7 +10927,7 @@
         <v>385</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="K63" s="7" t="s">
         <v>723</v>
@@ -9908,12 +10939,14 @@
       <c r="N63" s="3"/>
       <c r="O63" s="3"/>
       <c r="P63" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q63" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q63" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R63" s="3"/>
+      <c r="R63" s="3" t="s">
+        <v>823</v>
+      </c>
     </row>
     <row r="64" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A64" s="3">
@@ -9945,7 +10978,7 @@
         <v>105</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="K64" s="7" t="s">
         <v>723</v>
@@ -9957,12 +10990,14 @@
       <c r="N64" s="3"/>
       <c r="O64" s="3"/>
       <c r="P64" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q64" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R64" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R64" s="3" t="s">
+        <v>824</v>
+      </c>
     </row>
     <row r="65" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A65" s="3">
@@ -9994,7 +11029,7 @@
         <v>465</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K65" s="3" t="s">
         <v>110</v>
@@ -10006,12 +11041,14 @@
       <c r="N65" s="3"/>
       <c r="O65" s="3"/>
       <c r="P65" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q65" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R65" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R65" s="3" t="s">
+        <v>825</v>
+      </c>
     </row>
     <row r="66" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A66" s="3">
@@ -10043,7 +11080,7 @@
         <v>112</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>110</v>
@@ -10055,12 +11092,14 @@
       <c r="N66" s="3"/>
       <c r="O66" s="3"/>
       <c r="P66" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q66" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R66" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>826</v>
+      </c>
     </row>
     <row r="67" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A67" s="3">
@@ -10092,7 +11131,7 @@
         <v>463</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K67" s="3" t="s">
         <v>110</v>
@@ -10104,12 +11143,14 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q67" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R67" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R67" s="3" t="s">
+        <v>827</v>
+      </c>
     </row>
     <row r="68" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A68" s="3">
@@ -10141,7 +11182,7 @@
         <v>113</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K68" s="3" t="s">
         <v>110</v>
@@ -10153,12 +11194,14 @@
       <c r="N68" s="3"/>
       <c r="O68" s="3"/>
       <c r="P68" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q68" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R68" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R68" s="3" t="s">
+        <v>828</v>
+      </c>
     </row>
     <row r="69" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A69" s="3">
@@ -10190,7 +11233,7 @@
         <v>114</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K69" s="3" t="s">
         <v>115</v>
@@ -10202,12 +11245,14 @@
       <c r="N69" s="3"/>
       <c r="O69" s="3"/>
       <c r="P69" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q69" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R69" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R69" s="3" t="s">
+        <v>829</v>
+      </c>
     </row>
     <row r="70" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A70" s="3">
@@ -10239,7 +11284,7 @@
         <v>117</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K70" s="3" t="s">
         <v>115</v>
@@ -10251,12 +11296,14 @@
       <c r="N70" s="3"/>
       <c r="O70" s="3"/>
       <c r="P70" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q70" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R70" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R70" s="3" t="s">
+        <v>830</v>
+      </c>
     </row>
     <row r="71" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A71" s="3">
@@ -10288,7 +11335,7 @@
         <v>119</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K71" s="3" t="s">
         <v>110</v>
@@ -10300,12 +11347,14 @@
       <c r="N71" s="3"/>
       <c r="O71" s="3"/>
       <c r="P71" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q71" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R71" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R71" s="3" t="s">
+        <v>831</v>
+      </c>
     </row>
     <row r="72" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A72" s="3">
@@ -10337,7 +11386,7 @@
         <v>120</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>110</v>
@@ -10349,12 +11398,14 @@
       <c r="N72" s="3"/>
       <c r="O72" s="3"/>
       <c r="P72" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q72" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q72" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R72" s="3"/>
+      <c r="R72" s="3" t="s">
+        <v>832</v>
+      </c>
     </row>
     <row r="73" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A73" s="3">
@@ -10386,7 +11437,7 @@
         <v>121</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K73" s="3" t="s">
         <v>110</v>
@@ -10398,12 +11449,14 @@
       <c r="N73" s="3"/>
       <c r="O73" s="3"/>
       <c r="P73" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q73" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R73" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R73" s="3" t="s">
+        <v>833</v>
+      </c>
     </row>
     <row r="74" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A74" s="3">
@@ -10435,7 +11488,7 @@
         <v>122</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K74" s="3" t="s">
         <v>110</v>
@@ -10447,12 +11500,14 @@
       <c r="N74" s="3"/>
       <c r="O74" s="3"/>
       <c r="P74" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q74" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q74" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R74" s="3"/>
+      <c r="R74" s="3" t="s">
+        <v>834</v>
+      </c>
     </row>
     <row r="75" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A75" s="3">
@@ -10484,7 +11539,7 @@
         <v>123</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K75" s="3" t="s">
         <v>115</v>
@@ -10496,12 +11551,14 @@
       <c r="N75" s="3"/>
       <c r="O75" s="3"/>
       <c r="P75" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q75" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R75" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R75" s="3" t="s">
+        <v>835</v>
+      </c>
     </row>
     <row r="76" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A76" s="3">
@@ -10533,7 +11590,7 @@
         <v>124</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>115</v>
@@ -10545,12 +11602,14 @@
       <c r="N76" s="3"/>
       <c r="O76" s="3"/>
       <c r="P76" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q76" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R76" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R76" s="3" t="s">
+        <v>836</v>
+      </c>
     </row>
     <row r="77" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A77" s="3">
@@ -10582,7 +11641,7 @@
         <v>126</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="K77" s="3" t="s">
         <v>110</v>
@@ -10594,12 +11653,14 @@
       <c r="N77" s="3"/>
       <c r="O77" s="3"/>
       <c r="P77" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q77" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R77" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R77" s="3" t="s">
+        <v>837</v>
+      </c>
     </row>
     <row r="78" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A78" s="3">
@@ -10631,7 +11692,7 @@
         <v>127</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="K78" s="3" t="s">
         <v>110</v>
@@ -10643,12 +11704,14 @@
       <c r="N78" s="3"/>
       <c r="O78" s="3"/>
       <c r="P78" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q78" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R78" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R78" s="3" t="s">
+        <v>838</v>
+      </c>
     </row>
     <row r="79" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A79" s="3">
@@ -10680,7 +11743,7 @@
         <v>128</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="K79" s="3" t="s">
         <v>110</v>
@@ -10692,12 +11755,14 @@
       <c r="N79" s="3"/>
       <c r="O79" s="3"/>
       <c r="P79" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q79" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R79" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R79" s="3" t="s">
+        <v>839</v>
+      </c>
     </row>
     <row r="80" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A80" s="3">
@@ -10729,7 +11794,7 @@
         <v>129</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="K80" s="3" t="s">
         <v>110</v>
@@ -10741,12 +11806,14 @@
       <c r="N80" s="3"/>
       <c r="O80" s="3"/>
       <c r="P80" s="7" t="s">
+        <v>754</v>
+      </c>
+      <c r="Q80" s="7" t="s">
         <v>755</v>
       </c>
-      <c r="Q80" s="7" t="s">
-        <v>756</v>
-      </c>
-      <c r="R80" s="3"/>
+      <c r="R80" s="3" t="s">
+        <v>840</v>
+      </c>
     </row>
     <row r="81" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A81" s="3">
@@ -10778,7 +11845,7 @@
         <v>130</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>115</v>
@@ -10790,12 +11857,14 @@
       <c r="N81" s="3"/>
       <c r="O81" s="3"/>
       <c r="P81" s="7" t="s">
+        <v>754</v>
+      </c>
+      <c r="Q81" s="7" t="s">
         <v>755</v>
       </c>
-      <c r="Q81" s="7" t="s">
-        <v>756</v>
-      </c>
-      <c r="R81" s="3"/>
+      <c r="R81" s="3" t="s">
+        <v>841</v>
+      </c>
     </row>
     <row r="82" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A82" s="3">
@@ -10827,7 +11896,7 @@
         <v>131</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="K82" s="3" t="s">
         <v>115</v>
@@ -10839,12 +11908,14 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="7" t="s">
+        <v>756</v>
+      </c>
+      <c r="Q82" s="7" t="s">
         <v>757</v>
       </c>
-      <c r="Q82" s="7" t="s">
-        <v>758</v>
-      </c>
-      <c r="R82" s="3"/>
+      <c r="R82" s="3" t="s">
+        <v>842</v>
+      </c>
     </row>
     <row r="83" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A83" s="3">
@@ -10876,7 +11947,7 @@
         <v>134</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>110</v>
@@ -10888,12 +11959,14 @@
       <c r="N83" s="3"/>
       <c r="O83" s="3"/>
       <c r="P83" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q83" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R83" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>843</v>
+      </c>
     </row>
     <row r="84" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A84" s="3">
@@ -10925,7 +11998,7 @@
         <v>135</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K84" s="3" t="s">
         <v>110</v>
@@ -10937,12 +12010,14 @@
       <c r="N84" s="3"/>
       <c r="O84" s="3"/>
       <c r="P84" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q84" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R84" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R84" s="3" t="s">
+        <v>844</v>
+      </c>
     </row>
     <row r="85" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A85" s="3">
@@ -10974,7 +12049,7 @@
         <v>467</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K85" s="3" t="s">
         <v>110</v>
@@ -10986,12 +12061,14 @@
       <c r="N85" s="3"/>
       <c r="O85" s="3"/>
       <c r="P85" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="Q85" s="7" t="s">
         <v>751</v>
       </c>
-      <c r="Q85" s="7" t="s">
-        <v>752</v>
-      </c>
-      <c r="R85" s="3"/>
+      <c r="R85" s="3" t="s">
+        <v>845</v>
+      </c>
     </row>
     <row r="86" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A86" s="3">
@@ -11023,7 +12100,7 @@
         <v>392</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K86" s="3" t="s">
         <v>110</v>
@@ -11035,12 +12112,14 @@
       <c r="N86" s="3"/>
       <c r="O86" s="3"/>
       <c r="P86" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q86" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R86" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R86" s="3" t="s">
+        <v>846</v>
+      </c>
     </row>
     <row r="87" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A87" s="3">
@@ -11072,7 +12151,7 @@
         <v>363</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K87" s="3" t="s">
         <v>115</v>
@@ -11084,12 +12163,14 @@
       <c r="N87" s="3"/>
       <c r="O87" s="3"/>
       <c r="P87" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q87" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R87" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R87" s="3" t="s">
+        <v>847</v>
+      </c>
     </row>
     <row r="88" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A88" s="3">
@@ -11121,7 +12202,7 @@
         <v>137</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K88" s="3" t="s">
         <v>115</v>
@@ -11133,12 +12214,14 @@
       <c r="N88" s="3"/>
       <c r="O88" s="3"/>
       <c r="P88" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q88" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R88" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R88" s="3" t="s">
+        <v>848</v>
+      </c>
     </row>
     <row r="89" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A89" s="3">
@@ -11170,7 +12253,7 @@
         <v>139</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>110</v>
@@ -11182,12 +12265,14 @@
       <c r="N89" s="3"/>
       <c r="O89" s="3"/>
       <c r="P89" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q89" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R89" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>849</v>
+      </c>
     </row>
     <row r="90" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A90" s="3">
@@ -11219,7 +12304,7 @@
         <v>140</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K90" s="3" t="s">
         <v>110</v>
@@ -11231,12 +12316,14 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q90" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R90" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R90" s="3" t="s">
+        <v>850</v>
+      </c>
     </row>
     <row r="91" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A91" s="3">
@@ -11268,7 +12355,7 @@
         <v>141</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>110</v>
@@ -11280,12 +12367,14 @@
       <c r="N91" s="3"/>
       <c r="O91" s="3"/>
       <c r="P91" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q91" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R91" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>851</v>
+      </c>
     </row>
     <row r="92" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A92" s="3">
@@ -11317,7 +12406,7 @@
         <v>142</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K92" s="3" t="s">
         <v>110</v>
@@ -11329,12 +12418,14 @@
       <c r="N92" s="3"/>
       <c r="O92" s="3"/>
       <c r="P92" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q92" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R92" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R92" s="3" t="s">
+        <v>852</v>
+      </c>
     </row>
     <row r="93" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A93" s="3">
@@ -11366,7 +12457,7 @@
         <v>143</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="K93" s="3" t="s">
         <v>115</v>
@@ -11378,12 +12469,14 @@
       <c r="N93" s="3"/>
       <c r="O93" s="3"/>
       <c r="P93" s="7" t="s">
+        <v>754</v>
+      </c>
+      <c r="Q93" s="7" t="s">
         <v>755</v>
       </c>
-      <c r="Q93" s="7" t="s">
-        <v>756</v>
-      </c>
-      <c r="R93" s="3"/>
+      <c r="R93" s="3" t="s">
+        <v>853</v>
+      </c>
     </row>
     <row r="94" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A94" s="3">
@@ -11402,7 +12495,7 @@
         <v>109</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="G94" s="5" t="s">
         <v>470</v>
@@ -11412,10 +12505,10 @@
         <v>9</v>
       </c>
       <c r="I94" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>115</v>
@@ -11427,12 +12520,14 @@
       <c r="N94" s="3"/>
       <c r="O94" s="3"/>
       <c r="P94" s="7" t="s">
+        <v>756</v>
+      </c>
+      <c r="Q94" s="7" t="s">
         <v>757</v>
       </c>
-      <c r="Q94" s="7" t="s">
-        <v>758</v>
-      </c>
-      <c r="R94" s="3"/>
+      <c r="R94" s="3" t="s">
+        <v>854</v>
+      </c>
     </row>
     <row r="95" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A95" s="3">
@@ -11464,7 +12559,7 @@
         <v>456</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="K95" s="3" t="s">
         <v>110</v>
@@ -11476,12 +12571,14 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q95" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R95" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R95" s="3" t="s">
+        <v>855</v>
+      </c>
     </row>
     <row r="96" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A96" s="3">
@@ -11513,7 +12610,7 @@
         <v>145</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>110</v>
@@ -11525,12 +12622,14 @@
       <c r="N96" s="3"/>
       <c r="O96" s="3"/>
       <c r="P96" s="7" t="s">
+        <v>754</v>
+      </c>
+      <c r="Q96" s="7" t="s">
         <v>755</v>
       </c>
-      <c r="Q96" s="7" t="s">
-        <v>756</v>
-      </c>
-      <c r="R96" s="3"/>
+      <c r="R96" s="3" t="s">
+        <v>856</v>
+      </c>
     </row>
     <row r="97" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A97" s="3">
@@ -11562,7 +12661,7 @@
         <v>146</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="K97" s="3" t="s">
         <v>110</v>
@@ -11574,12 +12673,14 @@
       <c r="N97" s="3"/>
       <c r="O97" s="3"/>
       <c r="P97" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q97" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R97" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R97" s="3" t="s">
+        <v>857</v>
+      </c>
     </row>
     <row r="98" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A98" s="3">
@@ -11611,7 +12712,7 @@
         <v>147</v>
       </c>
       <c r="J98" s="7" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="K98" s="3" t="s">
         <v>110</v>
@@ -11623,12 +12724,14 @@
       <c r="N98" s="3"/>
       <c r="O98" s="3"/>
       <c r="P98" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q98" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R98" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R98" s="3" t="s">
+        <v>858</v>
+      </c>
     </row>
     <row r="99" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A99" s="3">
@@ -11660,7 +12763,7 @@
         <v>148</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="K99" s="3" t="s">
         <v>115</v>
@@ -11672,12 +12775,14 @@
       <c r="N99" s="3"/>
       <c r="O99" s="3"/>
       <c r="P99" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q99" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R99" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R99" s="3" t="s">
+        <v>859</v>
+      </c>
     </row>
     <row r="100" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A100" s="3">
@@ -11709,7 +12814,7 @@
         <v>149</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>115</v>
@@ -11721,12 +12826,14 @@
       <c r="N100" s="3"/>
       <c r="O100" s="3"/>
       <c r="P100" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q100" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R100" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>860</v>
+      </c>
     </row>
     <row r="101" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A101" s="3">
@@ -11758,7 +12865,7 @@
         <v>151</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>110</v>
@@ -11770,12 +12877,14 @@
       <c r="N101" s="3"/>
       <c r="O101" s="3"/>
       <c r="P101" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q101" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R101" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>861</v>
+      </c>
     </row>
     <row r="102" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A102" s="3">
@@ -11807,7 +12916,7 @@
         <v>152</v>
       </c>
       <c r="J102" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>110</v>
@@ -11819,12 +12928,14 @@
       <c r="N102" s="3"/>
       <c r="O102" s="3"/>
       <c r="P102" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q102" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q102" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R102" s="3"/>
+      <c r="R102" s="3" t="s">
+        <v>862</v>
+      </c>
     </row>
     <row r="103" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A103" s="3">
@@ -11856,7 +12967,7 @@
         <v>395</v>
       </c>
       <c r="J103" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K103" s="3" t="s">
         <v>110</v>
@@ -11868,12 +12979,14 @@
       <c r="N103" s="3"/>
       <c r="O103" s="3"/>
       <c r="P103" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q103" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q103" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R103" s="3"/>
+      <c r="R103" s="3" t="s">
+        <v>863</v>
+      </c>
     </row>
     <row r="104" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A104" s="3">
@@ -11905,7 +13018,7 @@
         <v>478</v>
       </c>
       <c r="J104" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K104" s="3" t="s">
         <v>110</v>
@@ -11917,12 +13030,14 @@
       <c r="N104" s="3"/>
       <c r="O104" s="3"/>
       <c r="P104" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q104" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q104" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R104" s="3"/>
+      <c r="R104" s="3" t="s">
+        <v>864</v>
+      </c>
     </row>
     <row r="105" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A105" s="3">
@@ -11954,7 +13069,7 @@
         <v>153</v>
       </c>
       <c r="J105" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K105" s="3" t="s">
         <v>115</v>
@@ -11966,12 +13081,14 @@
       <c r="N105" s="3"/>
       <c r="O105" s="3"/>
       <c r="P105" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q105" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R105" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R105" s="3" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="106" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A106" s="3">
@@ -12003,7 +13120,7 @@
         <v>154</v>
       </c>
       <c r="J106" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K106" s="3" t="s">
         <v>115</v>
@@ -12015,12 +13132,14 @@
       <c r="N106" s="3"/>
       <c r="O106" s="3"/>
       <c r="P106" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q106" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q106" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R106" s="3"/>
+      <c r="R106" s="3" t="s">
+        <v>866</v>
+      </c>
     </row>
     <row r="107" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A107" s="3">
@@ -12052,7 +13171,7 @@
         <v>163</v>
       </c>
       <c r="J107" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K107" s="3" t="s">
         <v>110</v>
@@ -12064,12 +13183,14 @@
       <c r="N107" s="3"/>
       <c r="O107" s="3"/>
       <c r="P107" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="Q107" s="7" t="s">
         <v>753</v>
       </c>
-      <c r="Q107" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="R107" s="3"/>
+      <c r="R107" s="3" t="s">
+        <v>867</v>
+      </c>
     </row>
     <row r="108" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A108" s="3">
@@ -12101,7 +13222,7 @@
         <v>359</v>
       </c>
       <c r="J108" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K108" s="3" t="s">
         <v>110</v>
@@ -12113,12 +13234,14 @@
       <c r="N108" s="3"/>
       <c r="O108" s="3"/>
       <c r="P108" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="Q108" s="7" t="s">
         <v>753</v>
       </c>
-      <c r="Q108" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="R108" s="3"/>
+      <c r="R108" s="3" t="s">
+        <v>868</v>
+      </c>
     </row>
     <row r="109" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A109" s="3">
@@ -12150,7 +13273,7 @@
         <v>157</v>
       </c>
       <c r="J109" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K109" s="3" t="s">
         <v>110</v>
@@ -12162,12 +13285,14 @@
       <c r="N109" s="3"/>
       <c r="O109" s="3"/>
       <c r="P109" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q109" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R109" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R109" s="3" t="s">
+        <v>869</v>
+      </c>
     </row>
     <row r="110" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A110" s="3">
@@ -12199,7 +13324,7 @@
         <v>469</v>
       </c>
       <c r="J110" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K110" s="3" t="s">
         <v>110</v>
@@ -12211,12 +13336,14 @@
       <c r="N110" s="3"/>
       <c r="O110" s="3"/>
       <c r="P110" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="Q110" s="7" t="s">
         <v>751</v>
       </c>
-      <c r="Q110" s="7" t="s">
-        <v>752</v>
-      </c>
-      <c r="R110" s="3"/>
+      <c r="R110" s="3" t="s">
+        <v>870</v>
+      </c>
     </row>
     <row r="111" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A111" s="3">
@@ -12248,7 +13375,7 @@
         <v>361</v>
       </c>
       <c r="J111" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K111" s="3" t="s">
         <v>115</v>
@@ -12260,12 +13387,14 @@
       <c r="N111" s="3"/>
       <c r="O111" s="3"/>
       <c r="P111" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q111" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R111" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R111" s="3" t="s">
+        <v>871</v>
+      </c>
     </row>
     <row r="112" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A112" s="3">
@@ -12297,7 +13426,7 @@
         <v>357</v>
       </c>
       <c r="J112" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K112" s="3" t="s">
         <v>115</v>
@@ -12309,12 +13438,14 @@
       <c r="N112" s="3"/>
       <c r="O112" s="3"/>
       <c r="P112" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="Q112" s="7" t="s">
         <v>753</v>
       </c>
-      <c r="Q112" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="R112" s="3"/>
+      <c r="R112" s="3" t="s">
+        <v>872</v>
+      </c>
     </row>
     <row r="113" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A113" s="7">
@@ -12346,7 +13477,7 @@
         <v>164</v>
       </c>
       <c r="J113" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K113" s="7" t="s">
         <v>110</v>
@@ -12358,12 +13489,14 @@
       <c r="N113" s="3"/>
       <c r="O113" s="3"/>
       <c r="P113" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="Q113" s="7" t="s">
         <v>753</v>
       </c>
-      <c r="Q113" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="R113" s="3"/>
+      <c r="R113" s="3" t="s">
+        <v>873</v>
+      </c>
     </row>
     <row r="114" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A114" s="7">
@@ -12395,7 +13528,7 @@
         <v>165</v>
       </c>
       <c r="J114" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K114" s="7" t="s">
         <v>110</v>
@@ -12407,12 +13540,14 @@
       <c r="N114" s="3"/>
       <c r="O114" s="3"/>
       <c r="P114" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="Q114" s="7" t="s">
         <v>753</v>
       </c>
-      <c r="Q114" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="R114" s="3"/>
+      <c r="R114" s="3" t="s">
+        <v>874</v>
+      </c>
     </row>
     <row r="115" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A115" s="7">
@@ -12444,7 +13579,7 @@
         <v>136</v>
       </c>
       <c r="J115" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K115" s="7" t="s">
         <v>110</v>
@@ -12456,12 +13591,14 @@
       <c r="N115" s="3"/>
       <c r="O115" s="3"/>
       <c r="P115" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q115" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R115" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R115" s="3" t="s">
+        <v>875</v>
+      </c>
     </row>
     <row r="116" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A116" s="7">
@@ -12493,7 +13630,7 @@
         <v>166</v>
       </c>
       <c r="J116" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="K116" s="7" t="s">
         <v>110</v>
@@ -12505,12 +13642,14 @@
       <c r="N116" s="3"/>
       <c r="O116" s="3"/>
       <c r="P116" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q116" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R116" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R116" s="3" t="s">
+        <v>876</v>
+      </c>
     </row>
     <row r="117" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A117" s="7">
@@ -12542,7 +13681,7 @@
         <v>167</v>
       </c>
       <c r="J117" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="K117" s="7" t="s">
         <v>110</v>
@@ -12554,12 +13693,14 @@
       <c r="N117" s="3"/>
       <c r="O117" s="3"/>
       <c r="P117" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q117" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R117" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R117" s="3" t="s">
+        <v>877</v>
+      </c>
     </row>
     <row r="118" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A118" s="7">
@@ -12591,7 +13732,7 @@
         <v>168</v>
       </c>
       <c r="J118" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K118" s="7" t="s">
         <v>110</v>
@@ -12603,12 +13744,14 @@
       <c r="N118" s="3"/>
       <c r="O118" s="3"/>
       <c r="P118" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q118" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R118" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R118" s="3" t="s">
+        <v>878</v>
+      </c>
     </row>
     <row r="119" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A119" s="7">
@@ -12640,7 +13783,7 @@
         <v>347</v>
       </c>
       <c r="J119" s="7" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="K119" s="7" t="s">
         <v>110</v>
@@ -12652,12 +13795,14 @@
       <c r="N119" s="3"/>
       <c r="O119" s="3"/>
       <c r="P119" s="7" t="s">
+        <v>756</v>
+      </c>
+      <c r="Q119" s="7" t="s">
         <v>757</v>
       </c>
-      <c r="Q119" s="7" t="s">
-        <v>758</v>
-      </c>
-      <c r="R119" s="3"/>
+      <c r="R119" s="3" t="s">
+        <v>879</v>
+      </c>
     </row>
     <row r="120" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A120" s="7">
@@ -12689,7 +13834,7 @@
         <v>397</v>
       </c>
       <c r="J120" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K120" s="7" t="s">
         <v>398</v>
@@ -12701,12 +13846,14 @@
       <c r="N120" s="3"/>
       <c r="O120" s="3"/>
       <c r="P120" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q120" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R120" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R120" s="3" t="s">
+        <v>880</v>
+      </c>
     </row>
     <row r="121" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A121" s="7">
@@ -12738,7 +13885,7 @@
         <v>402</v>
       </c>
       <c r="J121" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K121" s="7" t="s">
         <v>398</v>
@@ -12750,12 +13897,14 @@
       <c r="N121" s="3"/>
       <c r="O121" s="3"/>
       <c r="P121" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q121" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R121" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R121" s="3" t="s">
+        <v>881</v>
+      </c>
     </row>
     <row r="122" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A122" s="7">
@@ -12787,7 +13936,7 @@
         <v>404</v>
       </c>
       <c r="J122" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K122" s="7" t="s">
         <v>110</v>
@@ -12799,12 +13948,14 @@
       <c r="N122" s="3"/>
       <c r="O122" s="3"/>
       <c r="P122" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q122" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q122" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R122" s="3"/>
+      <c r="R122" s="3" t="s">
+        <v>882</v>
+      </c>
     </row>
     <row r="123" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A123" s="7">
@@ -12836,7 +13987,7 @@
         <v>406</v>
       </c>
       <c r="J123" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K123" s="7" t="s">
         <v>110</v>
@@ -12848,12 +13999,14 @@
       <c r="N123" s="3"/>
       <c r="O123" s="3"/>
       <c r="P123" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q123" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q123" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R123" s="3"/>
+      <c r="R123" s="3" t="s">
+        <v>883</v>
+      </c>
     </row>
     <row r="124" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A124" s="7">
@@ -12885,7 +14038,7 @@
         <v>408</v>
       </c>
       <c r="J124" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K124" s="7" t="s">
         <v>110</v>
@@ -12897,12 +14050,14 @@
       <c r="N124" s="3"/>
       <c r="O124" s="3"/>
       <c r="P124" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q124" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q124" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R124" s="3"/>
+      <c r="R124" s="3" t="s">
+        <v>884</v>
+      </c>
     </row>
     <row r="125" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A125" s="7">
@@ -12934,7 +14089,7 @@
         <v>410</v>
       </c>
       <c r="J125" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K125" s="7" t="s">
         <v>110</v>
@@ -12946,12 +14101,14 @@
       <c r="N125" s="3"/>
       <c r="O125" s="3"/>
       <c r="P125" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q125" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q125" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R125" s="3"/>
+      <c r="R125" s="3" t="s">
+        <v>885</v>
+      </c>
     </row>
     <row r="126" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A126" s="7">
@@ -12983,7 +14140,7 @@
         <v>412</v>
       </c>
       <c r="J126" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K126" s="7" t="s">
         <v>110</v>
@@ -12995,12 +14152,14 @@
       <c r="N126" s="3"/>
       <c r="O126" s="3"/>
       <c r="P126" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q126" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R126" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R126" s="3" t="s">
+        <v>886</v>
+      </c>
     </row>
     <row r="127" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A127" s="7">
@@ -13032,7 +14191,7 @@
         <v>414</v>
       </c>
       <c r="J127" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K127" s="7" t="s">
         <v>110</v>
@@ -13044,12 +14203,14 @@
       <c r="N127" s="3"/>
       <c r="O127" s="3"/>
       <c r="P127" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q127" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R127" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R127" s="3" t="s">
+        <v>887</v>
+      </c>
     </row>
     <row r="128" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A128" s="7">
@@ -13081,7 +14242,7 @@
         <v>416</v>
       </c>
       <c r="J128" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="K128" s="7" t="s">
         <v>110</v>
@@ -13093,12 +14254,14 @@
       <c r="N128" s="3"/>
       <c r="O128" s="3"/>
       <c r="P128" s="7" t="s">
+        <v>754</v>
+      </c>
+      <c r="Q128" s="7" t="s">
         <v>755</v>
       </c>
-      <c r="Q128" s="7" t="s">
-        <v>756</v>
-      </c>
-      <c r="R128" s="3"/>
+      <c r="R128" s="3" t="s">
+        <v>888</v>
+      </c>
     </row>
     <row r="129" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A129" s="7">
@@ -13130,7 +14293,7 @@
         <v>418</v>
       </c>
       <c r="J129" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="K129" s="7" t="s">
         <v>110</v>
@@ -13142,12 +14305,14 @@
       <c r="N129" s="3"/>
       <c r="O129" s="3"/>
       <c r="P129" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q129" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R129" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R129" s="3" t="s">
+        <v>889</v>
+      </c>
     </row>
     <row r="130" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A130" s="7">
@@ -13179,7 +14344,7 @@
         <v>420</v>
       </c>
       <c r="J130" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="K130" s="7" t="s">
         <v>110</v>
@@ -13191,12 +14356,14 @@
       <c r="N130" s="3"/>
       <c r="O130" s="3"/>
       <c r="P130" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="Q130" s="7" t="s">
         <v>751</v>
       </c>
-      <c r="Q130" s="7" t="s">
-        <v>752</v>
-      </c>
-      <c r="R130" s="3"/>
+      <c r="R130" s="3" t="s">
+        <v>890</v>
+      </c>
     </row>
     <row r="131" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A131" s="7">
@@ -13228,7 +14395,7 @@
         <v>422</v>
       </c>
       <c r="J131" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K131" s="7" t="s">
         <v>110</v>
@@ -13240,12 +14407,14 @@
       <c r="N131" s="3"/>
       <c r="O131" s="3"/>
       <c r="P131" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="Q131" s="7" t="s">
         <v>751</v>
       </c>
-      <c r="Q131" s="7" t="s">
-        <v>752</v>
-      </c>
-      <c r="R131" s="3"/>
+      <c r="R131" s="3" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="132" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A132" s="7">
@@ -13277,7 +14446,7 @@
         <v>424</v>
       </c>
       <c r="J132" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K132" s="7" t="s">
         <v>110</v>
@@ -13289,12 +14458,14 @@
       <c r="N132" s="3"/>
       <c r="O132" s="3"/>
       <c r="P132" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q132" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R132" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R132" s="3" t="s">
+        <v>892</v>
+      </c>
     </row>
     <row r="133" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A133" s="7">
@@ -13326,7 +14497,7 @@
         <v>426</v>
       </c>
       <c r="J133" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K133" s="7" t="s">
         <v>110</v>
@@ -13338,12 +14509,14 @@
       <c r="N133" s="3"/>
       <c r="O133" s="3"/>
       <c r="P133" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="Q133" s="7" t="s">
         <v>753</v>
       </c>
-      <c r="Q133" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="R133" s="3"/>
+      <c r="R133" s="3" t="s">
+        <v>893</v>
+      </c>
     </row>
     <row r="134" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A134" s="7">
@@ -13375,7 +14548,7 @@
         <v>428</v>
       </c>
       <c r="J134" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K134" s="7" t="s">
         <v>110</v>
@@ -13387,12 +14560,14 @@
       <c r="N134" s="3"/>
       <c r="O134" s="3"/>
       <c r="P134" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="Q134" s="7" t="s">
         <v>753</v>
       </c>
-      <c r="Q134" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="R134" s="3"/>
+      <c r="R134" s="3" t="s">
+        <v>894</v>
+      </c>
     </row>
     <row r="135" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A135" s="7">
@@ -13424,7 +14599,7 @@
         <v>430</v>
       </c>
       <c r="J135" s="7" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="K135" s="7" t="s">
         <v>115</v>
@@ -13436,12 +14611,14 @@
       <c r="N135" s="3"/>
       <c r="O135" s="3"/>
       <c r="P135" s="7" t="s">
+        <v>754</v>
+      </c>
+      <c r="Q135" s="7" t="s">
         <v>755</v>
       </c>
-      <c r="Q135" s="7" t="s">
-        <v>756</v>
-      </c>
-      <c r="R135" s="3"/>
+      <c r="R135" s="3" t="s">
+        <v>895</v>
+      </c>
     </row>
     <row r="136" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A136" s="7">
@@ -13473,7 +14650,7 @@
         <v>432</v>
       </c>
       <c r="J136" s="7" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="K136" s="7" t="s">
         <v>115</v>
@@ -13485,12 +14662,14 @@
       <c r="N136" s="3"/>
       <c r="O136" s="3"/>
       <c r="P136" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q136" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R136" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R136" s="3" t="s">
+        <v>896</v>
+      </c>
     </row>
     <row r="137" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A137" s="7">
@@ -13522,7 +14701,7 @@
         <v>434</v>
       </c>
       <c r="J137" s="7" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="K137" s="7" t="s">
         <v>110</v>
@@ -13534,12 +14713,14 @@
       <c r="N137" s="3"/>
       <c r="O137" s="3"/>
       <c r="P137" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q137" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R137" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R137" s="3" t="s">
+        <v>897</v>
+      </c>
     </row>
     <row r="138" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A138" s="7">
@@ -13571,7 +14752,7 @@
         <v>436</v>
       </c>
       <c r="J138" s="7" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="K138" s="7" t="s">
         <v>110</v>
@@ -13583,12 +14764,14 @@
       <c r="N138" s="3"/>
       <c r="O138" s="3"/>
       <c r="P138" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="Q138" s="7" t="s">
         <v>751</v>
       </c>
-      <c r="Q138" s="7" t="s">
-        <v>752</v>
-      </c>
-      <c r="R138" s="3"/>
+      <c r="R138" s="3" t="s">
+        <v>898</v>
+      </c>
     </row>
     <row r="139" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A139" s="7">
@@ -13620,7 +14803,7 @@
         <v>484</v>
       </c>
       <c r="J139" s="7" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="K139" s="7" t="s">
         <v>110</v>
@@ -13632,12 +14815,14 @@
       <c r="N139" s="3"/>
       <c r="O139" s="3"/>
       <c r="P139" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q139" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R139" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R139" s="3" t="s">
+        <v>899</v>
+      </c>
     </row>
     <row r="140" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A140" s="7">
@@ -13669,7 +14854,7 @@
         <v>595</v>
       </c>
       <c r="J140" s="7" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="K140" s="7" t="s">
         <v>398</v>
@@ -13681,12 +14866,14 @@
       <c r="N140" s="3"/>
       <c r="O140" s="3"/>
       <c r="P140" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q140" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R140" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R140" s="3" t="s">
+        <v>900</v>
+      </c>
     </row>
     <row r="141" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A141" s="7">
@@ -13718,7 +14905,7 @@
         <v>598</v>
       </c>
       <c r="J141" s="7" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="K141" s="7" t="s">
         <v>398</v>
@@ -13730,12 +14917,14 @@
       <c r="N141" s="3"/>
       <c r="O141" s="3"/>
       <c r="P141" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q141" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R141" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R141" s="3" t="s">
+        <v>901</v>
+      </c>
     </row>
     <row r="142" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A142" s="7">
@@ -13767,7 +14956,7 @@
         <v>601</v>
       </c>
       <c r="J142" s="7" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="K142" s="7" t="s">
         <v>398</v>
@@ -13779,12 +14968,14 @@
       <c r="N142" s="3"/>
       <c r="O142" s="3"/>
       <c r="P142" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q142" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R142" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R142" s="3" t="s">
+        <v>902</v>
+      </c>
     </row>
     <row r="143" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A143" s="7">
@@ -13816,7 +15007,7 @@
         <v>604</v>
       </c>
       <c r="J143" s="7" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="K143" s="7" t="s">
         <v>398</v>
@@ -13828,12 +15019,14 @@
       <c r="N143" s="3"/>
       <c r="O143" s="3"/>
       <c r="P143" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q143" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R143" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R143" s="3" t="s">
+        <v>903</v>
+      </c>
     </row>
     <row r="144" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A144" s="7">
@@ -13865,7 +15058,7 @@
         <v>607</v>
       </c>
       <c r="J144" s="7" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="K144" s="7" t="s">
         <v>398</v>
@@ -13877,12 +15070,14 @@
       <c r="N144" s="3"/>
       <c r="O144" s="3"/>
       <c r="P144" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q144" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R144" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R144" s="3" t="s">
+        <v>904</v>
+      </c>
     </row>
     <row r="145" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A145" s="7">
@@ -13914,7 +15109,7 @@
         <v>665</v>
       </c>
       <c r="J145" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K145" s="7" t="s">
         <v>398</v>
@@ -13926,12 +15121,14 @@
       <c r="N145" s="3"/>
       <c r="O145" s="3"/>
       <c r="P145" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q145" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R145" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R145" s="3" t="s">
+        <v>905</v>
+      </c>
     </row>
     <row r="146" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A146" s="7">
@@ -13963,7 +15160,7 @@
         <v>668</v>
       </c>
       <c r="J146" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K146" s="7" t="s">
         <v>398</v>
@@ -13975,12 +15172,14 @@
       <c r="N146" s="3"/>
       <c r="O146" s="3"/>
       <c r="P146" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q146" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R146" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R146" s="3" t="s">
+        <v>906</v>
+      </c>
     </row>
     <row r="147" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A147" s="7">
@@ -14012,7 +15211,7 @@
         <v>671</v>
       </c>
       <c r="J147" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K147" s="7" t="s">
         <v>398</v>
@@ -14024,12 +15223,14 @@
       <c r="N147" s="3"/>
       <c r="O147" s="3"/>
       <c r="P147" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q147" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R147" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R147" s="3" t="s">
+        <v>907</v>
+      </c>
     </row>
     <row r="148" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A148" s="7">
@@ -14061,7 +15262,7 @@
         <v>485</v>
       </c>
       <c r="J148" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K148" s="7" t="s">
         <v>398</v>
@@ -14073,12 +15274,14 @@
       <c r="N148" s="3"/>
       <c r="O148" s="3"/>
       <c r="P148" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q148" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R148" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R148" s="3" t="s">
+        <v>908</v>
+      </c>
     </row>
     <row r="149" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A149" s="7">
@@ -14110,7 +15313,7 @@
         <v>631</v>
       </c>
       <c r="J149" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K149" s="7" t="s">
         <v>398</v>
@@ -14122,12 +15325,14 @@
       <c r="N149" s="3"/>
       <c r="O149" s="3"/>
       <c r="P149" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="Q149" s="7" t="s">
         <v>751</v>
       </c>
-      <c r="Q149" s="7" t="s">
-        <v>752</v>
-      </c>
-      <c r="R149" s="3"/>
+      <c r="R149" s="3" t="s">
+        <v>909</v>
+      </c>
     </row>
     <row r="150" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A150" s="7">
@@ -14159,7 +15364,7 @@
         <v>486</v>
       </c>
       <c r="J150" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K150" s="7" t="s">
         <v>398</v>
@@ -14171,12 +15376,14 @@
       <c r="N150" s="3"/>
       <c r="O150" s="3"/>
       <c r="P150" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q150" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q150" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R150" s="3"/>
+      <c r="R150" s="3" t="s">
+        <v>910</v>
+      </c>
     </row>
     <row r="151" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A151" s="7">
@@ -14208,7 +15415,7 @@
         <v>487</v>
       </c>
       <c r="J151" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K151" s="7" t="s">
         <v>398</v>
@@ -14220,12 +15427,14 @@
       <c r="N151" s="3"/>
       <c r="O151" s="3"/>
       <c r="P151" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q151" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q151" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R151" s="3"/>
+      <c r="R151" s="3" t="s">
+        <v>911</v>
+      </c>
     </row>
     <row r="152" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A152" s="7">
@@ -14257,7 +15466,7 @@
         <v>488</v>
       </c>
       <c r="J152" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K152" s="7" t="s">
         <v>398</v>
@@ -14269,12 +15478,14 @@
       <c r="N152" s="3"/>
       <c r="O152" s="3"/>
       <c r="P152" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q152" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q152" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R152" s="3"/>
+      <c r="R152" s="3" t="s">
+        <v>912</v>
+      </c>
     </row>
     <row r="153" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A153" s="7">
@@ -14306,7 +15517,7 @@
         <v>489</v>
       </c>
       <c r="J153" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K153" s="7" t="s">
         <v>398</v>
@@ -14318,12 +15529,14 @@
       <c r="N153" s="3"/>
       <c r="O153" s="3"/>
       <c r="P153" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q153" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q153" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R153" s="3"/>
+      <c r="R153" s="3" t="s">
+        <v>913</v>
+      </c>
     </row>
     <row r="154" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A154" s="7">
@@ -14355,7 +15568,7 @@
         <v>577</v>
       </c>
       <c r="J154" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K154" s="7" t="s">
         <v>398</v>
@@ -14367,12 +15580,14 @@
       <c r="N154" s="3"/>
       <c r="O154" s="3"/>
       <c r="P154" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q154" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q154" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R154" s="3"/>
+      <c r="R154" s="3" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="155" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A155" s="7">
@@ -14404,7 +15619,7 @@
         <v>674</v>
       </c>
       <c r="J155" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K155" s="7" t="s">
         <v>398</v>
@@ -14416,12 +15631,14 @@
       <c r="N155" s="3"/>
       <c r="O155" s="3"/>
       <c r="P155" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q155" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q155" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R155" s="3"/>
+      <c r="R155" s="3" t="s">
+        <v>915</v>
+      </c>
     </row>
     <row r="156" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A156" s="7">
@@ -14453,7 +15670,7 @@
         <v>579</v>
       </c>
       <c r="J156" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K156" s="7" t="s">
         <v>398</v>
@@ -14465,12 +15682,14 @@
       <c r="N156" s="3"/>
       <c r="O156" s="3"/>
       <c r="P156" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q156" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R156" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R156" s="3" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="157" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A157" s="7">
@@ -14502,7 +15721,7 @@
         <v>677</v>
       </c>
       <c r="J157" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K157" s="7" t="s">
         <v>398</v>
@@ -14514,12 +15733,14 @@
       <c r="N157" s="3"/>
       <c r="O157" s="3"/>
       <c r="P157" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q157" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R157" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R157" s="3" t="s">
+        <v>917</v>
+      </c>
     </row>
     <row r="158" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A158" s="7">
@@ -14551,7 +15772,7 @@
         <v>491</v>
       </c>
       <c r="J158" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K158" s="7" t="s">
         <v>399</v>
@@ -14563,12 +15784,14 @@
       <c r="N158" s="3"/>
       <c r="O158" s="3"/>
       <c r="P158" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="Q158" s="7" t="s">
         <v>753</v>
       </c>
-      <c r="Q158" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="R158" s="3"/>
+      <c r="R158" s="3" t="s">
+        <v>918</v>
+      </c>
     </row>
     <row r="159" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A159" s="7">
@@ -14600,7 +15823,7 @@
         <v>680</v>
       </c>
       <c r="J159" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K159" s="7" t="s">
         <v>399</v>
@@ -14612,12 +15835,14 @@
       <c r="N159" s="3"/>
       <c r="O159" s="3"/>
       <c r="P159" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="Q159" s="7" t="s">
         <v>753</v>
       </c>
-      <c r="Q159" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="R159" s="3"/>
+      <c r="R159" s="3" t="s">
+        <v>919</v>
+      </c>
     </row>
     <row r="160" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A160" s="7">
@@ -14649,7 +15874,7 @@
         <v>683</v>
       </c>
       <c r="J160" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K160" s="7" t="s">
         <v>399</v>
@@ -14661,12 +15886,14 @@
       <c r="N160" s="3"/>
       <c r="O160" s="3"/>
       <c r="P160" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="Q160" s="7" t="s">
         <v>753</v>
       </c>
-      <c r="Q160" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="R160" s="3"/>
+      <c r="R160" s="3" t="s">
+        <v>920</v>
+      </c>
     </row>
     <row r="161" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A161" s="7">
@@ -14698,7 +15925,7 @@
         <v>492</v>
       </c>
       <c r="J161" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K161" s="7" t="s">
         <v>399</v>
@@ -14710,12 +15937,14 @@
       <c r="N161" s="3"/>
       <c r="O161" s="3"/>
       <c r="P161" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="Q161" s="7" t="s">
         <v>753</v>
       </c>
-      <c r="Q161" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="R161" s="3"/>
+      <c r="R161" s="3" t="s">
+        <v>921</v>
+      </c>
     </row>
     <row r="162" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A162" s="7">
@@ -14747,7 +15976,7 @@
         <v>493</v>
       </c>
       <c r="J162" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K162" s="7" t="s">
         <v>399</v>
@@ -14759,12 +15988,14 @@
       <c r="N162" s="3"/>
       <c r="O162" s="3"/>
       <c r="P162" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q162" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R162" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R162" s="3" t="s">
+        <v>922</v>
+      </c>
     </row>
     <row r="163" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A163" s="7">
@@ -14796,7 +16027,7 @@
         <v>494</v>
       </c>
       <c r="J163" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K163" s="7" t="s">
         <v>399</v>
@@ -14808,12 +16039,14 @@
       <c r="N163" s="3"/>
       <c r="O163" s="3"/>
       <c r="P163" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q163" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R163" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R163" s="3" t="s">
+        <v>923</v>
+      </c>
     </row>
     <row r="164" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A164" s="7">
@@ -14845,7 +16078,7 @@
         <v>495</v>
       </c>
       <c r="J164" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K164" s="7" t="s">
         <v>399</v>
@@ -14857,12 +16090,14 @@
       <c r="N164" s="3"/>
       <c r="O164" s="3"/>
       <c r="P164" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q164" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q164" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R164" s="3"/>
+      <c r="R164" s="3" t="s">
+        <v>924</v>
+      </c>
     </row>
     <row r="165" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A165" s="7">
@@ -14894,7 +16129,7 @@
         <v>496</v>
       </c>
       <c r="J165" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K165" s="7" t="s">
         <v>399</v>
@@ -14906,12 +16141,14 @@
       <c r="N165" s="3"/>
       <c r="O165" s="3"/>
       <c r="P165" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q165" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q165" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R165" s="3"/>
+      <c r="R165" s="3" t="s">
+        <v>925</v>
+      </c>
     </row>
     <row r="166" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A166" s="7">
@@ -14943,7 +16180,7 @@
         <v>497</v>
       </c>
       <c r="J166" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K166" s="7" t="s">
         <v>399</v>
@@ -14955,12 +16192,14 @@
       <c r="N166" s="3"/>
       <c r="O166" s="3"/>
       <c r="P166" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q166" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q166" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R166" s="3"/>
+      <c r="R166" s="3" t="s">
+        <v>926</v>
+      </c>
     </row>
     <row r="167" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A167" s="7">
@@ -14992,7 +16231,7 @@
         <v>686</v>
       </c>
       <c r="J167" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K167" s="7" t="s">
         <v>399</v>
@@ -15004,12 +16243,14 @@
       <c r="N167" s="3"/>
       <c r="O167" s="3"/>
       <c r="P167" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q167" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q167" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R167" s="3"/>
+      <c r="R167" s="3" t="s">
+        <v>927</v>
+      </c>
     </row>
     <row r="168" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A168" s="7">
@@ -15041,7 +16282,7 @@
         <v>498</v>
       </c>
       <c r="J168" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K168" s="7" t="s">
         <v>399</v>
@@ -15053,12 +16294,14 @@
       <c r="N168" s="3"/>
       <c r="O168" s="3"/>
       <c r="P168" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q168" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q168" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R168" s="3"/>
+      <c r="R168" s="3" t="s">
+        <v>928</v>
+      </c>
     </row>
     <row r="169" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A169" s="7">
@@ -15090,7 +16333,7 @@
         <v>499</v>
       </c>
       <c r="J169" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K169" s="7" t="s">
         <v>399</v>
@@ -15102,12 +16345,14 @@
       <c r="N169" s="3"/>
       <c r="O169" s="3"/>
       <c r="P169" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q169" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R169" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R169" s="3" t="s">
+        <v>929</v>
+      </c>
     </row>
     <row r="170" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A170" s="7">
@@ -15139,7 +16384,7 @@
         <v>500</v>
       </c>
       <c r="J170" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K170" s="7" t="s">
         <v>399</v>
@@ -15151,12 +16396,14 @@
       <c r="N170" s="3"/>
       <c r="O170" s="3"/>
       <c r="P170" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q170" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R170" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R170" s="3" t="s">
+        <v>930</v>
+      </c>
     </row>
     <row r="171" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A171" s="7">
@@ -15188,7 +16435,7 @@
         <v>501</v>
       </c>
       <c r="J171" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K171" s="7" t="s">
         <v>399</v>
@@ -15200,12 +16447,14 @@
       <c r="N171" s="3"/>
       <c r="O171" s="3"/>
       <c r="P171" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q171" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R171" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R171" s="3" t="s">
+        <v>931</v>
+      </c>
     </row>
     <row r="172" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A172" s="7">
@@ -15237,7 +16486,7 @@
         <v>502</v>
       </c>
       <c r="J172" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K172" s="7" t="s">
         <v>399</v>
@@ -15249,12 +16498,14 @@
       <c r="N172" s="3"/>
       <c r="O172" s="3"/>
       <c r="P172" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q172" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R172" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R172" s="3" t="s">
+        <v>932</v>
+      </c>
     </row>
     <row r="173" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A173" s="7">
@@ -15286,7 +16537,7 @@
         <v>503</v>
       </c>
       <c r="J173" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K173" s="7" t="s">
         <v>399</v>
@@ -15298,12 +16549,14 @@
       <c r="N173" s="3"/>
       <c r="O173" s="3"/>
       <c r="P173" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q173" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R173" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R173" s="3" t="s">
+        <v>933</v>
+      </c>
     </row>
     <row r="174" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A174" s="7">
@@ -15335,7 +16588,7 @@
         <v>689</v>
       </c>
       <c r="J174" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K174" s="7" t="s">
         <v>399</v>
@@ -15347,12 +16600,14 @@
       <c r="N174" s="3"/>
       <c r="O174" s="3"/>
       <c r="P174" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q174" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R174" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R174" s="3" t="s">
+        <v>934</v>
+      </c>
     </row>
     <row r="175" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A175" s="7">
@@ -15384,7 +16639,7 @@
         <v>692</v>
       </c>
       <c r="J175" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K175" s="7" t="s">
         <v>399</v>
@@ -15396,12 +16651,14 @@
       <c r="N175" s="3"/>
       <c r="O175" s="3"/>
       <c r="P175" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q175" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R175" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R175" s="3" t="s">
+        <v>935</v>
+      </c>
     </row>
     <row r="176" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A176" s="7">
@@ -15433,7 +16690,7 @@
         <v>695</v>
       </c>
       <c r="J176" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K176" s="7" t="s">
         <v>399</v>
@@ -15445,12 +16702,14 @@
       <c r="N176" s="3"/>
       <c r="O176" s="3"/>
       <c r="P176" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q176" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R176" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R176" s="3" t="s">
+        <v>936</v>
+      </c>
     </row>
     <row r="177" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A177" s="7">
@@ -15482,7 +16741,7 @@
         <v>504</v>
       </c>
       <c r="J177" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K177" s="7" t="s">
         <v>399</v>
@@ -15494,12 +16753,14 @@
       <c r="N177" s="3"/>
       <c r="O177" s="3"/>
       <c r="P177" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q177" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R177" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R177" s="3" t="s">
+        <v>937</v>
+      </c>
     </row>
     <row r="178" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A178" s="7">
@@ -15531,7 +16792,7 @@
         <v>530</v>
       </c>
       <c r="J178" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K178" s="7" t="s">
         <v>399</v>
@@ -15543,12 +16804,14 @@
       <c r="N178" s="3"/>
       <c r="O178" s="3"/>
       <c r="P178" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="Q178" s="7" t="s">
         <v>753</v>
       </c>
-      <c r="Q178" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="R178" s="3"/>
+      <c r="R178" s="3" t="s">
+        <v>938</v>
+      </c>
     </row>
     <row r="179" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A179" s="7">
@@ -15580,7 +16843,7 @@
         <v>532</v>
       </c>
       <c r="J179" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K179" s="7" t="s">
         <v>399</v>
@@ -15592,12 +16855,14 @@
       <c r="N179" s="3"/>
       <c r="O179" s="3"/>
       <c r="P179" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q179" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R179" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R179" s="3" t="s">
+        <v>939</v>
+      </c>
     </row>
     <row r="180" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A180" s="7">
@@ -15629,7 +16894,7 @@
         <v>534</v>
       </c>
       <c r="J180" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K180" s="7" t="s">
         <v>399</v>
@@ -15641,12 +16906,14 @@
       <c r="N180" s="3"/>
       <c r="O180" s="3"/>
       <c r="P180" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q180" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R180" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R180" s="3" t="s">
+        <v>940</v>
+      </c>
     </row>
     <row r="181" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A181" s="7">
@@ -15678,7 +16945,7 @@
         <v>536</v>
       </c>
       <c r="J181" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K181" s="7" t="s">
         <v>399</v>
@@ -15690,12 +16957,14 @@
       <c r="N181" s="3"/>
       <c r="O181" s="3"/>
       <c r="P181" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="Q181" s="7" t="s">
         <v>753</v>
       </c>
-      <c r="Q181" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="R181" s="3"/>
+      <c r="R181" s="3" t="s">
+        <v>941</v>
+      </c>
     </row>
     <row r="182" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A182" s="7">
@@ -15727,7 +16996,7 @@
         <v>538</v>
       </c>
       <c r="J182" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K182" s="7" t="s">
         <v>399</v>
@@ -15739,12 +17008,14 @@
       <c r="N182" s="3"/>
       <c r="O182" s="3"/>
       <c r="P182" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q182" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R182" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R182" s="3" t="s">
+        <v>942</v>
+      </c>
     </row>
     <row r="183" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A183" s="7">
@@ -15776,7 +17047,7 @@
         <v>540</v>
       </c>
       <c r="J183" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K183" s="7" t="s">
         <v>399</v>
@@ -15788,12 +17059,14 @@
       <c r="N183" s="3"/>
       <c r="O183" s="3"/>
       <c r="P183" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q183" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q183" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R183" s="3"/>
+      <c r="R183" s="3" t="s">
+        <v>943</v>
+      </c>
     </row>
     <row r="184" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A184" s="7">
@@ -15825,7 +17098,7 @@
         <v>542</v>
       </c>
       <c r="J184" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K184" s="7" t="s">
         <v>399</v>
@@ -15837,12 +17110,14 @@
       <c r="N184" s="3"/>
       <c r="O184" s="3"/>
       <c r="P184" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q184" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q184" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R184" s="3"/>
+      <c r="R184" s="3" t="s">
+        <v>944</v>
+      </c>
     </row>
     <row r="185" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A185" s="7">
@@ -15874,7 +17149,7 @@
         <v>544</v>
       </c>
       <c r="J185" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K185" s="7" t="s">
         <v>399</v>
@@ -15886,12 +17161,14 @@
       <c r="N185" s="3"/>
       <c r="O185" s="3"/>
       <c r="P185" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q185" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q185" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R185" s="3"/>
+      <c r="R185" s="3" t="s">
+        <v>945</v>
+      </c>
     </row>
     <row r="186" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A186" s="7">
@@ -15923,7 +17200,7 @@
         <v>546</v>
       </c>
       <c r="J186" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K186" s="7" t="s">
         <v>399</v>
@@ -15935,12 +17212,14 @@
       <c r="N186" s="3"/>
       <c r="O186" s="3"/>
       <c r="P186" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q186" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R186" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R186" s="3" t="s">
+        <v>946</v>
+      </c>
     </row>
     <row r="187" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A187" s="7">
@@ -15972,7 +17251,7 @@
         <v>548</v>
       </c>
       <c r="J187" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K187" s="7" t="s">
         <v>399</v>
@@ -15984,12 +17263,14 @@
       <c r="N187" s="3"/>
       <c r="O187" s="3"/>
       <c r="P187" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q187" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R187" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R187" s="3" t="s">
+        <v>947</v>
+      </c>
     </row>
     <row r="188" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A188" s="7">
@@ -16021,7 +17302,7 @@
         <v>550</v>
       </c>
       <c r="J188" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K188" s="7" t="s">
         <v>399</v>
@@ -16033,12 +17314,14 @@
       <c r="N188" s="3"/>
       <c r="O188" s="3"/>
       <c r="P188" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q188" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R188" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R188" s="3" t="s">
+        <v>948</v>
+      </c>
     </row>
     <row r="189" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A189" s="7">
@@ -16070,7 +17353,7 @@
         <v>632</v>
       </c>
       <c r="J189" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K189" s="7" t="s">
         <v>399</v>
@@ -16082,12 +17365,14 @@
       <c r="N189" s="3"/>
       <c r="O189" s="3"/>
       <c r="P189" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="Q189" s="7" t="s">
         <v>751</v>
       </c>
-      <c r="Q189" s="7" t="s">
-        <v>752</v>
-      </c>
-      <c r="R189" s="3"/>
+      <c r="R189" s="3" t="s">
+        <v>949</v>
+      </c>
     </row>
     <row r="190" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A190" s="7">
@@ -16119,7 +17404,7 @@
         <v>552</v>
       </c>
       <c r="J190" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K190" s="7" t="s">
         <v>399</v>
@@ -16131,12 +17416,14 @@
       <c r="N190" s="3"/>
       <c r="O190" s="3"/>
       <c r="P190" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q190" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R190" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R190" s="3" t="s">
+        <v>950</v>
+      </c>
     </row>
     <row r="191" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A191" s="7">
@@ -16168,7 +17455,7 @@
         <v>554</v>
       </c>
       <c r="J191" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K191" s="7" t="s">
         <v>399</v>
@@ -16180,12 +17467,14 @@
       <c r="N191" s="3"/>
       <c r="O191" s="3"/>
       <c r="P191" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q191" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R191" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R191" s="3" t="s">
+        <v>951</v>
+      </c>
     </row>
     <row r="192" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A192" s="7">
@@ -16217,7 +17506,7 @@
         <v>556</v>
       </c>
       <c r="J192" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K192" s="7" t="s">
         <v>399</v>
@@ -16229,12 +17518,14 @@
       <c r="N192" s="3"/>
       <c r="O192" s="3"/>
       <c r="P192" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q192" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R192" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R192" s="3" t="s">
+        <v>952</v>
+      </c>
     </row>
     <row r="193" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A193" s="7">
@@ -16266,7 +17557,7 @@
         <v>558</v>
       </c>
       <c r="J193" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K193" s="7" t="s">
         <v>399</v>
@@ -16278,12 +17569,14 @@
       <c r="N193" s="3"/>
       <c r="O193" s="3"/>
       <c r="P193" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q193" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R193" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R193" s="3" t="s">
+        <v>953</v>
+      </c>
     </row>
     <row r="194" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A194" s="7">
@@ -16315,7 +17608,7 @@
         <v>560</v>
       </c>
       <c r="J194" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K194" s="7" t="s">
         <v>399</v>
@@ -16327,12 +17620,14 @@
       <c r="N194" s="3"/>
       <c r="O194" s="3"/>
       <c r="P194" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q194" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R194" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R194" s="3" t="s">
+        <v>954</v>
+      </c>
     </row>
     <row r="195" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A195" s="7">
@@ -16364,7 +17659,7 @@
         <v>698</v>
       </c>
       <c r="J195" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K195" s="7" t="s">
         <v>399</v>
@@ -16376,12 +17671,14 @@
       <c r="N195" s="3"/>
       <c r="O195" s="3"/>
       <c r="P195" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q195" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R195" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R195" s="3" t="s">
+        <v>955</v>
+      </c>
     </row>
     <row r="196" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A196" s="7">
@@ -16413,7 +17710,7 @@
         <v>701</v>
       </c>
       <c r="J196" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K196" s="7" t="s">
         <v>399</v>
@@ -16425,12 +17722,14 @@
       <c r="N196" s="3"/>
       <c r="O196" s="3"/>
       <c r="P196" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q196" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R196" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R196" s="3" t="s">
+        <v>956</v>
+      </c>
     </row>
     <row r="197" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A197" s="7">
@@ -16462,7 +17761,7 @@
         <v>704</v>
       </c>
       <c r="J197" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K197" s="7" t="s">
         <v>399</v>
@@ -16474,12 +17773,14 @@
       <c r="N197" s="3"/>
       <c r="O197" s="3"/>
       <c r="P197" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q197" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R197" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R197" s="3" t="s">
+        <v>957</v>
+      </c>
     </row>
     <row r="198" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A198" s="7">
@@ -16511,7 +17812,7 @@
         <v>562</v>
       </c>
       <c r="J198" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K198" s="7" t="s">
         <v>399</v>
@@ -16523,12 +17824,14 @@
       <c r="N198" s="3"/>
       <c r="O198" s="3"/>
       <c r="P198" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q198" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R198" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R198" s="3" t="s">
+        <v>958</v>
+      </c>
     </row>
     <row r="199" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A199" s="7">
@@ -16560,7 +17863,7 @@
         <v>610</v>
       </c>
       <c r="J199" s="7" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="K199" s="7" t="s">
         <v>398</v>
@@ -16572,12 +17875,14 @@
       <c r="N199" s="3"/>
       <c r="O199" s="3"/>
       <c r="P199" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q199" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R199" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R199" s="3" t="s">
+        <v>959</v>
+      </c>
     </row>
     <row r="200" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A200" s="7">
@@ -16609,7 +17914,7 @@
         <v>613</v>
       </c>
       <c r="J200" s="7" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="K200" s="7" t="s">
         <v>398</v>
@@ -16621,12 +17926,14 @@
       <c r="N200" s="3"/>
       <c r="O200" s="3"/>
       <c r="P200" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q200" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R200" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R200" s="3" t="s">
+        <v>960</v>
+      </c>
     </row>
     <row r="201" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A201" s="7">
@@ -16658,7 +17965,7 @@
         <v>616</v>
       </c>
       <c r="J201" s="7" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="K201" s="7" t="s">
         <v>398</v>
@@ -16670,12 +17977,14 @@
       <c r="N201" s="3"/>
       <c r="O201" s="3"/>
       <c r="P201" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q201" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R201" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R201" s="3" t="s">
+        <v>961</v>
+      </c>
     </row>
     <row r="202" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A202" s="7">
@@ -16707,7 +18016,7 @@
         <v>619</v>
       </c>
       <c r="J202" s="7" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="K202" s="7" t="s">
         <v>398</v>
@@ -16719,12 +18028,14 @@
       <c r="N202" s="3"/>
       <c r="O202" s="3"/>
       <c r="P202" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q202" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R202" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R202" s="3" t="s">
+        <v>962</v>
+      </c>
     </row>
     <row r="203" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A203" s="7">
@@ -16756,7 +18067,7 @@
         <v>707</v>
       </c>
       <c r="J203" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K203" s="7" t="s">
         <v>398</v>
@@ -16768,12 +18079,14 @@
       <c r="N203" s="3"/>
       <c r="O203" s="3"/>
       <c r="P203" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q203" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R203" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R203" s="3" t="s">
+        <v>963</v>
+      </c>
     </row>
     <row r="204" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A204" s="7">
@@ -16805,7 +18118,7 @@
         <v>660</v>
       </c>
       <c r="J204" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K204" s="7" t="s">
         <v>398</v>
@@ -16817,12 +18130,14 @@
       <c r="N204" s="3"/>
       <c r="O204" s="3"/>
       <c r="P204" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="Q204" s="7" t="s">
         <v>751</v>
       </c>
-      <c r="Q204" s="7" t="s">
-        <v>752</v>
-      </c>
-      <c r="R204" s="3"/>
+      <c r="R204" s="3" t="s">
+        <v>964</v>
+      </c>
     </row>
     <row r="205" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A205" s="7">
@@ -16854,7 +18169,7 @@
         <v>565</v>
       </c>
       <c r="J205" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K205" s="7" t="s">
         <v>398</v>
@@ -16866,12 +18181,14 @@
       <c r="N205" s="3"/>
       <c r="O205" s="3"/>
       <c r="P205" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q205" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R205" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R205" s="3" t="s">
+        <v>965</v>
+      </c>
     </row>
     <row r="206" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A206" s="7">
@@ -16903,7 +18220,7 @@
         <v>567</v>
       </c>
       <c r="J206" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K206" s="7" t="s">
         <v>398</v>
@@ -16915,12 +18232,14 @@
       <c r="N206" s="3"/>
       <c r="O206" s="3"/>
       <c r="P206" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q206" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q206" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R206" s="3"/>
+      <c r="R206" s="3" t="s">
+        <v>966</v>
+      </c>
     </row>
     <row r="207" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A207" s="7">
@@ -16952,7 +18271,7 @@
         <v>582</v>
       </c>
       <c r="J207" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K207" s="7" t="s">
         <v>398</v>
@@ -16964,12 +18283,14 @@
       <c r="N207" s="3"/>
       <c r="O207" s="3"/>
       <c r="P207" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q207" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q207" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R207" s="3"/>
+      <c r="R207" s="3" t="s">
+        <v>967</v>
+      </c>
     </row>
     <row r="208" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A208" s="7">
@@ -17001,7 +18322,7 @@
         <v>575</v>
       </c>
       <c r="J208" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K208" s="7" t="s">
         <v>398</v>
@@ -17013,12 +18334,14 @@
       <c r="N208" s="3"/>
       <c r="O208" s="3"/>
       <c r="P208" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q208" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q208" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R208" s="3"/>
+      <c r="R208" s="3" t="s">
+        <v>968</v>
+      </c>
     </row>
     <row r="209" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A209" s="7">
@@ -17050,7 +18373,7 @@
         <v>490</v>
       </c>
       <c r="J209" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K209" s="7" t="s">
         <v>398</v>
@@ -17062,12 +18385,14 @@
       <c r="N209" s="3"/>
       <c r="O209" s="3"/>
       <c r="P209" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q209" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R209" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R209" s="3" t="s">
+        <v>969</v>
+      </c>
     </row>
     <row r="210" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A210" s="7">
@@ -17099,7 +18424,7 @@
         <v>585</v>
       </c>
       <c r="J210" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="K210" s="7" t="s">
         <v>398</v>
@@ -17111,12 +18436,14 @@
       <c r="N210" s="3"/>
       <c r="O210" s="3"/>
       <c r="P210" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q210" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R210" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R210" s="3" t="s">
+        <v>970</v>
+      </c>
     </row>
     <row r="211" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A211" s="7">
@@ -17148,7 +18475,7 @@
         <v>712</v>
       </c>
       <c r="J211" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K211" s="7" t="s">
         <v>398</v>
@@ -17160,12 +18487,14 @@
       <c r="N211" s="3"/>
       <c r="O211" s="3"/>
       <c r="P211" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q211" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R211" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R211" s="3" t="s">
+        <v>971</v>
+      </c>
     </row>
     <row r="212" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
       <c r="A212" s="7">
@@ -17197,7 +18526,7 @@
         <v>715</v>
       </c>
       <c r="J212" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K212" s="7" t="s">
         <v>398</v>
@@ -17209,12 +18538,14 @@
       <c r="N212" s="3"/>
       <c r="O212" s="3"/>
       <c r="P212" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q212" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R212" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R212" s="3" t="s">
+        <v>972</v>
+      </c>
     </row>
     <row r="213" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A213" s="7">
@@ -17246,7 +18577,7 @@
         <v>622</v>
       </c>
       <c r="J213" s="7" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="K213" s="7" t="s">
         <v>398</v>
@@ -17258,12 +18589,14 @@
       <c r="N213" s="3"/>
       <c r="O213" s="3"/>
       <c r="P213" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q213" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R213" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R213" s="3" t="s">
+        <v>973</v>
+      </c>
     </row>
     <row r="214" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A214" s="7">
@@ -17295,7 +18628,7 @@
         <v>625</v>
       </c>
       <c r="J214" s="7" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="K214" s="7" t="s">
         <v>398</v>
@@ -17307,12 +18640,14 @@
       <c r="N214" s="3"/>
       <c r="O214" s="3"/>
       <c r="P214" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q214" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R214" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R214" s="3" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="215" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A215" s="7">
@@ -17344,7 +18679,7 @@
         <v>718</v>
       </c>
       <c r="J215" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K215" s="7" t="s">
         <v>398</v>
@@ -17356,12 +18691,14 @@
       <c r="N215" s="3"/>
       <c r="O215" s="3"/>
       <c r="P215" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q215" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R215" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R215" s="3" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="216" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A216" s="7">
@@ -17393,7 +18730,7 @@
         <v>721</v>
       </c>
       <c r="J216" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K216" s="7" t="s">
         <v>398</v>
@@ -17405,12 +18742,14 @@
       <c r="N216" s="3"/>
       <c r="O216" s="3"/>
       <c r="P216" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q216" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R216" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R216" s="3" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="217" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A217" s="7">
@@ -17442,7 +18781,7 @@
         <v>571</v>
       </c>
       <c r="J217" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K217" s="7" t="s">
         <v>398</v>
@@ -17454,12 +18793,14 @@
       <c r="N217" s="3"/>
       <c r="O217" s="3"/>
       <c r="P217" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q217" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="R217" s="3"/>
+        <v>747</v>
+      </c>
+      <c r="R217" s="3" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="218" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A218" s="7">
@@ -17491,7 +18832,7 @@
         <v>588</v>
       </c>
       <c r="J218" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K218" s="7" t="s">
         <v>398</v>
@@ -17503,12 +18844,14 @@
       <c r="N218" s="3"/>
       <c r="O218" s="3"/>
       <c r="P218" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q218" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q218" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R218" s="3"/>
+      <c r="R218" s="3" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="219" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A219" s="7">
@@ -17540,7 +18883,7 @@
         <v>591</v>
       </c>
       <c r="J219" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K219" s="7" t="s">
         <v>398</v>
@@ -17552,12 +18895,14 @@
       <c r="N219" s="3"/>
       <c r="O219" s="3"/>
       <c r="P219" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q219" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q219" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R219" s="3"/>
+      <c r="R219" s="3" t="s">
+        <v>979</v>
+      </c>
     </row>
     <row r="220" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A220" s="7">
@@ -17589,7 +18934,7 @@
         <v>575</v>
       </c>
       <c r="J220" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K220" s="7" t="s">
         <v>398</v>
@@ -17601,12 +18946,14 @@
       <c r="N220" s="3"/>
       <c r="O220" s="3"/>
       <c r="P220" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q220" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="Q220" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="R220" s="3"/>
+      <c r="R220" s="3" t="s">
+        <v>980</v>
+      </c>
     </row>
     <row r="221" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A221" s="7">
@@ -17638,7 +18985,7 @@
         <v>634</v>
       </c>
       <c r="J221" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K221" s="7" t="s">
         <v>398</v>
@@ -17650,12 +18997,14 @@
       <c r="N221" s="3"/>
       <c r="O221" s="3"/>
       <c r="P221" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="Q221" s="7" t="s">
         <v>751</v>
       </c>
-      <c r="Q221" s="7" t="s">
-        <v>752</v>
-      </c>
-      <c r="R221" s="3"/>
+      <c r="R221" s="3" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="222" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A222" s="7">
@@ -17687,7 +19036,7 @@
         <v>662</v>
       </c>
       <c r="J222" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K222" s="7" t="s">
         <v>398</v>
@@ -17699,12 +19048,14 @@
       <c r="N222" s="3"/>
       <c r="O222" s="3"/>
       <c r="P222" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="Q222" s="7" t="s">
         <v>751</v>
       </c>
-      <c r="Q222" s="7" t="s">
-        <v>752</v>
-      </c>
-      <c r="R222" s="3"/>
+      <c r="R222" s="3" t="s">
+        <v>982</v>
+      </c>
     </row>
     <row r="223" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A223" s="7">
@@ -17736,7 +19087,7 @@
         <v>637</v>
       </c>
       <c r="J223" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K223" s="7" t="s">
         <v>398</v>
@@ -17748,12 +19099,14 @@
       <c r="N223" s="3"/>
       <c r="O223" s="3"/>
       <c r="P223" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="Q223" s="7" t="s">
         <v>751</v>
       </c>
-      <c r="Q223" s="7" t="s">
-        <v>752</v>
-      </c>
-      <c r="R223" s="3"/>
+      <c r="R223" s="3" t="s">
+        <v>983</v>
+      </c>
     </row>
     <row r="224" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A224" s="7">
@@ -17785,7 +19138,7 @@
         <v>639</v>
       </c>
       <c r="J224" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K224" s="7" t="s">
         <v>399</v>
@@ -17797,12 +19150,14 @@
       <c r="N224" s="3"/>
       <c r="O224" s="3"/>
       <c r="P224" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="Q224" s="7" t="s">
         <v>751</v>
       </c>
-      <c r="Q224" s="7" t="s">
-        <v>752</v>
-      </c>
-      <c r="R224" s="3"/>
+      <c r="R224" s="3" t="s">
+        <v>984</v>
+      </c>
     </row>
     <row r="225" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A225" s="7">
@@ -17834,7 +19189,7 @@
         <v>641</v>
       </c>
       <c r="J225" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K225" s="7" t="s">
         <v>399</v>
@@ -17846,12 +19201,14 @@
       <c r="N225" s="3"/>
       <c r="O225" s="3"/>
       <c r="P225" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="Q225" s="7" t="s">
         <v>751</v>
       </c>
-      <c r="Q225" s="7" t="s">
-        <v>752</v>
-      </c>
-      <c r="R225" s="3"/>
+      <c r="R225" s="3" t="s">
+        <v>985</v>
+      </c>
     </row>
     <row r="226" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A226" s="7">
@@ -17883,7 +19240,7 @@
         <v>643</v>
       </c>
       <c r="J226" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K226" s="7" t="s">
         <v>399</v>
@@ -17895,12 +19252,14 @@
       <c r="N226" s="3"/>
       <c r="O226" s="3"/>
       <c r="P226" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="Q226" s="7" t="s">
         <v>751</v>
       </c>
-      <c r="Q226" s="7" t="s">
-        <v>752</v>
-      </c>
-      <c r="R226" s="3"/>
+      <c r="R226" s="3" t="s">
+        <v>986</v>
+      </c>
     </row>
     <row r="227" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A227" s="7">
@@ -17932,7 +19291,7 @@
         <v>645</v>
       </c>
       <c r="J227" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K227" s="7" t="s">
         <v>399</v>
@@ -17944,12 +19303,14 @@
       <c r="N227" s="3"/>
       <c r="O227" s="3"/>
       <c r="P227" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="Q227" s="7" t="s">
         <v>751</v>
       </c>
-      <c r="Q227" s="7" t="s">
-        <v>752</v>
-      </c>
-      <c r="R227" s="3"/>
+      <c r="R227" s="3" t="s">
+        <v>987</v>
+      </c>
     </row>
     <row r="228" spans="1:18" ht="25" x14ac:dyDescent="0.45">
       <c r="A228" s="7">
@@ -17981,7 +19342,7 @@
         <v>647</v>
       </c>
       <c r="J228" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K228" s="7" t="s">
         <v>399</v>
@@ -17993,12 +19354,14 @@
       <c r="N228" s="3"/>
       <c r="O228" s="3"/>
       <c r="P228" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="Q228" s="7" t="s">
         <v>751</v>
       </c>
-      <c r="Q228" s="7" t="s">
-        <v>752</v>
-      </c>
-      <c r="R228" s="3"/>
+      <c r="R228" s="3" t="s">
+        <v>988</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:R228" xr:uid="{243C8A1C-2FBA-4873-BD31-7545635970F1}"/>
@@ -18083,10 +19446,10 @@
         <v>330</v>
       </c>
       <c r="H2" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="I2" s="10" t="s">
         <v>741</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.45">
@@ -18114,10 +19477,10 @@
         <v>334</v>
       </c>
       <c r="H3" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="I3" s="10" t="s">
         <v>741</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.45">
@@ -18145,10 +19508,10 @@
         <v>334</v>
       </c>
       <c r="H4" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="I4" s="10" t="s">
         <v>741</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="16" x14ac:dyDescent="0.45">
@@ -18176,10 +19539,10 @@
         <v>334</v>
       </c>
       <c r="H5" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="I5" s="10" t="s">
         <v>741</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="16" x14ac:dyDescent="0.45">
@@ -18207,15 +19570,15 @@
         <v>334</v>
       </c>
       <c r="H6" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="I6" s="10" t="s">
         <v>741</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_추가문구_검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDC31C6-DA28-4B52-A533-AB14C17BB6BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A645ED-31EB-4F48-8A0D-C6A02A697024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{20856D29-42F9-4C84-8C0E-1E3497A2FD0E}"/>
   </bookViews>
@@ -6113,10 +6113,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Plan tomorrow's breakfast</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Write down your lunch time</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -7018,6 +7014,10 @@
   </si>
   <si>
     <t>Tuna salad, half dressing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pick tomorrow's breakfast menu</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7834,7 +7834,7 @@
         <v>747</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>762</v>
+        <v>988</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -7885,7 +7885,7 @@
         <v>747</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -7936,7 +7936,7 @@
         <v>747</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -7987,7 +7987,7 @@
         <v>747</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -8038,7 +8038,7 @@
         <v>749</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -8089,7 +8089,7 @@
         <v>747</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -8140,7 +8140,7 @@
         <v>747</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
@@ -8191,7 +8191,7 @@
         <v>751</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
@@ -8242,7 +8242,7 @@
         <v>747</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -8293,7 +8293,7 @@
         <v>747</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -8344,7 +8344,7 @@
         <v>747</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -8395,7 +8395,7 @@
         <v>747</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -8446,7 +8446,7 @@
         <v>751</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -8497,7 +8497,7 @@
         <v>747</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -8548,7 +8548,7 @@
         <v>749</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -8599,7 +8599,7 @@
         <v>753</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -8650,7 +8650,7 @@
         <v>753</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -8701,7 +8701,7 @@
         <v>747</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -8752,7 +8752,7 @@
         <v>747</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -8803,7 +8803,7 @@
         <v>749</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -8854,7 +8854,7 @@
         <v>747</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -8905,7 +8905,7 @@
         <v>747</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -8956,7 +8956,7 @@
         <v>747</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -9007,7 +9007,7 @@
         <v>749</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -9058,7 +9058,7 @@
         <v>755</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -9109,7 +9109,7 @@
         <v>747</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
@@ -9160,7 +9160,7 @@
         <v>747</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="29" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
@@ -9211,7 +9211,7 @@
         <v>747</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -9262,7 +9262,7 @@
         <v>747</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -9313,7 +9313,7 @@
         <v>747</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -9364,7 +9364,7 @@
         <v>747</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -9415,7 +9415,7 @@
         <v>747</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="34" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -9466,7 +9466,7 @@
         <v>747</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -9517,7 +9517,7 @@
         <v>747</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -9568,7 +9568,7 @@
         <v>753</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -9619,7 +9619,7 @@
         <v>747</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -9670,7 +9670,7 @@
         <v>749</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="39" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -9721,7 +9721,7 @@
         <v>747</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="40" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -9772,7 +9772,7 @@
         <v>747</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="41" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -9823,7 +9823,7 @@
         <v>747</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="42" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -9874,7 +9874,7 @@
         <v>747</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="43" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -9925,7 +9925,7 @@
         <v>747</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="44" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -9976,7 +9976,7 @@
         <v>747</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="45" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -10027,7 +10027,7 @@
         <v>747</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="46" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -10078,7 +10078,7 @@
         <v>757</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="47" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -10129,7 +10129,7 @@
         <v>757</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
@@ -10180,7 +10180,7 @@
         <v>747</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
@@ -10231,7 +10231,7 @@
         <v>747</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="50" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
@@ -10282,7 +10282,7 @@
         <v>747</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="51" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -10333,7 +10333,7 @@
         <v>747</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="52" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -10384,7 +10384,7 @@
         <v>747</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="53" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -10435,7 +10435,7 @@
         <v>747</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="54" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -10486,7 +10486,7 @@
         <v>747</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="55" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -10537,7 +10537,7 @@
         <v>747</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="56" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -10588,7 +10588,7 @@
         <v>747</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="57" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -10639,7 +10639,7 @@
         <v>747</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="58" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -10690,7 +10690,7 @@
         <v>747</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="59" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -10741,7 +10741,7 @@
         <v>747</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="60" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -10792,7 +10792,7 @@
         <v>747</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="61" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -10843,7 +10843,7 @@
         <v>753</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="62" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -10894,7 +10894,7 @@
         <v>753</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="63" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -10945,7 +10945,7 @@
         <v>749</v>
       </c>
       <c r="R63" s="3" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="64" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -10996,7 +10996,7 @@
         <v>747</v>
       </c>
       <c r="R64" s="3" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="65" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -11047,7 +11047,7 @@
         <v>747</v>
       </c>
       <c r="R65" s="3" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="66" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -11098,7 +11098,7 @@
         <v>747</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="67" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -11149,7 +11149,7 @@
         <v>747</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="68" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -11200,7 +11200,7 @@
         <v>747</v>
       </c>
       <c r="R68" s="3" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="69" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -11251,7 +11251,7 @@
         <v>747</v>
       </c>
       <c r="R69" s="3" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="70" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -11302,7 +11302,7 @@
         <v>747</v>
       </c>
       <c r="R70" s="3" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="71" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -11353,7 +11353,7 @@
         <v>747</v>
       </c>
       <c r="R71" s="3" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="72" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -11404,7 +11404,7 @@
         <v>749</v>
       </c>
       <c r="R72" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="73" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -11455,7 +11455,7 @@
         <v>747</v>
       </c>
       <c r="R73" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="74" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -11506,7 +11506,7 @@
         <v>749</v>
       </c>
       <c r="R74" s="3" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="75" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -11557,7 +11557,7 @@
         <v>747</v>
       </c>
       <c r="R75" s="3" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="76" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -11608,7 +11608,7 @@
         <v>747</v>
       </c>
       <c r="R76" s="3" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="77" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -11659,7 +11659,7 @@
         <v>747</v>
       </c>
       <c r="R77" s="3" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="78" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -11710,7 +11710,7 @@
         <v>747</v>
       </c>
       <c r="R78" s="3" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="79" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -11761,7 +11761,7 @@
         <v>747</v>
       </c>
       <c r="R79" s="3" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="80" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -11812,7 +11812,7 @@
         <v>755</v>
       </c>
       <c r="R80" s="3" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="81" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -11863,7 +11863,7 @@
         <v>755</v>
       </c>
       <c r="R81" s="3" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="82" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -11914,7 +11914,7 @@
         <v>757</v>
       </c>
       <c r="R82" s="3" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="83" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
@@ -11965,7 +11965,7 @@
         <v>747</v>
       </c>
       <c r="R83" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="84" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
@@ -12016,7 +12016,7 @@
         <v>747</v>
       </c>
       <c r="R84" s="3" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="85" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
@@ -12067,7 +12067,7 @@
         <v>751</v>
       </c>
       <c r="R85" s="3" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="86" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
@@ -12118,7 +12118,7 @@
         <v>747</v>
       </c>
       <c r="R86" s="3" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="87" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
@@ -12169,7 +12169,7 @@
         <v>747</v>
       </c>
       <c r="R87" s="3" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="88" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
@@ -12220,7 +12220,7 @@
         <v>747</v>
       </c>
       <c r="R88" s="3" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="89" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -12271,7 +12271,7 @@
         <v>747</v>
       </c>
       <c r="R89" s="3" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="90" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -12322,7 +12322,7 @@
         <v>747</v>
       </c>
       <c r="R90" s="3" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="91" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -12373,7 +12373,7 @@
         <v>747</v>
       </c>
       <c r="R91" s="3" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="92" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -12424,7 +12424,7 @@
         <v>747</v>
       </c>
       <c r="R92" s="3" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="93" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -12475,7 +12475,7 @@
         <v>755</v>
       </c>
       <c r="R93" s="3" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="94" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -12526,7 +12526,7 @@
         <v>757</v>
       </c>
       <c r="R94" s="3" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="95" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -12577,7 +12577,7 @@
         <v>747</v>
       </c>
       <c r="R95" s="3" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="96" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -12628,7 +12628,7 @@
         <v>755</v>
       </c>
       <c r="R96" s="3" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="97" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -12679,7 +12679,7 @@
         <v>747</v>
       </c>
       <c r="R97" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="98" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -12730,7 +12730,7 @@
         <v>747</v>
       </c>
       <c r="R98" s="3" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="99" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -12781,7 +12781,7 @@
         <v>747</v>
       </c>
       <c r="R99" s="3" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="100" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -12832,7 +12832,7 @@
         <v>747</v>
       </c>
       <c r="R100" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="101" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -12883,7 +12883,7 @@
         <v>747</v>
       </c>
       <c r="R101" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="102" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -12934,7 +12934,7 @@
         <v>749</v>
       </c>
       <c r="R102" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="103" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -12985,7 +12985,7 @@
         <v>749</v>
       </c>
       <c r="R103" s="3" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="104" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -13036,7 +13036,7 @@
         <v>749</v>
       </c>
       <c r="R104" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="105" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -13087,7 +13087,7 @@
         <v>747</v>
       </c>
       <c r="R105" s="3" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="106" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -13138,7 +13138,7 @@
         <v>749</v>
       </c>
       <c r="R106" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="107" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -13189,7 +13189,7 @@
         <v>753</v>
       </c>
       <c r="R107" s="3" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="108" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -13240,7 +13240,7 @@
         <v>753</v>
       </c>
       <c r="R108" s="3" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="109" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -13291,7 +13291,7 @@
         <v>747</v>
       </c>
       <c r="R109" s="3" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="110" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -13342,7 +13342,7 @@
         <v>751</v>
       </c>
       <c r="R110" s="3" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="111" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -13393,7 +13393,7 @@
         <v>747</v>
       </c>
       <c r="R111" s="3" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="112" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -13444,7 +13444,7 @@
         <v>753</v>
       </c>
       <c r="R112" s="3" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="113" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -13495,7 +13495,7 @@
         <v>753</v>
       </c>
       <c r="R113" s="3" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="114" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -13546,7 +13546,7 @@
         <v>753</v>
       </c>
       <c r="R114" s="3" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="115" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
@@ -13597,7 +13597,7 @@
         <v>747</v>
       </c>
       <c r="R115" s="3" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="116" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -13648,7 +13648,7 @@
         <v>747</v>
       </c>
       <c r="R116" s="3" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="117" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -13699,7 +13699,7 @@
         <v>747</v>
       </c>
       <c r="R117" s="3" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="118" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -13750,7 +13750,7 @@
         <v>747</v>
       </c>
       <c r="R118" s="3" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="119" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -13801,7 +13801,7 @@
         <v>757</v>
       </c>
       <c r="R119" s="3" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="120" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -13852,7 +13852,7 @@
         <v>747</v>
       </c>
       <c r="R120" s="3" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="121" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -13903,7 +13903,7 @@
         <v>747</v>
       </c>
       <c r="R121" s="3" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="122" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -13954,7 +13954,7 @@
         <v>749</v>
       </c>
       <c r="R122" s="3" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="123" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -14005,7 +14005,7 @@
         <v>749</v>
       </c>
       <c r="R123" s="3" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="124" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -14056,7 +14056,7 @@
         <v>749</v>
       </c>
       <c r="R124" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="125" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -14107,7 +14107,7 @@
         <v>749</v>
       </c>
       <c r="R125" s="3" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="126" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -14158,7 +14158,7 @@
         <v>747</v>
       </c>
       <c r="R126" s="3" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="127" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -14209,7 +14209,7 @@
         <v>747</v>
       </c>
       <c r="R127" s="3" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="128" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -14260,7 +14260,7 @@
         <v>755</v>
       </c>
       <c r="R128" s="3" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="129" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -14311,7 +14311,7 @@
         <v>747</v>
       </c>
       <c r="R129" s="3" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="130" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -14362,7 +14362,7 @@
         <v>751</v>
       </c>
       <c r="R130" s="3" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="131" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
@@ -14413,7 +14413,7 @@
         <v>751</v>
       </c>
       <c r="R131" s="3" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="132" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
@@ -14464,7 +14464,7 @@
         <v>747</v>
       </c>
       <c r="R132" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="133" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -14515,7 +14515,7 @@
         <v>753</v>
       </c>
       <c r="R133" s="3" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="134" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -14566,7 +14566,7 @@
         <v>753</v>
       </c>
       <c r="R134" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="135" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -14617,7 +14617,7 @@
         <v>755</v>
       </c>
       <c r="R135" s="3" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="136" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -14668,7 +14668,7 @@
         <v>747</v>
       </c>
       <c r="R136" s="3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="137" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -14719,7 +14719,7 @@
         <v>747</v>
       </c>
       <c r="R137" s="3" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="138" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -14770,7 +14770,7 @@
         <v>751</v>
       </c>
       <c r="R138" s="3" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="139" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -14821,7 +14821,7 @@
         <v>747</v>
       </c>
       <c r="R139" s="3" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="140" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -14872,7 +14872,7 @@
         <v>747</v>
       </c>
       <c r="R140" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="141" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -14923,7 +14923,7 @@
         <v>747</v>
       </c>
       <c r="R141" s="3" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="142" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -14974,7 +14974,7 @@
         <v>747</v>
       </c>
       <c r="R142" s="3" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="143" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -15025,7 +15025,7 @@
         <v>747</v>
       </c>
       <c r="R143" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="144" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -15076,7 +15076,7 @@
         <v>747</v>
       </c>
       <c r="R144" s="3" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="145" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -15127,7 +15127,7 @@
         <v>747</v>
       </c>
       <c r="R145" s="3" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="146" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -15178,7 +15178,7 @@
         <v>747</v>
       </c>
       <c r="R146" s="3" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="147" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -15229,7 +15229,7 @@
         <v>747</v>
       </c>
       <c r="R147" s="3" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="148" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -15280,7 +15280,7 @@
         <v>747</v>
       </c>
       <c r="R148" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="149" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -15331,7 +15331,7 @@
         <v>751</v>
       </c>
       <c r="R149" s="3" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="150" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -15382,7 +15382,7 @@
         <v>749</v>
       </c>
       <c r="R150" s="3" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="151" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -15433,7 +15433,7 @@
         <v>749</v>
       </c>
       <c r="R151" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="152" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -15484,7 +15484,7 @@
         <v>749</v>
       </c>
       <c r="R152" s="3" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="153" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -15535,7 +15535,7 @@
         <v>749</v>
       </c>
       <c r="R153" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="154" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -15586,7 +15586,7 @@
         <v>749</v>
       </c>
       <c r="R154" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="155" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -15637,7 +15637,7 @@
         <v>749</v>
       </c>
       <c r="R155" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="156" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -15688,7 +15688,7 @@
         <v>747</v>
       </c>
       <c r="R156" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="157" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
@@ -15739,7 +15739,7 @@
         <v>747</v>
       </c>
       <c r="R157" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="158" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -15790,7 +15790,7 @@
         <v>753</v>
       </c>
       <c r="R158" s="3" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="159" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -15841,7 +15841,7 @@
         <v>753</v>
       </c>
       <c r="R159" s="3" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="160" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -15892,7 +15892,7 @@
         <v>753</v>
       </c>
       <c r="R160" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="161" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -15943,7 +15943,7 @@
         <v>753</v>
       </c>
       <c r="R161" s="3" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="162" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -15994,7 +15994,7 @@
         <v>747</v>
       </c>
       <c r="R162" s="3" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="163" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -16045,7 +16045,7 @@
         <v>747</v>
       </c>
       <c r="R163" s="3" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="164" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -16096,7 +16096,7 @@
         <v>749</v>
       </c>
       <c r="R164" s="3" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="165" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -16147,7 +16147,7 @@
         <v>749</v>
       </c>
       <c r="R165" s="3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="166" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -16198,7 +16198,7 @@
         <v>749</v>
       </c>
       <c r="R166" s="3" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="167" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -16249,7 +16249,7 @@
         <v>749</v>
       </c>
       <c r="R167" s="3" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="168" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -16300,7 +16300,7 @@
         <v>749</v>
       </c>
       <c r="R168" s="3" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="169" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -16351,7 +16351,7 @@
         <v>747</v>
       </c>
       <c r="R169" s="3" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="170" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -16402,7 +16402,7 @@
         <v>747</v>
       </c>
       <c r="R170" s="3" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="171" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -16453,7 +16453,7 @@
         <v>747</v>
       </c>
       <c r="R171" s="3" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="172" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -16504,7 +16504,7 @@
         <v>747</v>
       </c>
       <c r="R172" s="3" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="173" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -16555,7 +16555,7 @@
         <v>747</v>
       </c>
       <c r="R173" s="3" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="174" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -16606,7 +16606,7 @@
         <v>747</v>
       </c>
       <c r="R174" s="3" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="175" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
@@ -16657,7 +16657,7 @@
         <v>747</v>
       </c>
       <c r="R175" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="176" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
@@ -16708,7 +16708,7 @@
         <v>747</v>
       </c>
       <c r="R176" s="3" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="177" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -16759,7 +16759,7 @@
         <v>747</v>
       </c>
       <c r="R177" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="178" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -16810,7 +16810,7 @@
         <v>753</v>
       </c>
       <c r="R178" s="3" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="179" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -16861,7 +16861,7 @@
         <v>747</v>
       </c>
       <c r="R179" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="180" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -16912,7 +16912,7 @@
         <v>747</v>
       </c>
       <c r="R180" s="3" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="181" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -16963,7 +16963,7 @@
         <v>753</v>
       </c>
       <c r="R181" s="3" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="182" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -17014,7 +17014,7 @@
         <v>747</v>
       </c>
       <c r="R182" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="183" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -17065,7 +17065,7 @@
         <v>749</v>
       </c>
       <c r="R183" s="3" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="184" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -17116,7 +17116,7 @@
         <v>749</v>
       </c>
       <c r="R184" s="3" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="185" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -17167,7 +17167,7 @@
         <v>749</v>
       </c>
       <c r="R185" s="3" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="186" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -17218,7 +17218,7 @@
         <v>747</v>
       </c>
       <c r="R186" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="187" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -17269,7 +17269,7 @@
         <v>747</v>
       </c>
       <c r="R187" s="3" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="188" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -17320,7 +17320,7 @@
         <v>747</v>
       </c>
       <c r="R188" s="3" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="189" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -17371,7 +17371,7 @@
         <v>751</v>
       </c>
       <c r="R189" s="3" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="190" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -17422,7 +17422,7 @@
         <v>747</v>
       </c>
       <c r="R190" s="3" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="191" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -17473,7 +17473,7 @@
         <v>747</v>
       </c>
       <c r="R191" s="3" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="192" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -17524,7 +17524,7 @@
         <v>747</v>
       </c>
       <c r="R192" s="3" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="193" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -17575,7 +17575,7 @@
         <v>747</v>
       </c>
       <c r="R193" s="3" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="194" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -17626,7 +17626,7 @@
         <v>747</v>
       </c>
       <c r="R194" s="3" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="195" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
@@ -17677,7 +17677,7 @@
         <v>747</v>
       </c>
       <c r="R195" s="3" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="196" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
@@ -17728,7 +17728,7 @@
         <v>747</v>
       </c>
       <c r="R196" s="3" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="197" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
@@ -17779,7 +17779,7 @@
         <v>747</v>
       </c>
       <c r="R197" s="3" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="198" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -17830,7 +17830,7 @@
         <v>747</v>
       </c>
       <c r="R198" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="199" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -17881,7 +17881,7 @@
         <v>747</v>
       </c>
       <c r="R199" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="200" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -17932,7 +17932,7 @@
         <v>747</v>
       </c>
       <c r="R200" s="3" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="201" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -17983,7 +17983,7 @@
         <v>747</v>
       </c>
       <c r="R201" s="3" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="202" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -18034,7 +18034,7 @@
         <v>747</v>
       </c>
       <c r="R202" s="3" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="203" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -18085,7 +18085,7 @@
         <v>747</v>
       </c>
       <c r="R203" s="3" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="204" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -18136,7 +18136,7 @@
         <v>751</v>
       </c>
       <c r="R204" s="3" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="205" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -18187,7 +18187,7 @@
         <v>747</v>
       </c>
       <c r="R205" s="3" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="206" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -18238,7 +18238,7 @@
         <v>749</v>
       </c>
       <c r="R206" s="3" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="207" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -18289,7 +18289,7 @@
         <v>749</v>
       </c>
       <c r="R207" s="3" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="208" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -18340,7 +18340,7 @@
         <v>749</v>
       </c>
       <c r="R208" s="3" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="209" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -18391,7 +18391,7 @@
         <v>747</v>
       </c>
       <c r="R209" s="3" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="210" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -18442,7 +18442,7 @@
         <v>747</v>
       </c>
       <c r="R210" s="3" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="211" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
@@ -18493,7 +18493,7 @@
         <v>747</v>
       </c>
       <c r="R211" s="3" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="212" spans="1:18" ht="37.5" x14ac:dyDescent="0.45">
@@ -18544,7 +18544,7 @@
         <v>747</v>
       </c>
       <c r="R212" s="3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="213" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -18595,7 +18595,7 @@
         <v>747</v>
       </c>
       <c r="R213" s="3" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="214" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -18646,7 +18646,7 @@
         <v>747</v>
       </c>
       <c r="R214" s="3" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="215" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -18697,7 +18697,7 @@
         <v>747</v>
       </c>
       <c r="R215" s="3" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="216" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -18748,7 +18748,7 @@
         <v>747</v>
       </c>
       <c r="R216" s="3" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="217" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -18799,7 +18799,7 @@
         <v>747</v>
       </c>
       <c r="R217" s="3" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="218" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -18850,7 +18850,7 @@
         <v>749</v>
       </c>
       <c r="R218" s="3" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="219" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -18901,7 +18901,7 @@
         <v>749</v>
       </c>
       <c r="R219" s="3" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="220" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -18952,7 +18952,7 @@
         <v>749</v>
       </c>
       <c r="R220" s="3" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="221" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -19003,7 +19003,7 @@
         <v>751</v>
       </c>
       <c r="R221" s="3" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="222" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -19054,7 +19054,7 @@
         <v>751</v>
       </c>
       <c r="R222" s="3" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="223" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -19105,7 +19105,7 @@
         <v>751</v>
       </c>
       <c r="R223" s="3" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="224" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -19156,7 +19156,7 @@
         <v>751</v>
       </c>
       <c r="R224" s="3" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="225" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -19207,7 +19207,7 @@
         <v>751</v>
       </c>
       <c r="R225" s="3" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="226" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -19258,7 +19258,7 @@
         <v>751</v>
       </c>
       <c r="R226" s="3" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="227" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -19309,7 +19309,7 @@
         <v>751</v>
       </c>
       <c r="R227" s="3" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="228" spans="1:18" ht="25" x14ac:dyDescent="0.45">
@@ -19360,7 +19360,7 @@
         <v>751</v>
       </c>
       <c r="R228" s="3" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
   </sheetData>
